--- a/curva_abc_reggae.xlsx
+++ b/curva_abc_reggae.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="R$ #,##0"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,13 +36,13 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00009B3A"/>
-      <sz val="32"/>
+      <sz val="30"/>
     </font>
     <font>
       <name val="Calibri"/>
       <i val="1"/>
       <color rgb="00FFD700"/>
-      <sz val="14"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -70,7 +70,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00009B3A"/>
-      <sz val="20"/>
+      <sz val="22"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -92,8 +92,14 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FF4444"/>
+      <color rgb="00FFD0D0"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00FFF5B0"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -105,24 +111,13 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="16"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00FFFFFF"/>
       <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="16"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -132,13 +127,8 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="00000000"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00FFF5B0"/>
       <sz val="8"/>
     </font>
     <font>
@@ -162,13 +152,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00E0E0E0"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="00B0B0B0"/>
       <sz val="8"/>
     </font>
     <font>
@@ -184,12 +168,7 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="00E0E0E0"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00C8F5DB"/>
+      <color rgb="00B0B0B0"/>
       <sz val="8"/>
     </font>
     <font>
@@ -197,12 +176,6 @@
       <b val="1"/>
       <color rgb="00FFD700"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="14">
@@ -218,9 +191,6 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid"/>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00009B3A"/>
       </patternFill>
@@ -234,6 +204,9 @@
       <patternFill patternType="solid">
         <fgColor rgb="00CC0000"/>
       </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -333,6 +306,20 @@
       </top>
       <bottom style="thin">
         <color rgb="00990000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00006B28"/>
+      </left>
+      <right style="thin">
+        <color rgb="00006B28"/>
+      </right>
+      <top style="thin">
+        <color rgb="00006B28"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00006B28"/>
       </bottom>
     </border>
     <border>
@@ -462,20 +449,6 @@
       </bottom>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00006B28"/>
-      </left>
-      <right style="thin">
-        <color rgb="00006B28"/>
-      </right>
-      <top style="thin">
-        <color rgb="00006B28"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00006B28"/>
-      </bottom>
-    </border>
-    <border>
       <left style="medium">
         <color rgb="00006B28"/>
       </left>
@@ -507,20 +480,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -538,34 +511,40 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -574,8 +553,8 @@
     <xf numFmtId="164" fontId="9" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -587,172 +566,141 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="9" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="8" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="7" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="8" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="166" fontId="16" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="16" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="26" fillId="11" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="23" fillId="11" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="11" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="23" fillId="11" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="10" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="23" fillId="10" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="25" fillId="10" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="22" fillId="10" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="27" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="27" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="28" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="15" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="15" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="3" fontId="24" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="24" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="24" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="24" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="24" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="12" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="23" fillId="12" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="25" fillId="12" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="22" fillId="12" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="13" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="23" fillId="13" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="25" fillId="13" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="22" fillId="13" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="14" fillId="3" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="14" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="3" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="14" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -876,7 +824,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Curva ABC — Valor Total por Item (Primeira)</a:t>
+              <a:t>Curva ABC — Valor Total por Item  (Primeira)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -885,7 +833,7 @@
     <plotArea>
       <barChart>
         <barDir val="col"/>
-        <grouping val="clustered"/>
+        <grouping val="stacked"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
@@ -905,12 +853,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Primeira'!$T$10:$T$19</f>
+              <f>'Primeira'!$P$10:$P$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Primeira'!$W$10:$W$19</f>
+              <f>'Primeira'!$S$10:$S$19</f>
             </numRef>
           </val>
         </ser>
@@ -933,12 +881,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Primeira'!$T$10:$T$19</f>
+              <f>'Primeira'!$P$10:$P$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Primeira'!$X$10:$X$19</f>
+              <f>'Primeira'!$T$10:$T$19</f>
             </numRef>
           </val>
         </ser>
@@ -961,12 +909,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Primeira'!$T$10:$T$19</f>
+              <f>'Primeira'!$P$10:$P$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Primeira'!$Y$10:$Y$19</f>
+              <f>'Primeira'!$U$10:$U$19</f>
             </numRef>
           </val>
         </ser>
@@ -989,7 +937,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Itens (ordenados por V.T.)</a:t>
+                  <a:t>Itens (ordenados por V.T. decrescente)</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -1049,7 +997,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Curva de Pareto — % Acumulado (Primeira)</a:t>
+              <a:t>Curva de Pareto — % Acumulado  (Primeira)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1065,7 +1013,7 @@
             <v>% Acumulado</v>
           </tx>
           <spPr>
-            <a:ln w="25000">
+            <a:ln w="28000">
               <a:solidFill>
                 <a:srgbClr val="009B3A"/>
               </a:solidFill>
@@ -1082,15 +1030,45 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Primeira'!$T$10:$T$19</f>
+              <f>'Primeira'!$P$10:$P$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Primeira'!$V$10:$V$19</f>
+              <f>'Primeira'!$R$10:$R$19</f>
             </numRef>
           </val>
           <smooth val="1"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Limite A (80%)</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Primeira'!$P$10:$P$19</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Primeira'!$Q$9</f>
+            </numRef>
+          </val>
         </ser>
         <axId val="10"/>
         <axId val="100"/>
@@ -1110,7 +1088,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Itens</a:t>
+                  <a:t>Itens (ordem decrescente de V.T.)</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -1125,6 +1103,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="1"/>
+          <min val="0"/>
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
@@ -1143,6 +1123,7 @@
             </rich>
           </tx>
         </title>
+        <numFmt formatCode="0%" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -1170,7 +1151,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Curva ABC — Valor Total por Item (01)</a:t>
+              <a:t>Curva ABC — Valor Total por Item  (01)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1179,7 +1160,7 @@
     <plotArea>
       <barChart>
         <barDir val="col"/>
-        <grouping val="clustered"/>
+        <grouping val="stacked"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
@@ -1199,12 +1180,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'01'!$T$10:$T$29</f>
+              <f>'01'!$P$10:$P$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'01'!$W$10:$W$29</f>
+              <f>'01'!$S$10:$S$29</f>
             </numRef>
           </val>
         </ser>
@@ -1227,12 +1208,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'01'!$T$10:$T$29</f>
+              <f>'01'!$P$10:$P$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'01'!$X$10:$X$29</f>
+              <f>'01'!$T$10:$T$29</f>
             </numRef>
           </val>
         </ser>
@@ -1255,12 +1236,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'01'!$T$10:$T$29</f>
+              <f>'01'!$P$10:$P$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'01'!$Y$10:$Y$29</f>
+              <f>'01'!$U$10:$U$29</f>
             </numRef>
           </val>
         </ser>
@@ -1283,7 +1264,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Itens (ordenados por V.T.)</a:t>
+                  <a:t>Itens (ordenados por V.T. decrescente)</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -1343,7 +1324,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Curva de Pareto — % Acumulado (01)</a:t>
+              <a:t>Curva de Pareto — % Acumulado  (01)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1359,7 +1340,7 @@
             <v>% Acumulado</v>
           </tx>
           <spPr>
-            <a:ln w="25000">
+            <a:ln w="28000">
               <a:solidFill>
                 <a:srgbClr val="009B3A"/>
               </a:solidFill>
@@ -1376,15 +1357,45 @@
           </marker>
           <cat>
             <numRef>
-              <f>'01'!$T$10:$T$29</f>
+              <f>'01'!$P$10:$P$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'01'!$V$10:$V$29</f>
+              <f>'01'!$R$10:$R$29</f>
             </numRef>
           </val>
           <smooth val="1"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Limite A (80%)</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'01'!$P$10:$P$29</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'01'!$Q$9</f>
+            </numRef>
+          </val>
         </ser>
         <axId val="10"/>
         <axId val="100"/>
@@ -1404,7 +1415,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Itens</a:t>
+                  <a:t>Itens (ordem decrescente de V.T.)</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -1419,6 +1430,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="1"/>
+          <min val="0"/>
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
@@ -1437,6 +1450,7 @@
             </rich>
           </tx>
         </title>
+        <numFmt formatCode="0%" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -1464,7 +1478,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Curva ABC — Valor Total por Item (02)</a:t>
+              <a:t>Curva ABC — Valor Total por Item  (02)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1473,7 +1487,7 @@
     <plotArea>
       <barChart>
         <barDir val="col"/>
-        <grouping val="clustered"/>
+        <grouping val="stacked"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
@@ -1493,12 +1507,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'02'!$T$10:$T$39</f>
+              <f>'02'!$P$10:$P$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'02'!$W$10:$W$39</f>
+              <f>'02'!$S$10:$S$39</f>
             </numRef>
           </val>
         </ser>
@@ -1521,12 +1535,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'02'!$T$10:$T$39</f>
+              <f>'02'!$P$10:$P$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'02'!$X$10:$X$39</f>
+              <f>'02'!$T$10:$T$39</f>
             </numRef>
           </val>
         </ser>
@@ -1549,12 +1563,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'02'!$T$10:$T$39</f>
+              <f>'02'!$P$10:$P$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'02'!$Y$10:$Y$39</f>
+              <f>'02'!$U$10:$U$39</f>
             </numRef>
           </val>
         </ser>
@@ -1577,7 +1591,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Itens (ordenados por V.T.)</a:t>
+                  <a:t>Itens (ordenados por V.T. decrescente)</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -1637,7 +1651,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Curva de Pareto — % Acumulado (02)</a:t>
+              <a:t>Curva de Pareto — % Acumulado  (02)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1653,7 +1667,7 @@
             <v>% Acumulado</v>
           </tx>
           <spPr>
-            <a:ln w="25000">
+            <a:ln w="28000">
               <a:solidFill>
                 <a:srgbClr val="009B3A"/>
               </a:solidFill>
@@ -1670,15 +1684,45 @@
           </marker>
           <cat>
             <numRef>
-              <f>'02'!$T$10:$T$39</f>
+              <f>'02'!$P$10:$P$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'02'!$V$10:$V$39</f>
+              <f>'02'!$R$10:$R$39</f>
             </numRef>
           </val>
           <smooth val="1"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Limite A (80%)</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'02'!$P$10:$P$39</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'02'!$Q$9</f>
+            </numRef>
+          </val>
         </ser>
         <axId val="10"/>
         <axId val="100"/>
@@ -1698,7 +1742,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Itens</a:t>
+                  <a:t>Itens (ordem decrescente de V.T.)</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -1713,6 +1757,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="1"/>
+          <min val="0"/>
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
@@ -1731,6 +1777,7 @@
             </rich>
           </tx>
         </title>
+        <numFmt formatCode="0%" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -1754,7 +1801,7 @@
       <row>22</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="5040000"/>
+    <ext cx="9360000" cy="5040000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1776,7 +1823,7 @@
       <row>22</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="5040000"/>
+    <ext cx="9360000" cy="5040000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1803,7 +1850,7 @@
       <row>32</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="5040000"/>
+    <ext cx="9360000" cy="5040000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1825,7 +1872,7 @@
       <row>32</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="5040000"/>
+    <ext cx="9360000" cy="5040000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1852,7 +1899,7 @@
       <row>42</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="5040000"/>
+    <ext cx="9360000" cy="5040000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1874,7 +1921,7 @@
       <row>42</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="5040000"/>
+    <ext cx="9360000" cy="5040000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -2182,37 +2229,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="8" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="n"/>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="n"/>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="5" t="n"/>
       <c r="F1" s="1" t="n"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="64" customHeight="1">
       <c r="A2" s="1" t="n"/>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>CURVA ABC REGGAE</t>
         </is>
       </c>
       <c r="F2" s="1" t="n"/>
     </row>
-    <row r="3" ht="20" customHeight="1">
+    <row r="3" ht="28" customHeight="1">
       <c r="A3" s="1" t="n"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Dashboard Profissional de Analise de Estoque</t>
         </is>
@@ -2221,10 +2268,10 @@
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="1" t="n"/>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="7" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="2" t="n"/>
       <c r="F4" s="1" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -2253,7 +2300,7 @@
       </c>
       <c r="F7" s="1" t="n"/>
     </row>
-    <row r="8" ht="8" customHeight="1">
+    <row r="8" ht="20" customHeight="1">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="9" t="inlineStr">
         <is>
@@ -2273,18 +2320,17 @@
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="1" t="n"/>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>Abas Disponíveis</t>
-        </is>
-      </c>
+      <c r="B10" s="1" t="n"/>
+      <c r="C10" s="1" t="n"/>
+      <c r="D10" s="1" t="n"/>
+      <c r="E10" s="1" t="n"/>
       <c r="F10" s="1" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="1" t="n"/>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Primeira: 10 itens</t>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Abas Disponiveis</t>
         </is>
       </c>
       <c r="F11" s="1" t="n"/>
@@ -2293,7 +2339,7 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Aba 01: 20 itens</t>
+          <t>Primeira: 10 itens</t>
         </is>
       </c>
       <c r="F12" s="1" t="n"/>
@@ -2302,17 +2348,18 @@
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="11" t="inlineStr">
         <is>
+          <t>Aba 01: 20 itens</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
           <t>Aba 02: 30 itens</t>
         </is>
       </c>
-      <c r="F13" s="1" t="n"/>
-    </row>
-    <row r="14" ht="8" customHeight="1">
-      <c r="A14" s="1" t="n"/>
-      <c r="B14" s="1" t="n"/>
-      <c r="C14" s="1" t="n"/>
-      <c r="D14" s="1" t="n"/>
-      <c r="E14" s="1" t="n"/>
       <c r="F14" s="1" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -2345,7 +2392,7 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>2. Edite Quant. e Custo</t>
+          <t>2. Edite Quant. e Custo Unit.</t>
         </is>
       </c>
       <c r="F18" s="1" t="n"/>
@@ -2354,12 +2401,12 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>3. ABC calcula automaticamente</t>
+          <t>3. ABC recalcula automaticamente</t>
         </is>
       </c>
       <c r="F19" s="1" t="n"/>
     </row>
-    <row r="20" ht="8" customHeight="1">
+    <row r="20" ht="20" customHeight="1">
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="1" t="n"/>
       <c r="C20" s="1" t="n"/>
@@ -2369,34 +2416,38 @@
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="1" t="n"/>
-      <c r="B21" s="1" t="n"/>
-      <c r="C21" s="1" t="n"/>
-      <c r="D21" s="1" t="n"/>
-      <c r="E21" s="1" t="n"/>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Protecao da Planilha</t>
+        </is>
+      </c>
       <c r="F21" s="1" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="1" t="n"/>
-      <c r="B22" s="1" t="n"/>
-      <c r="C22" s="1" t="n"/>
-      <c r="D22" s="1" t="n"/>
-      <c r="E22" s="1" t="n"/>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Senha: abc2026.</t>
+        </is>
+      </c>
       <c r="F22" s="1" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="1" t="n"/>
-      <c r="B23" s="1" t="n"/>
-      <c r="C23" s="1" t="n"/>
-      <c r="D23" s="1" t="n"/>
-      <c r="E23" s="1" t="n"/>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>Colunas D e E liberadas para edicao</t>
+        </is>
+      </c>
       <c r="F23" s="1" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="1" t="n"/>
-      <c r="B24" s="1" t="n"/>
-      <c r="C24" s="1" t="n"/>
-      <c r="D24" s="1" t="n"/>
-      <c r="E24" s="1" t="n"/>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>Demais celulas protegidas</t>
+        </is>
+      </c>
       <c r="F24" s="1" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -2457,11 +2508,10 @@
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="1" t="n"/>
-      <c r="B32" s="14" t="inlineStr">
-        <is>
-          <t>One Love, One Data  |  CURVA ABC REGGAE  |  2026  |  Senha: abc2026.</t>
-        </is>
-      </c>
+      <c r="B32" s="1" t="n"/>
+      <c r="C32" s="1" t="n"/>
+      <c r="D32" s="1" t="n"/>
+      <c r="E32" s="1" t="n"/>
       <c r="F32" s="1" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1">
@@ -2480,7 +2530,7 @@
       <c r="E34" s="1" t="n"/>
       <c r="F34" s="1" t="n"/>
     </row>
-    <row r="35">
+    <row r="35" ht="20" customHeight="1">
       <c r="A35" s="1" t="n"/>
       <c r="B35" s="1" t="n"/>
       <c r="C35" s="1" t="n"/>
@@ -2488,24 +2538,61 @@
       <c r="E35" s="1" t="n"/>
       <c r="F35" s="1" t="n"/>
     </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="1" t="n"/>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>One Love, One Data  |  CURVA ABC REGGAE  |  2026</t>
+        </is>
+      </c>
+      <c r="F36" s="1" t="n"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="1" t="n"/>
+      <c r="B37" s="1" t="n"/>
+      <c r="C37" s="1" t="n"/>
+      <c r="D37" s="1" t="n"/>
+      <c r="E37" s="1" t="n"/>
+      <c r="F37" s="1" t="n"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="1" t="n"/>
+      <c r="B38" s="1" t="n"/>
+      <c r="C38" s="1" t="n"/>
+      <c r="D38" s="1" t="n"/>
+      <c r="E38" s="1" t="n"/>
+      <c r="F38" s="1" t="n"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="1" t="n"/>
+      <c r="B39" s="1" t="n"/>
+      <c r="C39" s="1" t="n"/>
+      <c r="D39" s="1" t="n"/>
+      <c r="E39" s="1" t="n"/>
+      <c r="F39" s="1" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="B17:E17"/>
+  <mergeCells count="20">
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B36:E36"/>
     <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="B6:E6"/>
     <mergeCell ref="B16:E16"/>
     <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B21:E21"/>
     <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B3:E3"/>
     <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B13:E13"/>
     <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B32:E32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2518,7 +2605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y51"/>
+  <dimension ref="A1:U53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2535,1008 +2622,845 @@
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="2" customWidth="1" min="15" max="15"/>
-    <col width="2" customWidth="1" min="16" max="16"/>
-    <col width="2" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="38" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="16" customWidth="1" min="23" max="23"/>
-    <col width="16" customWidth="1" min="24" max="24"/>
-    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
-    <row r="1" ht="50" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
-        <is>
-          <t>CURVA ABC REGGAE  —  PRIMEIRA</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="n"/>
-      <c r="J1" s="16" t="inlineStr">
-        <is>
-          <t>A = ate 80%   |   B = 80-95%   |   C = 95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+    <row r="1" ht="48" customHeight="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>CURVA ABC — PRIMEIRA</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="n"/>
+      <c r="J1" s="18" t="inlineStr">
+        <is>
+          <t>A = ate 80%   |   B = 80–95%   |   C = 95–100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>V.T. TOTAL</t>
         </is>
       </c>
-      <c r="B2" s="18" t="n"/>
-      <c r="C2" s="19" t="inlineStr">
+      <c r="B2" s="20" t="n"/>
+      <c r="C2" s="21" t="inlineStr">
         <is>
           <t>V.T. CLASSE A</t>
         </is>
       </c>
-      <c r="D2" s="18" t="n"/>
-      <c r="E2" s="20" t="inlineStr">
+      <c r="D2" s="20" t="n"/>
+      <c r="E2" s="22" t="inlineStr">
         <is>
           <t>% ITENS A</t>
         </is>
       </c>
-      <c r="F2" s="18" t="n"/>
-      <c r="G2" s="21" t="inlineStr">
+      <c r="F2" s="20" t="n"/>
+      <c r="G2" s="23" t="inlineStr">
         <is>
           <t>MAIOR V.T.</t>
         </is>
       </c>
-      <c r="H2" s="22" t="n"/>
-      <c r="J2" s="1" t="n"/>
-      <c r="K2" s="1" t="n"/>
-      <c r="L2" s="1" t="n"/>
-      <c r="M2" s="1" t="n"/>
-      <c r="N2" s="1" t="n"/>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="23">
+      <c r="H2" s="24" t="n"/>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="25">
         <f>SUM($F$10:$F$19)</f>
         <v/>
       </c>
-      <c r="B3" s="24" t="n"/>
-      <c r="C3" s="25">
+      <c r="B3" s="26" t="n"/>
+      <c r="C3" s="27">
         <f>SUMIF($A$10:$A$19,"A",$F$10:$F$19)</f>
         <v/>
       </c>
-      <c r="D3" s="24" t="n"/>
-      <c r="E3" s="26">
+      <c r="D3" s="26" t="n"/>
+      <c r="E3" s="28">
         <f>IFERROR(COUNTIF($A$10:$A$19,"A")/COUNTA($B$10:$B$19),0)</f>
         <v/>
       </c>
-      <c r="F3" s="24" t="n"/>
-      <c r="G3" s="27">
+      <c r="F3" s="26" t="n"/>
+      <c r="G3" s="29">
         <f>MAX($F$10:$F$19)</f>
         <v/>
       </c>
-      <c r="H3" s="28" t="n"/>
-      <c r="J3" s="1" t="n"/>
-      <c r="K3" s="1" t="n"/>
-      <c r="L3" s="1" t="n"/>
-      <c r="M3" s="1" t="n"/>
-      <c r="N3" s="1" t="n"/>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="H3" s="30" t="n"/>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>MENOR V.T.</t>
         </is>
       </c>
-      <c r="B4" s="24" t="n"/>
-      <c r="C4" s="30" t="inlineStr">
+      <c r="B4" s="26" t="n"/>
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
       </c>
-      <c r="D4" s="24" t="n"/>
-      <c r="E4" s="31" t="inlineStr">
+      <c r="D4" s="26" t="n"/>
+      <c r="E4" s="33" t="inlineStr">
         <is>
           <t>LIMITE A</t>
         </is>
       </c>
-      <c r="F4" s="24" t="n"/>
-      <c r="G4" s="32" t="inlineStr">
+      <c r="F4" s="26" t="n"/>
+      <c r="G4" s="34" t="inlineStr">
         <is>
           <t>LIMITE B</t>
         </is>
       </c>
-      <c r="H4" s="28" t="n"/>
-      <c r="J4" s="1" t="n"/>
-      <c r="K4" s="1" t="n"/>
-      <c r="L4" s="1" t="n"/>
-      <c r="M4" s="1" t="n"/>
-      <c r="N4" s="1" t="n"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="33">
+      <c r="H4" s="30" t="n"/>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="35">
         <f>MIN($F$10:$F$19)</f>
         <v/>
       </c>
-      <c r="B5" s="34" t="n"/>
-      <c r="C5" s="35">
-        <f>IF(IFERROR(MAX($H$10:$H$19),0)&gt;1.0001,"VERIFICAR","CONSISTENTE")</f>
-        <v/>
-      </c>
-      <c r="D5" s="34" t="n"/>
-      <c r="E5" s="36" t="n">
+      <c r="B5" s="36" t="n"/>
+      <c r="C5" s="37">
+        <f>IF(IFERROR(MAX($H$10:$H$19),0)&gt;1.0001,"VERIFICAR","OK")</f>
+        <v/>
+      </c>
+      <c r="D5" s="36" t="n"/>
+      <c r="E5" s="38" t="n">
         <v>0.8</v>
       </c>
-      <c r="F5" s="34" t="n"/>
-      <c r="G5" s="37" t="n">
+      <c r="F5" s="36" t="n"/>
+      <c r="G5" s="39" t="n">
         <v>0.95</v>
       </c>
-      <c r="H5" s="38" t="n"/>
-      <c r="J5" s="1" t="n"/>
-      <c r="K5" s="1" t="n"/>
-      <c r="L5" s="1" t="n"/>
-      <c r="M5" s="1" t="n"/>
-      <c r="N5" s="1" t="n"/>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Gestao de Estoque &amp; Inventario | Classe A: ate 80%  |  Classe B: 80-95%  |  Classe C: 95-100%  |  Edite somente Quant. e Custo Unit. — formulas, ABC e graficos atualizam automaticamente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="J7" s="40" t="inlineStr">
+      <c r="H5" s="40" t="n"/>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Edite somente Quant. e Custo Unit. — ABC, V.T. e % recalculam automaticamente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="J7" s="42" t="inlineStr">
         <is>
           <t>Classe</t>
         </is>
       </c>
-      <c r="K7" s="40" t="inlineStr">
+      <c r="K7" s="42" t="inlineStr">
         <is>
           <t>Total V.T.</t>
         </is>
       </c>
-      <c r="L7" s="40" t="inlineStr">
+      <c r="L7" s="42" t="inlineStr">
         <is>
           <t>% Total</t>
         </is>
       </c>
-      <c r="M7" s="40" t="inlineStr">
+      <c r="M7" s="42" t="inlineStr">
         <is>
           <t>Qtd. Itens</t>
         </is>
       </c>
-      <c r="N7" s="40" t="inlineStr">
-        <is>
-          <t>Barra Rapida</t>
+      <c r="N7" s="42" t="inlineStr">
+        <is>
+          <t>Barra</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="41" t="inlineStr">
+      <c r="A8" s="43" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
-      <c r="B8" s="42" t="inlineStr">
-        <is>
-          <t>Descricao do Item</t>
-        </is>
-      </c>
-      <c r="C8" s="43" t="inlineStr">
-        <is>
-          <t>Cod./ID</t>
-        </is>
-      </c>
-      <c r="D8" s="44" t="inlineStr">
+      <c r="B8" s="44" t="inlineStr">
+        <is>
+          <t>Descricao</t>
+        </is>
+      </c>
+      <c r="C8" s="44" t="inlineStr">
+        <is>
+          <t>Cod.</t>
+        </is>
+      </c>
+      <c r="D8" s="45" t="inlineStr">
         <is>
           <t>Quant.</t>
         </is>
       </c>
-      <c r="E8" s="44" t="inlineStr">
-        <is>
-          <t>Custo Unit. (R$)</t>
-        </is>
-      </c>
-      <c r="F8" s="41" t="inlineStr">
+      <c r="E8" s="45" t="inlineStr">
+        <is>
+          <t>Custo Unit.(R$)</t>
+        </is>
+      </c>
+      <c r="F8" s="43" t="inlineStr">
         <is>
           <t>V.T. (R$)</t>
         </is>
       </c>
-      <c r="G8" s="43" t="inlineStr">
+      <c r="G8" s="44" t="inlineStr">
         <is>
           <t>% Individual</t>
         </is>
       </c>
-      <c r="H8" s="43" t="inlineStr">
+      <c r="H8" s="44" t="inlineStr">
         <is>
           <t>% Acumulado</t>
         </is>
       </c>
-      <c r="J8" s="45" t="inlineStr">
+      <c r="J8" s="46" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K8" s="46">
+      <c r="K8" s="47">
         <f>SUMIF($A$10:$A$19,"A",$F$10:$F$19)</f>
         <v/>
       </c>
-      <c r="L8" s="47">
+      <c r="L8" s="48">
         <f>IFERROR(K8/SUM($F$10:$F$19),0)</f>
         <v/>
       </c>
-      <c r="M8" s="48">
+      <c r="M8" s="46">
         <f>COUNTIF($A$10:$A$19,"A")</f>
         <v/>
       </c>
       <c r="N8" s="49">
-        <f>REPT("█",ROUND(L8*20,0))</f>
-        <v/>
+        <f>REPT(CHAR(9608),ROUND(L8*20,0))</f>
+        <v/>
+      </c>
+      <c r="P8" s="50" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="Q8" s="50" t="inlineStr">
+        <is>
+          <t>VT Ord.</t>
+        </is>
       </c>
       <c r="R8" s="50" t="inlineStr">
         <is>
-          <t>Rank</t>
+          <t>% Acum.</t>
         </is>
       </c>
       <c r="S8" s="50" t="inlineStr">
         <is>
-          <t>ABC Ord.</t>
+          <t>VT A</t>
         </is>
       </c>
       <c r="T8" s="50" t="inlineStr">
         <is>
-          <t>Rotulo</t>
+          <t>VT B</t>
         </is>
       </c>
       <c r="U8" s="50" t="inlineStr">
         <is>
-          <t>V.T. Ord.</t>
-        </is>
-      </c>
-      <c r="V8" s="50" t="inlineStr">
-        <is>
-          <t>% Acum. Ord.</t>
-        </is>
-      </c>
-      <c r="W8" s="51" t="inlineStr">
-        <is>
-          <t>V.T. A</t>
-        </is>
-      </c>
-      <c r="X8" s="52" t="inlineStr">
-        <is>
-          <t>V.T. B</t>
-        </is>
-      </c>
-      <c r="Y8" s="53" t="inlineStr">
-        <is>
-          <t>V.T. C</t>
+          <t>VT C</t>
         </is>
       </c>
     </row>
     <row r="9" ht="6" customHeight="1">
-      <c r="J9" s="54" t="inlineStr">
+      <c r="J9" s="51" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K9" s="55">
+      <c r="K9" s="52">
         <f>SUMIF($A$10:$A$19,"B",$F$10:$F$19)</f>
         <v/>
       </c>
-      <c r="L9" s="56">
+      <c r="L9" s="53">
         <f>IFERROR(K9/SUM($F$10:$F$19),0)</f>
         <v/>
       </c>
-      <c r="M9" s="57">
+      <c r="M9" s="51">
         <f>COUNTIF($A$10:$A$19,"B")</f>
         <v/>
       </c>
-      <c r="N9" s="58">
-        <f>REPT("█",ROUND(L9*20,0))</f>
+      <c r="N9" s="54">
+        <f>REPT(CHAR(9608),ROUND(L9*20,0))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
-      <c r="A10" s="48">
+      <c r="A10" s="46">
         <f>IF($H10&lt;=$E$5,"A",IF($H10&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B10" s="59" t="inlineStr">
+      <c r="B10" s="55" t="inlineStr">
         <is>
           <t>Servidor Backup</t>
         </is>
       </c>
-      <c r="C10" s="60" t="n">
+      <c r="C10" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="61" t="n">
+      <c r="D10" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="62" t="n">
+      <c r="E10" s="58" t="n">
         <v>25000</v>
       </c>
-      <c r="F10" s="63">
+      <c r="F10" s="59">
         <f>IFERROR(D10*E10,0)</f>
         <v/>
       </c>
-      <c r="G10" s="64">
+      <c r="G10" s="60">
         <f>IFERROR(F10/SUM($F$10:$F$19),0)</f>
         <v/>
       </c>
-      <c r="H10" s="64">
+      <c r="H10" s="60">
         <f>IFERROR(SUMIF($F$10:$F$19,"&gt;="&amp;F10,$F$10:$F$19)/SUM($F$10:$F$19),0)</f>
         <v/>
       </c>
-      <c r="J10" s="65" t="inlineStr">
+      <c r="J10" s="61" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="K10" s="66">
+      <c r="K10" s="62">
         <f>SUMIF($A$10:$A$19,"C",$F$10:$F$19)</f>
         <v/>
       </c>
-      <c r="L10" s="67">
+      <c r="L10" s="63">
         <f>IFERROR(K10/SUM($F$10:$F$19),0)</f>
         <v/>
       </c>
-      <c r="M10" s="68">
+      <c r="M10" s="61">
         <f>COUNTIF($A$10:$A$19,"C")</f>
         <v/>
       </c>
-      <c r="N10" s="69">
-        <f>REPT("█",ROUND(L10*20,0))</f>
-        <v/>
-      </c>
-      <c r="R10" s="70">
-        <f>RANK.EQ(F10,$F$10:$F$19,0)+COUNTIF($F$10:F10,F10)-1</f>
-        <v/>
-      </c>
-      <c r="S10" s="70">
-        <f>INDEX($A$10:$A$19,MATCH(ROWS($S$10:S10),$R$10:$R$19,0))</f>
-        <v/>
-      </c>
-      <c r="T10" s="71">
-        <f>INDEX($B$10:$B$19,MATCH(ROWS($T$10:T10),$R$10:$R$19,0))&amp;" ("&amp;S10&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U10" s="72">
-        <f>INDEX($F$10:$F$19,MATCH(ROWS($U$10:U10),$R$10:$R$19,0))</f>
-        <v/>
-      </c>
-      <c r="V10" s="73">
-        <f>INDEX($H$10:$H$19,MATCH(ROWS($V$10:V10),$R$10:$R$19,0))</f>
-        <v/>
-      </c>
-      <c r="W10" s="74">
-        <f>IF($S10="A",$U10,NA())</f>
-        <v/>
-      </c>
-      <c r="X10" s="75">
-        <f>IF($S10="B",$U10,NA())</f>
-        <v/>
-      </c>
-      <c r="Y10" s="76">
-        <f>IF($S10="C",$U10,NA())</f>
-        <v/>
+      <c r="N10" s="64">
+        <f>REPT(CHAR(9608),ROUND(L10*20,0))</f>
+        <v/>
+      </c>
+      <c r="P10" s="65" t="inlineStr">
+        <is>
+          <t>Servidor Backup (A)</t>
+        </is>
+      </c>
+      <c r="Q10" s="66" t="n">
+        <v>50000</v>
+      </c>
+      <c r="R10" s="67" t="n">
+        <v>0.3778</v>
+      </c>
+      <c r="S10" s="68" t="n">
+        <v>50000</v>
+      </c>
+      <c r="T10" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="48">
+      <c r="A11" s="46">
         <f>IF($H11&lt;=$E$5,"A",IF($H11&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B11" s="59" t="inlineStr">
+      <c r="B11" s="55" t="inlineStr">
         <is>
           <t>Monitor 27" 4K</t>
         </is>
       </c>
-      <c r="C11" s="60" t="n">
+      <c r="C11" s="56" t="n">
         <v>5</v>
       </c>
-      <c r="D11" s="61" t="n">
+      <c r="D11" s="57" t="n">
         <v>10</v>
       </c>
-      <c r="E11" s="62" t="n">
+      <c r="E11" s="58" t="n">
         <v>3000</v>
       </c>
-      <c r="F11" s="63">
+      <c r="F11" s="59">
         <f>IFERROR(D11*E11,0)</f>
         <v/>
       </c>
-      <c r="G11" s="64">
+      <c r="G11" s="60">
         <f>IFERROR(F11/SUM($F$10:$F$19),0)</f>
         <v/>
       </c>
-      <c r="H11" s="64">
+      <c r="H11" s="60">
         <f>IFERROR(SUMIF($F$10:$F$19,"&gt;="&amp;F11,$F$10:$F$19)/SUM($F$10:$F$19),0)</f>
         <v/>
       </c>
-      <c r="J11" s="77">
-        <f>IF(IFERROR(MAX($H$10:$H$19),0)&gt;1.0001,"ALERTA: acumulado &gt; 100%","OK - CONSISTENTE")</f>
-        <v/>
-      </c>
-      <c r="R11" s="70">
-        <f>RANK.EQ(F11,$F$10:$F$19,0)+COUNTIF($F$10:F11,F11)-1</f>
-        <v/>
-      </c>
-      <c r="S11" s="70">
-        <f>INDEX($A$10:$A$19,MATCH(ROWS($S$10:S11),$R$10:$R$19,0))</f>
-        <v/>
-      </c>
-      <c r="T11" s="71">
-        <f>INDEX($B$10:$B$19,MATCH(ROWS($T$10:T11),$R$10:$R$19,0))&amp;" ("&amp;S11&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U11" s="72">
-        <f>INDEX($F$10:$F$19,MATCH(ROWS($U$10:U11),$R$10:$R$19,0))</f>
-        <v/>
-      </c>
-      <c r="V11" s="73">
-        <f>INDEX($H$10:$H$19,MATCH(ROWS($V$10:V11),$R$10:$R$19,0))</f>
-        <v/>
-      </c>
-      <c r="W11" s="74">
-        <f>IF($S11="A",$U11,NA())</f>
-        <v/>
-      </c>
-      <c r="X11" s="75">
-        <f>IF($S11="B",$U11,NA())</f>
-        <v/>
-      </c>
-      <c r="Y11" s="76">
-        <f>IF($S11="C",$U11,NA())</f>
-        <v/>
+      <c r="P11" s="65" t="inlineStr">
+        <is>
+          <t>Monitor 27" 4K (A)</t>
+        </is>
+      </c>
+      <c r="Q11" s="66" t="n">
+        <v>30000</v>
+      </c>
+      <c r="R11" s="67" t="n">
+        <v>0.6045</v>
+      </c>
+      <c r="S11" s="68" t="n">
+        <v>30000</v>
+      </c>
+      <c r="T11" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1">
-      <c r="A12" s="78">
+      <c r="A12" s="71">
         <f>IF($H12&lt;=$E$5,"A",IF($H12&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B12" s="79" t="inlineStr">
+      <c r="B12" s="72" t="inlineStr">
         <is>
           <t>Notebook Administrativo</t>
         </is>
       </c>
-      <c r="C12" s="80" t="n">
+      <c r="C12" s="73" t="n">
         <v>9</v>
       </c>
-      <c r="D12" s="61" t="n">
+      <c r="D12" s="57" t="n">
         <v>6</v>
       </c>
-      <c r="E12" s="62" t="n">
+      <c r="E12" s="58" t="n">
         <v>4500</v>
       </c>
-      <c r="F12" s="81">
+      <c r="F12" s="74">
         <f>IFERROR(D12*E12,0)</f>
         <v/>
       </c>
-      <c r="G12" s="82">
+      <c r="G12" s="75">
         <f>IFERROR(F12/SUM($F$10:$F$19),0)</f>
         <v/>
       </c>
-      <c r="H12" s="82">
+      <c r="H12" s="75">
         <f>IFERROR(SUMIF($F$10:$F$19,"&gt;="&amp;F12,$F$10:$F$19)/SUM($F$10:$F$19),0)</f>
         <v/>
       </c>
-      <c r="R12" s="70">
-        <f>RANK.EQ(F12,$F$10:$F$19,0)+COUNTIF($F$10:F12,F12)-1</f>
-        <v/>
-      </c>
-      <c r="S12" s="70">
-        <f>INDEX($A$10:$A$19,MATCH(ROWS($S$10:S12),$R$10:$R$19,0))</f>
-        <v/>
-      </c>
-      <c r="T12" s="71">
-        <f>INDEX($B$10:$B$19,MATCH(ROWS($T$10:T12),$R$10:$R$19,0))&amp;" ("&amp;S12&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U12" s="72">
-        <f>INDEX($F$10:$F$19,MATCH(ROWS($U$10:U12),$R$10:$R$19,0))</f>
-        <v/>
-      </c>
-      <c r="V12" s="73">
-        <f>INDEX($H$10:$H$19,MATCH(ROWS($V$10:V12),$R$10:$R$19,0))</f>
-        <v/>
-      </c>
-      <c r="W12" s="74">
-        <f>IF($S12="A",$U12,NA())</f>
-        <v/>
-      </c>
-      <c r="X12" s="75">
-        <f>IF($S12="B",$U12,NA())</f>
-        <v/>
-      </c>
-      <c r="Y12" s="76">
-        <f>IF($S12="C",$U12,NA())</f>
-        <v/>
+      <c r="P12" s="65" t="inlineStr">
+        <is>
+          <t>Notebook Administrat (B)</t>
+        </is>
+      </c>
+      <c r="Q12" s="66" t="n">
+        <v>27000</v>
+      </c>
+      <c r="R12" s="67" t="n">
+        <v>0.8085</v>
+      </c>
+      <c r="S12" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="69" t="n">
+        <v>27000</v>
+      </c>
+      <c r="U12" s="70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="78">
+      <c r="A13" s="71">
         <f>IF($H13&lt;=$E$5,"A",IF($H13&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B13" s="79" t="inlineStr">
+      <c r="B13" s="72" t="inlineStr">
         <is>
           <t>Nobreak Profissional</t>
         </is>
       </c>
-      <c r="C13" s="80" t="n">
+      <c r="C13" s="73" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="61" t="n">
+      <c r="D13" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="E13" s="62" t="n">
+      <c r="E13" s="58" t="n">
         <v>2000</v>
       </c>
-      <c r="F13" s="81">
+      <c r="F13" s="74">
         <f>IFERROR(D13*E13,0)</f>
         <v/>
       </c>
-      <c r="G13" s="82">
+      <c r="G13" s="75">
         <f>IFERROR(F13/SUM($F$10:$F$19),0)</f>
         <v/>
       </c>
-      <c r="H13" s="82">
+      <c r="H13" s="75">
         <f>IFERROR(SUMIF($F$10:$F$19,"&gt;="&amp;F13,$F$10:$F$19)/SUM($F$10:$F$19),0)</f>
         <v/>
       </c>
-      <c r="R13" s="70">
-        <f>RANK.EQ(F13,$F$10:$F$19,0)+COUNTIF($F$10:F13,F13)-1</f>
-        <v/>
-      </c>
-      <c r="S13" s="70">
-        <f>INDEX($A$10:$A$19,MATCH(ROWS($S$10:S13),$R$10:$R$19,0))</f>
-        <v/>
-      </c>
-      <c r="T13" s="71">
-        <f>INDEX($B$10:$B$19,MATCH(ROWS($T$10:T13),$R$10:$R$19,0))&amp;" ("&amp;S13&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U13" s="72">
-        <f>INDEX($F$10:$F$19,MATCH(ROWS($U$10:U13),$R$10:$R$19,0))</f>
-        <v/>
-      </c>
-      <c r="V13" s="73">
-        <f>INDEX($H$10:$H$19,MATCH(ROWS($V$10:V13),$R$10:$R$19,0))</f>
-        <v/>
-      </c>
-      <c r="W13" s="74">
-        <f>IF($S13="A",$U13,NA())</f>
-        <v/>
-      </c>
-      <c r="X13" s="75">
-        <f>IF($S13="B",$U13,NA())</f>
-        <v/>
-      </c>
-      <c r="Y13" s="76">
-        <f>IF($S13="C",$U13,NA())</f>
-        <v/>
+      <c r="P13" s="65" t="inlineStr">
+        <is>
+          <t>Nobreak Profissional (B)</t>
+        </is>
+      </c>
+      <c r="Q13" s="66" t="n">
+        <v>10000</v>
+      </c>
+      <c r="R13" s="67" t="n">
+        <v>0.8841</v>
+      </c>
+      <c r="S13" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="69" t="n">
+        <v>10000</v>
+      </c>
+      <c r="U13" s="70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="78">
+      <c r="A14" s="71">
         <f>IF($H14&lt;=$E$5,"A",IF($H14&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B14" s="79" t="inlineStr">
+      <c r="B14" s="72" t="inlineStr">
         <is>
           <t>Switch Gerenciavel</t>
         </is>
       </c>
-      <c r="C14" s="80" t="n">
+      <c r="C14" s="73" t="n">
         <v>7</v>
       </c>
-      <c r="D14" s="61" t="n">
+      <c r="D14" s="57" t="n">
         <v>4</v>
       </c>
-      <c r="E14" s="62" t="n">
+      <c r="E14" s="58" t="n">
         <v>1500</v>
       </c>
-      <c r="F14" s="81">
+      <c r="F14" s="74">
         <f>IFERROR(D14*E14,0)</f>
         <v/>
       </c>
-      <c r="G14" s="82">
+      <c r="G14" s="75">
         <f>IFERROR(F14/SUM($F$10:$F$19),0)</f>
         <v/>
       </c>
-      <c r="H14" s="82">
+      <c r="H14" s="75">
         <f>IFERROR(SUMIF($F$10:$F$19,"&gt;="&amp;F14,$F$10:$F$19)/SUM($F$10:$F$19),0)</f>
         <v/>
       </c>
-      <c r="R14" s="70">
-        <f>RANK.EQ(F14,$F$10:$F$19,0)+COUNTIF($F$10:F14,F14)-1</f>
-        <v/>
-      </c>
-      <c r="S14" s="70">
-        <f>INDEX($A$10:$A$19,MATCH(ROWS($S$10:S14),$R$10:$R$19,0))</f>
-        <v/>
-      </c>
-      <c r="T14" s="71">
-        <f>INDEX($B$10:$B$19,MATCH(ROWS($T$10:T14),$R$10:$R$19,0))&amp;" ("&amp;S14&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U14" s="72">
-        <f>INDEX($F$10:$F$19,MATCH(ROWS($U$10:U14),$R$10:$R$19,0))</f>
-        <v/>
-      </c>
-      <c r="V14" s="73">
-        <f>INDEX($H$10:$H$19,MATCH(ROWS($V$10:V14),$R$10:$R$19,0))</f>
-        <v/>
-      </c>
-      <c r="W14" s="74">
-        <f>IF($S14="A",$U14,NA())</f>
-        <v/>
-      </c>
-      <c r="X14" s="75">
-        <f>IF($S14="B",$U14,NA())</f>
-        <v/>
-      </c>
-      <c r="Y14" s="76">
-        <f>IF($S14="C",$U14,NA())</f>
-        <v/>
+      <c r="P14" s="65" t="inlineStr">
+        <is>
+          <t>Switch Gerenciavel (B)</t>
+        </is>
+      </c>
+      <c r="Q14" s="66" t="n">
+        <v>6000</v>
+      </c>
+      <c r="R14" s="67" t="n">
+        <v>0.9294</v>
+      </c>
+      <c r="S14" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="69" t="n">
+        <v>6000</v>
+      </c>
+      <c r="U14" s="70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="68">
+      <c r="A15" s="61">
         <f>IF($H15&lt;=$E$5,"A",IF($H15&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B15" s="83" t="inlineStr">
+      <c r="B15" s="76" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
       </c>
-      <c r="C15" s="84" t="n">
+      <c r="C15" s="77" t="n">
         <v>4</v>
       </c>
-      <c r="D15" s="61" t="n">
+      <c r="D15" s="57" t="n">
         <v>40</v>
       </c>
-      <c r="E15" s="62" t="n">
+      <c r="E15" s="58" t="n">
         <v>50</v>
       </c>
-      <c r="F15" s="85">
+      <c r="F15" s="78">
         <f>IFERROR(D15*E15,0)</f>
         <v/>
       </c>
-      <c r="G15" s="86">
+      <c r="G15" s="79">
         <f>IFERROR(F15/SUM($F$10:$F$19),0)</f>
         <v/>
       </c>
-      <c r="H15" s="86">
+      <c r="H15" s="79">
         <f>IFERROR(SUMIF($F$10:$F$19,"&gt;="&amp;F15,$F$10:$F$19)/SUM($F$10:$F$19),0)</f>
         <v/>
       </c>
-      <c r="R15" s="70">
-        <f>RANK.EQ(F15,$F$10:$F$19,0)+COUNTIF($F$10:F15,F15)-1</f>
-        <v/>
-      </c>
-      <c r="S15" s="70">
-        <f>INDEX($A$10:$A$19,MATCH(ROWS($S$10:S15),$R$10:$R$19,0))</f>
-        <v/>
-      </c>
-      <c r="T15" s="71">
-        <f>INDEX($B$10:$B$19,MATCH(ROWS($T$10:T15),$R$10:$R$19,0))&amp;" ("&amp;S15&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U15" s="72">
-        <f>INDEX($F$10:$F$19,MATCH(ROWS($U$10:U15),$R$10:$R$19,0))</f>
-        <v/>
-      </c>
-      <c r="V15" s="73">
-        <f>INDEX($H$10:$H$19,MATCH(ROWS($V$10:V15),$R$10:$R$19,0))</f>
-        <v/>
-      </c>
-      <c r="W15" s="74">
-        <f>IF($S15="A",$U15,NA())</f>
-        <v/>
-      </c>
-      <c r="X15" s="75">
-        <f>IF($S15="B",$U15,NA())</f>
-        <v/>
-      </c>
-      <c r="Y15" s="76">
-        <f>IF($S15="C",$U15,NA())</f>
-        <v/>
+      <c r="P15" s="65" t="inlineStr">
+        <is>
+          <t>Teclado USB (C)</t>
+        </is>
+      </c>
+      <c r="Q15" s="66" t="n">
+        <v>2800</v>
+      </c>
+      <c r="R15" s="67" t="n">
+        <v>0.9506</v>
+      </c>
+      <c r="S15" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="70" t="n">
+        <v>2800</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="68">
+      <c r="A16" s="61">
         <f>IF($H16&lt;=$E$5,"A",IF($H16&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B16" s="83" t="inlineStr">
+      <c r="B16" s="76" t="inlineStr">
         <is>
           <t>Patch Cord 1m</t>
         </is>
       </c>
-      <c r="C16" s="84" t="n">
+      <c r="C16" s="77" t="n">
         <v>8</v>
       </c>
-      <c r="D16" s="61" t="n">
+      <c r="D16" s="57" t="n">
         <v>100</v>
       </c>
-      <c r="E16" s="62" t="n">
+      <c r="E16" s="58" t="n">
         <v>15</v>
       </c>
-      <c r="F16" s="85">
+      <c r="F16" s="78">
         <f>IFERROR(D16*E16,0)</f>
         <v/>
       </c>
-      <c r="G16" s="86">
+      <c r="G16" s="79">
         <f>IFERROR(F16/SUM($F$10:$F$19),0)</f>
         <v/>
       </c>
-      <c r="H16" s="86">
+      <c r="H16" s="79">
         <f>IFERROR(SUMIF($F$10:$F$19,"&gt;="&amp;F16,$F$10:$F$19)/SUM($F$10:$F$19),0)</f>
         <v/>
       </c>
-      <c r="R16" s="70">
-        <f>RANK.EQ(F16,$F$10:$F$19,0)+COUNTIF($F$10:F16,F16)-1</f>
-        <v/>
-      </c>
-      <c r="S16" s="70">
-        <f>INDEX($A$10:$A$19,MATCH(ROWS($S$10:S16),$R$10:$R$19,0))</f>
-        <v/>
-      </c>
-      <c r="T16" s="71">
-        <f>INDEX($B$10:$B$19,MATCH(ROWS($T$10:T16),$R$10:$R$19,0))&amp;" ("&amp;S16&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U16" s="72">
-        <f>INDEX($F$10:$F$19,MATCH(ROWS($U$10:U16),$R$10:$R$19,0))</f>
-        <v/>
-      </c>
-      <c r="V16" s="73">
-        <f>INDEX($H$10:$H$19,MATCH(ROWS($V$10:V16),$R$10:$R$19,0))</f>
-        <v/>
-      </c>
-      <c r="W16" s="74">
-        <f>IF($S16="A",$U16,NA())</f>
-        <v/>
-      </c>
-      <c r="X16" s="75">
-        <f>IF($S16="B",$U16,NA())</f>
-        <v/>
-      </c>
-      <c r="Y16" s="76">
-        <f>IF($S16="C",$U16,NA())</f>
-        <v/>
+      <c r="P16" s="65" t="inlineStr">
+        <is>
+          <t>Mouse sem fio (C)</t>
+        </is>
+      </c>
+      <c r="Q16" s="66" t="n">
+        <v>2000</v>
+      </c>
+      <c r="R16" s="67" t="n">
+        <v>0.9657</v>
+      </c>
+      <c r="S16" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="70" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="68">
+      <c r="A17" s="61">
         <f>IF($H17&lt;=$E$5,"A",IF($H17&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B17" s="83" t="inlineStr">
+      <c r="B17" s="76" t="inlineStr">
         <is>
           <t>Teclado USB</t>
         </is>
       </c>
-      <c r="C17" s="84" t="n">
+      <c r="C17" s="77" t="n">
         <v>6</v>
       </c>
-      <c r="D17" s="61" t="n">
+      <c r="D17" s="57" t="n">
         <v>80</v>
       </c>
-      <c r="E17" s="62" t="n">
+      <c r="E17" s="58" t="n">
         <v>35</v>
       </c>
-      <c r="F17" s="85">
+      <c r="F17" s="78">
         <f>IFERROR(D17*E17,0)</f>
         <v/>
       </c>
-      <c r="G17" s="86">
+      <c r="G17" s="79">
         <f>IFERROR(F17/SUM($F$10:$F$19),0)</f>
         <v/>
       </c>
-      <c r="H17" s="86">
+      <c r="H17" s="79">
         <f>IFERROR(SUMIF($F$10:$F$19,"&gt;="&amp;F17,$F$10:$F$19)/SUM($F$10:$F$19),0)</f>
         <v/>
       </c>
-      <c r="R17" s="70">
-        <f>RANK.EQ(F17,$F$10:$F$19,0)+COUNTIF($F$10:F17,F17)-1</f>
-        <v/>
-      </c>
-      <c r="S17" s="70">
-        <f>INDEX($A$10:$A$19,MATCH(ROWS($S$10:S17),$R$10:$R$19,0))</f>
-        <v/>
-      </c>
-      <c r="T17" s="71">
-        <f>INDEX($B$10:$B$19,MATCH(ROWS($T$10:T17),$R$10:$R$19,0))&amp;" ("&amp;S17&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U17" s="72">
-        <f>INDEX($F$10:$F$19,MATCH(ROWS($U$10:U17),$R$10:$R$19,0))</f>
-        <v/>
-      </c>
-      <c r="V17" s="73">
-        <f>INDEX($H$10:$H$19,MATCH(ROWS($V$10:V17),$R$10:$R$19,0))</f>
-        <v/>
-      </c>
-      <c r="W17" s="74">
-        <f>IF($S17="A",$U17,NA())</f>
-        <v/>
-      </c>
-      <c r="X17" s="75">
-        <f>IF($S17="B",$U17,NA())</f>
-        <v/>
-      </c>
-      <c r="Y17" s="76">
-        <f>IF($S17="C",$U17,NA())</f>
-        <v/>
+      <c r="P17" s="65" t="inlineStr">
+        <is>
+          <t>Cabo Rede Cat6 (m) (C)</t>
+        </is>
+      </c>
+      <c r="Q17" s="66" t="n">
+        <v>1600</v>
+      </c>
+      <c r="R17" s="67" t="n">
+        <v>0.9778</v>
+      </c>
+      <c r="S17" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="70" t="n">
+        <v>1600</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="68">
+      <c r="A18" s="61">
         <f>IF($H18&lt;=$E$5,"A",IF($H18&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B18" s="83" t="inlineStr">
+      <c r="B18" s="76" t="inlineStr">
         <is>
           <t>Cabo Rede Cat6 (m)</t>
         </is>
       </c>
-      <c r="C18" s="84" t="n">
+      <c r="C18" s="77" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="61" t="n">
+      <c r="D18" s="57" t="n">
         <v>200</v>
       </c>
-      <c r="E18" s="62" t="n">
+      <c r="E18" s="58" t="n">
         <v>8</v>
       </c>
-      <c r="F18" s="85">
+      <c r="F18" s="78">
         <f>IFERROR(D18*E18,0)</f>
         <v/>
       </c>
-      <c r="G18" s="86">
+      <c r="G18" s="79">
         <f>IFERROR(F18/SUM($F$10:$F$19),0)</f>
         <v/>
       </c>
-      <c r="H18" s="86">
+      <c r="H18" s="79">
         <f>IFERROR(SUMIF($F$10:$F$19,"&gt;="&amp;F18,$F$10:$F$19)/SUM($F$10:$F$19),0)</f>
         <v/>
       </c>
-      <c r="R18" s="70">
-        <f>RANK.EQ(F18,$F$10:$F$19,0)+COUNTIF($F$10:F18,F18)-1</f>
-        <v/>
-      </c>
-      <c r="S18" s="70">
-        <f>INDEX($A$10:$A$19,MATCH(ROWS($S$10:S18),$R$10:$R$19,0))</f>
-        <v/>
-      </c>
-      <c r="T18" s="71">
-        <f>INDEX($B$10:$B$19,MATCH(ROWS($T$10:T18),$R$10:$R$19,0))&amp;" ("&amp;S18&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U18" s="72">
-        <f>INDEX($F$10:$F$19,MATCH(ROWS($U$10:U18),$R$10:$R$19,0))</f>
-        <v/>
-      </c>
-      <c r="V18" s="73">
-        <f>INDEX($H$10:$H$19,MATCH(ROWS($V$10:V18),$R$10:$R$19,0))</f>
-        <v/>
-      </c>
-      <c r="W18" s="74">
-        <f>IF($S18="A",$U18,NA())</f>
-        <v/>
-      </c>
-      <c r="X18" s="75">
-        <f>IF($S18="B",$U18,NA())</f>
-        <v/>
-      </c>
-      <c r="Y18" s="76">
-        <f>IF($S18="C",$U18,NA())</f>
-        <v/>
+      <c r="P18" s="65" t="inlineStr">
+        <is>
+          <t>Patch Cord 1m (C)</t>
+        </is>
+      </c>
+      <c r="Q18" s="66" t="n">
+        <v>1500</v>
+      </c>
+      <c r="R18" s="67" t="n">
+        <v>0.9891</v>
+      </c>
+      <c r="S18" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="70" t="n">
+        <v>1500</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="68">
+      <c r="A19" s="61">
         <f>IF($H19&lt;=$E$5,"A",IF($H19&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B19" s="83" t="inlineStr">
+      <c r="B19" s="76" t="inlineStr">
         <is>
           <t>Mousepad Slim</t>
         </is>
       </c>
-      <c r="C19" s="84" t="n">
+      <c r="C19" s="77" t="n">
         <v>10</v>
       </c>
-      <c r="D19" s="61" t="n">
+      <c r="D19" s="57" t="n">
         <v>120</v>
       </c>
-      <c r="E19" s="62" t="n">
+      <c r="E19" s="58" t="n">
         <v>12</v>
       </c>
-      <c r="F19" s="85">
+      <c r="F19" s="78">
         <f>IFERROR(D19*E19,0)</f>
         <v/>
       </c>
-      <c r="G19" s="86">
+      <c r="G19" s="79">
         <f>IFERROR(F19/SUM($F$10:$F$19),0)</f>
         <v/>
       </c>
-      <c r="H19" s="86">
+      <c r="H19" s="79">
         <f>IFERROR(SUMIF($F$10:$F$19,"&gt;="&amp;F19,$F$10:$F$19)/SUM($F$10:$F$19),0)</f>
         <v/>
       </c>
-      <c r="R19" s="70">
-        <f>RANK.EQ(F19,$F$10:$F$19,0)+COUNTIF($F$10:F19,F19)-1</f>
-        <v/>
-      </c>
-      <c r="S19" s="70">
-        <f>INDEX($A$10:$A$19,MATCH(ROWS($S$10:S19),$R$10:$R$19,0))</f>
-        <v/>
-      </c>
-      <c r="T19" s="71">
-        <f>INDEX($B$10:$B$19,MATCH(ROWS($T$10:T19),$R$10:$R$19,0))&amp;" ("&amp;S19&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U19" s="72">
-        <f>INDEX($F$10:$F$19,MATCH(ROWS($U$10:U19),$R$10:$R$19,0))</f>
-        <v/>
-      </c>
-      <c r="V19" s="73">
-        <f>INDEX($H$10:$H$19,MATCH(ROWS($V$10:V19),$R$10:$R$19,0))</f>
-        <v/>
-      </c>
-      <c r="W19" s="74">
-        <f>IF($S19="A",$U19,NA())</f>
-        <v/>
-      </c>
-      <c r="X19" s="75">
-        <f>IF($S19="B",$U19,NA())</f>
-        <v/>
-      </c>
-      <c r="Y19" s="76">
-        <f>IF($S19="C",$U19,NA())</f>
-        <v/>
+      <c r="P19" s="65" t="inlineStr">
+        <is>
+          <t>Mousepad Slim (C)</t>
+        </is>
+      </c>
+      <c r="Q19" s="66" t="n">
+        <v>1440</v>
+      </c>
+      <c r="R19" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="70" t="n">
+        <v>1440</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="87" t="inlineStr">
+      <c r="A20" s="80" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B20" s="88" t="n"/>
-      <c r="C20" s="88" t="n"/>
-      <c r="D20" s="89">
+      <c r="B20" s="81" t="n"/>
+      <c r="C20" s="81" t="n"/>
+      <c r="D20" s="82">
         <f>SUM(D10:D19)</f>
         <v/>
       </c>
-      <c r="E20" s="90" t="n"/>
-      <c r="F20" s="91">
+      <c r="E20" s="83" t="n"/>
+      <c r="F20" s="84">
         <f>SUM(F10:F19)</f>
         <v/>
       </c>
-      <c r="G20" s="92" t="n">
+      <c r="G20" s="85" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="92" t="n">
+      <c r="H20" s="85" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CURVA ABC REGGAE  |  CURVA ABC REGGAE  —  PRIMEIRA  |  One Love, One Data  |  2026</t>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CURVA ABC REGGAE  |  CURVA ABC — PRIMEIRA  |  One Love, One Data  |  2026</t>
         </is>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="F0B1"/>
-  <mergeCells count="26">
+  <mergeCells count="21">
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A51:H51"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="J1:N1"/>
@@ -3544,20 +3468,17 @@
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E51:F51"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
-    <mergeCell ref="J11:N11"/>
     <mergeCell ref="E2:F2"/>
-    <mergeCell ref="C51:D51"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
-    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="A53:H53"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="E3:F3"/>
   </mergeCells>
@@ -3584,7 +3505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y61"/>
+  <dimension ref="A1:U63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3601,1653 +3522,1369 @@
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="2" customWidth="1" min="15" max="15"/>
-    <col width="2" customWidth="1" min="16" max="16"/>
-    <col width="2" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="38" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="16" customWidth="1" min="23" max="23"/>
-    <col width="16" customWidth="1" min="24" max="24"/>
-    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
-    <row r="1" ht="50" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
-        <is>
-          <t>CURVA ABC REGGAE  —  ABA 01</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="n"/>
-      <c r="J1" s="16" t="inlineStr">
-        <is>
-          <t>A = ate 80%   |   B = 80-95%   |   C = 95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+    <row r="1" ht="48" customHeight="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>CURVA ABC — ABA 01</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="n"/>
+      <c r="J1" s="18" t="inlineStr">
+        <is>
+          <t>A = ate 80%   |   B = 80–95%   |   C = 95–100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>V.T. TOTAL</t>
         </is>
       </c>
-      <c r="B2" s="18" t="n"/>
-      <c r="C2" s="19" t="inlineStr">
+      <c r="B2" s="20" t="n"/>
+      <c r="C2" s="21" t="inlineStr">
         <is>
           <t>V.T. CLASSE A</t>
         </is>
       </c>
-      <c r="D2" s="18" t="n"/>
-      <c r="E2" s="20" t="inlineStr">
+      <c r="D2" s="20" t="n"/>
+      <c r="E2" s="22" t="inlineStr">
         <is>
           <t>% ITENS A</t>
         </is>
       </c>
-      <c r="F2" s="18" t="n"/>
-      <c r="G2" s="21" t="inlineStr">
+      <c r="F2" s="20" t="n"/>
+      <c r="G2" s="23" t="inlineStr">
         <is>
           <t>MAIOR V.T.</t>
         </is>
       </c>
-      <c r="H2" s="22" t="n"/>
-      <c r="J2" s="1" t="n"/>
-      <c r="K2" s="1" t="n"/>
-      <c r="L2" s="1" t="n"/>
-      <c r="M2" s="1" t="n"/>
-      <c r="N2" s="1" t="n"/>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="23">
+      <c r="H2" s="24" t="n"/>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="25">
         <f>SUM($F$10:$F$29)</f>
         <v/>
       </c>
-      <c r="B3" s="24" t="n"/>
-      <c r="C3" s="25">
+      <c r="B3" s="26" t="n"/>
+      <c r="C3" s="27">
         <f>SUMIF($A$10:$A$29,"A",$F$10:$F$29)</f>
         <v/>
       </c>
-      <c r="D3" s="24" t="n"/>
-      <c r="E3" s="26">
+      <c r="D3" s="26" t="n"/>
+      <c r="E3" s="28">
         <f>IFERROR(COUNTIF($A$10:$A$29,"A")/COUNTA($B$10:$B$29),0)</f>
         <v/>
       </c>
-      <c r="F3" s="24" t="n"/>
-      <c r="G3" s="27">
+      <c r="F3" s="26" t="n"/>
+      <c r="G3" s="29">
         <f>MAX($F$10:$F$29)</f>
         <v/>
       </c>
-      <c r="H3" s="28" t="n"/>
-      <c r="J3" s="1" t="n"/>
-      <c r="K3" s="1" t="n"/>
-      <c r="L3" s="1" t="n"/>
-      <c r="M3" s="1" t="n"/>
-      <c r="N3" s="1" t="n"/>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="H3" s="30" t="n"/>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>MENOR V.T.</t>
         </is>
       </c>
-      <c r="B4" s="24" t="n"/>
-      <c r="C4" s="30" t="inlineStr">
+      <c r="B4" s="26" t="n"/>
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
       </c>
-      <c r="D4" s="24" t="n"/>
-      <c r="E4" s="31" t="inlineStr">
+      <c r="D4" s="26" t="n"/>
+      <c r="E4" s="33" t="inlineStr">
         <is>
           <t>LIMITE A</t>
         </is>
       </c>
-      <c r="F4" s="24" t="n"/>
-      <c r="G4" s="32" t="inlineStr">
+      <c r="F4" s="26" t="n"/>
+      <c r="G4" s="34" t="inlineStr">
         <is>
           <t>LIMITE B</t>
         </is>
       </c>
-      <c r="H4" s="28" t="n"/>
-      <c r="J4" s="1" t="n"/>
-      <c r="K4" s="1" t="n"/>
-      <c r="L4" s="1" t="n"/>
-      <c r="M4" s="1" t="n"/>
-      <c r="N4" s="1" t="n"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="33">
+      <c r="H4" s="30" t="n"/>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="35">
         <f>MIN($F$10:$F$29)</f>
         <v/>
       </c>
-      <c r="B5" s="34" t="n"/>
-      <c r="C5" s="35">
-        <f>IF(IFERROR(MAX($H$10:$H$29),0)&gt;1.0001,"VERIFICAR","CONSISTENTE")</f>
-        <v/>
-      </c>
-      <c r="D5" s="34" t="n"/>
-      <c r="E5" s="36" t="n">
+      <c r="B5" s="36" t="n"/>
+      <c r="C5" s="37">
+        <f>IF(IFERROR(MAX($H$10:$H$29),0)&gt;1.0001,"VERIFICAR","OK")</f>
+        <v/>
+      </c>
+      <c r="D5" s="36" t="n"/>
+      <c r="E5" s="38" t="n">
         <v>0.8</v>
       </c>
-      <c r="F5" s="34" t="n"/>
-      <c r="G5" s="37" t="n">
+      <c r="F5" s="36" t="n"/>
+      <c r="G5" s="39" t="n">
         <v>0.95</v>
       </c>
-      <c r="H5" s="38" t="n"/>
-      <c r="J5" s="1" t="n"/>
-      <c r="K5" s="1" t="n"/>
-      <c r="L5" s="1" t="n"/>
-      <c r="M5" s="1" t="n"/>
-      <c r="N5" s="1" t="n"/>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Analise de Estoque | Tecnologia da Informacao | Dashboard Premium  |  Edite somente Quant. e Custo Unit. — formulas, ABC e graficos atualizam automaticamente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="J7" s="40" t="inlineStr">
+      <c r="H5" s="40" t="n"/>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Edite somente Quant. e Custo Unit. — ABC, V.T. e % recalculam automaticamente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="J7" s="42" t="inlineStr">
         <is>
           <t>Classe</t>
         </is>
       </c>
-      <c r="K7" s="40" t="inlineStr">
+      <c r="K7" s="42" t="inlineStr">
         <is>
           <t>Total V.T.</t>
         </is>
       </c>
-      <c r="L7" s="40" t="inlineStr">
+      <c r="L7" s="42" t="inlineStr">
         <is>
           <t>% Total</t>
         </is>
       </c>
-      <c r="M7" s="40" t="inlineStr">
+      <c r="M7" s="42" t="inlineStr">
         <is>
           <t>Qtd. Itens</t>
         </is>
       </c>
-      <c r="N7" s="40" t="inlineStr">
-        <is>
-          <t>Barra Rapida</t>
+      <c r="N7" s="42" t="inlineStr">
+        <is>
+          <t>Barra</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="41" t="inlineStr">
+      <c r="A8" s="43" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
-      <c r="B8" s="42" t="inlineStr">
-        <is>
-          <t>Descricao do Item</t>
-        </is>
-      </c>
-      <c r="C8" s="43" t="inlineStr">
-        <is>
-          <t>Cod./ID</t>
-        </is>
-      </c>
-      <c r="D8" s="44" t="inlineStr">
+      <c r="B8" s="44" t="inlineStr">
+        <is>
+          <t>Descricao</t>
+        </is>
+      </c>
+      <c r="C8" s="44" t="inlineStr">
+        <is>
+          <t>Cod.</t>
+        </is>
+      </c>
+      <c r="D8" s="45" t="inlineStr">
         <is>
           <t>Quant.</t>
         </is>
       </c>
-      <c r="E8" s="44" t="inlineStr">
-        <is>
-          <t>Custo Unit. (R$)</t>
-        </is>
-      </c>
-      <c r="F8" s="41" t="inlineStr">
+      <c r="E8" s="45" t="inlineStr">
+        <is>
+          <t>Custo Unit.(R$)</t>
+        </is>
+      </c>
+      <c r="F8" s="43" t="inlineStr">
         <is>
           <t>V.T. (R$)</t>
         </is>
       </c>
-      <c r="G8" s="43" t="inlineStr">
+      <c r="G8" s="44" t="inlineStr">
         <is>
           <t>% Individual</t>
         </is>
       </c>
-      <c r="H8" s="43" t="inlineStr">
+      <c r="H8" s="44" t="inlineStr">
         <is>
           <t>% Acumulado</t>
         </is>
       </c>
-      <c r="J8" s="45" t="inlineStr">
+      <c r="J8" s="46" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K8" s="46">
+      <c r="K8" s="47">
         <f>SUMIF($A$10:$A$29,"A",$F$10:$F$29)</f>
         <v/>
       </c>
-      <c r="L8" s="47">
+      <c r="L8" s="48">
         <f>IFERROR(K8/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="M8" s="48">
+      <c r="M8" s="46">
         <f>COUNTIF($A$10:$A$29,"A")</f>
         <v/>
       </c>
       <c r="N8" s="49">
-        <f>REPT("█",ROUND(L8*20,0))</f>
-        <v/>
+        <f>REPT(CHAR(9608),ROUND(L8*20,0))</f>
+        <v/>
+      </c>
+      <c r="P8" s="50" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="Q8" s="50" t="inlineStr">
+        <is>
+          <t>VT Ord.</t>
+        </is>
       </c>
       <c r="R8" s="50" t="inlineStr">
         <is>
-          <t>Rank</t>
+          <t>% Acum.</t>
         </is>
       </c>
       <c r="S8" s="50" t="inlineStr">
         <is>
-          <t>ABC Ord.</t>
+          <t>VT A</t>
         </is>
       </c>
       <c r="T8" s="50" t="inlineStr">
         <is>
-          <t>Rotulo</t>
+          <t>VT B</t>
         </is>
       </c>
       <c r="U8" s="50" t="inlineStr">
         <is>
-          <t>V.T. Ord.</t>
-        </is>
-      </c>
-      <c r="V8" s="50" t="inlineStr">
-        <is>
-          <t>% Acum. Ord.</t>
-        </is>
-      </c>
-      <c r="W8" s="51" t="inlineStr">
-        <is>
-          <t>V.T. A</t>
-        </is>
-      </c>
-      <c r="X8" s="52" t="inlineStr">
-        <is>
-          <t>V.T. B</t>
-        </is>
-      </c>
-      <c r="Y8" s="53" t="inlineStr">
-        <is>
-          <t>V.T. C</t>
+          <t>VT C</t>
         </is>
       </c>
     </row>
     <row r="9" ht="6" customHeight="1">
-      <c r="J9" s="54" t="inlineStr">
+      <c r="J9" s="51" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K9" s="55">
+      <c r="K9" s="52">
         <f>SUMIF($A$10:$A$29,"B",$F$10:$F$29)</f>
         <v/>
       </c>
-      <c r="L9" s="56">
+      <c r="L9" s="53">
         <f>IFERROR(K9/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="M9" s="57">
+      <c r="M9" s="51">
         <f>COUNTIF($A$10:$A$29,"B")</f>
         <v/>
       </c>
-      <c r="N9" s="58">
-        <f>REPT("█",ROUND(L9*20,0))</f>
+      <c r="N9" s="54">
+        <f>REPT(CHAR(9608),ROUND(L9*20,0))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
-      <c r="A10" s="48">
+      <c r="A10" s="46">
         <f>IF($H10&lt;=$E$5,"A",IF($H10&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B10" s="59" t="inlineStr">
+      <c r="B10" s="55" t="inlineStr">
         <is>
           <t>Notebook Executivo i7</t>
         </is>
       </c>
-      <c r="C10" s="60" t="n">
+      <c r="C10" s="56" t="n">
         <v>10</v>
       </c>
-      <c r="D10" s="61" t="n">
+      <c r="D10" s="57" t="n">
         <v>35</v>
       </c>
-      <c r="E10" s="62" t="n">
+      <c r="E10" s="58" t="n">
         <v>6500</v>
       </c>
-      <c r="F10" s="63">
+      <c r="F10" s="59">
         <f>IFERROR(D10*E10,0)</f>
         <v/>
       </c>
-      <c r="G10" s="64">
+      <c r="G10" s="60">
         <f>IFERROR(F10/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="H10" s="64">
+      <c r="H10" s="60">
         <f>IFERROR(SUMIF($F$10:$F$29,"&gt;="&amp;F10,$F$10:$F$29)/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="J10" s="65" t="inlineStr">
+      <c r="J10" s="61" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="K10" s="66">
+      <c r="K10" s="62">
         <f>SUMIF($A$10:$A$29,"C",$F$10:$F$29)</f>
         <v/>
       </c>
-      <c r="L10" s="67">
+      <c r="L10" s="63">
         <f>IFERROR(K10/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="M10" s="68">
+      <c r="M10" s="61">
         <f>COUNTIF($A$10:$A$29,"C")</f>
         <v/>
       </c>
-      <c r="N10" s="69">
-        <f>REPT("█",ROUND(L10*20,0))</f>
-        <v/>
-      </c>
-      <c r="R10" s="70">
-        <f>RANK.EQ(F10,$F$10:$F$29,0)+COUNTIF($F$10:F10,F10)-1</f>
-        <v/>
-      </c>
-      <c r="S10" s="70">
-        <f>INDEX($A$10:$A$29,MATCH(ROWS($S$10:S10),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="T10" s="71">
-        <f>INDEX($B$10:$B$29,MATCH(ROWS($T$10:T10),$R$10:$R$29,0))&amp;" ("&amp;S10&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U10" s="72">
-        <f>INDEX($F$10:$F$29,MATCH(ROWS($U$10:U10),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="V10" s="73">
-        <f>INDEX($H$10:$H$29,MATCH(ROWS($V$10:V10),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="W10" s="74">
-        <f>IF($S10="A",$U10,NA())</f>
-        <v/>
-      </c>
-      <c r="X10" s="75">
-        <f>IF($S10="B",$U10,NA())</f>
-        <v/>
-      </c>
-      <c r="Y10" s="76">
-        <f>IF($S10="C",$U10,NA())</f>
-        <v/>
+      <c r="N10" s="64">
+        <f>REPT(CHAR(9608),ROUND(L10*20,0))</f>
+        <v/>
+      </c>
+      <c r="P10" s="65" t="inlineStr">
+        <is>
+          <t>Notebook Executivo i (A)</t>
+        </is>
+      </c>
+      <c r="Q10" s="66" t="n">
+        <v>227500</v>
+      </c>
+      <c r="R10" s="67" t="n">
+        <v>0.3531</v>
+      </c>
+      <c r="S10" s="68" t="n">
+        <v>227500</v>
+      </c>
+      <c r="T10" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="48">
+      <c r="A11" s="46">
         <f>IF($H11&lt;=$E$5,"A",IF($H11&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B11" s="59" t="inlineStr">
+      <c r="B11" s="55" t="inlineStr">
         <is>
           <t>Servidor de Dados Pro</t>
         </is>
       </c>
-      <c r="C11" s="60" t="n">
+      <c r="C11" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="61" t="n">
+      <c r="D11" s="57" t="n">
         <v>12</v>
       </c>
-      <c r="E11" s="62" t="n">
+      <c r="E11" s="58" t="n">
         <v>15000</v>
       </c>
-      <c r="F11" s="63">
+      <c r="F11" s="59">
         <f>IFERROR(D11*E11,0)</f>
         <v/>
       </c>
-      <c r="G11" s="64">
+      <c r="G11" s="60">
         <f>IFERROR(F11/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="H11" s="64">
+      <c r="H11" s="60">
         <f>IFERROR(SUMIF($F$10:$F$29,"&gt;="&amp;F11,$F$10:$F$29)/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="J11" s="77">
-        <f>IF(IFERROR(MAX($H$10:$H$29),0)&gt;1.0001,"ALERTA: acumulado &gt; 100%","OK - CONSISTENTE")</f>
-        <v/>
-      </c>
-      <c r="R11" s="70">
-        <f>RANK.EQ(F11,$F$10:$F$29,0)+COUNTIF($F$10:F11,F11)-1</f>
-        <v/>
-      </c>
-      <c r="S11" s="70">
-        <f>INDEX($A$10:$A$29,MATCH(ROWS($S$10:S11),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="T11" s="71">
-        <f>INDEX($B$10:$B$29,MATCH(ROWS($T$10:T11),$R$10:$R$29,0))&amp;" ("&amp;S11&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U11" s="72">
-        <f>INDEX($F$10:$F$29,MATCH(ROWS($U$10:U11),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="V11" s="73">
-        <f>INDEX($H$10:$H$29,MATCH(ROWS($V$10:V11),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="W11" s="74">
-        <f>IF($S11="A",$U11,NA())</f>
-        <v/>
-      </c>
-      <c r="X11" s="75">
-        <f>IF($S11="B",$U11,NA())</f>
-        <v/>
-      </c>
-      <c r="Y11" s="76">
-        <f>IF($S11="C",$U11,NA())</f>
-        <v/>
+      <c r="P11" s="65" t="inlineStr">
+        <is>
+          <t>Servidor de Dados Pr (A)</t>
+        </is>
+      </c>
+      <c r="Q11" s="66" t="n">
+        <v>180000</v>
+      </c>
+      <c r="R11" s="67" t="n">
+        <v>0.6324</v>
+      </c>
+      <c r="S11" s="68" t="n">
+        <v>180000</v>
+      </c>
+      <c r="T11" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1">
-      <c r="A12" s="48">
+      <c r="A12" s="46">
         <f>IF($H12&lt;=$E$5,"A",IF($H12&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B12" s="59" t="inlineStr">
+      <c r="B12" s="55" t="inlineStr">
         <is>
           <t>Impressora Multifuncional</t>
         </is>
       </c>
-      <c r="C12" s="60" t="n">
+      <c r="C12" s="56" t="n">
         <v>17</v>
       </c>
-      <c r="D12" s="61" t="n">
+      <c r="D12" s="57" t="n">
         <v>55</v>
       </c>
-      <c r="E12" s="62" t="n">
+      <c r="E12" s="58" t="n">
         <v>1100</v>
       </c>
-      <c r="F12" s="63">
+      <c r="F12" s="59">
         <f>IFERROR(D12*E12,0)</f>
         <v/>
       </c>
-      <c r="G12" s="64">
+      <c r="G12" s="60">
         <f>IFERROR(F12/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="H12" s="64">
+      <c r="H12" s="60">
         <f>IFERROR(SUMIF($F$10:$F$29,"&gt;="&amp;F12,$F$10:$F$29)/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="R12" s="70">
-        <f>RANK.EQ(F12,$F$10:$F$29,0)+COUNTIF($F$10:F12,F12)-1</f>
-        <v/>
-      </c>
-      <c r="S12" s="70">
-        <f>INDEX($A$10:$A$29,MATCH(ROWS($S$10:S12),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="T12" s="71">
-        <f>INDEX($B$10:$B$29,MATCH(ROWS($T$10:T12),$R$10:$R$29,0))&amp;" ("&amp;S12&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U12" s="72">
-        <f>INDEX($F$10:$F$29,MATCH(ROWS($U$10:U12),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="V12" s="73">
-        <f>INDEX($H$10:$H$29,MATCH(ROWS($V$10:V12),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="W12" s="74">
-        <f>IF($S12="A",$U12,NA())</f>
-        <v/>
-      </c>
-      <c r="X12" s="75">
-        <f>IF($S12="B",$U12,NA())</f>
-        <v/>
-      </c>
-      <c r="Y12" s="76">
-        <f>IF($S12="C",$U12,NA())</f>
-        <v/>
+      <c r="P12" s="65" t="inlineStr">
+        <is>
+          <t>Impressora Multifunc (A)</t>
+        </is>
+      </c>
+      <c r="Q12" s="66" t="n">
+        <v>60500</v>
+      </c>
+      <c r="R12" s="67" t="n">
+        <v>0.7262999999999999</v>
+      </c>
+      <c r="S12" s="68" t="n">
+        <v>60500</v>
+      </c>
+      <c r="T12" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="48">
+      <c r="A13" s="46">
         <f>IF($H13&lt;=$E$5,"A",IF($H13&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B13" s="59" t="inlineStr">
+      <c r="B13" s="55" t="inlineStr">
         <is>
           <t>Toner Impressora Laser</t>
         </is>
       </c>
-      <c r="C13" s="60" t="n">
+      <c r="C13" s="56" t="n">
         <v>12</v>
       </c>
-      <c r="D13" s="61" t="n">
+      <c r="D13" s="57" t="n">
         <v>68</v>
       </c>
-      <c r="E13" s="62" t="n">
+      <c r="E13" s="58" t="n">
         <v>680</v>
       </c>
-      <c r="F13" s="63">
+      <c r="F13" s="59">
         <f>IFERROR(D13*E13,0)</f>
         <v/>
       </c>
-      <c r="G13" s="64">
+      <c r="G13" s="60">
         <f>IFERROR(F13/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="H13" s="64">
+      <c r="H13" s="60">
         <f>IFERROR(SUMIF($F$10:$F$29,"&gt;="&amp;F13,$F$10:$F$29)/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="R13" s="70">
-        <f>RANK.EQ(F13,$F$10:$F$29,0)+COUNTIF($F$10:F13,F13)-1</f>
-        <v/>
-      </c>
-      <c r="S13" s="70">
-        <f>INDEX($A$10:$A$29,MATCH(ROWS($S$10:S13),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="T13" s="71">
-        <f>INDEX($B$10:$B$29,MATCH(ROWS($T$10:T13),$R$10:$R$29,0))&amp;" ("&amp;S13&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U13" s="72">
-        <f>INDEX($F$10:$F$29,MATCH(ROWS($U$10:U13),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="V13" s="73">
-        <f>INDEX($H$10:$H$29,MATCH(ROWS($V$10:V13),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="W13" s="74">
-        <f>IF($S13="A",$U13,NA())</f>
-        <v/>
-      </c>
-      <c r="X13" s="75">
-        <f>IF($S13="B",$U13,NA())</f>
-        <v/>
-      </c>
-      <c r="Y13" s="76">
-        <f>IF($S13="C",$U13,NA())</f>
-        <v/>
+      <c r="P13" s="65" t="inlineStr">
+        <is>
+          <t>Toner Impressora Las (A)</t>
+        </is>
+      </c>
+      <c r="Q13" s="66" t="n">
+        <v>46240</v>
+      </c>
+      <c r="R13" s="67" t="n">
+        <v>0.7981</v>
+      </c>
+      <c r="S13" s="68" t="n">
+        <v>46240</v>
+      </c>
+      <c r="T13" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="78">
+      <c r="A14" s="71">
         <f>IF($H14&lt;=$E$5,"A",IF($H14&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B14" s="79" t="inlineStr">
+      <c r="B14" s="72" t="inlineStr">
         <is>
           <t>Memoria RAM 16GB</t>
         </is>
       </c>
-      <c r="C14" s="80" t="n">
+      <c r="C14" s="73" t="n">
         <v>19</v>
       </c>
-      <c r="D14" s="61" t="n">
+      <c r="D14" s="57" t="n">
         <v>45</v>
       </c>
-      <c r="E14" s="62" t="n">
+      <c r="E14" s="58" t="n">
         <v>380</v>
       </c>
-      <c r="F14" s="81">
+      <c r="F14" s="74">
         <f>IFERROR(D14*E14,0)</f>
         <v/>
       </c>
-      <c r="G14" s="82">
+      <c r="G14" s="75">
         <f>IFERROR(F14/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="H14" s="82">
+      <c r="H14" s="75">
         <f>IFERROR(SUMIF($F$10:$F$29,"&gt;="&amp;F14,$F$10:$F$29)/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="R14" s="70">
-        <f>RANK.EQ(F14,$F$10:$F$29,0)+COUNTIF($F$10:F14,F14)-1</f>
-        <v/>
-      </c>
-      <c r="S14" s="70">
-        <f>INDEX($A$10:$A$29,MATCH(ROWS($S$10:S14),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="T14" s="71">
-        <f>INDEX($B$10:$B$29,MATCH(ROWS($T$10:T14),$R$10:$R$29,0))&amp;" ("&amp;S14&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U14" s="72">
-        <f>INDEX($F$10:$F$29,MATCH(ROWS($U$10:U14),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="V14" s="73">
-        <f>INDEX($H$10:$H$29,MATCH(ROWS($V$10:V14),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="W14" s="74">
-        <f>IF($S14="A",$U14,NA())</f>
-        <v/>
-      </c>
-      <c r="X14" s="75">
-        <f>IF($S14="B",$U14,NA())</f>
-        <v/>
-      </c>
-      <c r="Y14" s="76">
-        <f>IF($S14="C",$U14,NA())</f>
-        <v/>
+      <c r="P14" s="65" t="inlineStr">
+        <is>
+          <t>Memoria RAM 16GB (B)</t>
+        </is>
+      </c>
+      <c r="Q14" s="66" t="n">
+        <v>17100</v>
+      </c>
+      <c r="R14" s="67" t="n">
+        <v>0.8246</v>
+      </c>
+      <c r="S14" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="69" t="n">
+        <v>17100</v>
+      </c>
+      <c r="U14" s="70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="78">
+      <c r="A15" s="71">
         <f>IF($H15&lt;=$E$5,"A",IF($H15&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B15" s="79" t="inlineStr">
+      <c r="B15" s="72" t="inlineStr">
         <is>
           <t>Monitor LED 24"</t>
         </is>
       </c>
-      <c r="C15" s="80" t="n">
+      <c r="C15" s="73" t="n">
         <v>4</v>
       </c>
-      <c r="D15" s="61" t="n">
+      <c r="D15" s="57" t="n">
         <v>20</v>
       </c>
-      <c r="E15" s="62" t="n">
+      <c r="E15" s="58" t="n">
         <v>850</v>
       </c>
-      <c r="F15" s="81">
+      <c r="F15" s="74">
         <f>IFERROR(D15*E15,0)</f>
         <v/>
       </c>
-      <c r="G15" s="82">
+      <c r="G15" s="75">
         <f>IFERROR(F15/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="H15" s="82">
+      <c r="H15" s="75">
         <f>IFERROR(SUMIF($F$10:$F$29,"&gt;="&amp;F15,$F$10:$F$29)/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="R15" s="70">
-        <f>RANK.EQ(F15,$F$10:$F$29,0)+COUNTIF($F$10:F15,F15)-1</f>
-        <v/>
-      </c>
-      <c r="S15" s="70">
-        <f>INDEX($A$10:$A$29,MATCH(ROWS($S$10:S15),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="T15" s="71">
-        <f>INDEX($B$10:$B$29,MATCH(ROWS($T$10:T15),$R$10:$R$29,0))&amp;" ("&amp;S15&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U15" s="72">
-        <f>INDEX($F$10:$F$29,MATCH(ROWS($U$10:U15),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="V15" s="73">
-        <f>INDEX($H$10:$H$29,MATCH(ROWS($V$10:V15),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="W15" s="74">
-        <f>IF($S15="A",$U15,NA())</f>
-        <v/>
-      </c>
-      <c r="X15" s="75">
-        <f>IF($S15="B",$U15,NA())</f>
-        <v/>
-      </c>
-      <c r="Y15" s="76">
-        <f>IF($S15="C",$U15,NA())</f>
-        <v/>
+      <c r="P15" s="65" t="inlineStr">
+        <is>
+          <t>Monitor LED 24" (B)</t>
+        </is>
+      </c>
+      <c r="Q15" s="66" t="n">
+        <v>17000</v>
+      </c>
+      <c r="R15" s="67" t="n">
+        <v>0.851</v>
+      </c>
+      <c r="S15" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="69" t="n">
+        <v>17000</v>
+      </c>
+      <c r="U15" s="70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="78">
+      <c r="A16" s="71">
         <f>IF($H16&lt;=$E$5,"A",IF($H16&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B16" s="79" t="inlineStr">
+      <c r="B16" s="72" t="inlineStr">
         <is>
           <t>Webcam Full HD</t>
         </is>
       </c>
-      <c r="C16" s="80" t="n">
+      <c r="C16" s="73" t="n">
         <v>14</v>
       </c>
-      <c r="D16" s="61" t="n">
+      <c r="D16" s="57" t="n">
         <v>82</v>
       </c>
-      <c r="E16" s="62" t="n">
+      <c r="E16" s="58" t="n">
         <v>180</v>
       </c>
-      <c r="F16" s="81">
+      <c r="F16" s="74">
         <f>IFERROR(D16*E16,0)</f>
         <v/>
       </c>
-      <c r="G16" s="82">
+      <c r="G16" s="75">
         <f>IFERROR(F16/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="H16" s="82">
+      <c r="H16" s="75">
         <f>IFERROR(SUMIF($F$10:$F$29,"&gt;="&amp;F16,$F$10:$F$29)/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="R16" s="70">
-        <f>RANK.EQ(F16,$F$10:$F$29,0)+COUNTIF($F$10:F16,F16)-1</f>
-        <v/>
-      </c>
-      <c r="S16" s="70">
-        <f>INDEX($A$10:$A$29,MATCH(ROWS($S$10:S16),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="T16" s="71">
-        <f>INDEX($B$10:$B$29,MATCH(ROWS($T$10:T16),$R$10:$R$29,0))&amp;" ("&amp;S16&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U16" s="72">
-        <f>INDEX($F$10:$F$29,MATCH(ROWS($U$10:U16),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="V16" s="73">
-        <f>INDEX($H$10:$H$29,MATCH(ROWS($V$10:V16),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="W16" s="74">
-        <f>IF($S16="A",$U16,NA())</f>
-        <v/>
-      </c>
-      <c r="X16" s="75">
-        <f>IF($S16="B",$U16,NA())</f>
-        <v/>
-      </c>
-      <c r="Y16" s="76">
-        <f>IF($S16="C",$U16,NA())</f>
-        <v/>
+      <c r="P16" s="65" t="inlineStr">
+        <is>
+          <t>Webcam Full HD (B)</t>
+        </is>
+      </c>
+      <c r="Q16" s="66" t="n">
+        <v>14760</v>
+      </c>
+      <c r="R16" s="67" t="n">
+        <v>0.8739</v>
+      </c>
+      <c r="S16" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="69" t="n">
+        <v>14760</v>
+      </c>
+      <c r="U16" s="70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="78">
+      <c r="A17" s="71">
         <f>IF($H17&lt;=$E$5,"A",IF($H17&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B17" s="79" t="inlineStr">
+      <c r="B17" s="72" t="inlineStr">
         <is>
           <t>Roteador Wi-Fi 6</t>
         </is>
       </c>
-      <c r="C17" s="80" t="n">
+      <c r="C17" s="73" t="n">
         <v>11</v>
       </c>
-      <c r="D17" s="61" t="n">
+      <c r="D17" s="57" t="n">
         <v>15</v>
       </c>
-      <c r="E17" s="62" t="n">
+      <c r="E17" s="58" t="n">
         <v>650</v>
       </c>
-      <c r="F17" s="81">
+      <c r="F17" s="74">
         <f>IFERROR(D17*E17,0)</f>
         <v/>
       </c>
-      <c r="G17" s="82">
+      <c r="G17" s="75">
         <f>IFERROR(F17/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="H17" s="82">
+      <c r="H17" s="75">
         <f>IFERROR(SUMIF($F$10:$F$29,"&gt;="&amp;F17,$F$10:$F$29)/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="R17" s="70">
-        <f>RANK.EQ(F17,$F$10:$F$29,0)+COUNTIF($F$10:F17,F17)-1</f>
-        <v/>
-      </c>
-      <c r="S17" s="70">
-        <f>INDEX($A$10:$A$29,MATCH(ROWS($S$10:S17),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="T17" s="71">
-        <f>INDEX($B$10:$B$29,MATCH(ROWS($T$10:T17),$R$10:$R$29,0))&amp;" ("&amp;S17&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U17" s="72">
-        <f>INDEX($F$10:$F$29,MATCH(ROWS($U$10:U17),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="V17" s="73">
-        <f>INDEX($H$10:$H$29,MATCH(ROWS($V$10:V17),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="W17" s="74">
-        <f>IF($S17="A",$U17,NA())</f>
-        <v/>
-      </c>
-      <c r="X17" s="75">
-        <f>IF($S17="B",$U17,NA())</f>
-        <v/>
-      </c>
-      <c r="Y17" s="76">
-        <f>IF($S17="C",$U17,NA())</f>
-        <v/>
+      <c r="P17" s="65" t="inlineStr">
+        <is>
+          <t>SSD 480GB Sata (B)</t>
+        </is>
+      </c>
+      <c r="Q17" s="66" t="n">
+        <v>10450</v>
+      </c>
+      <c r="R17" s="67" t="n">
+        <v>0.8901</v>
+      </c>
+      <c r="S17" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="69" t="n">
+        <v>10450</v>
+      </c>
+      <c r="U17" s="70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="78">
+      <c r="A18" s="71">
         <f>IF($H18&lt;=$E$5,"A",IF($H18&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B18" s="79" t="inlineStr">
+      <c r="B18" s="72" t="inlineStr">
         <is>
           <t>SSD 480GB Sata</t>
         </is>
       </c>
-      <c r="C18" s="80" t="n">
+      <c r="C18" s="73" t="n">
         <v>15</v>
       </c>
-      <c r="D18" s="61" t="n">
+      <c r="D18" s="57" t="n">
         <v>55</v>
       </c>
-      <c r="E18" s="62" t="n">
+      <c r="E18" s="58" t="n">
         <v>190</v>
       </c>
-      <c r="F18" s="81">
+      <c r="F18" s="74">
         <f>IFERROR(D18*E18,0)</f>
         <v/>
       </c>
-      <c r="G18" s="82">
+      <c r="G18" s="75">
         <f>IFERROR(F18/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="H18" s="82">
+      <c r="H18" s="75">
         <f>IFERROR(SUMIF($F$10:$F$29,"&gt;="&amp;F18,$F$10:$F$29)/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="R18" s="70">
-        <f>RANK.EQ(F18,$F$10:$F$29,0)+COUNTIF($F$10:F18,F18)-1</f>
-        <v/>
-      </c>
-      <c r="S18" s="70">
-        <f>INDEX($A$10:$A$29,MATCH(ROWS($S$10:S18),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="T18" s="71">
-        <f>INDEX($B$10:$B$29,MATCH(ROWS($T$10:T18),$R$10:$R$29,0))&amp;" ("&amp;S18&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U18" s="72">
-        <f>INDEX($F$10:$F$29,MATCH(ROWS($U$10:U18),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="V18" s="73">
-        <f>INDEX($H$10:$H$29,MATCH(ROWS($V$10:V18),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="W18" s="74">
-        <f>IF($S18="A",$U18,NA())</f>
-        <v/>
-      </c>
-      <c r="X18" s="75">
-        <f>IF($S18="B",$U18,NA())</f>
-        <v/>
-      </c>
-      <c r="Y18" s="76">
-        <f>IF($S18="C",$U18,NA())</f>
-        <v/>
+      <c r="P18" s="65" t="inlineStr">
+        <is>
+          <t>Roteador Wi-Fi 6 (B)</t>
+        </is>
+      </c>
+      <c r="Q18" s="66" t="n">
+        <v>9750</v>
+      </c>
+      <c r="R18" s="67" t="n">
+        <v>0.9053</v>
+      </c>
+      <c r="S18" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="69" t="n">
+        <v>9750</v>
+      </c>
+      <c r="U18" s="70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="78">
+      <c r="A19" s="71">
         <f>IF($H19&lt;=$E$5,"A",IF($H19&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B19" s="79" t="inlineStr">
+      <c r="B19" s="72" t="inlineStr">
         <is>
           <t>Nobreak 1500VA</t>
         </is>
       </c>
-      <c r="C19" s="80" t="n">
+      <c r="C19" s="73" t="n">
         <v>6</v>
       </c>
-      <c r="D19" s="61" t="n">
+      <c r="D19" s="57" t="n">
         <v>8</v>
       </c>
-      <c r="E19" s="62" t="n">
+      <c r="E19" s="58" t="n">
         <v>1200</v>
       </c>
-      <c r="F19" s="81">
+      <c r="F19" s="74">
         <f>IFERROR(D19*E19,0)</f>
         <v/>
       </c>
-      <c r="G19" s="82">
+      <c r="G19" s="75">
         <f>IFERROR(F19/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="H19" s="82">
+      <c r="H19" s="75">
         <f>IFERROR(SUMIF($F$10:$F$29,"&gt;="&amp;F19,$F$10:$F$29)/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="R19" s="70">
-        <f>RANK.EQ(F19,$F$10:$F$29,0)+COUNTIF($F$10:F19,F19)-1</f>
-        <v/>
-      </c>
-      <c r="S19" s="70">
-        <f>INDEX($A$10:$A$29,MATCH(ROWS($S$10:S19),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="T19" s="71">
-        <f>INDEX($B$10:$B$29,MATCH(ROWS($T$10:T19),$R$10:$R$29,0))&amp;" ("&amp;S19&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U19" s="72">
-        <f>INDEX($F$10:$F$29,MATCH(ROWS($U$10:U19),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="V19" s="73">
-        <f>INDEX($H$10:$H$29,MATCH(ROWS($V$10:V19),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="W19" s="74">
-        <f>IF($S19="A",$U19,NA())</f>
-        <v/>
-      </c>
-      <c r="X19" s="75">
-        <f>IF($S19="B",$U19,NA())</f>
-        <v/>
-      </c>
-      <c r="Y19" s="76">
-        <f>IF($S19="C",$U19,NA())</f>
-        <v/>
+      <c r="P19" s="65" t="inlineStr">
+        <is>
+          <t>Nobreak 1500VA (B)</t>
+        </is>
+      </c>
+      <c r="Q19" s="66" t="n">
+        <v>9600</v>
+      </c>
+      <c r="R19" s="67" t="n">
+        <v>0.9202</v>
+      </c>
+      <c r="S19" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="69" t="n">
+        <v>9600</v>
+      </c>
+      <c r="U19" s="70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="78">
+      <c r="A20" s="71">
         <f>IF($H20&lt;=$E$5,"A",IF($H20&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B20" s="79" t="inlineStr">
+      <c r="B20" s="72" t="inlineStr">
         <is>
           <t>HD Externo 2TB</t>
         </is>
       </c>
-      <c r="C20" s="80" t="n">
+      <c r="C20" s="73" t="n">
         <v>20</v>
       </c>
-      <c r="D20" s="61" t="n">
+      <c r="D20" s="57" t="n">
         <v>18</v>
       </c>
-      <c r="E20" s="62" t="n">
+      <c r="E20" s="58" t="n">
         <v>420</v>
       </c>
-      <c r="F20" s="81">
+      <c r="F20" s="74">
         <f>IFERROR(D20*E20,0)</f>
         <v/>
       </c>
-      <c r="G20" s="82">
+      <c r="G20" s="75">
         <f>IFERROR(F20/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="H20" s="82">
+      <c r="H20" s="75">
         <f>IFERROR(SUMIF($F$10:$F$29,"&gt;="&amp;F20,$F$10:$F$29)/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="R20" s="70">
-        <f>RANK.EQ(F20,$F$10:$F$29,0)+COUNTIF($F$10:F20,F20)-1</f>
-        <v/>
-      </c>
-      <c r="S20" s="70">
-        <f>INDEX($A$10:$A$29,MATCH(ROWS($S$10:S20),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="T20" s="71">
-        <f>INDEX($B$10:$B$29,MATCH(ROWS($T$10:T20),$R$10:$R$29,0))&amp;" ("&amp;S20&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U20" s="72">
-        <f>INDEX($F$10:$F$29,MATCH(ROWS($U$10:U20),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="V20" s="73">
-        <f>INDEX($H$10:$H$29,MATCH(ROWS($V$10:V20),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="W20" s="74">
-        <f>IF($S20="A",$U20,NA())</f>
-        <v/>
-      </c>
-      <c r="X20" s="75">
-        <f>IF($S20="B",$U20,NA())</f>
-        <v/>
-      </c>
-      <c r="Y20" s="76">
-        <f>IF($S20="C",$U20,NA())</f>
-        <v/>
+      <c r="P20" s="65" t="inlineStr">
+        <is>
+          <t>HD Externo 2TB (B)</t>
+        </is>
+      </c>
+      <c r="Q20" s="66" t="n">
+        <v>7560</v>
+      </c>
+      <c r="R20" s="67" t="n">
+        <v>0.9319</v>
+      </c>
+      <c r="S20" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="69" t="n">
+        <v>7560</v>
+      </c>
+      <c r="U20" s="70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="78">
+      <c r="A21" s="71">
         <f>IF($H21&lt;=$E$5,"A",IF($H21&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B21" s="79" t="inlineStr">
+      <c r="B21" s="72" t="inlineStr">
         <is>
           <t>Teclado Mecanico RGB</t>
         </is>
       </c>
-      <c r="C21" s="80" t="n">
+      <c r="C21" s="73" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="61" t="n">
+      <c r="D21" s="57" t="n">
         <v>30</v>
       </c>
-      <c r="E21" s="62" t="n">
+      <c r="E21" s="58" t="n">
         <v>250</v>
       </c>
-      <c r="F21" s="81">
+      <c r="F21" s="74">
         <f>IFERROR(D21*E21,0)</f>
         <v/>
       </c>
-      <c r="G21" s="82">
+      <c r="G21" s="75">
         <f>IFERROR(F21/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="H21" s="82">
+      <c r="H21" s="75">
         <f>IFERROR(SUMIF($F$10:$F$29,"&gt;="&amp;F21,$F$10:$F$29)/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="R21" s="70">
-        <f>RANK.EQ(F21,$F$10:$F$29,0)+COUNTIF($F$10:F21,F21)-1</f>
-        <v/>
-      </c>
-      <c r="S21" s="70">
-        <f>INDEX($A$10:$A$29,MATCH(ROWS($S$10:S21),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="T21" s="71">
-        <f>INDEX($B$10:$B$29,MATCH(ROWS($T$10:T21),$R$10:$R$29,0))&amp;" ("&amp;S21&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U21" s="72">
-        <f>INDEX($F$10:$F$29,MATCH(ROWS($U$10:U21),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="V21" s="73">
-        <f>INDEX($H$10:$H$29,MATCH(ROWS($V$10:V21),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="W21" s="74">
-        <f>IF($S21="A",$U21,NA())</f>
-        <v/>
-      </c>
-      <c r="X21" s="75">
-        <f>IF($S21="B",$U21,NA())</f>
-        <v/>
-      </c>
-      <c r="Y21" s="76">
-        <f>IF($S21="C",$U21,NA())</f>
-        <v/>
+      <c r="P21" s="65" t="inlineStr">
+        <is>
+          <t>Teclado Mecanico RGB (B)</t>
+        </is>
+      </c>
+      <c r="Q21" s="66" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R21" s="67" t="n">
+        <v>0.9435</v>
+      </c>
+      <c r="S21" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="69" t="n">
+        <v>7500</v>
+      </c>
+      <c r="U21" s="70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="68">
+      <c r="A22" s="61">
         <f>IF($H22&lt;=$E$5,"A",IF($H22&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B22" s="83" t="inlineStr">
+      <c r="B22" s="76" t="inlineStr">
         <is>
           <t>Pen Drive 64GB</t>
         </is>
       </c>
-      <c r="C22" s="84" t="n">
+      <c r="C22" s="77" t="n">
         <v>9</v>
       </c>
-      <c r="D22" s="61" t="n">
+      <c r="D22" s="57" t="n">
         <v>160</v>
       </c>
-      <c r="E22" s="62" t="n">
+      <c r="E22" s="58" t="n">
         <v>45</v>
       </c>
-      <c r="F22" s="85">
+      <c r="F22" s="78">
         <f>IFERROR(D22*E22,0)</f>
         <v/>
       </c>
-      <c r="G22" s="86">
+      <c r="G22" s="79">
         <f>IFERROR(F22/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="H22" s="86">
+      <c r="H22" s="79">
         <f>IFERROR(SUMIF($F$10:$F$29,"&gt;="&amp;F22,$F$10:$F$29)/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="R22" s="70">
-        <f>RANK.EQ(F22,$F$10:$F$29,0)+COUNTIF($F$10:F22,F22)-1</f>
-        <v/>
-      </c>
-      <c r="S22" s="70">
-        <f>INDEX($A$10:$A$29,MATCH(ROWS($S$10:S22),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="T22" s="71">
-        <f>INDEX($B$10:$B$29,MATCH(ROWS($T$10:T22),$R$10:$R$29,0))&amp;" ("&amp;S22&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U22" s="72">
-        <f>INDEX($F$10:$F$29,MATCH(ROWS($U$10:U22),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="V22" s="73">
-        <f>INDEX($H$10:$H$29,MATCH(ROWS($V$10:V22),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="W22" s="74">
-        <f>IF($S22="A",$U22,NA())</f>
-        <v/>
-      </c>
-      <c r="X22" s="75">
-        <f>IF($S22="B",$U22,NA())</f>
-        <v/>
-      </c>
-      <c r="Y22" s="76">
-        <f>IF($S22="C",$U22,NA())</f>
-        <v/>
+      <c r="P22" s="65" t="inlineStr">
+        <is>
+          <t>Pen Drive 64GB (C)</t>
+        </is>
+      </c>
+      <c r="Q22" s="66" t="n">
+        <v>7200</v>
+      </c>
+      <c r="R22" s="67" t="n">
+        <v>0.9547</v>
+      </c>
+      <c r="S22" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="70" t="n">
+        <v>7200</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="68">
+      <c r="A23" s="61">
         <f>IF($H23&lt;=$E$5,"A",IF($H23&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B23" s="83" t="inlineStr">
+      <c r="B23" s="76" t="inlineStr">
         <is>
           <t>Headset com Microfone</t>
         </is>
       </c>
-      <c r="C23" s="84" t="n">
+      <c r="C23" s="77" t="n">
         <v>13</v>
       </c>
-      <c r="D23" s="61" t="n">
+      <c r="D23" s="57" t="n">
         <v>64</v>
       </c>
-      <c r="E23" s="62" t="n">
+      <c r="E23" s="58" t="n">
         <v>110</v>
       </c>
-      <c r="F23" s="85">
+      <c r="F23" s="78">
         <f>IFERROR(D23*E23,0)</f>
         <v/>
       </c>
-      <c r="G23" s="86">
+      <c r="G23" s="79">
         <f>IFERROR(F23/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="H23" s="86">
+      <c r="H23" s="79">
         <f>IFERROR(SUMIF($F$10:$F$29,"&gt;="&amp;F23,$F$10:$F$29)/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="R23" s="70">
-        <f>RANK.EQ(F23,$F$10:$F$29,0)+COUNTIF($F$10:F23,F23)-1</f>
-        <v/>
-      </c>
-      <c r="S23" s="70">
-        <f>INDEX($A$10:$A$29,MATCH(ROWS($S$10:S23),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="T23" s="71">
-        <f>INDEX($B$10:$B$29,MATCH(ROWS($T$10:T23),$R$10:$R$29,0))&amp;" ("&amp;S23&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U23" s="72">
-        <f>INDEX($F$10:$F$29,MATCH(ROWS($U$10:U23),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="V23" s="73">
-        <f>INDEX($H$10:$H$29,MATCH(ROWS($V$10:V23),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="W23" s="74">
-        <f>IF($S23="A",$U23,NA())</f>
-        <v/>
-      </c>
-      <c r="X23" s="75">
-        <f>IF($S23="B",$U23,NA())</f>
-        <v/>
-      </c>
-      <c r="Y23" s="76">
-        <f>IF($S23="C",$U23,NA())</f>
-        <v/>
+      <c r="P23" s="65" t="inlineStr">
+        <is>
+          <t>Headset com Microfon (C)</t>
+        </is>
+      </c>
+      <c r="Q23" s="66" t="n">
+        <v>7040</v>
+      </c>
+      <c r="R23" s="67" t="n">
+        <v>0.9656</v>
+      </c>
+      <c r="S23" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="70" t="n">
+        <v>7040</v>
       </c>
     </row>
     <row r="24" ht="19" customHeight="1">
-      <c r="A24" s="68">
+      <c r="A24" s="61">
         <f>IF($H24&lt;=$E$5,"A",IF($H24&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B24" s="83" t="inlineStr">
-        <is>
-          <t>Pacote de Papel A4 (500fls)</t>
-        </is>
-      </c>
-      <c r="C24" s="84" t="n">
+      <c r="B24" s="76" t="inlineStr">
+        <is>
+          <t>Pacote de Papel A4</t>
+        </is>
+      </c>
+      <c r="C24" s="77" t="n">
         <v>7</v>
       </c>
-      <c r="D24" s="61" t="n">
+      <c r="D24" s="57" t="n">
         <v>237</v>
       </c>
-      <c r="E24" s="62" t="n">
+      <c r="E24" s="58" t="n">
         <v>28</v>
       </c>
-      <c r="F24" s="85">
+      <c r="F24" s="78">
         <f>IFERROR(D24*E24,0)</f>
         <v/>
       </c>
-      <c r="G24" s="86">
+      <c r="G24" s="79">
         <f>IFERROR(F24/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="H24" s="86">
+      <c r="H24" s="79">
         <f>IFERROR(SUMIF($F$10:$F$29,"&gt;="&amp;F24,$F$10:$F$29)/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="R24" s="70">
-        <f>RANK.EQ(F24,$F$10:$F$29,0)+COUNTIF($F$10:F24,F24)-1</f>
-        <v/>
-      </c>
-      <c r="S24" s="70">
-        <f>INDEX($A$10:$A$29,MATCH(ROWS($S$10:S24),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="T24" s="71">
-        <f>INDEX($B$10:$B$29,MATCH(ROWS($T$10:T24),$R$10:$R$29,0))&amp;" ("&amp;S24&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U24" s="72">
-        <f>INDEX($F$10:$F$29,MATCH(ROWS($U$10:U24),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="V24" s="73">
-        <f>INDEX($H$10:$H$29,MATCH(ROWS($V$10:V24),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="W24" s="74">
-        <f>IF($S24="A",$U24,NA())</f>
-        <v/>
-      </c>
-      <c r="X24" s="75">
-        <f>IF($S24="B",$U24,NA())</f>
-        <v/>
-      </c>
-      <c r="Y24" s="76">
-        <f>IF($S24="C",$U24,NA())</f>
-        <v/>
+      <c r="P24" s="65" t="inlineStr">
+        <is>
+          <t>Pacote de Papel A4 (C)</t>
+        </is>
+      </c>
+      <c r="Q24" s="66" t="n">
+        <v>6636</v>
+      </c>
+      <c r="R24" s="67" t="n">
+        <v>0.9759</v>
+      </c>
+      <c r="S24" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="70" t="n">
+        <v>6636</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
-      <c r="A25" s="68">
+      <c r="A25" s="61">
         <f>IF($H25&lt;=$E$5,"A",IF($H25&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B25" s="83" t="inlineStr">
+      <c r="B25" s="76" t="inlineStr">
         <is>
           <t>Filtro de Linha 5 Tom.</t>
         </is>
       </c>
-      <c r="C25" s="84" t="n">
+      <c r="C25" s="77" t="n">
         <v>18</v>
       </c>
-      <c r="D25" s="61" t="n">
+      <c r="D25" s="57" t="n">
         <v>110</v>
       </c>
-      <c r="E25" s="62" t="n">
+      <c r="E25" s="58" t="n">
         <v>40</v>
       </c>
-      <c r="F25" s="85">
+      <c r="F25" s="78">
         <f>IFERROR(D25*E25,0)</f>
         <v/>
       </c>
-      <c r="G25" s="86">
+      <c r="G25" s="79">
         <f>IFERROR(F25/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="H25" s="86">
+      <c r="H25" s="79">
         <f>IFERROR(SUMIF($F$10:$F$29,"&gt;="&amp;F25,$F$10:$F$29)/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="R25" s="70">
-        <f>RANK.EQ(F25,$F$10:$F$29,0)+COUNTIF($F$10:F25,F25)-1</f>
-        <v/>
-      </c>
-      <c r="S25" s="70">
-        <f>INDEX($A$10:$A$29,MATCH(ROWS($S$10:S25),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="T25" s="71">
-        <f>INDEX($B$10:$B$29,MATCH(ROWS($T$10:T25),$R$10:$R$29,0))&amp;" ("&amp;S25&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U25" s="72">
-        <f>INDEX($F$10:$F$29,MATCH(ROWS($U$10:U25),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="V25" s="73">
-        <f>INDEX($H$10:$H$29,MATCH(ROWS($V$10:V25),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="W25" s="74">
-        <f>IF($S25="A",$U25,NA())</f>
-        <v/>
-      </c>
-      <c r="X25" s="75">
-        <f>IF($S25="B",$U25,NA())</f>
-        <v/>
-      </c>
-      <c r="Y25" s="76">
-        <f>IF($S25="C",$U25,NA())</f>
-        <v/>
+      <c r="P25" s="65" t="inlineStr">
+        <is>
+          <t>Filtro de Linha 5 To (C)</t>
+        </is>
+      </c>
+      <c r="Q25" s="66" t="n">
+        <v>4400</v>
+      </c>
+      <c r="R25" s="67" t="n">
+        <v>0.9828</v>
+      </c>
+      <c r="S25" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="70" t="n">
+        <v>4400</v>
       </c>
     </row>
     <row r="26" ht="19" customHeight="1">
-      <c r="A26" s="68">
+      <c r="A26" s="61">
         <f>IF($H26&lt;=$E$5,"A",IF($H26&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B26" s="83" t="inlineStr">
+      <c r="B26" s="76" t="inlineStr">
         <is>
           <t>Cabo HDMI 2m</t>
         </is>
       </c>
-      <c r="C26" s="84" t="n">
+      <c r="C26" s="77" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="61" t="n">
+      <c r="D26" s="57" t="n">
         <v>150</v>
       </c>
-      <c r="E26" s="62" t="n">
+      <c r="E26" s="58" t="n">
         <v>25</v>
       </c>
-      <c r="F26" s="85">
+      <c r="F26" s="78">
         <f>IFERROR(D26*E26,0)</f>
         <v/>
       </c>
-      <c r="G26" s="86">
+      <c r="G26" s="79">
         <f>IFERROR(F26/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="H26" s="86">
+      <c r="H26" s="79">
         <f>IFERROR(SUMIF($F$10:$F$29,"&gt;="&amp;F26,$F$10:$F$29)/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="R26" s="70">
-        <f>RANK.EQ(F26,$F$10:$F$29,0)+COUNTIF($F$10:F26,F26)-1</f>
-        <v/>
-      </c>
-      <c r="S26" s="70">
-        <f>INDEX($A$10:$A$29,MATCH(ROWS($S$10:S26),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="T26" s="71">
-        <f>INDEX($B$10:$B$29,MATCH(ROWS($T$10:T26),$R$10:$R$29,0))&amp;" ("&amp;S26&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U26" s="72">
-        <f>INDEX($F$10:$F$29,MATCH(ROWS($U$10:U26),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="V26" s="73">
-        <f>INDEX($H$10:$H$29,MATCH(ROWS($V$10:V26),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="W26" s="74">
-        <f>IF($S26="A",$U26,NA())</f>
-        <v/>
-      </c>
-      <c r="X26" s="75">
-        <f>IF($S26="B",$U26,NA())</f>
-        <v/>
-      </c>
-      <c r="Y26" s="76">
-        <f>IF($S26="C",$U26,NA())</f>
-        <v/>
+      <c r="P26" s="65" t="inlineStr">
+        <is>
+          <t>Cabo HDMI 2m (C)</t>
+        </is>
+      </c>
+      <c r="Q26" s="66" t="n">
+        <v>3750</v>
+      </c>
+      <c r="R26" s="67" t="n">
+        <v>0.9886</v>
+      </c>
+      <c r="S26" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="70" t="n">
+        <v>3750</v>
       </c>
     </row>
     <row r="27" ht="19" customHeight="1">
-      <c r="A27" s="68">
+      <c r="A27" s="61">
         <f>IF($H27&lt;=$E$5,"A",IF($H27&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B27" s="83" t="inlineStr">
+      <c r="B27" s="76" t="inlineStr">
         <is>
           <t>Adaptador USB-C</t>
         </is>
       </c>
-      <c r="C27" s="84" t="n">
+      <c r="C27" s="77" t="n">
         <v>16</v>
       </c>
-      <c r="D27" s="61" t="n">
+      <c r="D27" s="57" t="n">
         <v>90</v>
       </c>
-      <c r="E27" s="62" t="n">
+      <c r="E27" s="58" t="n">
         <v>35</v>
       </c>
-      <c r="F27" s="85">
+      <c r="F27" s="78">
         <f>IFERROR(D27*E27,0)</f>
         <v/>
       </c>
-      <c r="G27" s="86">
+      <c r="G27" s="79">
         <f>IFERROR(F27/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="H27" s="86">
+      <c r="H27" s="79">
         <f>IFERROR(SUMIF($F$10:$F$29,"&gt;="&amp;F27,$F$10:$F$29)/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="R27" s="70">
-        <f>RANK.EQ(F27,$F$10:$F$29,0)+COUNTIF($F$10:F27,F27)-1</f>
-        <v/>
-      </c>
-      <c r="S27" s="70">
-        <f>INDEX($A$10:$A$29,MATCH(ROWS($S$10:S27),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="T27" s="71">
-        <f>INDEX($B$10:$B$29,MATCH(ROWS($T$10:T27),$R$10:$R$29,0))&amp;" ("&amp;S27&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U27" s="72">
-        <f>INDEX($F$10:$F$29,MATCH(ROWS($U$10:U27),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="V27" s="73">
-        <f>INDEX($H$10:$H$29,MATCH(ROWS($V$10:V27),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="W27" s="74">
-        <f>IF($S27="A",$U27,NA())</f>
-        <v/>
-      </c>
-      <c r="X27" s="75">
-        <f>IF($S27="B",$U27,NA())</f>
-        <v/>
-      </c>
-      <c r="Y27" s="76">
-        <f>IF($S27="C",$U27,NA())</f>
-        <v/>
+      <c r="P27" s="65" t="inlineStr">
+        <is>
+          <t>Adaptador USB-C (C)</t>
+        </is>
+      </c>
+      <c r="Q27" s="66" t="n">
+        <v>3150</v>
+      </c>
+      <c r="R27" s="67" t="n">
+        <v>0.9935</v>
+      </c>
+      <c r="S27" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="70" t="n">
+        <v>3150</v>
       </c>
     </row>
     <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="68">
+      <c r="A28" s="61">
         <f>IF($H28&lt;=$E$5,"A",IF($H28&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B28" s="83" t="inlineStr">
+      <c r="B28" s="76" t="inlineStr">
         <is>
           <t>Mouse Optico Simples</t>
         </is>
       </c>
-      <c r="C28" s="84" t="n">
+      <c r="C28" s="77" t="n">
         <v>3</v>
       </c>
-      <c r="D28" s="61" t="n">
+      <c r="D28" s="57" t="n">
         <v>120</v>
       </c>
-      <c r="E28" s="62" t="n">
+      <c r="E28" s="58" t="n">
         <v>15</v>
       </c>
-      <c r="F28" s="85">
+      <c r="F28" s="78">
         <f>IFERROR(D28*E28,0)</f>
         <v/>
       </c>
-      <c r="G28" s="86">
+      <c r="G28" s="79">
         <f>IFERROR(F28/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="H28" s="86">
+      <c r="H28" s="79">
         <f>IFERROR(SUMIF($F$10:$F$29,"&gt;="&amp;F28,$F$10:$F$29)/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="R28" s="70">
-        <f>RANK.EQ(F28,$F$10:$F$29,0)+COUNTIF($F$10:F28,F28)-1</f>
-        <v/>
-      </c>
-      <c r="S28" s="70">
-        <f>INDEX($A$10:$A$29,MATCH(ROWS($S$10:S28),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="T28" s="71">
-        <f>INDEX($B$10:$B$29,MATCH(ROWS($T$10:T28),$R$10:$R$29,0))&amp;" ("&amp;S28&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U28" s="72">
-        <f>INDEX($F$10:$F$29,MATCH(ROWS($U$10:U28),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="V28" s="73">
-        <f>INDEX($H$10:$H$29,MATCH(ROWS($V$10:V28),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="W28" s="74">
-        <f>IF($S28="A",$U28,NA())</f>
-        <v/>
-      </c>
-      <c r="X28" s="75">
-        <f>IF($S28="B",$U28,NA())</f>
-        <v/>
-      </c>
-      <c r="Y28" s="76">
-        <f>IF($S28="C",$U28,NA())</f>
-        <v/>
+      <c r="P28" s="65" t="inlineStr">
+        <is>
+          <t>Patch Cord RJ45 1m (C)</t>
+        </is>
+      </c>
+      <c r="Q28" s="66" t="n">
+        <v>2400</v>
+      </c>
+      <c r="R28" s="67" t="n">
+        <v>0.9972</v>
+      </c>
+      <c r="S28" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" s="70" t="n">
+        <v>2400</v>
       </c>
     </row>
     <row r="29" ht="19" customHeight="1">
-      <c r="A29" s="68">
+      <c r="A29" s="61">
         <f>IF($H29&lt;=$E$5,"A",IF($H29&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B29" s="83" t="inlineStr">
+      <c r="B29" s="76" t="inlineStr">
         <is>
           <t>Patch Cord RJ45 1m</t>
         </is>
       </c>
-      <c r="C29" s="84" t="n">
+      <c r="C29" s="77" t="n">
         <v>8</v>
       </c>
-      <c r="D29" s="61" t="n">
+      <c r="D29" s="57" t="n">
         <v>200</v>
       </c>
-      <c r="E29" s="62" t="n">
+      <c r="E29" s="58" t="n">
         <v>12</v>
       </c>
-      <c r="F29" s="85">
+      <c r="F29" s="78">
         <f>IFERROR(D29*E29,0)</f>
         <v/>
       </c>
-      <c r="G29" s="86">
+      <c r="G29" s="79">
         <f>IFERROR(F29/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="H29" s="86">
+      <c r="H29" s="79">
         <f>IFERROR(SUMIF($F$10:$F$29,"&gt;="&amp;F29,$F$10:$F$29)/SUM($F$10:$F$29),0)</f>
         <v/>
       </c>
-      <c r="R29" s="70">
-        <f>RANK.EQ(F29,$F$10:$F$29,0)+COUNTIF($F$10:F29,F29)-1</f>
-        <v/>
-      </c>
-      <c r="S29" s="70">
-        <f>INDEX($A$10:$A$29,MATCH(ROWS($S$10:S29),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="T29" s="71">
-        <f>INDEX($B$10:$B$29,MATCH(ROWS($T$10:T29),$R$10:$R$29,0))&amp;" ("&amp;S29&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U29" s="72">
-        <f>INDEX($F$10:$F$29,MATCH(ROWS($U$10:U29),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="V29" s="73">
-        <f>INDEX($H$10:$H$29,MATCH(ROWS($V$10:V29),$R$10:$R$29,0))</f>
-        <v/>
-      </c>
-      <c r="W29" s="74">
-        <f>IF($S29="A",$U29,NA())</f>
-        <v/>
-      </c>
-      <c r="X29" s="75">
-        <f>IF($S29="B",$U29,NA())</f>
-        <v/>
-      </c>
-      <c r="Y29" s="76">
-        <f>IF($S29="C",$U29,NA())</f>
-        <v/>
+      <c r="P29" s="65" t="inlineStr">
+        <is>
+          <t>Mouse Optico Simples (C)</t>
+        </is>
+      </c>
+      <c r="Q29" s="66" t="n">
+        <v>1800</v>
+      </c>
+      <c r="R29" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="S29" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" s="70" t="n">
+        <v>1800</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="87" t="inlineStr">
+      <c r="A30" s="80" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B30" s="88" t="n"/>
-      <c r="C30" s="88" t="n"/>
-      <c r="D30" s="89">
+      <c r="B30" s="81" t="n"/>
+      <c r="C30" s="81" t="n"/>
+      <c r="D30" s="82">
         <f>SUM(D10:D29)</f>
         <v/>
       </c>
-      <c r="E30" s="90" t="n"/>
-      <c r="F30" s="91">
+      <c r="E30" s="83" t="n"/>
+      <c r="F30" s="84">
         <f>SUM(F10:F29)</f>
         <v/>
       </c>
-      <c r="G30" s="92" t="n">
+      <c r="G30" s="85" t="n">
         <v>1</v>
       </c>
-      <c r="H30" s="92" t="n">
+      <c r="H30" s="85" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CURVA ABC REGGAE  |  CURVA ABC REGGAE  —  ABA 01  |  One Love, One Data  |  2026</t>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CURVA ABC REGGAE  |  CURVA ABC — ABA 01  |  One Love, One Data  |  2026</t>
         </is>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="F0B1"/>
-  <mergeCells count="26">
+  <mergeCells count="21">
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="J1:N1"/>
-    <mergeCell ref="G61:H61"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A61:H61"/>
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="E4:F4"/>
@@ -5255,15 +4892,13 @@
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
-    <mergeCell ref="J11:N11"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="G5:H5"/>
-    <mergeCell ref="C61:D61"/>
     <mergeCell ref="A30:C30"/>
-    <mergeCell ref="E61:F61"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
+    <mergeCell ref="A63:H63"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="E3:F3"/>
   </mergeCells>
@@ -5290,7 +4925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y71"/>
+  <dimension ref="A1:U73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5307,2289 +4942,1887 @@
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="2" customWidth="1" min="15" max="15"/>
-    <col width="2" customWidth="1" min="16" max="16"/>
-    <col width="2" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="38" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="16" customWidth="1" min="23" max="23"/>
-    <col width="16" customWidth="1" min="24" max="24"/>
-    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
-    <row r="1" ht="50" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
-        <is>
-          <t>CURVA ABC REGGAE  —  ABA 02</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="n"/>
-      <c r="J1" s="16" t="inlineStr">
-        <is>
-          <t>A = ate 80%   |   B = 80-95%   |   C = 95-100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+    <row r="1" ht="48" customHeight="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>CURVA ABC — ABA 02</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="n"/>
+      <c r="J1" s="18" t="inlineStr">
+        <is>
+          <t>A = ate 80%   |   B = 80–95%   |   C = 95–100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>V.T. TOTAL</t>
         </is>
       </c>
-      <c r="B2" s="18" t="n"/>
-      <c r="C2" s="19" t="inlineStr">
+      <c r="B2" s="20" t="n"/>
+      <c r="C2" s="21" t="inlineStr">
         <is>
           <t>V.T. CLASSE A</t>
         </is>
       </c>
-      <c r="D2" s="18" t="n"/>
-      <c r="E2" s="20" t="inlineStr">
+      <c r="D2" s="20" t="n"/>
+      <c r="E2" s="22" t="inlineStr">
         <is>
           <t>% ITENS A</t>
         </is>
       </c>
-      <c r="F2" s="18" t="n"/>
-      <c r="G2" s="21" t="inlineStr">
+      <c r="F2" s="20" t="n"/>
+      <c r="G2" s="23" t="inlineStr">
         <is>
           <t>MAIOR V.T.</t>
         </is>
       </c>
-      <c r="H2" s="22" t="n"/>
-      <c r="J2" s="1" t="n"/>
-      <c r="K2" s="1" t="n"/>
-      <c r="L2" s="1" t="n"/>
-      <c r="M2" s="1" t="n"/>
-      <c r="N2" s="1" t="n"/>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="23">
+      <c r="H2" s="24" t="n"/>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="25">
         <f>SUM($F$10:$F$39)</f>
         <v/>
       </c>
-      <c r="B3" s="24" t="n"/>
-      <c r="C3" s="25">
+      <c r="B3" s="26" t="n"/>
+      <c r="C3" s="27">
         <f>SUMIF($A$10:$A$39,"A",$F$10:$F$39)</f>
         <v/>
       </c>
-      <c r="D3" s="24" t="n"/>
-      <c r="E3" s="26">
+      <c r="D3" s="26" t="n"/>
+      <c r="E3" s="28">
         <f>IFERROR(COUNTIF($A$10:$A$39,"A")/COUNTA($B$10:$B$39),0)</f>
         <v/>
       </c>
-      <c r="F3" s="24" t="n"/>
-      <c r="G3" s="27">
+      <c r="F3" s="26" t="n"/>
+      <c r="G3" s="29">
         <f>MAX($F$10:$F$39)</f>
         <v/>
       </c>
-      <c r="H3" s="28" t="n"/>
-      <c r="J3" s="1" t="n"/>
-      <c r="K3" s="1" t="n"/>
-      <c r="L3" s="1" t="n"/>
-      <c r="M3" s="1" t="n"/>
-      <c r="N3" s="1" t="n"/>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="H3" s="30" t="n"/>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>MENOR V.T.</t>
         </is>
       </c>
-      <c r="B4" s="24" t="n"/>
-      <c r="C4" s="30" t="inlineStr">
+      <c r="B4" s="26" t="n"/>
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
       </c>
-      <c r="D4" s="24" t="n"/>
-      <c r="E4" s="31" t="inlineStr">
+      <c r="D4" s="26" t="n"/>
+      <c r="E4" s="33" t="inlineStr">
         <is>
           <t>LIMITE A</t>
         </is>
       </c>
-      <c r="F4" s="24" t="n"/>
-      <c r="G4" s="32" t="inlineStr">
+      <c r="F4" s="26" t="n"/>
+      <c r="G4" s="34" t="inlineStr">
         <is>
           <t>LIMITE B</t>
         </is>
       </c>
-      <c r="H4" s="28" t="n"/>
-      <c r="J4" s="1" t="n"/>
-      <c r="K4" s="1" t="n"/>
-      <c r="L4" s="1" t="n"/>
-      <c r="M4" s="1" t="n"/>
-      <c r="N4" s="1" t="n"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="33">
+      <c r="H4" s="30" t="n"/>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="35">
         <f>MIN($F$10:$F$39)</f>
         <v/>
       </c>
-      <c r="B5" s="34" t="n"/>
-      <c r="C5" s="35">
-        <f>IF(IFERROR(MAX($H$10:$H$39),0)&gt;1.0001,"VERIFICAR","CONSISTENTE")</f>
-        <v/>
-      </c>
-      <c r="D5" s="34" t="n"/>
-      <c r="E5" s="36" t="n">
+      <c r="B5" s="36" t="n"/>
+      <c r="C5" s="37">
+        <f>IF(IFERROR(MAX($H$10:$H$39),0)&gt;1.0001,"VERIFICAR","OK")</f>
+        <v/>
+      </c>
+      <c r="D5" s="36" t="n"/>
+      <c r="E5" s="38" t="n">
         <v>0.8</v>
       </c>
-      <c r="F5" s="34" t="n"/>
-      <c r="G5" s="37" t="n">
+      <c r="F5" s="36" t="n"/>
+      <c r="G5" s="39" t="n">
         <v>0.95</v>
       </c>
-      <c r="H5" s="38" t="n"/>
-      <c r="J5" s="1" t="n"/>
-      <c r="K5" s="1" t="n"/>
-      <c r="L5" s="1" t="n"/>
-      <c r="M5" s="1" t="n"/>
-      <c r="N5" s="1" t="n"/>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Analise Avancada | 30 SKUs | Pareto Automatico | Dashboard Executivo  |  Edite somente Quant. e Custo Unit. — formulas, ABC e graficos atualizam automaticamente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="J7" s="40" t="inlineStr">
+      <c r="H5" s="40" t="n"/>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Edite somente Quant. e Custo Unit. — ABC, V.T. e % recalculam automaticamente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="J7" s="42" t="inlineStr">
         <is>
           <t>Classe</t>
         </is>
       </c>
-      <c r="K7" s="40" t="inlineStr">
+      <c r="K7" s="42" t="inlineStr">
         <is>
           <t>Total V.T.</t>
         </is>
       </c>
-      <c r="L7" s="40" t="inlineStr">
+      <c r="L7" s="42" t="inlineStr">
         <is>
           <t>% Total</t>
         </is>
       </c>
-      <c r="M7" s="40" t="inlineStr">
+      <c r="M7" s="42" t="inlineStr">
         <is>
           <t>Qtd. Itens</t>
         </is>
       </c>
-      <c r="N7" s="40" t="inlineStr">
-        <is>
-          <t>Barra Rapida</t>
+      <c r="N7" s="42" t="inlineStr">
+        <is>
+          <t>Barra</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="41" t="inlineStr">
+      <c r="A8" s="43" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
-      <c r="B8" s="42" t="inlineStr">
-        <is>
-          <t>Descricao do Item</t>
-        </is>
-      </c>
-      <c r="C8" s="43" t="inlineStr">
-        <is>
-          <t>Cod./ID</t>
-        </is>
-      </c>
-      <c r="D8" s="44" t="inlineStr">
+      <c r="B8" s="44" t="inlineStr">
+        <is>
+          <t>Descricao</t>
+        </is>
+      </c>
+      <c r="C8" s="44" t="inlineStr">
+        <is>
+          <t>Cod.</t>
+        </is>
+      </c>
+      <c r="D8" s="45" t="inlineStr">
         <is>
           <t>Quant.</t>
         </is>
       </c>
-      <c r="E8" s="44" t="inlineStr">
-        <is>
-          <t>Custo Unit. (R$)</t>
-        </is>
-      </c>
-      <c r="F8" s="41" t="inlineStr">
+      <c r="E8" s="45" t="inlineStr">
+        <is>
+          <t>Custo Unit.(R$)</t>
+        </is>
+      </c>
+      <c r="F8" s="43" t="inlineStr">
         <is>
           <t>V.T. (R$)</t>
         </is>
       </c>
-      <c r="G8" s="43" t="inlineStr">
+      <c r="G8" s="44" t="inlineStr">
         <is>
           <t>% Individual</t>
         </is>
       </c>
-      <c r="H8" s="43" t="inlineStr">
+      <c r="H8" s="44" t="inlineStr">
         <is>
           <t>% Acumulado</t>
         </is>
       </c>
-      <c r="J8" s="45" t="inlineStr">
+      <c r="J8" s="46" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K8" s="46">
+      <c r="K8" s="47">
         <f>SUMIF($A$10:$A$39,"A",$F$10:$F$39)</f>
         <v/>
       </c>
-      <c r="L8" s="47">
+      <c r="L8" s="48">
         <f>IFERROR(K8/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="M8" s="48">
+      <c r="M8" s="46">
         <f>COUNTIF($A$10:$A$39,"A")</f>
         <v/>
       </c>
       <c r="N8" s="49">
-        <f>REPT("█",ROUND(L8*20,0))</f>
-        <v/>
+        <f>REPT(CHAR(9608),ROUND(L8*20,0))</f>
+        <v/>
+      </c>
+      <c r="P8" s="50" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="Q8" s="50" t="inlineStr">
+        <is>
+          <t>VT Ord.</t>
+        </is>
       </c>
       <c r="R8" s="50" t="inlineStr">
         <is>
-          <t>Rank</t>
+          <t>% Acum.</t>
         </is>
       </c>
       <c r="S8" s="50" t="inlineStr">
         <is>
-          <t>ABC Ord.</t>
+          <t>VT A</t>
         </is>
       </c>
       <c r="T8" s="50" t="inlineStr">
         <is>
-          <t>Rotulo</t>
+          <t>VT B</t>
         </is>
       </c>
       <c r="U8" s="50" t="inlineStr">
         <is>
-          <t>V.T. Ord.</t>
-        </is>
-      </c>
-      <c r="V8" s="50" t="inlineStr">
-        <is>
-          <t>% Acum. Ord.</t>
-        </is>
-      </c>
-      <c r="W8" s="51" t="inlineStr">
-        <is>
-          <t>V.T. A</t>
-        </is>
-      </c>
-      <c r="X8" s="52" t="inlineStr">
-        <is>
-          <t>V.T. B</t>
-        </is>
-      </c>
-      <c r="Y8" s="53" t="inlineStr">
-        <is>
-          <t>V.T. C</t>
+          <t>VT C</t>
         </is>
       </c>
     </row>
     <row r="9" ht="6" customHeight="1">
-      <c r="J9" s="54" t="inlineStr">
+      <c r="J9" s="51" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K9" s="55">
+      <c r="K9" s="52">
         <f>SUMIF($A$10:$A$39,"B",$F$10:$F$39)</f>
         <v/>
       </c>
-      <c r="L9" s="56">
+      <c r="L9" s="53">
         <f>IFERROR(K9/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="M9" s="57">
+      <c r="M9" s="51">
         <f>COUNTIF($A$10:$A$39,"B")</f>
         <v/>
       </c>
-      <c r="N9" s="58">
-        <f>REPT("█",ROUND(L9*20,0))</f>
+      <c r="N9" s="54">
+        <f>REPT(CHAR(9608),ROUND(L9*20,0))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
-      <c r="A10" s="48">
+      <c r="A10" s="46">
         <f>IF($H10&lt;=$E$5,"A",IF($H10&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B10" s="59" t="inlineStr">
+      <c r="B10" s="55" t="inlineStr">
         <is>
           <t>Servidor Rack Dell Pro</t>
         </is>
       </c>
-      <c r="C10" s="60" t="n">
+      <c r="C10" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="61" t="n">
+      <c r="D10" s="57" t="n">
         <v>15</v>
       </c>
-      <c r="E10" s="62" t="n">
+      <c r="E10" s="58" t="n">
         <v>22500</v>
       </c>
-      <c r="F10" s="63">
+      <c r="F10" s="59">
         <f>IFERROR(D10*E10,0)</f>
         <v/>
       </c>
-      <c r="G10" s="64">
+      <c r="G10" s="60">
         <f>IFERROR(F10/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="H10" s="64">
+      <c r="H10" s="60">
         <f>IFERROR(SUMIF($F$10:$F$39,"&gt;="&amp;F10,$F$10:$F$39)/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="J10" s="65" t="inlineStr">
+      <c r="J10" s="61" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="K10" s="66">
+      <c r="K10" s="62">
         <f>SUMIF($A$10:$A$39,"C",$F$10:$F$39)</f>
         <v/>
       </c>
-      <c r="L10" s="67">
+      <c r="L10" s="63">
         <f>IFERROR(K10/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="M10" s="68">
+      <c r="M10" s="61">
         <f>COUNTIF($A$10:$A$39,"C")</f>
         <v/>
       </c>
-      <c r="N10" s="69">
-        <f>REPT("█",ROUND(L10*20,0))</f>
-        <v/>
-      </c>
-      <c r="R10" s="70">
-        <f>RANK.EQ(F10,$F$10:$F$39,0)+COUNTIF($F$10:F10,F10)-1</f>
-        <v/>
-      </c>
-      <c r="S10" s="70">
-        <f>INDEX($A$10:$A$39,MATCH(ROWS($S$10:S10),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="T10" s="71">
-        <f>INDEX($B$10:$B$39,MATCH(ROWS($T$10:T10),$R$10:$R$39,0))&amp;" ("&amp;S10&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U10" s="72">
-        <f>INDEX($F$10:$F$39,MATCH(ROWS($U$10:U10),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="V10" s="73">
-        <f>INDEX($H$10:$H$39,MATCH(ROWS($V$10:V10),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="W10" s="74">
-        <f>IF($S10="A",$U10,NA())</f>
-        <v/>
-      </c>
-      <c r="X10" s="75">
-        <f>IF($S10="B",$U10,NA())</f>
-        <v/>
-      </c>
-      <c r="Y10" s="76">
-        <f>IF($S10="C",$U10,NA())</f>
-        <v/>
+      <c r="N10" s="64">
+        <f>REPT(CHAR(9608),ROUND(L10*20,0))</f>
+        <v/>
+      </c>
+      <c r="P10" s="65" t="inlineStr">
+        <is>
+          <t>Servidor Rack Dell P (A)</t>
+        </is>
+      </c>
+      <c r="Q10" s="66" t="n">
+        <v>337500</v>
+      </c>
+      <c r="R10" s="67" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="S10" s="68" t="n">
+        <v>337500</v>
+      </c>
+      <c r="T10" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="48">
+      <c r="A11" s="46">
         <f>IF($H11&lt;=$E$5,"A",IF($H11&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B11" s="59" t="inlineStr">
+      <c r="B11" s="55" t="inlineStr">
         <is>
           <t>Workstation Grafica</t>
         </is>
       </c>
-      <c r="C11" s="60" t="n">
+      <c r="C11" s="56" t="n">
         <v>17</v>
       </c>
-      <c r="D11" s="61" t="n">
+      <c r="D11" s="57" t="n">
         <v>19</v>
       </c>
-      <c r="E11" s="62" t="n">
+      <c r="E11" s="58" t="n">
         <v>12000</v>
       </c>
-      <c r="F11" s="63">
+      <c r="F11" s="59">
         <f>IFERROR(D11*E11,0)</f>
         <v/>
       </c>
-      <c r="G11" s="64">
+      <c r="G11" s="60">
         <f>IFERROR(F11/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="H11" s="64">
+      <c r="H11" s="60">
         <f>IFERROR(SUMIF($F$10:$F$39,"&gt;="&amp;F11,$F$10:$F$39)/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="J11" s="77">
-        <f>IF(IFERROR(MAX($H$10:$H$39),0)&gt;1.0001,"ALERTA: acumulado &gt; 100%","OK - CONSISTENTE")</f>
-        <v/>
-      </c>
-      <c r="R11" s="70">
-        <f>RANK.EQ(F11,$F$10:$F$39,0)+COUNTIF($F$10:F11,F11)-1</f>
-        <v/>
-      </c>
-      <c r="S11" s="70">
-        <f>INDEX($A$10:$A$39,MATCH(ROWS($S$10:S11),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="T11" s="71">
-        <f>INDEX($B$10:$B$39,MATCH(ROWS($T$10:T11),$R$10:$R$39,0))&amp;" ("&amp;S11&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U11" s="72">
-        <f>INDEX($F$10:$F$39,MATCH(ROWS($U$10:U11),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="V11" s="73">
-        <f>INDEX($H$10:$H$39,MATCH(ROWS($V$10:V11),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="W11" s="74">
-        <f>IF($S11="A",$U11,NA())</f>
-        <v/>
-      </c>
-      <c r="X11" s="75">
-        <f>IF($S11="B",$U11,NA())</f>
-        <v/>
-      </c>
-      <c r="Y11" s="76">
-        <f>IF($S11="C",$U11,NA())</f>
-        <v/>
+      <c r="P11" s="65" t="inlineStr">
+        <is>
+          <t>Workstation Grafica (A)</t>
+        </is>
+      </c>
+      <c r="Q11" s="66" t="n">
+        <v>228000</v>
+      </c>
+      <c r="R11" s="67" t="n">
+        <v>0.5444</v>
+      </c>
+      <c r="S11" s="68" t="n">
+        <v>228000</v>
+      </c>
+      <c r="T11" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1">
-      <c r="A12" s="48">
+      <c r="A12" s="46">
         <f>IF($H12&lt;=$E$5,"A",IF($H12&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B12" s="59" t="inlineStr">
+      <c r="B12" s="55" t="inlineStr">
         <is>
           <t>Notebook i7 32GB RAM</t>
         </is>
       </c>
-      <c r="C12" s="60" t="n">
+      <c r="C12" s="56" t="n">
         <v>10</v>
       </c>
-      <c r="D12" s="61" t="n">
+      <c r="D12" s="57" t="n">
         <v>28</v>
       </c>
-      <c r="E12" s="62" t="n">
+      <c r="E12" s="58" t="n">
         <v>7200</v>
       </c>
-      <c r="F12" s="63">
+      <c r="F12" s="59">
         <f>IFERROR(D12*E12,0)</f>
         <v/>
       </c>
-      <c r="G12" s="64">
+      <c r="G12" s="60">
         <f>IFERROR(F12/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="H12" s="64">
+      <c r="H12" s="60">
         <f>IFERROR(SUMIF($F$10:$F$39,"&gt;="&amp;F12,$F$10:$F$39)/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="R12" s="70">
-        <f>RANK.EQ(F12,$F$10:$F$39,0)+COUNTIF($F$10:F12,F12)-1</f>
-        <v/>
-      </c>
-      <c r="S12" s="70">
-        <f>INDEX($A$10:$A$39,MATCH(ROWS($S$10:S12),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="T12" s="71">
-        <f>INDEX($B$10:$B$39,MATCH(ROWS($T$10:T12),$R$10:$R$39,0))&amp;" ("&amp;S12&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U12" s="72">
-        <f>INDEX($F$10:$F$39,MATCH(ROWS($U$10:U12),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="V12" s="73">
-        <f>INDEX($H$10:$H$39,MATCH(ROWS($V$10:V12),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="W12" s="74">
-        <f>IF($S12="A",$U12,NA())</f>
-        <v/>
-      </c>
-      <c r="X12" s="75">
-        <f>IF($S12="B",$U12,NA())</f>
-        <v/>
-      </c>
-      <c r="Y12" s="76">
-        <f>IF($S12="C",$U12,NA())</f>
-        <v/>
+      <c r="P12" s="65" t="inlineStr">
+        <is>
+          <t>Notebook i7 32GB RAM (A)</t>
+        </is>
+      </c>
+      <c r="Q12" s="66" t="n">
+        <v>201600</v>
+      </c>
+      <c r="R12" s="67" t="n">
+        <v>0.7383999999999999</v>
+      </c>
+      <c r="S12" s="68" t="n">
+        <v>201600</v>
+      </c>
+      <c r="T12" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="48">
+      <c r="A13" s="46">
         <f>IF($H13&lt;=$E$5,"A",IF($H13&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B13" s="59" t="inlineStr">
+      <c r="B13" s="55" t="inlineStr">
         <is>
           <t>Switch Gerenciavel 48p</t>
         </is>
       </c>
-      <c r="C13" s="60" t="n">
+      <c r="C13" s="56" t="n">
         <v>8</v>
       </c>
-      <c r="D13" s="61" t="n">
+      <c r="D13" s="57" t="n">
         <v>10</v>
       </c>
-      <c r="E13" s="62" t="n">
+      <c r="E13" s="58" t="n">
         <v>4800</v>
       </c>
-      <c r="F13" s="63">
+      <c r="F13" s="59">
         <f>IFERROR(D13*E13,0)</f>
         <v/>
       </c>
-      <c r="G13" s="64">
+      <c r="G13" s="60">
         <f>IFERROR(F13/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="H13" s="64">
+      <c r="H13" s="60">
         <f>IFERROR(SUMIF($F$10:$F$39,"&gt;="&amp;F13,$F$10:$F$39)/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="R13" s="70">
-        <f>RANK.EQ(F13,$F$10:$F$39,0)+COUNTIF($F$10:F13,F13)-1</f>
-        <v/>
-      </c>
-      <c r="S13" s="70">
-        <f>INDEX($A$10:$A$39,MATCH(ROWS($S$10:S13),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="T13" s="71">
-        <f>INDEX($B$10:$B$39,MATCH(ROWS($T$10:T13),$R$10:$R$39,0))&amp;" ("&amp;S13&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U13" s="72">
-        <f>INDEX($F$10:$F$39,MATCH(ROWS($U$10:U13),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="V13" s="73">
-        <f>INDEX($H$10:$H$39,MATCH(ROWS($V$10:V13),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="W13" s="74">
-        <f>IF($S13="A",$U13,NA())</f>
-        <v/>
-      </c>
-      <c r="X13" s="75">
-        <f>IF($S13="B",$U13,NA())</f>
-        <v/>
-      </c>
-      <c r="Y13" s="76">
-        <f>IF($S13="C",$U13,NA())</f>
-        <v/>
+      <c r="P13" s="65" t="inlineStr">
+        <is>
+          <t>Switch Gerenciavel 4 (A)</t>
+        </is>
+      </c>
+      <c r="Q13" s="66" t="n">
+        <v>48000</v>
+      </c>
+      <c r="R13" s="67" t="n">
+        <v>0.7846</v>
+      </c>
+      <c r="S13" s="68" t="n">
+        <v>48000</v>
+      </c>
+      <c r="T13" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="78">
+      <c r="A14" s="71">
         <f>IF($H14&lt;=$E$5,"A",IF($H14&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B14" s="79" t="inlineStr">
+      <c r="B14" s="72" t="inlineStr">
         <is>
           <t>Placa de Video RTX</t>
         </is>
       </c>
-      <c r="C14" s="80" t="n">
+      <c r="C14" s="73" t="n">
         <v>22</v>
       </c>
-      <c r="D14" s="61" t="n">
+      <c r="D14" s="57" t="n">
         <v>8</v>
       </c>
-      <c r="E14" s="62" t="n">
+      <c r="E14" s="58" t="n">
         <v>5500</v>
       </c>
-      <c r="F14" s="81">
+      <c r="F14" s="74">
         <f>IFERROR(D14*E14,0)</f>
         <v/>
       </c>
-      <c r="G14" s="82">
+      <c r="G14" s="75">
         <f>IFERROR(F14/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="H14" s="82">
+      <c r="H14" s="75">
         <f>IFERROR(SUMIF($F$10:$F$39,"&gt;="&amp;F14,$F$10:$F$39)/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="R14" s="70">
-        <f>RANK.EQ(F14,$F$10:$F$39,0)+COUNTIF($F$10:F14,F14)-1</f>
-        <v/>
-      </c>
-      <c r="S14" s="70">
-        <f>INDEX($A$10:$A$39,MATCH(ROWS($S$10:S14),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="T14" s="71">
-        <f>INDEX($B$10:$B$39,MATCH(ROWS($T$10:T14),$R$10:$R$39,0))&amp;" ("&amp;S14&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U14" s="72">
-        <f>INDEX($F$10:$F$39,MATCH(ROWS($U$10:U14),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="V14" s="73">
-        <f>INDEX($H$10:$H$39,MATCH(ROWS($V$10:V14),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="W14" s="74">
-        <f>IF($S14="A",$U14,NA())</f>
-        <v/>
-      </c>
-      <c r="X14" s="75">
-        <f>IF($S14="B",$U14,NA())</f>
-        <v/>
-      </c>
-      <c r="Y14" s="76">
-        <f>IF($S14="C",$U14,NA())</f>
-        <v/>
+      <c r="P14" s="65" t="inlineStr">
+        <is>
+          <t>Placa de Video RTX (B)</t>
+        </is>
+      </c>
+      <c r="Q14" s="66" t="n">
+        <v>44000</v>
+      </c>
+      <c r="R14" s="67" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="S14" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="69" t="n">
+        <v>44000</v>
+      </c>
+      <c r="U14" s="70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="78">
+      <c r="A15" s="71">
         <f>IF($H15&lt;=$E$5,"A",IF($H15&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B15" s="79" t="inlineStr">
+      <c r="B15" s="72" t="inlineStr">
         <is>
           <t>Storage NAS 40TB</t>
         </is>
       </c>
-      <c r="C15" s="80" t="n">
+      <c r="C15" s="73" t="n">
         <v>21</v>
       </c>
-      <c r="D15" s="61" t="n">
+      <c r="D15" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="E15" s="62" t="n">
+      <c r="E15" s="58" t="n">
         <v>18500</v>
       </c>
-      <c r="F15" s="81">
+      <c r="F15" s="74">
         <f>IFERROR(D15*E15,0)</f>
         <v/>
       </c>
-      <c r="G15" s="82">
+      <c r="G15" s="75">
         <f>IFERROR(F15/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="H15" s="82">
+      <c r="H15" s="75">
         <f>IFERROR(SUMIF($F$10:$F$39,"&gt;="&amp;F15,$F$10:$F$39)/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="R15" s="70">
-        <f>RANK.EQ(F15,$F$10:$F$39,0)+COUNTIF($F$10:F15,F15)-1</f>
-        <v/>
-      </c>
-      <c r="S15" s="70">
-        <f>INDEX($A$10:$A$39,MATCH(ROWS($S$10:S15),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="T15" s="71">
-        <f>INDEX($B$10:$B$39,MATCH(ROWS($T$10:T15),$R$10:$R$39,0))&amp;" ("&amp;S15&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U15" s="72">
-        <f>INDEX($F$10:$F$39,MATCH(ROWS($U$10:U15),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="V15" s="73">
-        <f>INDEX($H$10:$H$39,MATCH(ROWS($V$10:V15),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="W15" s="74">
-        <f>IF($S15="A",$U15,NA())</f>
-        <v/>
-      </c>
-      <c r="X15" s="75">
-        <f>IF($S15="B",$U15,NA())</f>
-        <v/>
-      </c>
-      <c r="Y15" s="76">
-        <f>IF($S15="C",$U15,NA())</f>
-        <v/>
+      <c r="P15" s="65" t="inlineStr">
+        <is>
+          <t>Storage NAS 40TB (B)</t>
+        </is>
+      </c>
+      <c r="Q15" s="66" t="n">
+        <v>37000</v>
+      </c>
+      <c r="R15" s="67" t="n">
+        <v>0.8626</v>
+      </c>
+      <c r="S15" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="69" t="n">
+        <v>37000</v>
+      </c>
+      <c r="U15" s="70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="78">
+      <c r="A16" s="71">
         <f>IF($H16&lt;=$E$5,"A",IF($H16&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B16" s="79" t="inlineStr">
+      <c r="B16" s="72" t="inlineStr">
         <is>
           <t>Memoria RAM 16GB</t>
         </is>
       </c>
-      <c r="C16" s="80" t="n">
+      <c r="C16" s="73" t="n">
         <v>19</v>
       </c>
-      <c r="D16" s="61" t="n">
+      <c r="D16" s="57" t="n">
         <v>45</v>
       </c>
-      <c r="E16" s="62" t="n">
+      <c r="E16" s="58" t="n">
         <v>380</v>
       </c>
-      <c r="F16" s="81">
+      <c r="F16" s="74">
         <f>IFERROR(D16*E16,0)</f>
         <v/>
       </c>
-      <c r="G16" s="82">
+      <c r="G16" s="75">
         <f>IFERROR(F16/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="H16" s="82">
+      <c r="H16" s="75">
         <f>IFERROR(SUMIF($F$10:$F$39,"&gt;="&amp;F16,$F$10:$F$39)/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="R16" s="70">
-        <f>RANK.EQ(F16,$F$10:$F$39,0)+COUNTIF($F$10:F16,F16)-1</f>
-        <v/>
-      </c>
-      <c r="S16" s="70">
-        <f>INDEX($A$10:$A$39,MATCH(ROWS($S$10:S16),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="T16" s="71">
-        <f>INDEX($B$10:$B$39,MATCH(ROWS($T$10:T16),$R$10:$R$39,0))&amp;" ("&amp;S16&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U16" s="72">
-        <f>INDEX($F$10:$F$39,MATCH(ROWS($U$10:U16),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="V16" s="73">
-        <f>INDEX($H$10:$H$39,MATCH(ROWS($V$10:V16),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="W16" s="74">
-        <f>IF($S16="A",$U16,NA())</f>
-        <v/>
-      </c>
-      <c r="X16" s="75">
-        <f>IF($S16="B",$U16,NA())</f>
-        <v/>
-      </c>
-      <c r="Y16" s="76">
-        <f>IF($S16="C",$U16,NA())</f>
-        <v/>
+      <c r="P16" s="65" t="inlineStr">
+        <is>
+          <t>Memoria RAM 16GB (B)</t>
+        </is>
+      </c>
+      <c r="Q16" s="66" t="n">
+        <v>17100</v>
+      </c>
+      <c r="R16" s="67" t="n">
+        <v>0.8791</v>
+      </c>
+      <c r="S16" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="69" t="n">
+        <v>17100</v>
+      </c>
+      <c r="U16" s="70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="78">
+      <c r="A17" s="71">
         <f>IF($H17&lt;=$E$5,"A",IF($H17&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B17" s="79" t="inlineStr">
+      <c r="B17" s="72" t="inlineStr">
         <is>
           <t>Toner Impressora Laser</t>
         </is>
       </c>
-      <c r="C17" s="80" t="n">
+      <c r="C17" s="73" t="n">
         <v>12</v>
       </c>
-      <c r="D17" s="61" t="n">
+      <c r="D17" s="57" t="n">
         <v>40</v>
       </c>
-      <c r="E17" s="62" t="n">
+      <c r="E17" s="58" t="n">
         <v>320</v>
       </c>
-      <c r="F17" s="81">
+      <c r="F17" s="74">
         <f>IFERROR(D17*E17,0)</f>
         <v/>
       </c>
-      <c r="G17" s="82">
+      <c r="G17" s="75">
         <f>IFERROR(F17/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="H17" s="82">
+      <c r="H17" s="75">
         <f>IFERROR(SUMIF($F$10:$F$39,"&gt;="&amp;F17,$F$10:$F$39)/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="R17" s="70">
-        <f>RANK.EQ(F17,$F$10:$F$39,0)+COUNTIF($F$10:F17,F17)-1</f>
-        <v/>
-      </c>
-      <c r="S17" s="70">
-        <f>INDEX($A$10:$A$39,MATCH(ROWS($S$10:S17),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="T17" s="71">
-        <f>INDEX($B$10:$B$39,MATCH(ROWS($T$10:T17),$R$10:$R$39,0))&amp;" ("&amp;S17&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U17" s="72">
-        <f>INDEX($F$10:$F$39,MATCH(ROWS($U$10:U17),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="V17" s="73">
-        <f>INDEX($H$10:$H$39,MATCH(ROWS($V$10:V17),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="W17" s="74">
-        <f>IF($S17="A",$U17,NA())</f>
-        <v/>
-      </c>
-      <c r="X17" s="75">
-        <f>IF($S17="B",$U17,NA())</f>
-        <v/>
-      </c>
-      <c r="Y17" s="76">
-        <f>IF($S17="C",$U17,NA())</f>
-        <v/>
+      <c r="P17" s="65" t="inlineStr">
+        <is>
+          <t>Toner Impressora Las (B)</t>
+        </is>
+      </c>
+      <c r="Q17" s="66" t="n">
+        <v>12800</v>
+      </c>
+      <c r="R17" s="67" t="n">
+        <v>0.8914</v>
+      </c>
+      <c r="S17" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="69" t="n">
+        <v>12800</v>
+      </c>
+      <c r="U17" s="70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="78">
+      <c r="A18" s="71">
         <f>IF($H18&lt;=$E$5,"A",IF($H18&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B18" s="79" t="inlineStr">
+      <c r="B18" s="72" t="inlineStr">
         <is>
           <t>Monitor LED 24"</t>
         </is>
       </c>
-      <c r="C18" s="80" t="n">
+      <c r="C18" s="73" t="n">
         <v>4</v>
       </c>
-      <c r="D18" s="61" t="n">
+      <c r="D18" s="57" t="n">
         <v>15</v>
       </c>
-      <c r="E18" s="62" t="n">
+      <c r="E18" s="58" t="n">
         <v>850</v>
       </c>
-      <c r="F18" s="81">
+      <c r="F18" s="74">
         <f>IFERROR(D18*E18,0)</f>
         <v/>
       </c>
-      <c r="G18" s="82">
+      <c r="G18" s="75">
         <f>IFERROR(F18/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="H18" s="82">
+      <c r="H18" s="75">
         <f>IFERROR(SUMIF($F$10:$F$39,"&gt;="&amp;F18,$F$10:$F$39)/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="R18" s="70">
-        <f>RANK.EQ(F18,$F$10:$F$39,0)+COUNTIF($F$10:F18,F18)-1</f>
-        <v/>
-      </c>
-      <c r="S18" s="70">
-        <f>INDEX($A$10:$A$39,MATCH(ROWS($S$10:S18),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="T18" s="71">
-        <f>INDEX($B$10:$B$39,MATCH(ROWS($T$10:T18),$R$10:$R$39,0))&amp;" ("&amp;S18&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U18" s="72">
-        <f>INDEX($F$10:$F$39,MATCH(ROWS($U$10:U18),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="V18" s="73">
-        <f>INDEX($H$10:$H$39,MATCH(ROWS($V$10:V18),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="W18" s="74">
-        <f>IF($S18="A",$U18,NA())</f>
-        <v/>
-      </c>
-      <c r="X18" s="75">
-        <f>IF($S18="B",$U18,NA())</f>
-        <v/>
-      </c>
-      <c r="Y18" s="76">
-        <f>IF($S18="C",$U18,NA())</f>
-        <v/>
+      <c r="P18" s="65" t="inlineStr">
+        <is>
+          <t>Monitor LED 24" (B)</t>
+        </is>
+      </c>
+      <c r="Q18" s="66" t="n">
+        <v>12750</v>
+      </c>
+      <c r="R18" s="67" t="n">
+        <v>0.9036</v>
+      </c>
+      <c r="S18" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="69" t="n">
+        <v>12750</v>
+      </c>
+      <c r="U18" s="70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="78">
+      <c r="A19" s="71">
         <f>IF($H19&lt;=$E$5,"A",IF($H19&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B19" s="79" t="inlineStr">
+      <c r="B19" s="72" t="inlineStr">
         <is>
           <t>Roteador Wi-Fi 6</t>
         </is>
       </c>
-      <c r="C19" s="80" t="n">
+      <c r="C19" s="73" t="n">
         <v>11</v>
       </c>
-      <c r="D19" s="61" t="n">
+      <c r="D19" s="57" t="n">
         <v>25</v>
       </c>
-      <c r="E19" s="62" t="n">
+      <c r="E19" s="58" t="n">
         <v>450</v>
       </c>
-      <c r="F19" s="81">
+      <c r="F19" s="74">
         <f>IFERROR(D19*E19,0)</f>
         <v/>
       </c>
-      <c r="G19" s="82">
+      <c r="G19" s="75">
         <f>IFERROR(F19/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="H19" s="82">
+      <c r="H19" s="75">
         <f>IFERROR(SUMIF($F$10:$F$39,"&gt;="&amp;F19,$F$10:$F$39)/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="R19" s="70">
-        <f>RANK.EQ(F19,$F$10:$F$39,0)+COUNTIF($F$10:F19,F19)-1</f>
-        <v/>
-      </c>
-      <c r="S19" s="70">
-        <f>INDEX($A$10:$A$39,MATCH(ROWS($S$10:S19),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="T19" s="71">
-        <f>INDEX($B$10:$B$39,MATCH(ROWS($T$10:T19),$R$10:$R$39,0))&amp;" ("&amp;S19&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U19" s="72">
-        <f>INDEX($F$10:$F$39,MATCH(ROWS($U$10:U19),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="V19" s="73">
-        <f>INDEX($H$10:$H$39,MATCH(ROWS($V$10:V19),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="W19" s="74">
-        <f>IF($S19="A",$U19,NA())</f>
-        <v/>
-      </c>
-      <c r="X19" s="75">
-        <f>IF($S19="B",$U19,NA())</f>
-        <v/>
-      </c>
-      <c r="Y19" s="76">
-        <f>IF($S19="C",$U19,NA())</f>
-        <v/>
+      <c r="P19" s="65" t="inlineStr">
+        <is>
+          <t>Roteador Wi-Fi 6 (B)</t>
+        </is>
+      </c>
+      <c r="Q19" s="66" t="n">
+        <v>11250</v>
+      </c>
+      <c r="R19" s="67" t="n">
+        <v>0.9145</v>
+      </c>
+      <c r="S19" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="69" t="n">
+        <v>11250</v>
+      </c>
+      <c r="U19" s="70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="78">
+      <c r="A20" s="71">
         <f>IF($H20&lt;=$E$5,"A",IF($H20&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B20" s="79" t="inlineStr">
+      <c r="B20" s="72" t="inlineStr">
         <is>
           <t>SSD 480GB Sata</t>
         </is>
       </c>
-      <c r="C20" s="80" t="n">
+      <c r="C20" s="73" t="n">
         <v>15</v>
       </c>
-      <c r="D20" s="61" t="n">
+      <c r="D20" s="57" t="n">
         <v>55</v>
       </c>
-      <c r="E20" s="62" t="n">
+      <c r="E20" s="58" t="n">
         <v>190</v>
       </c>
-      <c r="F20" s="81">
+      <c r="F20" s="74">
         <f>IFERROR(D20*E20,0)</f>
         <v/>
       </c>
-      <c r="G20" s="82">
+      <c r="G20" s="75">
         <f>IFERROR(F20/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="H20" s="82">
+      <c r="H20" s="75">
         <f>IFERROR(SUMIF($F$10:$F$39,"&gt;="&amp;F20,$F$10:$F$39)/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="R20" s="70">
-        <f>RANK.EQ(F20,$F$10:$F$39,0)+COUNTIF($F$10:F20,F20)-1</f>
-        <v/>
-      </c>
-      <c r="S20" s="70">
-        <f>INDEX($A$10:$A$39,MATCH(ROWS($S$10:S20),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="T20" s="71">
-        <f>INDEX($B$10:$B$39,MATCH(ROWS($T$10:T20),$R$10:$R$39,0))&amp;" ("&amp;S20&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U20" s="72">
-        <f>INDEX($F$10:$F$39,MATCH(ROWS($U$10:U20),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="V20" s="73">
-        <f>INDEX($H$10:$H$39,MATCH(ROWS($V$10:V20),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="W20" s="74">
-        <f>IF($S20="A",$U20,NA())</f>
-        <v/>
-      </c>
-      <c r="X20" s="75">
-        <f>IF($S20="B",$U20,NA())</f>
-        <v/>
-      </c>
-      <c r="Y20" s="76">
-        <f>IF($S20="C",$U20,NA())</f>
-        <v/>
+      <c r="P20" s="65" t="inlineStr">
+        <is>
+          <t>SSD 480GB Sata (B)</t>
+        </is>
+      </c>
+      <c r="Q20" s="66" t="n">
+        <v>10450</v>
+      </c>
+      <c r="R20" s="67" t="n">
+        <v>0.9245</v>
+      </c>
+      <c r="S20" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="69" t="n">
+        <v>10450</v>
+      </c>
+      <c r="U20" s="70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="78">
+      <c r="A21" s="71">
         <f>IF($H21&lt;=$E$5,"A",IF($H21&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B21" s="79" t="inlineStr">
+      <c r="B21" s="72" t="inlineStr">
         <is>
           <t>Nobreak 1500VA</t>
         </is>
       </c>
-      <c r="C21" s="80" t="n">
+      <c r="C21" s="73" t="n">
         <v>6</v>
       </c>
-      <c r="D21" s="61" t="n">
+      <c r="D21" s="57" t="n">
         <v>8</v>
       </c>
-      <c r="E21" s="62" t="n">
+      <c r="E21" s="58" t="n">
         <v>1200</v>
       </c>
-      <c r="F21" s="81">
+      <c r="F21" s="74">
         <f>IFERROR(D21*E21,0)</f>
         <v/>
       </c>
-      <c r="G21" s="82">
+      <c r="G21" s="75">
         <f>IFERROR(F21/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="H21" s="82">
+      <c r="H21" s="75">
         <f>IFERROR(SUMIF($F$10:$F$39,"&gt;="&amp;F21,$F$10:$F$39)/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="R21" s="70">
-        <f>RANK.EQ(F21,$F$10:$F$39,0)+COUNTIF($F$10:F21,F21)-1</f>
-        <v/>
-      </c>
-      <c r="S21" s="70">
-        <f>INDEX($A$10:$A$39,MATCH(ROWS($S$10:S21),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="T21" s="71">
-        <f>INDEX($B$10:$B$39,MATCH(ROWS($T$10:T21),$R$10:$R$39,0))&amp;" ("&amp;S21&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U21" s="72">
-        <f>INDEX($F$10:$F$39,MATCH(ROWS($U$10:U21),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="V21" s="73">
-        <f>INDEX($H$10:$H$39,MATCH(ROWS($V$10:V21),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="W21" s="74">
-        <f>IF($S21="A",$U21,NA())</f>
-        <v/>
-      </c>
-      <c r="X21" s="75">
-        <f>IF($S21="B",$U21,NA())</f>
-        <v/>
-      </c>
-      <c r="Y21" s="76">
-        <f>IF($S21="C",$U21,NA())</f>
-        <v/>
+      <c r="P21" s="65" t="inlineStr">
+        <is>
+          <t>Nobreak 1500VA (B)</t>
+        </is>
+      </c>
+      <c r="Q21" s="66" t="n">
+        <v>9600</v>
+      </c>
+      <c r="R21" s="67" t="n">
+        <v>0.9338</v>
+      </c>
+      <c r="S21" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="69" t="n">
+        <v>9600</v>
+      </c>
+      <c r="U21" s="70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="78">
+      <c r="A22" s="71">
         <f>IF($H22&lt;=$E$5,"A",IF($H22&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B22" s="79" t="inlineStr">
+      <c r="B22" s="72" t="inlineStr">
         <is>
           <t>HD Externo 2TB</t>
         </is>
       </c>
-      <c r="C22" s="80" t="n">
+      <c r="C22" s="73" t="n">
         <v>20</v>
       </c>
-      <c r="D22" s="61" t="n">
+      <c r="D22" s="57" t="n">
         <v>18</v>
       </c>
-      <c r="E22" s="62" t="n">
+      <c r="E22" s="58" t="n">
         <v>420</v>
       </c>
-      <c r="F22" s="81">
+      <c r="F22" s="74">
         <f>IFERROR(D22*E22,0)</f>
         <v/>
       </c>
-      <c r="G22" s="82">
+      <c r="G22" s="75">
         <f>IFERROR(F22/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="H22" s="82">
+      <c r="H22" s="75">
         <f>IFERROR(SUMIF($F$10:$F$39,"&gt;="&amp;F22,$F$10:$F$39)/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="R22" s="70">
-        <f>RANK.EQ(F22,$F$10:$F$39,0)+COUNTIF($F$10:F22,F22)-1</f>
-        <v/>
-      </c>
-      <c r="S22" s="70">
-        <f>INDEX($A$10:$A$39,MATCH(ROWS($S$10:S22),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="T22" s="71">
-        <f>INDEX($B$10:$B$39,MATCH(ROWS($T$10:T22),$R$10:$R$39,0))&amp;" ("&amp;S22&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U22" s="72">
-        <f>INDEX($F$10:$F$39,MATCH(ROWS($U$10:U22),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="V22" s="73">
-        <f>INDEX($H$10:$H$39,MATCH(ROWS($V$10:V22),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="W22" s="74">
-        <f>IF($S22="A",$U22,NA())</f>
-        <v/>
-      </c>
-      <c r="X22" s="75">
-        <f>IF($S22="B",$U22,NA())</f>
-        <v/>
-      </c>
-      <c r="Y22" s="76">
-        <f>IF($S22="C",$U22,NA())</f>
-        <v/>
+      <c r="P22" s="65" t="inlineStr">
+        <is>
+          <t>HD Externo 2TB (B)</t>
+        </is>
+      </c>
+      <c r="Q22" s="66" t="n">
+        <v>7560</v>
+      </c>
+      <c r="R22" s="67" t="n">
+        <v>0.9411</v>
+      </c>
+      <c r="S22" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="69" t="n">
+        <v>7560</v>
+      </c>
+      <c r="U22" s="70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="78">
+      <c r="A23" s="71">
         <f>IF($H23&lt;=$E$5,"A",IF($H23&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B23" s="79" t="inlineStr">
+      <c r="B23" s="72" t="inlineStr">
         <is>
           <t>Teclado Mecanico RGB</t>
         </is>
       </c>
-      <c r="C23" s="80" t="n">
+      <c r="C23" s="73" t="n">
         <v>5</v>
       </c>
-      <c r="D23" s="61" t="n">
+      <c r="D23" s="57" t="n">
         <v>30</v>
       </c>
-      <c r="E23" s="62" t="n">
+      <c r="E23" s="58" t="n">
         <v>250</v>
       </c>
-      <c r="F23" s="81">
+      <c r="F23" s="74">
         <f>IFERROR(D23*E23,0)</f>
         <v/>
       </c>
-      <c r="G23" s="82">
+      <c r="G23" s="75">
         <f>IFERROR(F23/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="H23" s="82">
+      <c r="H23" s="75">
         <f>IFERROR(SUMIF($F$10:$F$39,"&gt;="&amp;F23,$F$10:$F$39)/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="R23" s="70">
-        <f>RANK.EQ(F23,$F$10:$F$39,0)+COUNTIF($F$10:F23,F23)-1</f>
-        <v/>
-      </c>
-      <c r="S23" s="70">
-        <f>INDEX($A$10:$A$39,MATCH(ROWS($S$10:S23),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="T23" s="71">
-        <f>INDEX($B$10:$B$39,MATCH(ROWS($T$10:T23),$R$10:$R$39,0))&amp;" ("&amp;S23&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U23" s="72">
-        <f>INDEX($F$10:$F$39,MATCH(ROWS($U$10:U23),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="V23" s="73">
-        <f>INDEX($H$10:$H$39,MATCH(ROWS($V$10:V23),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="W23" s="74">
-        <f>IF($S23="A",$U23,NA())</f>
-        <v/>
-      </c>
-      <c r="X23" s="75">
-        <f>IF($S23="B",$U23,NA())</f>
-        <v/>
-      </c>
-      <c r="Y23" s="76">
-        <f>IF($S23="C",$U23,NA())</f>
-        <v/>
+      <c r="P23" s="65" t="inlineStr">
+        <is>
+          <t>Teclado Mecanico RGB (B)</t>
+        </is>
+      </c>
+      <c r="Q23" s="66" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R23" s="67" t="n">
+        <v>0.9483</v>
+      </c>
+      <c r="S23" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="69" t="n">
+        <v>7500</v>
+      </c>
+      <c r="U23" s="70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24" ht="19" customHeight="1">
-      <c r="A24" s="68">
+      <c r="A24" s="61">
         <f>IF($H24&lt;=$E$5,"A",IF($H24&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B24" s="83" t="inlineStr">
+      <c r="B24" s="76" t="inlineStr">
         <is>
           <t>Pen Drive 64GB</t>
         </is>
       </c>
-      <c r="C24" s="84" t="n">
+      <c r="C24" s="77" t="n">
         <v>9</v>
       </c>
-      <c r="D24" s="61" t="n">
+      <c r="D24" s="57" t="n">
         <v>150</v>
       </c>
-      <c r="E24" s="62" t="n">
+      <c r="E24" s="58" t="n">
         <v>45</v>
       </c>
-      <c r="F24" s="85">
+      <c r="F24" s="78">
         <f>IFERROR(D24*E24,0)</f>
         <v/>
       </c>
-      <c r="G24" s="86">
+      <c r="G24" s="79">
         <f>IFERROR(F24/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="H24" s="86">
+      <c r="H24" s="79">
         <f>IFERROR(SUMIF($F$10:$F$39,"&gt;="&amp;F24,$F$10:$F$39)/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="R24" s="70">
-        <f>RANK.EQ(F24,$F$10:$F$39,0)+COUNTIF($F$10:F24,F24)-1</f>
-        <v/>
-      </c>
-      <c r="S24" s="70">
-        <f>INDEX($A$10:$A$39,MATCH(ROWS($S$10:S24),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="T24" s="71">
-        <f>INDEX($B$10:$B$39,MATCH(ROWS($T$10:T24),$R$10:$R$39,0))&amp;" ("&amp;S24&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U24" s="72">
-        <f>INDEX($F$10:$F$39,MATCH(ROWS($U$10:U24),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="V24" s="73">
-        <f>INDEX($H$10:$H$39,MATCH(ROWS($V$10:V24),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="W24" s="74">
-        <f>IF($S24="A",$U24,NA())</f>
-        <v/>
-      </c>
-      <c r="X24" s="75">
-        <f>IF($S24="B",$U24,NA())</f>
-        <v/>
-      </c>
-      <c r="Y24" s="76">
-        <f>IF($S24="C",$U24,NA())</f>
-        <v/>
+      <c r="P24" s="65" t="inlineStr">
+        <is>
+          <t>Pen Drive 64GB (C)</t>
+        </is>
+      </c>
+      <c r="Q24" s="66" t="n">
+        <v>6750</v>
+      </c>
+      <c r="R24" s="67" t="n">
+        <v>0.9548</v>
+      </c>
+      <c r="S24" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="70" t="n">
+        <v>6750</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
-      <c r="A25" s="68">
+      <c r="A25" s="61">
         <f>IF($H25&lt;=$E$5,"A",IF($H25&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B25" s="83" t="inlineStr">
+      <c r="B25" s="76" t="inlineStr">
         <is>
           <t>Headset com Microfone</t>
         </is>
       </c>
-      <c r="C25" s="84" t="n">
+      <c r="C25" s="77" t="n">
         <v>13</v>
       </c>
-      <c r="D25" s="61" t="n">
+      <c r="D25" s="57" t="n">
         <v>60</v>
       </c>
-      <c r="E25" s="62" t="n">
+      <c r="E25" s="58" t="n">
         <v>110</v>
       </c>
-      <c r="F25" s="85">
+      <c r="F25" s="78">
         <f>IFERROR(D25*E25,0)</f>
         <v/>
       </c>
-      <c r="G25" s="86">
+      <c r="G25" s="79">
         <f>IFERROR(F25/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="H25" s="86">
+      <c r="H25" s="79">
         <f>IFERROR(SUMIF($F$10:$F$39,"&gt;="&amp;F25,$F$10:$F$39)/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="R25" s="70">
-        <f>RANK.EQ(F25,$F$10:$F$39,0)+COUNTIF($F$10:F25,F25)-1</f>
-        <v/>
-      </c>
-      <c r="S25" s="70">
-        <f>INDEX($A$10:$A$39,MATCH(ROWS($S$10:S25),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="T25" s="71">
-        <f>INDEX($B$10:$B$39,MATCH(ROWS($T$10:T25),$R$10:$R$39,0))&amp;" ("&amp;S25&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U25" s="72">
-        <f>INDEX($F$10:$F$39,MATCH(ROWS($U$10:U25),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="V25" s="73">
-        <f>INDEX($H$10:$H$39,MATCH(ROWS($V$10:V25),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="W25" s="74">
-        <f>IF($S25="A",$U25,NA())</f>
-        <v/>
-      </c>
-      <c r="X25" s="75">
-        <f>IF($S25="B",$U25,NA())</f>
-        <v/>
-      </c>
-      <c r="Y25" s="76">
-        <f>IF($S25="C",$U25,NA())</f>
-        <v/>
+      <c r="P25" s="65" t="inlineStr">
+        <is>
+          <t>Headset com Microfon (C)</t>
+        </is>
+      </c>
+      <c r="Q25" s="66" t="n">
+        <v>6600</v>
+      </c>
+      <c r="R25" s="67" t="n">
+        <v>0.9611</v>
+      </c>
+      <c r="S25" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="70" t="n">
+        <v>6600</v>
       </c>
     </row>
     <row r="26" ht="19" customHeight="1">
-      <c r="A26" s="68">
+      <c r="A26" s="61">
         <f>IF($H26&lt;=$E$5,"A",IF($H26&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B26" s="83" t="inlineStr">
+      <c r="B26" s="76" t="inlineStr">
         <is>
           <t>Pacote de Papel A4</t>
         </is>
       </c>
-      <c r="C26" s="84" t="n">
+      <c r="C26" s="77" t="n">
         <v>7</v>
       </c>
-      <c r="D26" s="61" t="n">
+      <c r="D26" s="57" t="n">
         <v>200</v>
       </c>
-      <c r="E26" s="62" t="n">
+      <c r="E26" s="58" t="n">
         <v>28</v>
       </c>
-      <c r="F26" s="85">
+      <c r="F26" s="78">
         <f>IFERROR(D26*E26,0)</f>
         <v/>
       </c>
-      <c r="G26" s="86">
+      <c r="G26" s="79">
         <f>IFERROR(F26/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="H26" s="86">
+      <c r="H26" s="79">
         <f>IFERROR(SUMIF($F$10:$F$39,"&gt;="&amp;F26,$F$10:$F$39)/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="R26" s="70">
-        <f>RANK.EQ(F26,$F$10:$F$39,0)+COUNTIF($F$10:F26,F26)-1</f>
-        <v/>
-      </c>
-      <c r="S26" s="70">
-        <f>INDEX($A$10:$A$39,MATCH(ROWS($S$10:S26),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="T26" s="71">
-        <f>INDEX($B$10:$B$39,MATCH(ROWS($T$10:T26),$R$10:$R$39,0))&amp;" ("&amp;S26&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U26" s="72">
-        <f>INDEX($F$10:$F$39,MATCH(ROWS($U$10:U26),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="V26" s="73">
-        <f>INDEX($H$10:$H$39,MATCH(ROWS($V$10:V26),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="W26" s="74">
-        <f>IF($S26="A",$U26,NA())</f>
-        <v/>
-      </c>
-      <c r="X26" s="75">
-        <f>IF($S26="B",$U26,NA())</f>
-        <v/>
-      </c>
-      <c r="Y26" s="76">
-        <f>IF($S26="C",$U26,NA())</f>
-        <v/>
+      <c r="P26" s="65" t="inlineStr">
+        <is>
+          <t>Pacote de Papel A4 (C)</t>
+        </is>
+      </c>
+      <c r="Q26" s="66" t="n">
+        <v>5600</v>
+      </c>
+      <c r="R26" s="67" t="n">
+        <v>0.9665</v>
+      </c>
+      <c r="S26" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="70" t="n">
+        <v>5600</v>
       </c>
     </row>
     <row r="27" ht="19" customHeight="1">
-      <c r="A27" s="68">
+      <c r="A27" s="61">
         <f>IF($H27&lt;=$E$5,"A",IF($H27&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B27" s="83" t="inlineStr">
+      <c r="B27" s="76" t="inlineStr">
         <is>
           <t>Teclado de Entrada</t>
         </is>
       </c>
-      <c r="C27" s="84" t="n">
+      <c r="C27" s="77" t="n">
         <v>29</v>
       </c>
-      <c r="D27" s="61" t="n">
+      <c r="D27" s="57" t="n">
         <v>100</v>
       </c>
-      <c r="E27" s="62" t="n">
+      <c r="E27" s="58" t="n">
         <v>45</v>
       </c>
-      <c r="F27" s="85">
+      <c r="F27" s="78">
         <f>IFERROR(D27*E27,0)</f>
         <v/>
       </c>
-      <c r="G27" s="86">
+      <c r="G27" s="79">
         <f>IFERROR(F27/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="H27" s="86">
+      <c r="H27" s="79">
         <f>IFERROR(SUMIF($F$10:$F$39,"&gt;="&amp;F27,$F$10:$F$39)/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="R27" s="70">
-        <f>RANK.EQ(F27,$F$10:$F$39,0)+COUNTIF($F$10:F27,F27)-1</f>
-        <v/>
-      </c>
-      <c r="S27" s="70">
-        <f>INDEX($A$10:$A$39,MATCH(ROWS($S$10:S27),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="T27" s="71">
-        <f>INDEX($B$10:$B$39,MATCH(ROWS($T$10:T27),$R$10:$R$39,0))&amp;" ("&amp;S27&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U27" s="72">
-        <f>INDEX($F$10:$F$39,MATCH(ROWS($U$10:U27),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="V27" s="73">
-        <f>INDEX($H$10:$H$39,MATCH(ROWS($V$10:V27),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="W27" s="74">
-        <f>IF($S27="A",$U27,NA())</f>
-        <v/>
-      </c>
-      <c r="X27" s="75">
-        <f>IF($S27="B",$U27,NA())</f>
-        <v/>
-      </c>
-      <c r="Y27" s="76">
-        <f>IF($S27="C",$U27,NA())</f>
-        <v/>
+      <c r="P27" s="65" t="inlineStr">
+        <is>
+          <t>Teclado de Entrada (C)</t>
+        </is>
+      </c>
+      <c r="Q27" s="66" t="n">
+        <v>4500</v>
+      </c>
+      <c r="R27" s="67" t="n">
+        <v>0.9708</v>
+      </c>
+      <c r="S27" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="70" t="n">
+        <v>4500</v>
       </c>
     </row>
     <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="68">
+      <c r="A28" s="61">
         <f>IF($H28&lt;=$E$5,"A",IF($H28&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B28" s="83" t="inlineStr">
+      <c r="B28" s="76" t="inlineStr">
         <is>
           <t>Filtro de Linha</t>
         </is>
       </c>
-      <c r="C28" s="84" t="n">
+      <c r="C28" s="77" t="n">
         <v>18</v>
       </c>
-      <c r="D28" s="61" t="n">
+      <c r="D28" s="57" t="n">
         <v>110</v>
       </c>
-      <c r="E28" s="62" t="n">
+      <c r="E28" s="58" t="n">
         <v>40</v>
       </c>
-      <c r="F28" s="85">
+      <c r="F28" s="78">
         <f>IFERROR(D28*E28,0)</f>
         <v/>
       </c>
-      <c r="G28" s="86">
+      <c r="G28" s="79">
         <f>IFERROR(F28/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="H28" s="86">
+      <c r="H28" s="79">
         <f>IFERROR(SUMIF($F$10:$F$39,"&gt;="&amp;F28,$F$10:$F$39)/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="R28" s="70">
-        <f>RANK.EQ(F28,$F$10:$F$39,0)+COUNTIF($F$10:F28,F28)-1</f>
-        <v/>
-      </c>
-      <c r="S28" s="70">
-        <f>INDEX($A$10:$A$39,MATCH(ROWS($S$10:S28),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="T28" s="71">
-        <f>INDEX($B$10:$B$39,MATCH(ROWS($T$10:T28),$R$10:$R$39,0))&amp;" ("&amp;S28&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U28" s="72">
-        <f>INDEX($F$10:$F$39,MATCH(ROWS($U$10:U28),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="V28" s="73">
-        <f>INDEX($H$10:$H$39,MATCH(ROWS($V$10:V28),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="W28" s="74">
-        <f>IF($S28="A",$U28,NA())</f>
-        <v/>
-      </c>
-      <c r="X28" s="75">
-        <f>IF($S28="B",$U28,NA())</f>
-        <v/>
-      </c>
-      <c r="Y28" s="76">
-        <f>IF($S28="C",$U28,NA())</f>
-        <v/>
+      <c r="P28" s="65" t="inlineStr">
+        <is>
+          <t>Filtro de Linha (C)</t>
+        </is>
+      </c>
+      <c r="Q28" s="66" t="n">
+        <v>4400</v>
+      </c>
+      <c r="R28" s="67" t="n">
+        <v>0.9751</v>
+      </c>
+      <c r="S28" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" s="70" t="n">
+        <v>4400</v>
       </c>
     </row>
     <row r="29" ht="19" customHeight="1">
-      <c r="A29" s="68">
+      <c r="A29" s="61">
         <f>IF($H29&lt;=$E$5,"A",IF($H29&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B29" s="83" t="inlineStr">
+      <c r="B29" s="76" t="inlineStr">
         <is>
           <t>Webcam Full HD</t>
         </is>
       </c>
-      <c r="C29" s="84" t="n">
+      <c r="C29" s="77" t="n">
         <v>14</v>
       </c>
-      <c r="D29" s="61" t="n">
+      <c r="D29" s="57" t="n">
         <v>22</v>
       </c>
-      <c r="E29" s="62" t="n">
+      <c r="E29" s="58" t="n">
         <v>180</v>
       </c>
-      <c r="F29" s="85">
+      <c r="F29" s="78">
         <f>IFERROR(D29*E29,0)</f>
         <v/>
       </c>
-      <c r="G29" s="86">
+      <c r="G29" s="79">
         <f>IFERROR(F29/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="H29" s="86">
+      <c r="H29" s="79">
         <f>IFERROR(SUMIF($F$10:$F$39,"&gt;="&amp;F29,$F$10:$F$39)/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="R29" s="70">
-        <f>RANK.EQ(F29,$F$10:$F$39,0)+COUNTIF($F$10:F29,F29)-1</f>
-        <v/>
-      </c>
-      <c r="S29" s="70">
-        <f>INDEX($A$10:$A$39,MATCH(ROWS($S$10:S29),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="T29" s="71">
-        <f>INDEX($B$10:$B$39,MATCH(ROWS($T$10:T29),$R$10:$R$39,0))&amp;" ("&amp;S29&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U29" s="72">
-        <f>INDEX($F$10:$F$39,MATCH(ROWS($U$10:U29),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="V29" s="73">
-        <f>INDEX($H$10:$H$39,MATCH(ROWS($V$10:V29),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="W29" s="74">
-        <f>IF($S29="A",$U29,NA())</f>
-        <v/>
-      </c>
-      <c r="X29" s="75">
-        <f>IF($S29="B",$U29,NA())</f>
-        <v/>
-      </c>
-      <c r="Y29" s="76">
-        <f>IF($S29="C",$U29,NA())</f>
-        <v/>
+      <c r="P29" s="65" t="inlineStr">
+        <is>
+          <t>Webcam Full HD (C)</t>
+        </is>
+      </c>
+      <c r="Q29" s="66" t="n">
+        <v>3960</v>
+      </c>
+      <c r="R29" s="67" t="n">
+        <v>0.9789</v>
+      </c>
+      <c r="S29" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" s="70" t="n">
+        <v>3960</v>
       </c>
     </row>
     <row r="30" ht="19" customHeight="1">
-      <c r="A30" s="68">
+      <c r="A30" s="61">
         <f>IF($H30&lt;=$E$5,"A",IF($H30&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B30" s="83" t="inlineStr">
+      <c r="B30" s="76" t="inlineStr">
         <is>
           <t>Pilhas AA (Pacote)</t>
         </is>
       </c>
-      <c r="C30" s="84" t="n">
+      <c r="C30" s="77" t="n">
         <v>23</v>
       </c>
-      <c r="D30" s="61" t="n">
+      <c r="D30" s="57" t="n">
         <v>300</v>
       </c>
-      <c r="E30" s="62" t="n">
+      <c r="E30" s="58" t="n">
         <v>12</v>
       </c>
-      <c r="F30" s="85">
+      <c r="F30" s="78">
         <f>IFERROR(D30*E30,0)</f>
         <v/>
       </c>
-      <c r="G30" s="86">
+      <c r="G30" s="79">
         <f>IFERROR(F30/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="H30" s="86">
+      <c r="H30" s="79">
         <f>IFERROR(SUMIF($F$10:$F$39,"&gt;="&amp;F30,$F$10:$F$39)/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="R30" s="70">
-        <f>RANK.EQ(F30,$F$10:$F$39,0)+COUNTIF($F$10:F30,F30)-1</f>
-        <v/>
-      </c>
-      <c r="S30" s="70">
-        <f>INDEX($A$10:$A$39,MATCH(ROWS($S$10:S30),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="T30" s="71">
-        <f>INDEX($B$10:$B$39,MATCH(ROWS($T$10:T30),$R$10:$R$39,0))&amp;" ("&amp;S30&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U30" s="72">
-        <f>INDEX($F$10:$F$39,MATCH(ROWS($U$10:U30),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="V30" s="73">
-        <f>INDEX($H$10:$H$39,MATCH(ROWS($V$10:V30),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="W30" s="74">
-        <f>IF($S30="A",$U30,NA())</f>
-        <v/>
-      </c>
-      <c r="X30" s="75">
-        <f>IF($S30="B",$U30,NA())</f>
-        <v/>
-      </c>
-      <c r="Y30" s="76">
-        <f>IF($S30="C",$U30,NA())</f>
-        <v/>
+      <c r="P30" s="65" t="inlineStr">
+        <is>
+          <t>Pilhas AA (Pacote) (C)</t>
+        </is>
+      </c>
+      <c r="Q30" s="66" t="n">
+        <v>3600</v>
+      </c>
+      <c r="R30" s="67" t="n">
+        <v>0.9824000000000001</v>
+      </c>
+      <c r="S30" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="70" t="n">
+        <v>3600</v>
       </c>
     </row>
     <row r="31" ht="19" customHeight="1">
-      <c r="A31" s="68">
+      <c r="A31" s="61">
         <f>IF($H31&lt;=$E$5,"A",IF($H31&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B31" s="83" t="inlineStr">
+      <c r="B31" s="76" t="inlineStr">
         <is>
           <t>Adaptador USB-C</t>
         </is>
       </c>
-      <c r="C31" s="84" t="n">
+      <c r="C31" s="77" t="n">
         <v>16</v>
       </c>
-      <c r="D31" s="61" t="n">
+      <c r="D31" s="57" t="n">
         <v>90</v>
       </c>
-      <c r="E31" s="62" t="n">
+      <c r="E31" s="58" t="n">
         <v>35</v>
       </c>
-      <c r="F31" s="85">
+      <c r="F31" s="78">
         <f>IFERROR(D31*E31,0)</f>
         <v/>
       </c>
-      <c r="G31" s="86">
+      <c r="G31" s="79">
         <f>IFERROR(F31/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="H31" s="86">
+      <c r="H31" s="79">
         <f>IFERROR(SUMIF($F$10:$F$39,"&gt;="&amp;F31,$F$10:$F$39)/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="R31" s="70">
-        <f>RANK.EQ(F31,$F$10:$F$39,0)+COUNTIF($F$10:F31,F31)-1</f>
-        <v/>
-      </c>
-      <c r="S31" s="70">
-        <f>INDEX($A$10:$A$39,MATCH(ROWS($S$10:S31),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="T31" s="71">
-        <f>INDEX($B$10:$B$39,MATCH(ROWS($T$10:T31),$R$10:$R$39,0))&amp;" ("&amp;S31&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U31" s="72">
-        <f>INDEX($F$10:$F$39,MATCH(ROWS($U$10:U31),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="V31" s="73">
-        <f>INDEX($H$10:$H$39,MATCH(ROWS($V$10:V31),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="W31" s="74">
-        <f>IF($S31="A",$U31,NA())</f>
-        <v/>
-      </c>
-      <c r="X31" s="75">
-        <f>IF($S31="B",$U31,NA())</f>
-        <v/>
-      </c>
-      <c r="Y31" s="76">
-        <f>IF($S31="C",$U31,NA())</f>
-        <v/>
+      <c r="P31" s="65" t="inlineStr">
+        <is>
+          <t>Adaptador USB-C (C)</t>
+        </is>
+      </c>
+      <c r="Q31" s="66" t="n">
+        <v>3150</v>
+      </c>
+      <c r="R31" s="67" t="n">
+        <v>0.9854000000000001</v>
+      </c>
+      <c r="S31" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" s="70" t="n">
+        <v>3150</v>
       </c>
     </row>
     <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="68">
+      <c r="A32" s="61">
         <f>IF($H32&lt;=$E$5,"A",IF($H32&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B32" s="83" t="inlineStr">
+      <c r="B32" s="76" t="inlineStr">
         <is>
           <t>Suporte para Monitor</t>
         </is>
       </c>
-      <c r="C32" s="84" t="n">
+      <c r="C32" s="77" t="n">
         <v>28</v>
       </c>
-      <c r="D32" s="61" t="n">
+      <c r="D32" s="57" t="n">
         <v>20</v>
       </c>
-      <c r="E32" s="62" t="n">
+      <c r="E32" s="58" t="n">
         <v>140</v>
       </c>
-      <c r="F32" s="85">
+      <c r="F32" s="78">
         <f>IFERROR(D32*E32,0)</f>
         <v/>
       </c>
-      <c r="G32" s="86">
+      <c r="G32" s="79">
         <f>IFERROR(F32/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="H32" s="86">
+      <c r="H32" s="79">
         <f>IFERROR(SUMIF($F$10:$F$39,"&gt;="&amp;F32,$F$10:$F$39)/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="R32" s="70">
-        <f>RANK.EQ(F32,$F$10:$F$39,0)+COUNTIF($F$10:F32,F32)-1</f>
-        <v/>
-      </c>
-      <c r="S32" s="70">
-        <f>INDEX($A$10:$A$39,MATCH(ROWS($S$10:S32),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="T32" s="71">
-        <f>INDEX($B$10:$B$39,MATCH(ROWS($T$10:T32),$R$10:$R$39,0))&amp;" ("&amp;S32&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U32" s="72">
-        <f>INDEX($F$10:$F$39,MATCH(ROWS($U$10:U32),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="V32" s="73">
-        <f>INDEX($H$10:$H$39,MATCH(ROWS($V$10:V32),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="W32" s="74">
-        <f>IF($S32="A",$U32,NA())</f>
-        <v/>
-      </c>
-      <c r="X32" s="75">
-        <f>IF($S32="B",$U32,NA())</f>
-        <v/>
-      </c>
-      <c r="Y32" s="76">
-        <f>IF($S32="C",$U32,NA())</f>
-        <v/>
+      <c r="P32" s="65" t="inlineStr">
+        <is>
+          <t>Suporte para Monitor (C)</t>
+        </is>
+      </c>
+      <c r="Q32" s="66" t="n">
+        <v>2800</v>
+      </c>
+      <c r="R32" s="67" t="n">
+        <v>0.9881</v>
+      </c>
+      <c r="S32" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="70" t="n">
+        <v>2800</v>
       </c>
     </row>
     <row r="33" ht="19" customHeight="1">
-      <c r="A33" s="68">
+      <c r="A33" s="61">
         <f>IF($H33&lt;=$E$5,"A",IF($H33&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B33" s="83" t="inlineStr">
+      <c r="B33" s="76" t="inlineStr">
         <is>
           <t>Cabo HDMI 2m</t>
         </is>
       </c>
-      <c r="C33" s="84" t="n">
+      <c r="C33" s="77" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="61" t="n">
+      <c r="D33" s="57" t="n">
         <v>85</v>
       </c>
-      <c r="E33" s="62" t="n">
+      <c r="E33" s="58" t="n">
         <v>25</v>
       </c>
-      <c r="F33" s="85">
+      <c r="F33" s="78">
         <f>IFERROR(D33*E33,0)</f>
         <v/>
       </c>
-      <c r="G33" s="86">
+      <c r="G33" s="79">
         <f>IFERROR(F33/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="H33" s="86">
+      <c r="H33" s="79">
         <f>IFERROR(SUMIF($F$10:$F$39,"&gt;="&amp;F33,$F$10:$F$39)/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="R33" s="70">
-        <f>RANK.EQ(F33,$F$10:$F$39,0)+COUNTIF($F$10:F33,F33)-1</f>
-        <v/>
-      </c>
-      <c r="S33" s="70">
-        <f>INDEX($A$10:$A$39,MATCH(ROWS($S$10:S33),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="T33" s="71">
-        <f>INDEX($B$10:$B$39,MATCH(ROWS($T$10:T33),$R$10:$R$39,0))&amp;" ("&amp;S33&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U33" s="72">
-        <f>INDEX($F$10:$F$39,MATCH(ROWS($U$10:U33),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="V33" s="73">
-        <f>INDEX($H$10:$H$39,MATCH(ROWS($V$10:V33),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="W33" s="74">
-        <f>IF($S33="A",$U33,NA())</f>
-        <v/>
-      </c>
-      <c r="X33" s="75">
-        <f>IF($S33="B",$U33,NA())</f>
-        <v/>
-      </c>
-      <c r="Y33" s="76">
-        <f>IF($S33="C",$U33,NA())</f>
-        <v/>
+      <c r="P33" s="65" t="inlineStr">
+        <is>
+          <t>Cabo HDMI 2m (C)</t>
+        </is>
+      </c>
+      <c r="Q33" s="66" t="n">
+        <v>2125</v>
+      </c>
+      <c r="R33" s="67" t="n">
+        <v>0.9901</v>
+      </c>
+      <c r="S33" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="70" t="n">
+        <v>2125</v>
       </c>
     </row>
     <row r="34" ht="19" customHeight="1">
-      <c r="A34" s="68">
+      <c r="A34" s="61">
         <f>IF($H34&lt;=$E$5,"A",IF($H34&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B34" s="83" t="inlineStr">
+      <c r="B34" s="76" t="inlineStr">
         <is>
           <t>Mousepad Simples</t>
         </is>
       </c>
-      <c r="C34" s="84" t="n">
+      <c r="C34" s="77" t="n">
         <v>24</v>
       </c>
-      <c r="D34" s="61" t="n">
+      <c r="D34" s="57" t="n">
         <v>250</v>
       </c>
-      <c r="E34" s="62" t="n">
+      <c r="E34" s="58" t="n">
         <v>8</v>
       </c>
-      <c r="F34" s="85">
+      <c r="F34" s="78">
         <f>IFERROR(D34*E34,0)</f>
         <v/>
       </c>
-      <c r="G34" s="86">
+      <c r="G34" s="79">
         <f>IFERROR(F34/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="H34" s="86">
+      <c r="H34" s="79">
         <f>IFERROR(SUMIF($F$10:$F$39,"&gt;="&amp;F34,$F$10:$F$39)/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="R34" s="70">
-        <f>RANK.EQ(F34,$F$10:$F$39,0)+COUNTIF($F$10:F34,F34)-1</f>
-        <v/>
-      </c>
-      <c r="S34" s="70">
-        <f>INDEX($A$10:$A$39,MATCH(ROWS($S$10:S34),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="T34" s="71">
-        <f>INDEX($B$10:$B$39,MATCH(ROWS($T$10:T34),$R$10:$R$39,0))&amp;" ("&amp;S34&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U34" s="72">
-        <f>INDEX($F$10:$F$39,MATCH(ROWS($U$10:U34),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="V34" s="73">
-        <f>INDEX($H$10:$H$39,MATCH(ROWS($V$10:V34),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="W34" s="74">
-        <f>IF($S34="A",$U34,NA())</f>
-        <v/>
-      </c>
-      <c r="X34" s="75">
-        <f>IF($S34="B",$U34,NA())</f>
-        <v/>
-      </c>
-      <c r="Y34" s="76">
-        <f>IF($S34="C",$U34,NA())</f>
-        <v/>
+      <c r="P34" s="65" t="inlineStr">
+        <is>
+          <t>Mousepad Simples (C)</t>
+        </is>
+      </c>
+      <c r="Q34" s="66" t="n">
+        <v>2000</v>
+      </c>
+      <c r="R34" s="67" t="n">
+        <v>0.9921</v>
+      </c>
+      <c r="S34" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="70" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="35" ht="19" customHeight="1">
-      <c r="A35" s="68">
+      <c r="A35" s="61">
         <f>IF($H35&lt;=$E$5,"A",IF($H35&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B35" s="83" t="inlineStr">
+      <c r="B35" s="76" t="inlineStr">
         <is>
           <t>Mouse Optico Simples</t>
         </is>
       </c>
-      <c r="C35" s="84" t="n">
+      <c r="C35" s="77" t="n">
         <v>3</v>
       </c>
-      <c r="D35" s="61" t="n">
+      <c r="D35" s="57" t="n">
         <v>120</v>
       </c>
-      <c r="E35" s="62" t="n">
+      <c r="E35" s="58" t="n">
         <v>15</v>
       </c>
-      <c r="F35" s="85">
+      <c r="F35" s="78">
         <f>IFERROR(D35*E35,0)</f>
         <v/>
       </c>
-      <c r="G35" s="86">
+      <c r="G35" s="79">
         <f>IFERROR(F35/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="H35" s="86">
+      <c r="H35" s="79">
         <f>IFERROR(SUMIF($F$10:$F$39,"&gt;="&amp;F35,$F$10:$F$39)/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="R35" s="70">
-        <f>RANK.EQ(F35,$F$10:$F$39,0)+COUNTIF($F$10:F35,F35)-1</f>
-        <v/>
-      </c>
-      <c r="S35" s="70">
-        <f>INDEX($A$10:$A$39,MATCH(ROWS($S$10:S35),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="T35" s="71">
-        <f>INDEX($B$10:$B$39,MATCH(ROWS($T$10:T35),$R$10:$R$39,0))&amp;" ("&amp;S35&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U35" s="72">
-        <f>INDEX($F$10:$F$39,MATCH(ROWS($U$10:U35),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="V35" s="73">
-        <f>INDEX($H$10:$H$39,MATCH(ROWS($V$10:V35),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="W35" s="74">
-        <f>IF($S35="A",$U35,NA())</f>
-        <v/>
-      </c>
-      <c r="X35" s="75">
-        <f>IF($S35="B",$U35,NA())</f>
-        <v/>
-      </c>
-      <c r="Y35" s="76">
-        <f>IF($S35="C",$U35,NA())</f>
-        <v/>
+      <c r="P35" s="65" t="inlineStr">
+        <is>
+          <t>Mouse Optico Simples (C)</t>
+        </is>
+      </c>
+      <c r="Q35" s="66" t="n">
+        <v>1800</v>
+      </c>
+      <c r="R35" s="67" t="n">
+        <v>0.9938</v>
+      </c>
+      <c r="S35" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" s="70" t="n">
+        <v>1800</v>
       </c>
     </row>
     <row r="36" ht="19" customHeight="1">
-      <c r="A36" s="68">
+      <c r="A36" s="61">
         <f>IF($H36&lt;=$E$5,"A",IF($H36&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B36" s="83" t="inlineStr">
+      <c r="B36" s="76" t="inlineStr">
         <is>
           <t>Organizador de Cabos</t>
         </is>
       </c>
-      <c r="C36" s="84" t="n">
+      <c r="C36" s="77" t="n">
         <v>25</v>
       </c>
-      <c r="D36" s="61" t="n">
+      <c r="D36" s="57" t="n">
         <v>180</v>
       </c>
-      <c r="E36" s="62" t="n">
+      <c r="E36" s="58" t="n">
         <v>10</v>
       </c>
-      <c r="F36" s="85">
+      <c r="F36" s="78">
         <f>IFERROR(D36*E36,0)</f>
         <v/>
       </c>
-      <c r="G36" s="86">
+      <c r="G36" s="79">
         <f>IFERROR(F36/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="H36" s="86">
+      <c r="H36" s="79">
         <f>IFERROR(SUMIF($F$10:$F$39,"&gt;="&amp;F36,$F$10:$F$39)/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="R36" s="70">
-        <f>RANK.EQ(F36,$F$10:$F$39,0)+COUNTIF($F$10:F36,F36)-1</f>
-        <v/>
-      </c>
-      <c r="S36" s="70">
-        <f>INDEX($A$10:$A$39,MATCH(ROWS($S$10:S36),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="T36" s="71">
-        <f>INDEX($B$10:$B$39,MATCH(ROWS($T$10:T36),$R$10:$R$39,0))&amp;" ("&amp;S36&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U36" s="72">
-        <f>INDEX($F$10:$F$39,MATCH(ROWS($U$10:U36),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="V36" s="73">
-        <f>INDEX($H$10:$H$39,MATCH(ROWS($V$10:V36),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="W36" s="74">
-        <f>IF($S36="A",$U36,NA())</f>
-        <v/>
-      </c>
-      <c r="X36" s="75">
-        <f>IF($S36="B",$U36,NA())</f>
-        <v/>
-      </c>
-      <c r="Y36" s="76">
-        <f>IF($S36="C",$U36,NA())</f>
-        <v/>
+      <c r="P36" s="65" t="inlineStr">
+        <is>
+          <t>Organizador de Cabos (C)</t>
+        </is>
+      </c>
+      <c r="Q36" s="66" t="n">
+        <v>1800</v>
+      </c>
+      <c r="R36" s="67" t="n">
+        <v>0.9955000000000001</v>
+      </c>
+      <c r="S36" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="70" t="n">
+        <v>1800</v>
       </c>
     </row>
     <row r="37" ht="19" customHeight="1">
-      <c r="A37" s="68">
+      <c r="A37" s="61">
         <f>IF($H37&lt;=$E$5,"A",IF($H37&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B37" s="83" t="inlineStr">
+      <c r="B37" s="76" t="inlineStr">
         <is>
           <t>Ar comprimido (Lata)</t>
         </is>
       </c>
-      <c r="C37" s="84" t="n">
+      <c r="C37" s="77" t="n">
         <v>27</v>
       </c>
-      <c r="D37" s="61" t="n">
+      <c r="D37" s="57" t="n">
         <v>35</v>
       </c>
-      <c r="E37" s="62" t="n">
+      <c r="E37" s="58" t="n">
         <v>45</v>
       </c>
-      <c r="F37" s="85">
+      <c r="F37" s="78">
         <f>IFERROR(D37*E37,0)</f>
         <v/>
       </c>
-      <c r="G37" s="86">
+      <c r="G37" s="79">
         <f>IFERROR(F37/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="H37" s="86">
+      <c r="H37" s="79">
         <f>IFERROR(SUMIF($F$10:$F$39,"&gt;="&amp;F37,$F$10:$F$39)/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="R37" s="70">
-        <f>RANK.EQ(F37,$F$10:$F$39,0)+COUNTIF($F$10:F37,F37)-1</f>
-        <v/>
-      </c>
-      <c r="S37" s="70">
-        <f>INDEX($A$10:$A$39,MATCH(ROWS($S$10:S37),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="T37" s="71">
-        <f>INDEX($B$10:$B$39,MATCH(ROWS($T$10:T37),$R$10:$R$39,0))&amp;" ("&amp;S37&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U37" s="72">
-        <f>INDEX($F$10:$F$39,MATCH(ROWS($U$10:U37),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="V37" s="73">
-        <f>INDEX($H$10:$H$39,MATCH(ROWS($V$10:V37),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="W37" s="74">
-        <f>IF($S37="A",$U37,NA())</f>
-        <v/>
-      </c>
-      <c r="X37" s="75">
-        <f>IF($S37="B",$U37,NA())</f>
-        <v/>
-      </c>
-      <c r="Y37" s="76">
-        <f>IF($S37="C",$U37,NA())</f>
-        <v/>
+      <c r="P37" s="65" t="inlineStr">
+        <is>
+          <t>Ar comprimido (Lata) (C)</t>
+        </is>
+      </c>
+      <c r="Q37" s="66" t="n">
+        <v>1575</v>
+      </c>
+      <c r="R37" s="67" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="S37" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" s="70" t="n">
+        <v>1575</v>
       </c>
     </row>
     <row r="38" ht="19" customHeight="1">
-      <c r="A38" s="68">
+      <c r="A38" s="61">
         <f>IF($H38&lt;=$E$5,"A",IF($H38&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B38" s="83" t="inlineStr">
+      <c r="B38" s="76" t="inlineStr">
         <is>
           <t>Pasta Termica</t>
         </is>
       </c>
-      <c r="C38" s="84" t="n">
+      <c r="C38" s="77" t="n">
         <v>26</v>
       </c>
-      <c r="D38" s="61" t="n">
+      <c r="D38" s="57" t="n">
         <v>45</v>
       </c>
-      <c r="E38" s="62" t="n">
+      <c r="E38" s="58" t="n">
         <v>35</v>
       </c>
-      <c r="F38" s="85">
+      <c r="F38" s="78">
         <f>IFERROR(D38*E38,0)</f>
         <v/>
       </c>
-      <c r="G38" s="86">
+      <c r="G38" s="79">
         <f>IFERROR(F38/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="H38" s="86">
+      <c r="H38" s="79">
         <f>IFERROR(SUMIF($F$10:$F$39,"&gt;="&amp;F38,$F$10:$F$39)/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="R38" s="70">
-        <f>RANK.EQ(F38,$F$10:$F$39,0)+COUNTIF($F$10:F38,F38)-1</f>
-        <v/>
-      </c>
-      <c r="S38" s="70">
-        <f>INDEX($A$10:$A$39,MATCH(ROWS($S$10:S38),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="T38" s="71">
-        <f>INDEX($B$10:$B$39,MATCH(ROWS($T$10:T38),$R$10:$R$39,0))&amp;" ("&amp;S38&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U38" s="72">
-        <f>INDEX($F$10:$F$39,MATCH(ROWS($U$10:U38),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="V38" s="73">
-        <f>INDEX($H$10:$H$39,MATCH(ROWS($V$10:V38),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="W38" s="74">
-        <f>IF($S38="A",$U38,NA())</f>
-        <v/>
-      </c>
-      <c r="X38" s="75">
-        <f>IF($S38="B",$U38,NA())</f>
-        <v/>
-      </c>
-      <c r="Y38" s="76">
-        <f>IF($S38="C",$U38,NA())</f>
-        <v/>
+      <c r="P38" s="65" t="inlineStr">
+        <is>
+          <t>Pasta Termica (C)</t>
+        </is>
+      </c>
+      <c r="Q38" s="66" t="n">
+        <v>1575</v>
+      </c>
+      <c r="R38" s="67" t="n">
+        <v>0.9986</v>
+      </c>
+      <c r="S38" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" s="70" t="n">
+        <v>1575</v>
       </c>
     </row>
     <row r="39" ht="19" customHeight="1">
-      <c r="A39" s="68">
+      <c r="A39" s="61">
         <f>IF($H39&lt;=$E$5,"A",IF($H39&lt;=$G$5,"B","C"))</f>
         <v/>
       </c>
-      <c r="B39" s="83" t="inlineStr">
+      <c r="B39" s="76" t="inlineStr">
         <is>
           <t>Conector RJ45 (Cento)</t>
         </is>
       </c>
-      <c r="C39" s="84" t="n">
+      <c r="C39" s="77" t="n">
         <v>30</v>
       </c>
-      <c r="D39" s="61" t="n">
+      <c r="D39" s="57" t="n">
         <v>50</v>
       </c>
-      <c r="E39" s="62" t="n">
+      <c r="E39" s="58" t="n">
         <v>30</v>
       </c>
-      <c r="F39" s="85">
+      <c r="F39" s="78">
         <f>IFERROR(D39*E39,0)</f>
         <v/>
       </c>
-      <c r="G39" s="86">
+      <c r="G39" s="79">
         <f>IFERROR(F39/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="H39" s="86">
+      <c r="H39" s="79">
         <f>IFERROR(SUMIF($F$10:$F$39,"&gt;="&amp;F39,$F$10:$F$39)/SUM($F$10:$F$39),0)</f>
         <v/>
       </c>
-      <c r="R39" s="70">
-        <f>RANK.EQ(F39,$F$10:$F$39,0)+COUNTIF($F$10:F39,F39)-1</f>
-        <v/>
-      </c>
-      <c r="S39" s="70">
-        <f>INDEX($A$10:$A$39,MATCH(ROWS($S$10:S39),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="T39" s="71">
-        <f>INDEX($B$10:$B$39,MATCH(ROWS($T$10:T39),$R$10:$R$39,0))&amp;" ("&amp;S39&amp;")"</f>
-        <v/>
-      </c>
-      <c r="U39" s="72">
-        <f>INDEX($F$10:$F$39,MATCH(ROWS($U$10:U39),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="V39" s="73">
-        <f>INDEX($H$10:$H$39,MATCH(ROWS($V$10:V39),$R$10:$R$39,0))</f>
-        <v/>
-      </c>
-      <c r="W39" s="74">
-        <f>IF($S39="A",$U39,NA())</f>
-        <v/>
-      </c>
-      <c r="X39" s="75">
-        <f>IF($S39="B",$U39,NA())</f>
-        <v/>
-      </c>
-      <c r="Y39" s="76">
-        <f>IF($S39="C",$U39,NA())</f>
-        <v/>
+      <c r="P39" s="65" t="inlineStr">
+        <is>
+          <t>Conector RJ45 (Cento (C)</t>
+        </is>
+      </c>
+      <c r="Q39" s="66" t="n">
+        <v>1500</v>
+      </c>
+      <c r="R39" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="S39" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" s="70" t="n">
+        <v>1500</v>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="87" t="inlineStr">
+      <c r="A40" s="80" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B40" s="88" t="n"/>
-      <c r="C40" s="88" t="n"/>
-      <c r="D40" s="89">
+      <c r="B40" s="81" t="n"/>
+      <c r="C40" s="81" t="n"/>
+      <c r="D40" s="82">
         <f>SUM(D10:D39)</f>
         <v/>
       </c>
-      <c r="E40" s="90" t="n"/>
-      <c r="F40" s="91">
+      <c r="E40" s="83" t="n"/>
+      <c r="F40" s="84">
         <f>SUM(F10:F39)</f>
         <v/>
       </c>
-      <c r="G40" s="92" t="n">
+      <c r="G40" s="85" t="n">
         <v>1</v>
       </c>
-      <c r="H40" s="92" t="n">
+      <c r="H40" s="85" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="71" ht="18" customHeight="1">
-      <c r="A71" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CURVA ABC REGGAE  |  CURVA ABC REGGAE  —  ABA 02  |  One Love, One Data  |  2026</t>
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CURVA ABC REGGAE  |  CURVA ABC — ABA 02  |  One Love, One Data  |  2026</t>
         </is>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="F0B1"/>
-  <mergeCells count="26">
+  <mergeCells count="21">
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="A73:H73"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="G71:H71"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="J1:N1"/>
     <mergeCell ref="A1:H1"/>
@@ -7600,11 +6833,7 @@
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
-    <mergeCell ref="J11:N11"/>
     <mergeCell ref="E2:F2"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A71:H71"/>
-    <mergeCell ref="C71:D71"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="A40:C40"/>

--- a/curva_abc_reggae.xlsx
+++ b/curva_abc_reggae.xlsx
@@ -10,6 +10,7 @@
     <sheet name="🟢 Primeira" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="🟡 01" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="🔴 02" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="📅 CALENDÁRIO" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="R$ #,##0"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,9 +63,9 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+      <i val="1"/>
+      <color rgb="00C8F5DB"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -75,26 +76,32 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="00FFD700"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00C8F5DB"/>
-      <sz val="8"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="13"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00000000"/>
-      <sz val="13"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -105,13 +112,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFD700"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00B0B0B0"/>
+      <color rgb="00999999"/>
       <sz val="7"/>
     </font>
     <font>
@@ -138,23 +139,51 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="00B0B0B0"/>
+      <color rgb="00999999"/>
       <sz val="7"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFD700"/>
-      <sz val="11"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <color rgb="00009B3A"/>
+      <sz val="24"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFF8D0"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00D6F5E3"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00FFEDED"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFEDED"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -181,7 +210,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001A1A1A"/>
+        <fgColor rgb="001E1E1E"/>
       </patternFill>
     </fill>
     <fill>
@@ -201,7 +230,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8F5DB"/>
+        <fgColor rgb="00222222"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6F5E3"/>
       </patternFill>
     </fill>
     <fill>
@@ -211,16 +245,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF5B0"/>
+        <fgColor rgb="00FFF8D0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD0D0"/>
+        <fgColor rgb="00FFEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00141414"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000A0A0A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000D1A0D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A0000"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -356,16 +410,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00999999"/>
       </left>
       <right style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00999999"/>
       </right>
       <top style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00999999"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00999999"/>
       </bottom>
     </border>
     <border>
@@ -397,6 +451,20 @@
       </bottom>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
+    <border>
       <left style="medium">
         <color rgb="00006B28"/>
       </left>
@@ -404,10 +472,10 @@
         <color rgb="00006B28"/>
       </right>
       <top style="thin">
-        <color rgb="00E8E8E8"/>
+        <color rgb="00DDDDDD"/>
       </top>
       <bottom style="thin">
-        <color rgb="00E8E8E8"/>
+        <color rgb="00DDDDDD"/>
       </bottom>
     </border>
     <border>
@@ -424,11 +492,44 @@
         <color rgb="00009B3A"/>
       </bottom>
     </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="00FFFFFF"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00141414"/>
+      </left>
+      <right style="thin">
+        <color rgb="00141414"/>
+      </right>
+      <top style="thin">
+        <color rgb="00141414"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00141414"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="001A1A1A"/>
+      </left>
+      <right style="hair">
+        <color rgb="001A1A1A"/>
+      </right>
+      <top style="hair">
+        <color rgb="001A1A1A"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="001A1A1A"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -436,8 +537,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -485,72 +586,72 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="10" fillId="3" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="7" fillId="3" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="10" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="4" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="4" fillId="8" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="8" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="12" fillId="8" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="8" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="12" fillId="8" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="9" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="9" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="10" fillId="9" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="9" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -559,29 +660,32 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="11" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="12" fillId="12" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="11" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="12" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="10" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="11" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="17" fillId="10" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="17" fillId="11" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="19" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="19" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="19" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="19" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -589,45 +693,83 @@
     <xf numFmtId="0" fontId="18" fillId="8" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="12" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="13" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="17" fillId="12" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="17" fillId="13" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="9" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="13" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="14" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="17" fillId="13" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="17" fillId="14" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="21" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="15" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="21" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="21" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="15" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -641,7 +783,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00C8F5DB"/>
+          <fgColor rgb="00D6F5E3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -651,7 +793,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFF5B0"/>
+          <fgColor rgb="00FFF8D0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -661,7 +803,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFD0D0"/>
+          <fgColor rgb="00FFEDED"/>
         </patternFill>
       </fill>
     </dxf>
@@ -751,7 +893,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>🇯🇲 CURVA ABC REGGAE — PRIMEIRA — Curva de Pareto &amp; Classificação ABC</a:t>
+              <a:t>🇯🇲  CURVA ABC REGGAE — PRIMEIRA  —  Curva ABC de Pareto</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -764,71 +906,15 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <v>🟢 Zona A (≤80%)</v>
+            <v>🟢 Faixa A (≤80%)</v>
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="ADEBAD"/>
+              <a:srgbClr val="A8E6C0"/>
             </a:solidFill>
-            <a:ln w="5000">
+            <a:ln w="6000">
               <a:solidFill>
                 <a:srgbClr val="009B3A"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'🟢 Primeira'!$P$12:$P$21</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'🟢 Primeira'!$S$12:$S$21</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <v>🟡 Zona B (80-95%)</v>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="FFE87C"/>
-            </a:solidFill>
-            <a:ln w="5000">
-              <a:solidFill>
-                <a:srgbClr val="C8A400"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'🟢 Primeira'!$P$12:$P$21</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'🟢 Primeira'!$T$12:$T$21</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <v>🔴 Zona C (95-100%)</v>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="FFAD99"/>
-            </a:solidFill>
-            <a:ln w="5000">
-              <a:solidFill>
-                <a:srgbClr val="990000"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -844,25 +930,81 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>🟡 Faixa B (80-95%)</v>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFE87C"/>
+            </a:solidFill>
+            <a:ln w="6000">
+              <a:solidFill>
+                <a:srgbClr val="C8A400"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'🟢 Primeira'!$P$12:$P$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'🟢 Primeira'!$V$12:$V$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>🔴 Faixa C (&gt;95%)</v>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFAD99"/>
+            </a:solidFill>
+            <a:ln w="6000">
+              <a:solidFill>
+                <a:srgbClr val="990000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'🟢 Primeira'!$P$12:$P$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'🟢 Primeira'!$W$12:$W$21</f>
+            </numRef>
+          </val>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </areaChart>
       <barChart>
         <barDir val="col"/>
-        <grouping val="clustered"/>
+        <grouping val="stacked"/>
         <ser>
           <idx val="3"/>
           <order val="3"/>
           <tx>
-            <v>📊 % Individual por Produto</v>
+            <v>🟢 Classe A</v>
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="2E75B6"/>
+              <a:srgbClr val="009B3A"/>
             </a:solidFill>
             <a:ln w="8000">
               <a:solidFill>
-                <a:srgbClr val="1A4E8A"/>
+                <a:srgbClr val="006B28"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -875,6 +1017,62 @@
           <val>
             <numRef>
               <f>'🟢 Primeira'!$Q$12:$Q$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <v>🟡 Classe B</v>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFD700"/>
+            </a:solidFill>
+            <a:ln w="8000">
+              <a:solidFill>
+                <a:srgbClr val="C8A400"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'🟢 Primeira'!$P$12:$P$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'🟢 Primeira'!$R$12:$R$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <v>🔴 Classe C</v>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="CC0000"/>
+            </a:solidFill>
+            <a:ln w="8000">
+              <a:solidFill>
+                <a:srgbClr val="990000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'🟢 Primeira'!$P$12:$P$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'🟢 Primeira'!$S$12:$S$21</f>
             </numRef>
           </val>
         </ser>
@@ -891,15 +1089,15 @@
       <lineChart>
         <grouping val="standard"/>
         <ser>
-          <idx val="4"/>
-          <order val="4"/>
+          <idx val="6"/>
+          <order val="6"/>
           <tx>
             <v>📈 % Acumulado (Curva Pareto)</v>
           </tx>
           <spPr>
-            <a:ln w="30000">
+            <a:ln w="28000">
               <a:solidFill>
-                <a:srgbClr val="990000"/>
+                <a:srgbClr val="111111"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -909,11 +1107,11 @@
             <size val="5"/>
             <spPr>
               <a:solidFill>
-                <a:srgbClr val="CC0000"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:ln>
                 <a:solidFill>
-                  <a:srgbClr val="990000"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -926,7 +1124,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'🟢 Primeira'!$R$12:$R$21</f>
+              <f>'🟢 Primeira'!$T$12:$T$21</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -949,13 +1147,12 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Produtos (ordenados por V.T. decrescente)</a:t>
+                  <a:t>Produtos (ordenados por V.T. decrescente — nome do produto no eixo X)</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
         </title>
-        <numFmt formatCode="General" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -1013,7 +1210,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>🇯🇲 CURVA ABC REGGAE — ABA 01 — Curva de Pareto &amp; Classificação ABC</a:t>
+              <a:t>🇯🇲  CURVA ABC REGGAE — ABA 01  —  Curva ABC de Pareto</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1026,71 +1223,15 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <v>🟢 Zona A (≤80%)</v>
+            <v>🟢 Faixa A (≤80%)</v>
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="ADEBAD"/>
+              <a:srgbClr val="A8E6C0"/>
             </a:solidFill>
-            <a:ln w="5000">
+            <a:ln w="6000">
               <a:solidFill>
                 <a:srgbClr val="009B3A"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'🟡 01'!$P$12:$P$31</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'🟡 01'!$S$12:$S$31</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <v>🟡 Zona B (80-95%)</v>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="FFE87C"/>
-            </a:solidFill>
-            <a:ln w="5000">
-              <a:solidFill>
-                <a:srgbClr val="C8A400"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'🟡 01'!$P$12:$P$31</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'🟡 01'!$T$12:$T$31</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <v>🔴 Zona C (95-100%)</v>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="FFAD99"/>
-            </a:solidFill>
-            <a:ln w="5000">
-              <a:solidFill>
-                <a:srgbClr val="990000"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1106,25 +1247,81 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>🟡 Faixa B (80-95%)</v>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFE87C"/>
+            </a:solidFill>
+            <a:ln w="6000">
+              <a:solidFill>
+                <a:srgbClr val="C8A400"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'🟡 01'!$P$12:$P$31</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'🟡 01'!$V$12:$V$31</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>🔴 Faixa C (&gt;95%)</v>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFAD99"/>
+            </a:solidFill>
+            <a:ln w="6000">
+              <a:solidFill>
+                <a:srgbClr val="990000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'🟡 01'!$P$12:$P$31</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'🟡 01'!$W$12:$W$31</f>
+            </numRef>
+          </val>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </areaChart>
       <barChart>
         <barDir val="col"/>
-        <grouping val="clustered"/>
+        <grouping val="stacked"/>
         <ser>
           <idx val="3"/>
           <order val="3"/>
           <tx>
-            <v>📊 % Individual por Produto</v>
+            <v>🟢 Classe A</v>
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="2E75B6"/>
+              <a:srgbClr val="009B3A"/>
             </a:solidFill>
             <a:ln w="8000">
               <a:solidFill>
-                <a:srgbClr val="1A4E8A"/>
+                <a:srgbClr val="006B28"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1137,6 +1334,62 @@
           <val>
             <numRef>
               <f>'🟡 01'!$Q$12:$Q$31</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <v>🟡 Classe B</v>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFD700"/>
+            </a:solidFill>
+            <a:ln w="8000">
+              <a:solidFill>
+                <a:srgbClr val="C8A400"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'🟡 01'!$P$12:$P$31</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'🟡 01'!$R$12:$R$31</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <v>🔴 Classe C</v>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="CC0000"/>
+            </a:solidFill>
+            <a:ln w="8000">
+              <a:solidFill>
+                <a:srgbClr val="990000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'🟡 01'!$P$12:$P$31</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'🟡 01'!$S$12:$S$31</f>
             </numRef>
           </val>
         </ser>
@@ -1153,15 +1406,15 @@
       <lineChart>
         <grouping val="standard"/>
         <ser>
-          <idx val="4"/>
-          <order val="4"/>
+          <idx val="6"/>
+          <order val="6"/>
           <tx>
             <v>📈 % Acumulado (Curva Pareto)</v>
           </tx>
           <spPr>
-            <a:ln w="30000">
+            <a:ln w="28000">
               <a:solidFill>
-                <a:srgbClr val="990000"/>
+                <a:srgbClr val="111111"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1171,11 +1424,11 @@
             <size val="5"/>
             <spPr>
               <a:solidFill>
-                <a:srgbClr val="CC0000"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:ln>
                 <a:solidFill>
-                  <a:srgbClr val="990000"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1188,7 +1441,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'🟡 01'!$R$12:$R$31</f>
+              <f>'🟡 01'!$T$12:$T$31</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -1211,13 +1464,12 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Produtos (ordenados por V.T. decrescente)</a:t>
+                  <a:t>Produtos (ordenados por V.T. decrescente — nome do produto no eixo X)</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
         </title>
-        <numFmt formatCode="General" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -1275,7 +1527,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>🇯🇲 CURVA ABC REGGAE — ABA 02 — Curva de Pareto &amp; Classificação ABC</a:t>
+              <a:t>🇯🇲  CURVA ABC REGGAE — ABA 02  —  Curva ABC de Pareto</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1288,71 +1540,15 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <v>🟢 Zona A (≤80%)</v>
+            <v>🟢 Faixa A (≤80%)</v>
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="ADEBAD"/>
+              <a:srgbClr val="A8E6C0"/>
             </a:solidFill>
-            <a:ln w="5000">
+            <a:ln w="6000">
               <a:solidFill>
                 <a:srgbClr val="009B3A"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'🔴 02'!$P$12:$P$41</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'🔴 02'!$S$12:$S$41</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <v>🟡 Zona B (80-95%)</v>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="FFE87C"/>
-            </a:solidFill>
-            <a:ln w="5000">
-              <a:solidFill>
-                <a:srgbClr val="C8A400"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'🔴 02'!$P$12:$P$41</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'🔴 02'!$T$12:$T$41</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <v>🔴 Zona C (95-100%)</v>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="FFAD99"/>
-            </a:solidFill>
-            <a:ln w="5000">
-              <a:solidFill>
-                <a:srgbClr val="990000"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1368,25 +1564,81 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>🟡 Faixa B (80-95%)</v>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFE87C"/>
+            </a:solidFill>
+            <a:ln w="6000">
+              <a:solidFill>
+                <a:srgbClr val="C8A400"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'🔴 02'!$P$12:$P$41</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'🔴 02'!$V$12:$V$41</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>🔴 Faixa C (&gt;95%)</v>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFAD99"/>
+            </a:solidFill>
+            <a:ln w="6000">
+              <a:solidFill>
+                <a:srgbClr val="990000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'🔴 02'!$P$12:$P$41</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'🔴 02'!$W$12:$W$41</f>
+            </numRef>
+          </val>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </areaChart>
       <barChart>
         <barDir val="col"/>
-        <grouping val="clustered"/>
+        <grouping val="stacked"/>
         <ser>
           <idx val="3"/>
           <order val="3"/>
           <tx>
-            <v>📊 % Individual por Produto</v>
+            <v>🟢 Classe A</v>
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="2E75B6"/>
+              <a:srgbClr val="009B3A"/>
             </a:solidFill>
             <a:ln w="8000">
               <a:solidFill>
-                <a:srgbClr val="1A4E8A"/>
+                <a:srgbClr val="006B28"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1399,6 +1651,62 @@
           <val>
             <numRef>
               <f>'🔴 02'!$Q$12:$Q$41</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <v>🟡 Classe B</v>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFD700"/>
+            </a:solidFill>
+            <a:ln w="8000">
+              <a:solidFill>
+                <a:srgbClr val="C8A400"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'🔴 02'!$P$12:$P$41</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'🔴 02'!$R$12:$R$41</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <v>🔴 Classe C</v>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="CC0000"/>
+            </a:solidFill>
+            <a:ln w="8000">
+              <a:solidFill>
+                <a:srgbClr val="990000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'🔴 02'!$P$12:$P$41</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'🔴 02'!$S$12:$S$41</f>
             </numRef>
           </val>
         </ser>
@@ -1415,15 +1723,15 @@
       <lineChart>
         <grouping val="standard"/>
         <ser>
-          <idx val="4"/>
-          <order val="4"/>
+          <idx val="6"/>
+          <order val="6"/>
           <tx>
             <v>📈 % Acumulado (Curva Pareto)</v>
           </tx>
           <spPr>
-            <a:ln w="30000">
+            <a:ln w="28000">
               <a:solidFill>
-                <a:srgbClr val="990000"/>
+                <a:srgbClr val="111111"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1433,11 +1741,11 @@
             <size val="5"/>
             <spPr>
               <a:solidFill>
-                <a:srgbClr val="CC0000"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:ln>
                 <a:solidFill>
-                  <a:srgbClr val="990000"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1450,7 +1758,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'🔴 02'!$R$12:$R$41</f>
+              <f>'🔴 02'!$T$12:$T$41</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -1473,13 +1781,12 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Produtos (ordenados por V.T. decrescente)</a:t>
+                  <a:t>Produtos (ordenados por V.T. decrescente — nome do produto no eixo X)</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
         </title>
-        <numFmt formatCode="General" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -1533,7 +1840,7 @@
       <row>24</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="11520000" cy="5760000"/>
+    <ext cx="12240000" cy="5760000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1560,7 +1867,7 @@
       <row>34</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="11520000" cy="5760000"/>
+    <ext cx="12240000" cy="5760000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1587,7 +1894,7 @@
       <row>44</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="11520000" cy="5760000"/>
+    <ext cx="12240000" cy="5760000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1895,7 +2202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U22"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1916,12 +2223,14 @@
     <col width="28" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
-    <row r="1" ht="52" customHeight="1">
+    <row r="1" ht="54" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>🇯🇲  CURVA ABC REGGAE — PRIMEIRA  —  One Love, One Excel! ✌️</t>
@@ -1929,22 +2238,28 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>🟢 A=até 80%  |  🟡 B=80-95%  |  🔴 C=95-100%</t>
-        </is>
-      </c>
+          <t>🟢 A = até 80%  |  🟡 B = 80–95%  |  🔴 C = 95–100%</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="n"/>
     </row>
     <row r="2" ht="8" customHeight="1">
-      <c r="A2" s="3" t="n"/>
-      <c r="B2" s="4" t="n"/>
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="3" t="n"/>
       <c r="C2" s="5" t="n"/>
       <c r="D2" s="6" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="3" t="n"/>
       <c r="G2" s="5" t="n"/>
       <c r="H2" s="6" t="n"/>
-      <c r="I2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="26" customHeight="1">
+      <c r="I2" s="4" t="n"/>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="5" t="n"/>
+      <c r="L2" s="6" t="n"/>
+      <c r="M2" s="4" t="n"/>
+      <c r="N2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="24" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>💰 V.T. TOTAL</t>
@@ -1971,7 +2286,7 @@
       <c r="H3" s="8" t="n"/>
       <c r="I3" s="11" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="12">
         <f>SUM($G$12:$G$21)</f>
         <v/>
@@ -1994,10 +2309,10 @@
       <c r="H4" s="13" t="n"/>
       <c r="I4" s="17" t="n"/>
     </row>
-    <row r="5" ht="26" customHeight="1">
+    <row r="5" ht="24" customHeight="1">
       <c r="A5" s="18" t="inlineStr">
         <is>
-          <t>📦 TOTAL ITENS</t>
+          <t>📦 TOTAL DE ITENS</t>
         </is>
       </c>
       <c r="B5" s="13" t="n"/>
@@ -2021,7 +2336,7 @@
       <c r="H5" s="13" t="n"/>
       <c r="I5" s="17" t="n"/>
     </row>
-    <row r="6" ht="30" customHeight="1">
+    <row r="6" ht="32" customHeight="1">
       <c r="A6" s="20">
         <f>COUNTA($D$12:$D$21)</f>
         <v/>
@@ -2046,73 +2361,66 @@
     </row>
     <row r="7" ht="8" customHeight="1">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="3" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="4" t="n"/>
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="5" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="4" t="n"/>
       <c r="H7" s="6" t="n"/>
       <c r="I7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="22" customHeight="1">
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="4" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="3" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  🌿  Edite somente Qtd. (col F) e Custo Unit. (col G)  |  Limites: E9=Classe A (80%)  E10=Classe B (95%)</t>
+          <t xml:space="preserve">  ✏️  Edite somente: Qtd. (col E) e Custo Unit. (col F)  |  Limite A → célula B9  |  Limite B → célula B10  |  As fórmulas V.T., % e ABC recalculam automaticamente</t>
         </is>
       </c>
       <c r="K8" s="27" t="inlineStr">
         <is>
-          <t>Classe</t>
-        </is>
-      </c>
-      <c r="L8" s="27" t="inlineStr">
-        <is>
-          <t>Total V.T.</t>
-        </is>
-      </c>
-      <c r="M8" s="27" t="inlineStr">
-        <is>
-          <t>% Total</t>
-        </is>
-      </c>
-      <c r="N8" s="27" t="inlineStr">
-        <is>
-          <t>Qtd.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="28" t="inlineStr">
-        <is>
-          <t>Limite A:</t>
-        </is>
-      </c>
-      <c r="B9" s="29" t="n">
+          <t>RESUMO POR CLASSE</t>
+        </is>
+      </c>
+      <c r="L8" s="28" t="n"/>
+      <c r="M8" s="28" t="n"/>
+      <c r="N8" s="28" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>Limite A (Classe A):</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="n">
         <v>0.8</v>
       </c>
-      <c r="K9" s="30" t="inlineStr">
+      <c r="K9" s="31" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L9" s="31">
+      <c r="L9" s="32">
         <f>SUMIF($A$12:$A$21,"A",$G$12:$G$21)</f>
         <v/>
       </c>
-      <c r="M9" s="32">
+      <c r="M9" s="33">
         <f>IFERROR(L9/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
-      <c r="N9" s="33">
+      <c r="N9" s="34">
         <f>COUNTIF($A$12:$A$21,"A")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="34" t="inlineStr">
-        <is>
-          <t>Limite B:</t>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>Limite B (Classe B):</t>
         </is>
       </c>
       <c r="B10" s="35" t="n">
@@ -2136,7 +2444,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="26" customHeight="1">
       <c r="A11" s="40" t="inlineStr">
         <is>
           <t>ABC</t>
@@ -2154,7 +2462,7 @@
       </c>
       <c r="D11" s="42" t="inlineStr">
         <is>
-          <t>Descrição do Item</t>
+          <t>Descrição do Produto</t>
         </is>
       </c>
       <c r="E11" s="43" t="inlineStr">
@@ -2206,25 +2514,35 @@
       </c>
       <c r="Q11" s="48" t="inlineStr">
         <is>
-          <t>% Ind</t>
+          <t>%IndA</t>
         </is>
       </c>
       <c r="R11" s="48" t="inlineStr">
         <is>
-          <t>% Acc</t>
+          <t>%IndB</t>
         </is>
       </c>
       <c r="S11" s="48" t="inlineStr">
         <is>
+          <t>%IndC</t>
+        </is>
+      </c>
+      <c r="T11" s="48" t="inlineStr">
+        <is>
+          <t>%Acum.</t>
+        </is>
+      </c>
+      <c r="U11" s="48" t="inlineStr">
+        <is>
           <t>ZonaA</t>
         </is>
       </c>
-      <c r="T11" s="48" t="inlineStr">
+      <c r="V11" s="48" t="inlineStr">
         <is>
           <t>ZonaB</t>
         </is>
       </c>
-      <c r="U11" s="48" t="inlineStr">
+      <c r="W11" s="48" t="inlineStr">
         <is>
           <t>ZonaC</t>
         </is>
@@ -2274,16 +2592,22 @@
       <c r="Q12" s="57" t="n">
         <v>0.37781</v>
       </c>
-      <c r="R12" s="57" t="n">
+      <c r="R12" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="60" t="n">
         <v>0.37781</v>
       </c>
-      <c r="S12" s="58" t="n">
+      <c r="U12" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="T12" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="60" t="n">
+      <c r="V12" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2331,33 +2655,39 @@
       <c r="Q13" s="57" t="n">
         <v>0.22669</v>
       </c>
-      <c r="R13" s="57" t="n">
+      <c r="R13" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="60" t="n">
         <v>0.6045</v>
       </c>
-      <c r="S13" s="58" t="n">
+      <c r="U13" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="T13" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" s="60" t="n">
+      <c r="V13" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="61">
+      <c r="A14" s="64">
         <f>IF($I14&lt;=$B$9,"A",IF($I14&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B14" s="62" t="inlineStr">
+      <c r="B14" s="65" t="inlineStr">
         <is>
           <t>SKU03</t>
         </is>
       </c>
-      <c r="C14" s="62" t="n">
+      <c r="C14" s="65" t="n">
         <v>9</v>
       </c>
-      <c r="D14" s="63" t="inlineStr">
+      <c r="D14" s="66" t="inlineStr">
         <is>
           <t>Notebook Administrativo</t>
         </is>
@@ -2368,53 +2698,59 @@
       <c r="F14" s="53" t="n">
         <v>4500</v>
       </c>
-      <c r="G14" s="64">
+      <c r="G14" s="67">
         <f>IFERROR(E14*F14,0)</f>
         <v/>
       </c>
-      <c r="H14" s="65">
+      <c r="H14" s="68">
         <f>IFERROR(G14/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
-      <c r="I14" s="65">
+      <c r="I14" s="68">
         <f>IFERROR(SUMIF($G$12:$G$21,"&gt;="&amp;G14,$G$12:$G$21)/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
       <c r="P14" s="56" t="inlineStr">
         <is>
-          <t>B — SKU03 — Notebook Administrativ</t>
+          <t>B — SKU03 — Notebook Administrat</t>
         </is>
       </c>
       <c r="Q14" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="58" t="n">
         <v>0.20402</v>
       </c>
-      <c r="R14" s="57" t="n">
+      <c r="S14" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="60" t="n">
         <v>0.80852</v>
       </c>
-      <c r="S14" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" s="59" t="n">
+      <c r="U14" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="U14" s="60" t="n">
+      <c r="W14" s="63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="61">
+      <c r="A15" s="64">
         <f>IF($I15&lt;=$B$9,"A",IF($I15&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B15" s="62" t="inlineStr">
+      <c r="B15" s="65" t="inlineStr">
         <is>
           <t>SKU04</t>
         </is>
       </c>
-      <c r="C15" s="62" t="n">
+      <c r="C15" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="63" t="inlineStr">
+      <c r="D15" s="66" t="inlineStr">
         <is>
           <t>Nobreak Profissional</t>
         </is>
@@ -2425,15 +2761,15 @@
       <c r="F15" s="53" t="n">
         <v>2000</v>
       </c>
-      <c r="G15" s="64">
+      <c r="G15" s="67">
         <f>IFERROR(E15*F15,0)</f>
         <v/>
       </c>
-      <c r="H15" s="65">
+      <c r="H15" s="68">
         <f>IFERROR(G15/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
-      <c r="I15" s="65">
+      <c r="I15" s="68">
         <f>IFERROR(SUMIF($G$12:$G$21,"&gt;="&amp;G15,$G$12:$G$21)/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
@@ -2443,35 +2779,41 @@
         </is>
       </c>
       <c r="Q15" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="58" t="n">
         <v>0.07556</v>
       </c>
-      <c r="R15" s="57" t="n">
+      <c r="S15" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="60" t="n">
         <v>0.88409</v>
       </c>
-      <c r="S15" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="59" t="n">
+      <c r="U15" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="U15" s="60" t="n">
+      <c r="W15" s="63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="61">
+      <c r="A16" s="64">
         <f>IF($I16&lt;=$B$9,"A",IF($I16&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B16" s="62" t="inlineStr">
+      <c r="B16" s="65" t="inlineStr">
         <is>
           <t>SKU05</t>
         </is>
       </c>
-      <c r="C16" s="62" t="n">
+      <c r="C16" s="65" t="n">
         <v>7</v>
       </c>
-      <c r="D16" s="63" t="inlineStr">
+      <c r="D16" s="66" t="inlineStr">
         <is>
           <t>Switch Gerenciavel</t>
         </is>
@@ -2482,15 +2824,15 @@
       <c r="F16" s="53" t="n">
         <v>1500</v>
       </c>
-      <c r="G16" s="64">
+      <c r="G16" s="67">
         <f>IFERROR(E16*F16,0)</f>
         <v/>
       </c>
-      <c r="H16" s="65">
+      <c r="H16" s="68">
         <f>IFERROR(G16/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
-      <c r="I16" s="65">
+      <c r="I16" s="68">
         <f>IFERROR(SUMIF($G$12:$G$21,"&gt;="&amp;G16,$G$12:$G$21)/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
@@ -2500,35 +2842,41 @@
         </is>
       </c>
       <c r="Q16" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="58" t="n">
         <v>0.04534</v>
       </c>
-      <c r="R16" s="57" t="n">
+      <c r="S16" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="60" t="n">
         <v>0.92942</v>
       </c>
-      <c r="S16" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" s="59" t="n">
+      <c r="U16" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="U16" s="60" t="n">
+      <c r="W16" s="63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="66">
+      <c r="A17" s="69">
         <f>IF($I17&lt;=$B$9,"A",IF($I17&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B17" s="67" t="inlineStr">
+      <c r="B17" s="70" t="inlineStr">
         <is>
           <t>SKU06</t>
         </is>
       </c>
-      <c r="C17" s="67" t="n">
+      <c r="C17" s="70" t="n">
         <v>4</v>
       </c>
-      <c r="D17" s="68" t="inlineStr">
+      <c r="D17" s="71" t="inlineStr">
         <is>
           <t>Mouse sem fio</t>
         </is>
@@ -2539,15 +2887,15 @@
       <c r="F17" s="53" t="n">
         <v>50</v>
       </c>
-      <c r="G17" s="69">
+      <c r="G17" s="72">
         <f>IFERROR(E17*F17,0)</f>
         <v/>
       </c>
-      <c r="H17" s="70">
+      <c r="H17" s="73">
         <f>IFERROR(G17/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
-      <c r="I17" s="70">
+      <c r="I17" s="73">
         <f>IFERROR(SUMIF($G$12:$G$21,"&gt;="&amp;G17,$G$12:$G$21)/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
@@ -2557,35 +2905,41 @@
         </is>
       </c>
       <c r="Q17" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="59" t="n">
         <v>0.02116</v>
       </c>
-      <c r="R17" s="57" t="n">
+      <c r="T17" s="60" t="n">
         <v>0.95058</v>
       </c>
-      <c r="S17" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" s="60" t="n">
+      <c r="U17" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" s="63" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="66">
+      <c r="A18" s="69">
         <f>IF($I18&lt;=$B$9,"A",IF($I18&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B18" s="67" t="inlineStr">
+      <c r="B18" s="70" t="inlineStr">
         <is>
           <t>SKU07</t>
         </is>
       </c>
-      <c r="C18" s="67" t="n">
+      <c r="C18" s="70" t="n">
         <v>8</v>
       </c>
-      <c r="D18" s="68" t="inlineStr">
+      <c r="D18" s="71" t="inlineStr">
         <is>
           <t>Patch Cord 1m</t>
         </is>
@@ -2596,15 +2950,15 @@
       <c r="F18" s="53" t="n">
         <v>15</v>
       </c>
-      <c r="G18" s="69">
+      <c r="G18" s="72">
         <f>IFERROR(E18*F18,0)</f>
         <v/>
       </c>
-      <c r="H18" s="70">
+      <c r="H18" s="73">
         <f>IFERROR(G18/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
-      <c r="I18" s="70">
+      <c r="I18" s="73">
         <f>IFERROR(SUMIF($G$12:$G$21,"&gt;="&amp;G18,$G$12:$G$21)/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
@@ -2614,35 +2968,41 @@
         </is>
       </c>
       <c r="Q18" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="59" t="n">
         <v>0.01511</v>
       </c>
-      <c r="R18" s="57" t="n">
+      <c r="T18" s="60" t="n">
         <v>0.96569</v>
       </c>
-      <c r="S18" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" s="60" t="n">
+      <c r="U18" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" s="63" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="66">
+      <c r="A19" s="69">
         <f>IF($I19&lt;=$B$9,"A",IF($I19&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B19" s="67" t="inlineStr">
+      <c r="B19" s="70" t="inlineStr">
         <is>
           <t>SKU08</t>
         </is>
       </c>
-      <c r="C19" s="67" t="n">
+      <c r="C19" s="70" t="n">
         <v>6</v>
       </c>
-      <c r="D19" s="68" t="inlineStr">
+      <c r="D19" s="71" t="inlineStr">
         <is>
           <t>Teclado USB</t>
         </is>
@@ -2653,15 +3013,15 @@
       <c r="F19" s="53" t="n">
         <v>35</v>
       </c>
-      <c r="G19" s="69">
+      <c r="G19" s="72">
         <f>IFERROR(E19*F19,0)</f>
         <v/>
       </c>
-      <c r="H19" s="70">
+      <c r="H19" s="73">
         <f>IFERROR(G19/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
-      <c r="I19" s="70">
+      <c r="I19" s="73">
         <f>IFERROR(SUMIF($G$12:$G$21,"&gt;="&amp;G19,$G$12:$G$21)/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
@@ -2671,35 +3031,41 @@
         </is>
       </c>
       <c r="Q19" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="59" t="n">
         <v>0.01209</v>
       </c>
-      <c r="R19" s="57" t="n">
+      <c r="T19" s="60" t="n">
         <v>0.97778</v>
       </c>
-      <c r="S19" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" s="60" t="n">
+      <c r="U19" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" s="63" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="66">
+      <c r="A20" s="69">
         <f>IF($I20&lt;=$B$9,"A",IF($I20&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B20" s="67" t="inlineStr">
+      <c r="B20" s="70" t="inlineStr">
         <is>
           <t>SKU09</t>
         </is>
       </c>
-      <c r="C20" s="67" t="n">
+      <c r="C20" s="70" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="68" t="inlineStr">
+      <c r="D20" s="71" t="inlineStr">
         <is>
           <t>Cabo Rede Cat6 (m)</t>
         </is>
@@ -2710,15 +3076,15 @@
       <c r="F20" s="53" t="n">
         <v>8</v>
       </c>
-      <c r="G20" s="69">
+      <c r="G20" s="72">
         <f>IFERROR(E20*F20,0)</f>
         <v/>
       </c>
-      <c r="H20" s="70">
+      <c r="H20" s="73">
         <f>IFERROR(G20/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
-      <c r="I20" s="70">
+      <c r="I20" s="73">
         <f>IFERROR(SUMIF($G$12:$G$21,"&gt;="&amp;G20,$G$12:$G$21)/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
@@ -2728,35 +3094,41 @@
         </is>
       </c>
       <c r="Q20" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="59" t="n">
         <v>0.01133</v>
       </c>
-      <c r="R20" s="57" t="n">
+      <c r="T20" s="60" t="n">
         <v>0.98912</v>
       </c>
-      <c r="S20" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" s="60" t="n">
+      <c r="U20" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="63" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="66">
+      <c r="A21" s="69">
         <f>IF($I21&lt;=$B$9,"A",IF($I21&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B21" s="67" t="inlineStr">
+      <c r="B21" s="70" t="inlineStr">
         <is>
           <t>SKU10</t>
         </is>
       </c>
-      <c r="C21" s="67" t="n">
+      <c r="C21" s="70" t="n">
         <v>10</v>
       </c>
-      <c r="D21" s="68" t="inlineStr">
+      <c r="D21" s="71" t="inlineStr">
         <is>
           <t>Mousepad Slim</t>
         </is>
@@ -2767,15 +3139,15 @@
       <c r="F21" s="53" t="n">
         <v>12</v>
       </c>
-      <c r="G21" s="69">
+      <c r="G21" s="72">
         <f>IFERROR(E21*F21,0)</f>
         <v/>
       </c>
-      <c r="H21" s="70">
+      <c r="H21" s="73">
         <f>IFERROR(G21/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
-      <c r="I21" s="70">
+      <c r="I21" s="73">
         <f>IFERROR(SUMIF($G$12:$G$21,"&gt;="&amp;G21,$G$12:$G$21)/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
@@ -2785,49 +3157,55 @@
         </is>
       </c>
       <c r="Q21" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="59" t="n">
         <v>0.01088</v>
       </c>
-      <c r="R21" s="57" t="n">
+      <c r="T21" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="S21" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" s="60" t="n">
+      <c r="U21" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" s="63" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="71" t="inlineStr">
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="74" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B22" s="72" t="n"/>
-      <c r="C22" s="72" t="n"/>
-      <c r="D22" s="72" t="n"/>
-      <c r="E22" s="73">
+      <c r="B22" s="75" t="n"/>
+      <c r="C22" s="75" t="n"/>
+      <c r="D22" s="75" t="n"/>
+      <c r="E22" s="76">
         <f>SUM(E12:E21)</f>
         <v/>
       </c>
-      <c r="F22" s="74" t="n"/>
-      <c r="G22" s="75">
+      <c r="F22" s="77" t="n"/>
+      <c r="G22" s="78">
         <f>SUM(G12:G21)</f>
         <v/>
       </c>
-      <c r="H22" s="76" t="n">
+      <c r="H22" s="79" t="n">
         <v>1</v>
       </c>
-      <c r="I22" s="76" t="n">
+      <c r="I22" s="79" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="F0B1"/>
-  <mergeCells count="20">
+  <mergeCells count="21">
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="C5:D5"/>
@@ -2846,6 +3224,7 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="K8:N8"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="E3:F3"/>
   </mergeCells>
@@ -2861,11 +3240,11 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="❌ Valor Inválido" error="Limite A: entre 50% e 89%" type="decimal" operator="between">
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="❌ Valor Inválido — Tente Novamente" error="Digite um valor entre 0,50 e 0,89 (ex: 0,80 para 80%)" promptTitle="ℹ️ Dica de Preenchimento" prompt="Digite um percentual decimal (ex: 0,80 para 80%)" type="decimal" operator="between">
       <formula1>0.5</formula1>
-      <formula2>0.89</formula2>
+      <formula2>0.99</formula2>
     </dataValidation>
-    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="❌ Valor Inválido" error="Limite B: entre 50% e 99%" type="decimal" operator="between">
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="❌ Valor Inválido — Tente Novamente" error="Digite um valor entre 0,50 e 0,99 (ex: 0,95 para 95%)" promptTitle="ℹ️ Dica de Preenchimento" prompt="Digite um percentual decimal (ex: 0,80 para 80%)" type="decimal" operator="between">
       <formula1>0.5</formula1>
       <formula2>0.99</formula2>
     </dataValidation>
@@ -2882,7 +3261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:W32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2903,12 +3282,14 @@
     <col width="28" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
-    <row r="1" ht="52" customHeight="1">
+    <row r="1" ht="54" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>🇯🇲  CURVA ABC REGGAE — ABA 01  —  One Love, One Excel! ✌️</t>
@@ -2916,22 +3297,28 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>🟢 A=até 80%  |  🟡 B=80-95%  |  🔴 C=95-100%</t>
-        </is>
-      </c>
+          <t>🟢 A = até 80%  |  🟡 B = 80–95%  |  🔴 C = 95–100%</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="n"/>
     </row>
     <row r="2" ht="8" customHeight="1">
-      <c r="A2" s="3" t="n"/>
-      <c r="B2" s="4" t="n"/>
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="3" t="n"/>
       <c r="C2" s="5" t="n"/>
       <c r="D2" s="6" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="3" t="n"/>
       <c r="G2" s="5" t="n"/>
       <c r="H2" s="6" t="n"/>
-      <c r="I2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="26" customHeight="1">
+      <c r="I2" s="4" t="n"/>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="5" t="n"/>
+      <c r="L2" s="6" t="n"/>
+      <c r="M2" s="4" t="n"/>
+      <c r="N2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="24" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>💰 V.T. TOTAL</t>
@@ -2958,7 +3345,7 @@
       <c r="H3" s="8" t="n"/>
       <c r="I3" s="11" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="12">
         <f>SUM($G$12:$G$31)</f>
         <v/>
@@ -2981,10 +3368,10 @@
       <c r="H4" s="13" t="n"/>
       <c r="I4" s="17" t="n"/>
     </row>
-    <row r="5" ht="26" customHeight="1">
+    <row r="5" ht="24" customHeight="1">
       <c r="A5" s="18" t="inlineStr">
         <is>
-          <t>📦 TOTAL ITENS</t>
+          <t>📦 TOTAL DE ITENS</t>
         </is>
       </c>
       <c r="B5" s="13" t="n"/>
@@ -3008,7 +3395,7 @@
       <c r="H5" s="13" t="n"/>
       <c r="I5" s="17" t="n"/>
     </row>
-    <row r="6" ht="30" customHeight="1">
+    <row r="6" ht="32" customHeight="1">
       <c r="A6" s="20">
         <f>COUNTA($D$12:$D$31)</f>
         <v/>
@@ -3033,73 +3420,66 @@
     </row>
     <row r="7" ht="8" customHeight="1">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="3" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="4" t="n"/>
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="5" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="4" t="n"/>
       <c r="H7" s="6" t="n"/>
       <c r="I7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="22" customHeight="1">
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="4" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="3" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  🌿  Edite somente Qtd. (col F) e Custo Unit. (col G)  |  Limites: E9=Classe A (80%)  E10=Classe B (95%)</t>
+          <t xml:space="preserve">  ✏️  Edite somente: Qtd. (col E) e Custo Unit. (col F)  |  Limite A → célula B9  |  Limite B → célula B10  |  As fórmulas V.T., % e ABC recalculam automaticamente</t>
         </is>
       </c>
       <c r="K8" s="27" t="inlineStr">
         <is>
-          <t>Classe</t>
-        </is>
-      </c>
-      <c r="L8" s="27" t="inlineStr">
-        <is>
-          <t>Total V.T.</t>
-        </is>
-      </c>
-      <c r="M8" s="27" t="inlineStr">
-        <is>
-          <t>% Total</t>
-        </is>
-      </c>
-      <c r="N8" s="27" t="inlineStr">
-        <is>
-          <t>Qtd.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="28" t="inlineStr">
-        <is>
-          <t>Limite A:</t>
-        </is>
-      </c>
-      <c r="B9" s="29" t="n">
+          <t>RESUMO POR CLASSE</t>
+        </is>
+      </c>
+      <c r="L8" s="28" t="n"/>
+      <c r="M8" s="28" t="n"/>
+      <c r="N8" s="28" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>Limite A (Classe A):</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="n">
         <v>0.8</v>
       </c>
-      <c r="K9" s="30" t="inlineStr">
+      <c r="K9" s="31" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L9" s="31">
+      <c r="L9" s="32">
         <f>SUMIF($A$12:$A$31,"A",$G$12:$G$31)</f>
         <v/>
       </c>
-      <c r="M9" s="32">
+      <c r="M9" s="33">
         <f>IFERROR(L9/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="N9" s="33">
+      <c r="N9" s="34">
         <f>COUNTIF($A$12:$A$31,"A")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="34" t="inlineStr">
-        <is>
-          <t>Limite B:</t>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>Limite B (Classe B):</t>
         </is>
       </c>
       <c r="B10" s="35" t="n">
@@ -3123,7 +3503,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="26" customHeight="1">
       <c r="A11" s="40" t="inlineStr">
         <is>
           <t>ABC</t>
@@ -3141,7 +3521,7 @@
       </c>
       <c r="D11" s="42" t="inlineStr">
         <is>
-          <t>Descrição do Item</t>
+          <t>Descrição do Produto</t>
         </is>
       </c>
       <c r="E11" s="43" t="inlineStr">
@@ -3193,25 +3573,35 @@
       </c>
       <c r="Q11" s="48" t="inlineStr">
         <is>
-          <t>% Ind</t>
+          <t>%IndA</t>
         </is>
       </c>
       <c r="R11" s="48" t="inlineStr">
         <is>
-          <t>% Acc</t>
+          <t>%IndB</t>
         </is>
       </c>
       <c r="S11" s="48" t="inlineStr">
         <is>
+          <t>%IndC</t>
+        </is>
+      </c>
+      <c r="T11" s="48" t="inlineStr">
+        <is>
+          <t>%Acum.</t>
+        </is>
+      </c>
+      <c r="U11" s="48" t="inlineStr">
+        <is>
           <t>ZonaA</t>
         </is>
       </c>
-      <c r="T11" s="48" t="inlineStr">
+      <c r="V11" s="48" t="inlineStr">
         <is>
           <t>ZonaB</t>
         </is>
       </c>
-      <c r="U11" s="48" t="inlineStr">
+      <c r="W11" s="48" t="inlineStr">
         <is>
           <t>ZonaC</t>
         </is>
@@ -3255,22 +3645,28 @@
       </c>
       <c r="P12" s="56" t="inlineStr">
         <is>
-          <t>A — SKU01 — Notebook Executivo i7</t>
+          <t>A — SKU01 — Notebook Executivo i</t>
         </is>
       </c>
       <c r="Q12" s="57" t="n">
         <v>0.35308</v>
       </c>
-      <c r="R12" s="57" t="n">
+      <c r="R12" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="60" t="n">
         <v>0.35308</v>
       </c>
-      <c r="S12" s="58" t="n">
+      <c r="U12" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="T12" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="60" t="n">
+      <c r="V12" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3312,22 +3708,28 @@
       </c>
       <c r="P13" s="56" t="inlineStr">
         <is>
-          <t>A — SKU02 — Servidor de Dados Pro</t>
+          <t>A — SKU02 — Servidor de Dados Pr</t>
         </is>
       </c>
       <c r="Q13" s="57" t="n">
         <v>0.27936</v>
       </c>
-      <c r="R13" s="57" t="n">
+      <c r="R13" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="60" t="n">
         <v>0.63243</v>
       </c>
-      <c r="S13" s="58" t="n">
+      <c r="U13" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="T13" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" s="60" t="n">
+      <c r="V13" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3369,22 +3771,28 @@
       </c>
       <c r="P14" s="56" t="inlineStr">
         <is>
-          <t>A — SKU03 — Impressora Multifuncio</t>
+          <t>A — SKU03 — Impressora Multifunc</t>
         </is>
       </c>
       <c r="Q14" s="57" t="n">
         <v>0.0939</v>
       </c>
-      <c r="R14" s="57" t="n">
+      <c r="R14" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="60" t="n">
         <v>0.72633</v>
       </c>
-      <c r="S14" s="58" t="n">
+      <c r="U14" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" s="60" t="n">
+      <c r="V14" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3426,39 +3834,45 @@
       </c>
       <c r="P15" s="56" t="inlineStr">
         <is>
-          <t>A — SKU04 — Toner Impressora Laser</t>
+          <t>A — SKU04 — Toner Impressora Las</t>
         </is>
       </c>
       <c r="Q15" s="57" t="n">
         <v>0.07176</v>
       </c>
-      <c r="R15" s="57" t="n">
+      <c r="R15" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="60" t="n">
         <v>0.79809</v>
       </c>
-      <c r="S15" s="58" t="n">
+      <c r="U15" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="T15" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" s="60" t="n">
+      <c r="V15" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" s="63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="61">
+      <c r="A16" s="64">
         <f>IF($I16&lt;=$B$9,"A",IF($I16&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B16" s="62" t="inlineStr">
+      <c r="B16" s="65" t="inlineStr">
         <is>
           <t>SKU05</t>
         </is>
       </c>
-      <c r="C16" s="62" t="n">
+      <c r="C16" s="65" t="n">
         <v>19</v>
       </c>
-      <c r="D16" s="63" t="inlineStr">
+      <c r="D16" s="66" t="inlineStr">
         <is>
           <t>Memoria RAM 16GB</t>
         </is>
@@ -3469,15 +3883,15 @@
       <c r="F16" s="53" t="n">
         <v>380</v>
       </c>
-      <c r="G16" s="64">
+      <c r="G16" s="67">
         <f>IFERROR(E16*F16,0)</f>
         <v/>
       </c>
-      <c r="H16" s="65">
+      <c r="H16" s="68">
         <f>IFERROR(G16/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="I16" s="65">
+      <c r="I16" s="68">
         <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G16,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
@@ -3487,35 +3901,41 @@
         </is>
       </c>
       <c r="Q16" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="58" t="n">
         <v>0.02654</v>
       </c>
-      <c r="R16" s="57" t="n">
+      <c r="S16" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="60" t="n">
         <v>0.82463</v>
       </c>
-      <c r="S16" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" s="59" t="n">
+      <c r="U16" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="U16" s="60" t="n">
+      <c r="W16" s="63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="61">
+      <c r="A17" s="64">
         <f>IF($I17&lt;=$B$9,"A",IF($I17&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B17" s="62" t="inlineStr">
+      <c r="B17" s="65" t="inlineStr">
         <is>
           <t>SKU06</t>
         </is>
       </c>
-      <c r="C17" s="62" t="n">
+      <c r="C17" s="65" t="n">
         <v>4</v>
       </c>
-      <c r="D17" s="63" t="inlineStr">
+      <c r="D17" s="66" t="inlineStr">
         <is>
           <t>Monitor LED 24"</t>
         </is>
@@ -3526,15 +3946,15 @@
       <c r="F17" s="53" t="n">
         <v>850</v>
       </c>
-      <c r="G17" s="64">
+      <c r="G17" s="67">
         <f>IFERROR(E17*F17,0)</f>
         <v/>
       </c>
-      <c r="H17" s="65">
+      <c r="H17" s="68">
         <f>IFERROR(G17/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="I17" s="65">
+      <c r="I17" s="68">
         <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G17,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
@@ -3544,35 +3964,41 @@
         </is>
       </c>
       <c r="Q17" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="58" t="n">
         <v>0.02638</v>
       </c>
-      <c r="R17" s="57" t="n">
+      <c r="S17" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="60" t="n">
         <v>0.85102</v>
       </c>
-      <c r="S17" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" s="59" t="n">
+      <c r="U17" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="U17" s="60" t="n">
+      <c r="W17" s="63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="61">
+      <c r="A18" s="64">
         <f>IF($I18&lt;=$B$9,"A",IF($I18&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B18" s="62" t="inlineStr">
+      <c r="B18" s="65" t="inlineStr">
         <is>
           <t>SKU07</t>
         </is>
       </c>
-      <c r="C18" s="62" t="n">
+      <c r="C18" s="65" t="n">
         <v>14</v>
       </c>
-      <c r="D18" s="63" t="inlineStr">
+      <c r="D18" s="66" t="inlineStr">
         <is>
           <t>Webcam Full HD</t>
         </is>
@@ -3583,15 +4009,15 @@
       <c r="F18" s="53" t="n">
         <v>180</v>
       </c>
-      <c r="G18" s="64">
+      <c r="G18" s="67">
         <f>IFERROR(E18*F18,0)</f>
         <v/>
       </c>
-      <c r="H18" s="65">
+      <c r="H18" s="68">
         <f>IFERROR(G18/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="I18" s="65">
+      <c r="I18" s="68">
         <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G18,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
@@ -3601,35 +4027,41 @@
         </is>
       </c>
       <c r="Q18" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="58" t="n">
         <v>0.02291</v>
       </c>
-      <c r="R18" s="57" t="n">
+      <c r="S18" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="60" t="n">
         <v>0.87392</v>
       </c>
-      <c r="S18" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="59" t="n">
+      <c r="U18" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="U18" s="60" t="n">
+      <c r="W18" s="63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="61">
+      <c r="A19" s="64">
         <f>IF($I19&lt;=$B$9,"A",IF($I19&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B19" s="62" t="inlineStr">
+      <c r="B19" s="65" t="inlineStr">
         <is>
           <t>SKU08</t>
         </is>
       </c>
-      <c r="C19" s="62" t="n">
+      <c r="C19" s="65" t="n">
         <v>11</v>
       </c>
-      <c r="D19" s="63" t="inlineStr">
+      <c r="D19" s="66" t="inlineStr">
         <is>
           <t>Roteador Wi-Fi 6</t>
         </is>
@@ -3640,15 +4072,15 @@
       <c r="F19" s="53" t="n">
         <v>650</v>
       </c>
-      <c r="G19" s="64">
+      <c r="G19" s="67">
         <f>IFERROR(E19*F19,0)</f>
         <v/>
       </c>
-      <c r="H19" s="65">
+      <c r="H19" s="68">
         <f>IFERROR(G19/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="I19" s="65">
+      <c r="I19" s="68">
         <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G19,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
@@ -3658,35 +4090,41 @@
         </is>
       </c>
       <c r="Q19" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="58" t="n">
         <v>0.01622</v>
       </c>
-      <c r="R19" s="57" t="n">
+      <c r="S19" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="60" t="n">
         <v>0.89014</v>
       </c>
-      <c r="S19" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="59" t="n">
+      <c r="U19" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="U19" s="60" t="n">
+      <c r="W19" s="63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="61">
+      <c r="A20" s="64">
         <f>IF($I20&lt;=$B$9,"A",IF($I20&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B20" s="62" t="inlineStr">
+      <c r="B20" s="65" t="inlineStr">
         <is>
           <t>SKU09</t>
         </is>
       </c>
-      <c r="C20" s="62" t="n">
+      <c r="C20" s="65" t="n">
         <v>15</v>
       </c>
-      <c r="D20" s="63" t="inlineStr">
+      <c r="D20" s="66" t="inlineStr">
         <is>
           <t>SSD 480GB Sata</t>
         </is>
@@ -3697,15 +4135,15 @@
       <c r="F20" s="53" t="n">
         <v>190</v>
       </c>
-      <c r="G20" s="64">
+      <c r="G20" s="67">
         <f>IFERROR(E20*F20,0)</f>
         <v/>
       </c>
-      <c r="H20" s="65">
+      <c r="H20" s="68">
         <f>IFERROR(G20/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="I20" s="65">
+      <c r="I20" s="68">
         <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G20,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
@@ -3715,35 +4153,41 @@
         </is>
       </c>
       <c r="Q20" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="58" t="n">
         <v>0.01513</v>
       </c>
-      <c r="R20" s="57" t="n">
+      <c r="S20" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="60" t="n">
         <v>0.90527</v>
       </c>
-      <c r="S20" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="59" t="n">
+      <c r="U20" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="U20" s="60" t="n">
+      <c r="W20" s="63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="61">
+      <c r="A21" s="64">
         <f>IF($I21&lt;=$B$9,"A",IF($I21&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B21" s="62" t="inlineStr">
+      <c r="B21" s="65" t="inlineStr">
         <is>
           <t>SKU10</t>
         </is>
       </c>
-      <c r="C21" s="62" t="n">
+      <c r="C21" s="65" t="n">
         <v>6</v>
       </c>
-      <c r="D21" s="63" t="inlineStr">
+      <c r="D21" s="66" t="inlineStr">
         <is>
           <t>Nobreak 1500VA</t>
         </is>
@@ -3754,15 +4198,15 @@
       <c r="F21" s="53" t="n">
         <v>1200</v>
       </c>
-      <c r="G21" s="64">
+      <c r="G21" s="67">
         <f>IFERROR(E21*F21,0)</f>
         <v/>
       </c>
-      <c r="H21" s="65">
+      <c r="H21" s="68">
         <f>IFERROR(G21/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="I21" s="65">
+      <c r="I21" s="68">
         <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G21,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
@@ -3772,35 +4216,41 @@
         </is>
       </c>
       <c r="Q21" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="58" t="n">
         <v>0.0149</v>
       </c>
-      <c r="R21" s="57" t="n">
+      <c r="S21" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="60" t="n">
         <v>0.92017</v>
       </c>
-      <c r="S21" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="59" t="n">
+      <c r="U21" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="U21" s="60" t="n">
+      <c r="W21" s="63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="61">
+      <c r="A22" s="64">
         <f>IF($I22&lt;=$B$9,"A",IF($I22&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B22" s="62" t="inlineStr">
+      <c r="B22" s="65" t="inlineStr">
         <is>
           <t>SKU11</t>
         </is>
       </c>
-      <c r="C22" s="62" t="n">
+      <c r="C22" s="65" t="n">
         <v>20</v>
       </c>
-      <c r="D22" s="63" t="inlineStr">
+      <c r="D22" s="66" t="inlineStr">
         <is>
           <t>HD Externo 2TB</t>
         </is>
@@ -3811,15 +4261,15 @@
       <c r="F22" s="53" t="n">
         <v>420</v>
       </c>
-      <c r="G22" s="64">
+      <c r="G22" s="67">
         <f>IFERROR(E22*F22,0)</f>
         <v/>
       </c>
-      <c r="H22" s="65">
+      <c r="H22" s="68">
         <f>IFERROR(G22/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="I22" s="65">
+      <c r="I22" s="68">
         <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G22,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
@@ -3829,35 +4279,41 @@
         </is>
       </c>
       <c r="Q22" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="58" t="n">
         <v>0.01173</v>
       </c>
-      <c r="R22" s="57" t="n">
+      <c r="S22" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="60" t="n">
         <v>0.93191</v>
       </c>
-      <c r="S22" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" s="59" t="n">
+      <c r="U22" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="U22" s="60" t="n">
+      <c r="W22" s="63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="61">
+      <c r="A23" s="64">
         <f>IF($I23&lt;=$B$9,"A",IF($I23&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B23" s="62" t="inlineStr">
+      <c r="B23" s="65" t="inlineStr">
         <is>
           <t>SKU12</t>
         </is>
       </c>
-      <c r="C23" s="62" t="n">
+      <c r="C23" s="65" t="n">
         <v>5</v>
       </c>
-      <c r="D23" s="63" t="inlineStr">
+      <c r="D23" s="66" t="inlineStr">
         <is>
           <t>Teclado Mecanico RGB</t>
         </is>
@@ -3868,15 +4324,15 @@
       <c r="F23" s="53" t="n">
         <v>250</v>
       </c>
-      <c r="G23" s="64">
+      <c r="G23" s="67">
         <f>IFERROR(E23*F23,0)</f>
         <v/>
       </c>
-      <c r="H23" s="65">
+      <c r="H23" s="68">
         <f>IFERROR(G23/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="I23" s="65">
+      <c r="I23" s="68">
         <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G23,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
@@ -3886,35 +4342,41 @@
         </is>
       </c>
       <c r="Q23" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="58" t="n">
         <v>0.01164</v>
       </c>
-      <c r="R23" s="57" t="n">
+      <c r="S23" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="60" t="n">
         <v>0.94354</v>
       </c>
-      <c r="S23" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" s="59" t="n">
+      <c r="U23" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="U23" s="60" t="n">
+      <c r="W23" s="63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="66">
+      <c r="A24" s="69">
         <f>IF($I24&lt;=$B$9,"A",IF($I24&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B24" s="67" t="inlineStr">
+      <c r="B24" s="70" t="inlineStr">
         <is>
           <t>SKU13</t>
         </is>
       </c>
-      <c r="C24" s="67" t="n">
+      <c r="C24" s="70" t="n">
         <v>9</v>
       </c>
-      <c r="D24" s="68" t="inlineStr">
+      <c r="D24" s="71" t="inlineStr">
         <is>
           <t>Pen Drive 64GB</t>
         </is>
@@ -3925,15 +4387,15 @@
       <c r="F24" s="53" t="n">
         <v>45</v>
       </c>
-      <c r="G24" s="69">
+      <c r="G24" s="72">
         <f>IFERROR(E24*F24,0)</f>
         <v/>
       </c>
-      <c r="H24" s="70">
+      <c r="H24" s="73">
         <f>IFERROR(G24/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="I24" s="70">
+      <c r="I24" s="73">
         <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G24,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
@@ -3943,35 +4405,41 @@
         </is>
       </c>
       <c r="Q24" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="59" t="n">
         <v>0.01117</v>
       </c>
-      <c r="R24" s="57" t="n">
+      <c r="T24" s="60" t="n">
         <v>0.95472</v>
       </c>
-      <c r="S24" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" s="60" t="n">
+      <c r="U24" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" s="63" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="66">
+      <c r="A25" s="69">
         <f>IF($I25&lt;=$B$9,"A",IF($I25&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B25" s="67" t="inlineStr">
+      <c r="B25" s="70" t="inlineStr">
         <is>
           <t>SKU14</t>
         </is>
       </c>
-      <c r="C25" s="67" t="n">
+      <c r="C25" s="70" t="n">
         <v>13</v>
       </c>
-      <c r="D25" s="68" t="inlineStr">
+      <c r="D25" s="71" t="inlineStr">
         <is>
           <t>Headset com Microfone</t>
         </is>
@@ -3982,53 +4450,59 @@
       <c r="F25" s="53" t="n">
         <v>110</v>
       </c>
-      <c r="G25" s="69">
+      <c r="G25" s="72">
         <f>IFERROR(E25*F25,0)</f>
         <v/>
       </c>
-      <c r="H25" s="70">
+      <c r="H25" s="73">
         <f>IFERROR(G25/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="I25" s="70">
+      <c r="I25" s="73">
         <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G25,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P25" s="56" t="inlineStr">
         <is>
-          <t>C — SKU14 — Headset com Microfone</t>
+          <t>C — SKU14 — Headset com Microfon</t>
         </is>
       </c>
       <c r="Q25" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="59" t="n">
         <v>0.01093</v>
       </c>
-      <c r="R25" s="57" t="n">
+      <c r="T25" s="60" t="n">
         <v>0.96565</v>
       </c>
-      <c r="S25" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" s="60" t="n">
+      <c r="U25" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" s="63" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="66">
+      <c r="A26" s="69">
         <f>IF($I26&lt;=$B$9,"A",IF($I26&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B26" s="67" t="inlineStr">
+      <c r="B26" s="70" t="inlineStr">
         <is>
           <t>SKU15</t>
         </is>
       </c>
-      <c r="C26" s="67" t="n">
+      <c r="C26" s="70" t="n">
         <v>7</v>
       </c>
-      <c r="D26" s="68" t="inlineStr">
+      <c r="D26" s="71" t="inlineStr">
         <is>
           <t>Pacote de Papel A4</t>
         </is>
@@ -4039,15 +4513,15 @@
       <c r="F26" s="53" t="n">
         <v>28</v>
       </c>
-      <c r="G26" s="69">
+      <c r="G26" s="72">
         <f>IFERROR(E26*F26,0)</f>
         <v/>
       </c>
-      <c r="H26" s="70">
+      <c r="H26" s="73">
         <f>IFERROR(G26/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="I26" s="70">
+      <c r="I26" s="73">
         <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G26,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
@@ -4057,35 +4531,41 @@
         </is>
       </c>
       <c r="Q26" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="59" t="n">
         <v>0.0103</v>
       </c>
-      <c r="R26" s="57" t="n">
+      <c r="T26" s="60" t="n">
         <v>0.97594</v>
       </c>
-      <c r="S26" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" s="60" t="n">
+      <c r="U26" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" s="63" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="66">
+      <c r="A27" s="69">
         <f>IF($I27&lt;=$B$9,"A",IF($I27&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B27" s="67" t="inlineStr">
+      <c r="B27" s="70" t="inlineStr">
         <is>
           <t>SKU16</t>
         </is>
       </c>
-      <c r="C27" s="67" t="n">
+      <c r="C27" s="70" t="n">
         <v>18</v>
       </c>
-      <c r="D27" s="68" t="inlineStr">
+      <c r="D27" s="71" t="inlineStr">
         <is>
           <t>Filtro de Linha 5 Tom.</t>
         </is>
@@ -4096,53 +4576,59 @@
       <c r="F27" s="53" t="n">
         <v>40</v>
       </c>
-      <c r="G27" s="69">
+      <c r="G27" s="72">
         <f>IFERROR(E27*F27,0)</f>
         <v/>
       </c>
-      <c r="H27" s="70">
+      <c r="H27" s="73">
         <f>IFERROR(G27/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="I27" s="70">
+      <c r="I27" s="73">
         <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G27,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P27" s="56" t="inlineStr">
         <is>
-          <t>C — SKU16 — Filtro de Linha 5 Tom.</t>
+          <t>C — SKU16 — Filtro de Linha 5 To</t>
         </is>
       </c>
       <c r="Q27" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="59" t="n">
         <v>0.00683</v>
       </c>
-      <c r="R27" s="57" t="n">
+      <c r="T27" s="60" t="n">
         <v>0.98277</v>
       </c>
-      <c r="S27" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" s="60" t="n">
+      <c r="U27" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" s="63" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="66">
+      <c r="A28" s="69">
         <f>IF($I28&lt;=$B$9,"A",IF($I28&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B28" s="67" t="inlineStr">
+      <c r="B28" s="70" t="inlineStr">
         <is>
           <t>SKU17</t>
         </is>
       </c>
-      <c r="C28" s="67" t="n">
+      <c r="C28" s="70" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="68" t="inlineStr">
+      <c r="D28" s="71" t="inlineStr">
         <is>
           <t>Cabo HDMI 2m</t>
         </is>
@@ -4153,15 +4639,15 @@
       <c r="F28" s="53" t="n">
         <v>25</v>
       </c>
-      <c r="G28" s="69">
+      <c r="G28" s="72">
         <f>IFERROR(E28*F28,0)</f>
         <v/>
       </c>
-      <c r="H28" s="70">
+      <c r="H28" s="73">
         <f>IFERROR(G28/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="I28" s="70">
+      <c r="I28" s="73">
         <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G28,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
@@ -4171,35 +4657,41 @@
         </is>
       </c>
       <c r="Q28" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="59" t="n">
         <v>0.00582</v>
       </c>
-      <c r="R28" s="57" t="n">
+      <c r="T28" s="60" t="n">
         <v>0.98859</v>
       </c>
-      <c r="S28" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" s="60" t="n">
+      <c r="U28" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" s="63" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="66">
+      <c r="A29" s="69">
         <f>IF($I29&lt;=$B$9,"A",IF($I29&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B29" s="67" t="inlineStr">
+      <c r="B29" s="70" t="inlineStr">
         <is>
           <t>SKU18</t>
         </is>
       </c>
-      <c r="C29" s="67" t="n">
+      <c r="C29" s="70" t="n">
         <v>16</v>
       </c>
-      <c r="D29" s="68" t="inlineStr">
+      <c r="D29" s="71" t="inlineStr">
         <is>
           <t>Adaptador USB-C</t>
         </is>
@@ -4210,15 +4702,15 @@
       <c r="F29" s="53" t="n">
         <v>35</v>
       </c>
-      <c r="G29" s="69">
+      <c r="G29" s="72">
         <f>IFERROR(E29*F29,0)</f>
         <v/>
       </c>
-      <c r="H29" s="70">
+      <c r="H29" s="73">
         <f>IFERROR(G29/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="I29" s="70">
+      <c r="I29" s="73">
         <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G29,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
@@ -4228,35 +4720,41 @@
         </is>
       </c>
       <c r="Q29" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="59" t="n">
         <v>0.00489</v>
       </c>
-      <c r="R29" s="57" t="n">
+      <c r="T29" s="60" t="n">
         <v>0.99348</v>
       </c>
-      <c r="S29" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" s="60" t="n">
+      <c r="U29" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" s="63" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="66">
+      <c r="A30" s="69">
         <f>IF($I30&lt;=$B$9,"A",IF($I30&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B30" s="67" t="inlineStr">
+      <c r="B30" s="70" t="inlineStr">
         <is>
           <t>SKU19</t>
         </is>
       </c>
-      <c r="C30" s="67" t="n">
+      <c r="C30" s="70" t="n">
         <v>3</v>
       </c>
-      <c r="D30" s="68" t="inlineStr">
+      <c r="D30" s="71" t="inlineStr">
         <is>
           <t>Mouse Optico Simples</t>
         </is>
@@ -4267,15 +4765,15 @@
       <c r="F30" s="53" t="n">
         <v>15</v>
       </c>
-      <c r="G30" s="69">
+      <c r="G30" s="72">
         <f>IFERROR(E30*F30,0)</f>
         <v/>
       </c>
-      <c r="H30" s="70">
+      <c r="H30" s="73">
         <f>IFERROR(G30/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="I30" s="70">
+      <c r="I30" s="73">
         <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G30,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
@@ -4285,35 +4783,41 @@
         </is>
       </c>
       <c r="Q30" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="59" t="n">
         <v>0.00372</v>
       </c>
-      <c r="R30" s="57" t="n">
+      <c r="T30" s="60" t="n">
         <v>0.99721</v>
       </c>
-      <c r="S30" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" s="60" t="n">
+      <c r="U30" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" s="63" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="66">
+      <c r="A31" s="69">
         <f>IF($I31&lt;=$B$9,"A",IF($I31&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B31" s="67" t="inlineStr">
+      <c r="B31" s="70" t="inlineStr">
         <is>
           <t>SKU20</t>
         </is>
       </c>
-      <c r="C31" s="67" t="n">
+      <c r="C31" s="70" t="n">
         <v>8</v>
       </c>
-      <c r="D31" s="68" t="inlineStr">
+      <c r="D31" s="71" t="inlineStr">
         <is>
           <t>Patch Cord RJ45 1m</t>
         </is>
@@ -4324,15 +4828,15 @@
       <c r="F31" s="53" t="n">
         <v>12</v>
       </c>
-      <c r="G31" s="69">
+      <c r="G31" s="72">
         <f>IFERROR(E31*F31,0)</f>
         <v/>
       </c>
-      <c r="H31" s="70">
+      <c r="H31" s="73">
         <f>IFERROR(G31/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="I31" s="70">
+      <c r="I31" s="73">
         <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G31,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
@@ -4342,49 +4846,55 @@
         </is>
       </c>
       <c r="Q31" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="59" t="n">
         <v>0.00279</v>
       </c>
-      <c r="R31" s="57" t="n">
+      <c r="T31" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="S31" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" s="60" t="n">
+      <c r="U31" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" s="63" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="71" t="inlineStr">
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="74" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B32" s="72" t="n"/>
-      <c r="C32" s="72" t="n"/>
-      <c r="D32" s="72" t="n"/>
-      <c r="E32" s="73">
+      <c r="B32" s="75" t="n"/>
+      <c r="C32" s="75" t="n"/>
+      <c r="D32" s="75" t="n"/>
+      <c r="E32" s="76">
         <f>SUM(E12:E31)</f>
         <v/>
       </c>
-      <c r="F32" s="74" t="n"/>
-      <c r="G32" s="75">
+      <c r="F32" s="77" t="n"/>
+      <c r="G32" s="78">
         <f>SUM(G12:G31)</f>
         <v/>
       </c>
-      <c r="H32" s="76" t="n">
+      <c r="H32" s="79" t="n">
         <v>1</v>
       </c>
-      <c r="I32" s="76" t="n">
+      <c r="I32" s="79" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="F0B1"/>
-  <mergeCells count="20">
+  <mergeCells count="21">
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
@@ -4402,6 +4912,7 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="K8:N8"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="A32:D32"/>
     <mergeCell ref="E3:F3"/>
@@ -4418,11 +4929,11 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="❌ Valor Inválido" error="Limite A: entre 50% e 89%" type="decimal" operator="between">
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="❌ Valor Inválido — Tente Novamente" error="Digite um valor entre 0,50 e 0,89 (ex: 0,80 para 80%)" promptTitle="ℹ️ Dica de Preenchimento" prompt="Digite um percentual decimal (ex: 0,80 para 80%)" type="decimal" operator="between">
       <formula1>0.5</formula1>
-      <formula2>0.89</formula2>
+      <formula2>0.99</formula2>
     </dataValidation>
-    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="❌ Valor Inválido" error="Limite B: entre 50% e 99%" type="decimal" operator="between">
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="❌ Valor Inválido — Tente Novamente" error="Digite um valor entre 0,50 e 0,99 (ex: 0,95 para 95%)" promptTitle="ℹ️ Dica de Preenchimento" prompt="Digite um percentual decimal (ex: 0,80 para 80%)" type="decimal" operator="between">
       <formula1>0.5</formula1>
       <formula2>0.99</formula2>
     </dataValidation>
@@ -4439,7 +4950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U42"/>
+  <dimension ref="A1:W42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4460,12 +4971,14 @@
     <col width="28" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
-    <row r="1" ht="52" customHeight="1">
+    <row r="1" ht="54" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>🇯🇲  CURVA ABC REGGAE — ABA 02  —  One Love, One Excel! ✌️</t>
@@ -4473,22 +4986,28 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>🟢 A=até 80%  |  🟡 B=80-95%  |  🔴 C=95-100%</t>
-        </is>
-      </c>
+          <t>🟢 A = até 80%  |  🟡 B = 80–95%  |  🔴 C = 95–100%</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="n"/>
     </row>
     <row r="2" ht="8" customHeight="1">
-      <c r="A2" s="3" t="n"/>
-      <c r="B2" s="4" t="n"/>
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="3" t="n"/>
       <c r="C2" s="5" t="n"/>
       <c r="D2" s="6" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="3" t="n"/>
       <c r="G2" s="5" t="n"/>
       <c r="H2" s="6" t="n"/>
-      <c r="I2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="26" customHeight="1">
+      <c r="I2" s="4" t="n"/>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="5" t="n"/>
+      <c r="L2" s="6" t="n"/>
+      <c r="M2" s="4" t="n"/>
+      <c r="N2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="24" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>💰 V.T. TOTAL</t>
@@ -4515,7 +5034,7 @@
       <c r="H3" s="8" t="n"/>
       <c r="I3" s="11" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="12">
         <f>SUM($G$12:$G$41)</f>
         <v/>
@@ -4538,10 +5057,10 @@
       <c r="H4" s="13" t="n"/>
       <c r="I4" s="17" t="n"/>
     </row>
-    <row r="5" ht="26" customHeight="1">
+    <row r="5" ht="24" customHeight="1">
       <c r="A5" s="18" t="inlineStr">
         <is>
-          <t>📦 TOTAL ITENS</t>
+          <t>📦 TOTAL DE ITENS</t>
         </is>
       </c>
       <c r="B5" s="13" t="n"/>
@@ -4565,7 +5084,7 @@
       <c r="H5" s="13" t="n"/>
       <c r="I5" s="17" t="n"/>
     </row>
-    <row r="6" ht="30" customHeight="1">
+    <row r="6" ht="32" customHeight="1">
       <c r="A6" s="20">
         <f>COUNTA($D$12:$D$41)</f>
         <v/>
@@ -4590,73 +5109,66 @@
     </row>
     <row r="7" ht="8" customHeight="1">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="3" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="4" t="n"/>
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="5" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="4" t="n"/>
       <c r="H7" s="6" t="n"/>
       <c r="I7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="22" customHeight="1">
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="4" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="3" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  🌿  Edite somente Qtd. (col F) e Custo Unit. (col G)  |  Limites: E9=Classe A (80%)  E10=Classe B (95%)</t>
+          <t xml:space="preserve">  ✏️  Edite somente: Qtd. (col E) e Custo Unit. (col F)  |  Limite A → célula B9  |  Limite B → célula B10  |  As fórmulas V.T., % e ABC recalculam automaticamente</t>
         </is>
       </c>
       <c r="K8" s="27" t="inlineStr">
         <is>
-          <t>Classe</t>
-        </is>
-      </c>
-      <c r="L8" s="27" t="inlineStr">
-        <is>
-          <t>Total V.T.</t>
-        </is>
-      </c>
-      <c r="M8" s="27" t="inlineStr">
-        <is>
-          <t>% Total</t>
-        </is>
-      </c>
-      <c r="N8" s="27" t="inlineStr">
-        <is>
-          <t>Qtd.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="28" t="inlineStr">
-        <is>
-          <t>Limite A:</t>
-        </is>
-      </c>
-      <c r="B9" s="29" t="n">
+          <t>RESUMO POR CLASSE</t>
+        </is>
+      </c>
+      <c r="L8" s="28" t="n"/>
+      <c r="M8" s="28" t="n"/>
+      <c r="N8" s="28" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>Limite A (Classe A):</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="n">
         <v>0.8</v>
       </c>
-      <c r="K9" s="30" t="inlineStr">
+      <c r="K9" s="31" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L9" s="31">
+      <c r="L9" s="32">
         <f>SUMIF($A$12:$A$41,"A",$G$12:$G$41)</f>
         <v/>
       </c>
-      <c r="M9" s="32">
+      <c r="M9" s="33">
         <f>IFERROR(L9/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="N9" s="33">
+      <c r="N9" s="34">
         <f>COUNTIF($A$12:$A$41,"A")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="34" t="inlineStr">
-        <is>
-          <t>Limite B:</t>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>Limite B (Classe B):</t>
         </is>
       </c>
       <c r="B10" s="35" t="n">
@@ -4680,7 +5192,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="26" customHeight="1">
       <c r="A11" s="40" t="inlineStr">
         <is>
           <t>ABC</t>
@@ -4698,7 +5210,7 @@
       </c>
       <c r="D11" s="42" t="inlineStr">
         <is>
-          <t>Descrição do Item</t>
+          <t>Descrição do Produto</t>
         </is>
       </c>
       <c r="E11" s="43" t="inlineStr">
@@ -4750,25 +5262,35 @@
       </c>
       <c r="Q11" s="48" t="inlineStr">
         <is>
-          <t>% Ind</t>
+          <t>%IndA</t>
         </is>
       </c>
       <c r="R11" s="48" t="inlineStr">
         <is>
-          <t>% Acc</t>
+          <t>%IndB</t>
         </is>
       </c>
       <c r="S11" s="48" t="inlineStr">
         <is>
+          <t>%IndC</t>
+        </is>
+      </c>
+      <c r="T11" s="48" t="inlineStr">
+        <is>
+          <t>%Acum.</t>
+        </is>
+      </c>
+      <c r="U11" s="48" t="inlineStr">
+        <is>
           <t>ZonaA</t>
         </is>
       </c>
-      <c r="T11" s="48" t="inlineStr">
+      <c r="V11" s="48" t="inlineStr">
         <is>
           <t>ZonaB</t>
         </is>
       </c>
-      <c r="U11" s="48" t="inlineStr">
+      <c r="W11" s="48" t="inlineStr">
         <is>
           <t>ZonaC</t>
         </is>
@@ -4812,22 +5334,28 @@
       </c>
       <c r="P12" s="56" t="inlineStr">
         <is>
-          <t>A — SKU01 — Servidor Rack Dell Pro</t>
+          <t>A — SKU01 — Servidor Rack Dell P</t>
         </is>
       </c>
       <c r="Q12" s="57" t="n">
         <v>0.32488</v>
       </c>
-      <c r="R12" s="57" t="n">
+      <c r="R12" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="60" t="n">
         <v>0.32488</v>
       </c>
-      <c r="S12" s="58" t="n">
+      <c r="U12" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="T12" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="60" t="n">
+      <c r="V12" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4875,16 +5403,22 @@
       <c r="Q13" s="57" t="n">
         <v>0.21947</v>
       </c>
-      <c r="R13" s="57" t="n">
+      <c r="R13" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="60" t="n">
         <v>0.54435</v>
       </c>
-      <c r="S13" s="58" t="n">
+      <c r="U13" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="T13" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" s="60" t="n">
+      <c r="V13" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4932,16 +5466,22 @@
       <c r="Q14" s="57" t="n">
         <v>0.19406</v>
       </c>
-      <c r="R14" s="57" t="n">
+      <c r="R14" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="60" t="n">
         <v>0.73842</v>
       </c>
-      <c r="S14" s="58" t="n">
+      <c r="U14" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" s="60" t="n">
+      <c r="V14" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4983,39 +5523,45 @@
       </c>
       <c r="P15" s="56" t="inlineStr">
         <is>
-          <t>A — SKU04 — Switch Gerenciavel 48p</t>
+          <t>A — SKU04 — Switch Gerenciavel 4</t>
         </is>
       </c>
       <c r="Q15" s="57" t="n">
         <v>0.04621</v>
       </c>
-      <c r="R15" s="57" t="n">
+      <c r="R15" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="60" t="n">
         <v>0.78462</v>
       </c>
-      <c r="S15" s="58" t="n">
+      <c r="U15" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="T15" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" s="60" t="n">
+      <c r="V15" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" s="63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="61">
+      <c r="A16" s="64">
         <f>IF($I16&lt;=$B$9,"A",IF($I16&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B16" s="62" t="inlineStr">
+      <c r="B16" s="65" t="inlineStr">
         <is>
           <t>SKU05</t>
         </is>
       </c>
-      <c r="C16" s="62" t="n">
+      <c r="C16" s="65" t="n">
         <v>22</v>
       </c>
-      <c r="D16" s="63" t="inlineStr">
+      <c r="D16" s="66" t="inlineStr">
         <is>
           <t>Placa de Video RTX</t>
         </is>
@@ -5026,15 +5572,15 @@
       <c r="F16" s="53" t="n">
         <v>5500</v>
       </c>
-      <c r="G16" s="64">
+      <c r="G16" s="67">
         <f>IFERROR(E16*F16,0)</f>
         <v/>
       </c>
-      <c r="H16" s="65">
+      <c r="H16" s="68">
         <f>IFERROR(G16/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="I16" s="65">
+      <c r="I16" s="68">
         <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G16,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
@@ -5044,35 +5590,41 @@
         </is>
       </c>
       <c r="Q16" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="58" t="n">
         <v>0.04235</v>
       </c>
-      <c r="R16" s="57" t="n">
+      <c r="S16" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="60" t="n">
         <v>0.82698</v>
       </c>
-      <c r="S16" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" s="59" t="n">
+      <c r="U16" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="U16" s="60" t="n">
+      <c r="W16" s="63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="61">
+      <c r="A17" s="64">
         <f>IF($I17&lt;=$B$9,"A",IF($I17&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B17" s="62" t="inlineStr">
+      <c r="B17" s="65" t="inlineStr">
         <is>
           <t>SKU06</t>
         </is>
       </c>
-      <c r="C17" s="62" t="n">
+      <c r="C17" s="65" t="n">
         <v>21</v>
       </c>
-      <c r="D17" s="63" t="inlineStr">
+      <c r="D17" s="66" t="inlineStr">
         <is>
           <t>Storage NAS 40TB</t>
         </is>
@@ -5083,15 +5635,15 @@
       <c r="F17" s="53" t="n">
         <v>18500</v>
       </c>
-      <c r="G17" s="64">
+      <c r="G17" s="67">
         <f>IFERROR(E17*F17,0)</f>
         <v/>
       </c>
-      <c r="H17" s="65">
+      <c r="H17" s="68">
         <f>IFERROR(G17/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="I17" s="65">
+      <c r="I17" s="68">
         <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G17,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
@@ -5101,35 +5653,41 @@
         </is>
       </c>
       <c r="Q17" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="58" t="n">
         <v>0.03562</v>
       </c>
-      <c r="R17" s="57" t="n">
+      <c r="S17" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="60" t="n">
         <v>0.86259</v>
       </c>
-      <c r="S17" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" s="59" t="n">
+      <c r="U17" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="U17" s="60" t="n">
+      <c r="W17" s="63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="61">
+      <c r="A18" s="64">
         <f>IF($I18&lt;=$B$9,"A",IF($I18&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B18" s="62" t="inlineStr">
+      <c r="B18" s="65" t="inlineStr">
         <is>
           <t>SKU07</t>
         </is>
       </c>
-      <c r="C18" s="62" t="n">
+      <c r="C18" s="65" t="n">
         <v>19</v>
       </c>
-      <c r="D18" s="63" t="inlineStr">
+      <c r="D18" s="66" t="inlineStr">
         <is>
           <t>Memoria RAM 16GB</t>
         </is>
@@ -5140,15 +5698,15 @@
       <c r="F18" s="53" t="n">
         <v>380</v>
       </c>
-      <c r="G18" s="64">
+      <c r="G18" s="67">
         <f>IFERROR(E18*F18,0)</f>
         <v/>
       </c>
-      <c r="H18" s="65">
+      <c r="H18" s="68">
         <f>IFERROR(G18/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="I18" s="65">
+      <c r="I18" s="68">
         <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G18,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
@@ -5158,35 +5716,41 @@
         </is>
       </c>
       <c r="Q18" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="58" t="n">
         <v>0.01646</v>
       </c>
-      <c r="R18" s="57" t="n">
+      <c r="S18" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="60" t="n">
         <v>0.87905</v>
       </c>
-      <c r="S18" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="59" t="n">
+      <c r="U18" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="U18" s="60" t="n">
+      <c r="W18" s="63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="61">
+      <c r="A19" s="64">
         <f>IF($I19&lt;=$B$9,"A",IF($I19&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B19" s="62" t="inlineStr">
+      <c r="B19" s="65" t="inlineStr">
         <is>
           <t>SKU08</t>
         </is>
       </c>
-      <c r="C19" s="62" t="n">
+      <c r="C19" s="65" t="n">
         <v>12</v>
       </c>
-      <c r="D19" s="63" t="inlineStr">
+      <c r="D19" s="66" t="inlineStr">
         <is>
           <t>Toner Impressora Laser</t>
         </is>
@@ -5197,53 +5761,59 @@
       <c r="F19" s="53" t="n">
         <v>320</v>
       </c>
-      <c r="G19" s="64">
+      <c r="G19" s="67">
         <f>IFERROR(E19*F19,0)</f>
         <v/>
       </c>
-      <c r="H19" s="65">
+      <c r="H19" s="68">
         <f>IFERROR(G19/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="I19" s="65">
+      <c r="I19" s="68">
         <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G19,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P19" s="56" t="inlineStr">
         <is>
-          <t>B — SKU08 — Toner Impressora Laser</t>
+          <t>B — SKU08 — Toner Impressora Las</t>
         </is>
       </c>
       <c r="Q19" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="58" t="n">
         <v>0.01232</v>
       </c>
-      <c r="R19" s="57" t="n">
+      <c r="S19" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="60" t="n">
         <v>0.89137</v>
       </c>
-      <c r="S19" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="59" t="n">
+      <c r="U19" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="U19" s="60" t="n">
+      <c r="W19" s="63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="61">
+      <c r="A20" s="64">
         <f>IF($I20&lt;=$B$9,"A",IF($I20&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B20" s="62" t="inlineStr">
+      <c r="B20" s="65" t="inlineStr">
         <is>
           <t>SKU09</t>
         </is>
       </c>
-      <c r="C20" s="62" t="n">
+      <c r="C20" s="65" t="n">
         <v>4</v>
       </c>
-      <c r="D20" s="63" t="inlineStr">
+      <c r="D20" s="66" t="inlineStr">
         <is>
           <t>Monitor LED 24"</t>
         </is>
@@ -5254,15 +5824,15 @@
       <c r="F20" s="53" t="n">
         <v>850</v>
       </c>
-      <c r="G20" s="64">
+      <c r="G20" s="67">
         <f>IFERROR(E20*F20,0)</f>
         <v/>
       </c>
-      <c r="H20" s="65">
+      <c r="H20" s="68">
         <f>IFERROR(G20/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="I20" s="65">
+      <c r="I20" s="68">
         <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G20,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
@@ -5272,35 +5842,41 @@
         </is>
       </c>
       <c r="Q20" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="58" t="n">
         <v>0.01227</v>
       </c>
-      <c r="R20" s="57" t="n">
+      <c r="S20" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="60" t="n">
         <v>0.90365</v>
       </c>
-      <c r="S20" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="59" t="n">
+      <c r="U20" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="U20" s="60" t="n">
+      <c r="W20" s="63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="61">
+      <c r="A21" s="64">
         <f>IF($I21&lt;=$B$9,"A",IF($I21&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B21" s="62" t="inlineStr">
+      <c r="B21" s="65" t="inlineStr">
         <is>
           <t>SKU10</t>
         </is>
       </c>
-      <c r="C21" s="62" t="n">
+      <c r="C21" s="65" t="n">
         <v>11</v>
       </c>
-      <c r="D21" s="63" t="inlineStr">
+      <c r="D21" s="66" t="inlineStr">
         <is>
           <t>Roteador Wi-Fi 6</t>
         </is>
@@ -5311,15 +5887,15 @@
       <c r="F21" s="53" t="n">
         <v>450</v>
       </c>
-      <c r="G21" s="64">
+      <c r="G21" s="67">
         <f>IFERROR(E21*F21,0)</f>
         <v/>
       </c>
-      <c r="H21" s="65">
+      <c r="H21" s="68">
         <f>IFERROR(G21/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="I21" s="65">
+      <c r="I21" s="68">
         <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G21,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
@@ -5329,35 +5905,41 @@
         </is>
       </c>
       <c r="Q21" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="58" t="n">
         <v>0.01083</v>
       </c>
-      <c r="R21" s="57" t="n">
+      <c r="S21" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="60" t="n">
         <v>0.91448</v>
       </c>
-      <c r="S21" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="59" t="n">
+      <c r="U21" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="U21" s="60" t="n">
+      <c r="W21" s="63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="61">
+      <c r="A22" s="64">
         <f>IF($I22&lt;=$B$9,"A",IF($I22&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B22" s="62" t="inlineStr">
+      <c r="B22" s="65" t="inlineStr">
         <is>
           <t>SKU11</t>
         </is>
       </c>
-      <c r="C22" s="62" t="n">
+      <c r="C22" s="65" t="n">
         <v>15</v>
       </c>
-      <c r="D22" s="63" t="inlineStr">
+      <c r="D22" s="66" t="inlineStr">
         <is>
           <t>SSD 480GB Sata</t>
         </is>
@@ -5368,15 +5950,15 @@
       <c r="F22" s="53" t="n">
         <v>190</v>
       </c>
-      <c r="G22" s="64">
+      <c r="G22" s="67">
         <f>IFERROR(E22*F22,0)</f>
         <v/>
       </c>
-      <c r="H22" s="65">
+      <c r="H22" s="68">
         <f>IFERROR(G22/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="I22" s="65">
+      <c r="I22" s="68">
         <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G22,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
@@ -5386,35 +5968,41 @@
         </is>
       </c>
       <c r="Q22" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="58" t="n">
         <v>0.01006</v>
       </c>
-      <c r="R22" s="57" t="n">
+      <c r="S22" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="60" t="n">
         <v>0.92454</v>
       </c>
-      <c r="S22" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" s="59" t="n">
+      <c r="U22" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="U22" s="60" t="n">
+      <c r="W22" s="63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="61">
+      <c r="A23" s="64">
         <f>IF($I23&lt;=$B$9,"A",IF($I23&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B23" s="62" t="inlineStr">
+      <c r="B23" s="65" t="inlineStr">
         <is>
           <t>SKU12</t>
         </is>
       </c>
-      <c r="C23" s="62" t="n">
+      <c r="C23" s="65" t="n">
         <v>6</v>
       </c>
-      <c r="D23" s="63" t="inlineStr">
+      <c r="D23" s="66" t="inlineStr">
         <is>
           <t>Nobreak 1500VA</t>
         </is>
@@ -5425,15 +6013,15 @@
       <c r="F23" s="53" t="n">
         <v>1200</v>
       </c>
-      <c r="G23" s="64">
+      <c r="G23" s="67">
         <f>IFERROR(E23*F23,0)</f>
         <v/>
       </c>
-      <c r="H23" s="65">
+      <c r="H23" s="68">
         <f>IFERROR(G23/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="I23" s="65">
+      <c r="I23" s="68">
         <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G23,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
@@ -5443,35 +6031,41 @@
         </is>
       </c>
       <c r="Q23" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="58" t="n">
         <v>0.00924</v>
       </c>
-      <c r="R23" s="57" t="n">
+      <c r="S23" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="60" t="n">
         <v>0.9337800000000001</v>
       </c>
-      <c r="S23" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" s="59" t="n">
+      <c r="U23" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="U23" s="60" t="n">
+      <c r="W23" s="63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="61">
+      <c r="A24" s="64">
         <f>IF($I24&lt;=$B$9,"A",IF($I24&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B24" s="62" t="inlineStr">
+      <c r="B24" s="65" t="inlineStr">
         <is>
           <t>SKU13</t>
         </is>
       </c>
-      <c r="C24" s="62" t="n">
+      <c r="C24" s="65" t="n">
         <v>20</v>
       </c>
-      <c r="D24" s="63" t="inlineStr">
+      <c r="D24" s="66" t="inlineStr">
         <is>
           <t>HD Externo 2TB</t>
         </is>
@@ -5482,15 +6076,15 @@
       <c r="F24" s="53" t="n">
         <v>420</v>
       </c>
-      <c r="G24" s="64">
+      <c r="G24" s="67">
         <f>IFERROR(E24*F24,0)</f>
         <v/>
       </c>
-      <c r="H24" s="65">
+      <c r="H24" s="68">
         <f>IFERROR(G24/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="I24" s="65">
+      <c r="I24" s="68">
         <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G24,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
@@ -5500,35 +6094,41 @@
         </is>
       </c>
       <c r="Q24" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="58" t="n">
         <v>0.00728</v>
       </c>
-      <c r="R24" s="57" t="n">
+      <c r="S24" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="60" t="n">
         <v>0.9410500000000001</v>
       </c>
-      <c r="S24" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" s="59" t="n">
+      <c r="U24" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="U24" s="60" t="n">
+      <c r="W24" s="63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="61">
+      <c r="A25" s="64">
         <f>IF($I25&lt;=$B$9,"A",IF($I25&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B25" s="62" t="inlineStr">
+      <c r="B25" s="65" t="inlineStr">
         <is>
           <t>SKU14</t>
         </is>
       </c>
-      <c r="C25" s="62" t="n">
+      <c r="C25" s="65" t="n">
         <v>5</v>
       </c>
-      <c r="D25" s="63" t="inlineStr">
+      <c r="D25" s="66" t="inlineStr">
         <is>
           <t>Teclado Mecanico RGB</t>
         </is>
@@ -5539,15 +6139,15 @@
       <c r="F25" s="53" t="n">
         <v>250</v>
       </c>
-      <c r="G25" s="64">
+      <c r="G25" s="67">
         <f>IFERROR(E25*F25,0)</f>
         <v/>
       </c>
-      <c r="H25" s="65">
+      <c r="H25" s="68">
         <f>IFERROR(G25/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="I25" s="65">
+      <c r="I25" s="68">
         <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G25,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
@@ -5557,35 +6157,41 @@
         </is>
       </c>
       <c r="Q25" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="58" t="n">
         <v>0.00722</v>
       </c>
-      <c r="R25" s="57" t="n">
+      <c r="S25" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="60" t="n">
         <v>0.9482699999999999</v>
       </c>
-      <c r="S25" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" s="59" t="n">
+      <c r="U25" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="U25" s="60" t="n">
+      <c r="W25" s="63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="66">
+      <c r="A26" s="69">
         <f>IF($I26&lt;=$B$9,"A",IF($I26&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B26" s="67" t="inlineStr">
+      <c r="B26" s="70" t="inlineStr">
         <is>
           <t>SKU15</t>
         </is>
       </c>
-      <c r="C26" s="67" t="n">
+      <c r="C26" s="70" t="n">
         <v>9</v>
       </c>
-      <c r="D26" s="68" t="inlineStr">
+      <c r="D26" s="71" t="inlineStr">
         <is>
           <t>Pen Drive 64GB</t>
         </is>
@@ -5596,15 +6202,15 @@
       <c r="F26" s="53" t="n">
         <v>45</v>
       </c>
-      <c r="G26" s="69">
+      <c r="G26" s="72">
         <f>IFERROR(E26*F26,0)</f>
         <v/>
       </c>
-      <c r="H26" s="70">
+      <c r="H26" s="73">
         <f>IFERROR(G26/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="I26" s="70">
+      <c r="I26" s="73">
         <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G26,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
@@ -5614,35 +6220,41 @@
         </is>
       </c>
       <c r="Q26" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="59" t="n">
         <v>0.0065</v>
       </c>
-      <c r="R26" s="57" t="n">
+      <c r="T26" s="60" t="n">
         <v>0.95477</v>
       </c>
-      <c r="S26" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" s="60" t="n">
+      <c r="U26" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" s="63" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="66">
+      <c r="A27" s="69">
         <f>IF($I27&lt;=$B$9,"A",IF($I27&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B27" s="67" t="inlineStr">
+      <c r="B27" s="70" t="inlineStr">
         <is>
           <t>SKU16</t>
         </is>
       </c>
-      <c r="C27" s="67" t="n">
+      <c r="C27" s="70" t="n">
         <v>13</v>
       </c>
-      <c r="D27" s="68" t="inlineStr">
+      <c r="D27" s="71" t="inlineStr">
         <is>
           <t>Headset com Microfone</t>
         </is>
@@ -5653,53 +6265,59 @@
       <c r="F27" s="53" t="n">
         <v>110</v>
       </c>
-      <c r="G27" s="69">
+      <c r="G27" s="72">
         <f>IFERROR(E27*F27,0)</f>
         <v/>
       </c>
-      <c r="H27" s="70">
+      <c r="H27" s="73">
         <f>IFERROR(G27/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="I27" s="70">
+      <c r="I27" s="73">
         <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G27,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P27" s="56" t="inlineStr">
         <is>
-          <t>C — SKU16 — Headset com Microfone</t>
+          <t>C — SKU16 — Headset com Microfon</t>
         </is>
       </c>
       <c r="Q27" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="59" t="n">
         <v>0.00635</v>
       </c>
-      <c r="R27" s="57" t="n">
+      <c r="T27" s="60" t="n">
         <v>0.96113</v>
       </c>
-      <c r="S27" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" s="60" t="n">
+      <c r="U27" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" s="63" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="66">
+      <c r="A28" s="69">
         <f>IF($I28&lt;=$B$9,"A",IF($I28&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B28" s="67" t="inlineStr">
+      <c r="B28" s="70" t="inlineStr">
         <is>
           <t>SKU17</t>
         </is>
       </c>
-      <c r="C28" s="67" t="n">
+      <c r="C28" s="70" t="n">
         <v>7</v>
       </c>
-      <c r="D28" s="68" t="inlineStr">
+      <c r="D28" s="71" t="inlineStr">
         <is>
           <t>Pacote de Papel A4</t>
         </is>
@@ -5710,15 +6328,15 @@
       <c r="F28" s="53" t="n">
         <v>28</v>
       </c>
-      <c r="G28" s="69">
+      <c r="G28" s="72">
         <f>IFERROR(E28*F28,0)</f>
         <v/>
       </c>
-      <c r="H28" s="70">
+      <c r="H28" s="73">
         <f>IFERROR(G28/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="I28" s="70">
+      <c r="I28" s="73">
         <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G28,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
@@ -5728,35 +6346,41 @@
         </is>
       </c>
       <c r="Q28" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="59" t="n">
         <v>0.00539</v>
       </c>
-      <c r="R28" s="57" t="n">
+      <c r="T28" s="60" t="n">
         <v>0.96652</v>
       </c>
-      <c r="S28" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" s="60" t="n">
+      <c r="U28" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" s="63" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="66">
+      <c r="A29" s="69">
         <f>IF($I29&lt;=$B$9,"A",IF($I29&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B29" s="67" t="inlineStr">
+      <c r="B29" s="70" t="inlineStr">
         <is>
           <t>SKU18</t>
         </is>
       </c>
-      <c r="C29" s="67" t="n">
+      <c r="C29" s="70" t="n">
         <v>29</v>
       </c>
-      <c r="D29" s="68" t="inlineStr">
+      <c r="D29" s="71" t="inlineStr">
         <is>
           <t>Teclado de Entrada</t>
         </is>
@@ -5767,15 +6391,15 @@
       <c r="F29" s="53" t="n">
         <v>45</v>
       </c>
-      <c r="G29" s="69">
+      <c r="G29" s="72">
         <f>IFERROR(E29*F29,0)</f>
         <v/>
       </c>
-      <c r="H29" s="70">
+      <c r="H29" s="73">
         <f>IFERROR(G29/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="I29" s="70">
+      <c r="I29" s="73">
         <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G29,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
@@ -5785,35 +6409,41 @@
         </is>
       </c>
       <c r="Q29" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="59" t="n">
         <v>0.00433</v>
       </c>
-      <c r="R29" s="57" t="n">
+      <c r="T29" s="60" t="n">
         <v>0.97085</v>
       </c>
-      <c r="S29" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" s="60" t="n">
+      <c r="U29" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" s="63" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="66">
+      <c r="A30" s="69">
         <f>IF($I30&lt;=$B$9,"A",IF($I30&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B30" s="67" t="inlineStr">
+      <c r="B30" s="70" t="inlineStr">
         <is>
           <t>SKU19</t>
         </is>
       </c>
-      <c r="C30" s="67" t="n">
+      <c r="C30" s="70" t="n">
         <v>18</v>
       </c>
-      <c r="D30" s="68" t="inlineStr">
+      <c r="D30" s="71" t="inlineStr">
         <is>
           <t>Filtro de Linha</t>
         </is>
@@ -5824,15 +6454,15 @@
       <c r="F30" s="53" t="n">
         <v>40</v>
       </c>
-      <c r="G30" s="69">
+      <c r="G30" s="72">
         <f>IFERROR(E30*F30,0)</f>
         <v/>
       </c>
-      <c r="H30" s="70">
+      <c r="H30" s="73">
         <f>IFERROR(G30/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="I30" s="70">
+      <c r="I30" s="73">
         <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G30,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
@@ -5842,35 +6472,41 @@
         </is>
       </c>
       <c r="Q30" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="59" t="n">
         <v>0.00424</v>
       </c>
-      <c r="R30" s="57" t="n">
+      <c r="T30" s="60" t="n">
         <v>0.9750799999999999</v>
       </c>
-      <c r="S30" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" s="60" t="n">
+      <c r="U30" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" s="63" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="66">
+      <c r="A31" s="69">
         <f>IF($I31&lt;=$B$9,"A",IF($I31&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B31" s="67" t="inlineStr">
+      <c r="B31" s="70" t="inlineStr">
         <is>
           <t>SKU20</t>
         </is>
       </c>
-      <c r="C31" s="67" t="n">
+      <c r="C31" s="70" t="n">
         <v>14</v>
       </c>
-      <c r="D31" s="68" t="inlineStr">
+      <c r="D31" s="71" t="inlineStr">
         <is>
           <t>Webcam Full HD</t>
         </is>
@@ -5881,15 +6517,15 @@
       <c r="F31" s="53" t="n">
         <v>180</v>
       </c>
-      <c r="G31" s="69">
+      <c r="G31" s="72">
         <f>IFERROR(E31*F31,0)</f>
         <v/>
       </c>
-      <c r="H31" s="70">
+      <c r="H31" s="73">
         <f>IFERROR(G31/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="I31" s="70">
+      <c r="I31" s="73">
         <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G31,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
@@ -5899,35 +6535,41 @@
         </is>
       </c>
       <c r="Q31" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="59" t="n">
         <v>0.00381</v>
       </c>
-      <c r="R31" s="57" t="n">
+      <c r="T31" s="60" t="n">
         <v>0.97889</v>
       </c>
-      <c r="S31" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" s="60" t="n">
+      <c r="U31" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" s="63" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="66">
+      <c r="A32" s="69">
         <f>IF($I32&lt;=$B$9,"A",IF($I32&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B32" s="67" t="inlineStr">
+      <c r="B32" s="70" t="inlineStr">
         <is>
           <t>SKU21</t>
         </is>
       </c>
-      <c r="C32" s="67" t="n">
+      <c r="C32" s="70" t="n">
         <v>23</v>
       </c>
-      <c r="D32" s="68" t="inlineStr">
+      <c r="D32" s="71" t="inlineStr">
         <is>
           <t>Pilhas AA (Pacote)</t>
         </is>
@@ -5938,15 +6580,15 @@
       <c r="F32" s="53" t="n">
         <v>12</v>
       </c>
-      <c r="G32" s="69">
+      <c r="G32" s="72">
         <f>IFERROR(E32*F32,0)</f>
         <v/>
       </c>
-      <c r="H32" s="70">
+      <c r="H32" s="73">
         <f>IFERROR(G32/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="I32" s="70">
+      <c r="I32" s="73">
         <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G32,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
@@ -5956,35 +6598,41 @@
         </is>
       </c>
       <c r="Q32" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="59" t="n">
         <v>0.00347</v>
       </c>
-      <c r="R32" s="57" t="n">
+      <c r="T32" s="60" t="n">
         <v>0.98236</v>
       </c>
-      <c r="S32" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" s="60" t="n">
+      <c r="U32" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" s="63" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="66">
+      <c r="A33" s="69">
         <f>IF($I33&lt;=$B$9,"A",IF($I33&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B33" s="67" t="inlineStr">
+      <c r="B33" s="70" t="inlineStr">
         <is>
           <t>SKU22</t>
         </is>
       </c>
-      <c r="C33" s="67" t="n">
+      <c r="C33" s="70" t="n">
         <v>16</v>
       </c>
-      <c r="D33" s="68" t="inlineStr">
+      <c r="D33" s="71" t="inlineStr">
         <is>
           <t>Adaptador USB-C</t>
         </is>
@@ -5995,15 +6643,15 @@
       <c r="F33" s="53" t="n">
         <v>35</v>
       </c>
-      <c r="G33" s="69">
+      <c r="G33" s="72">
         <f>IFERROR(E33*F33,0)</f>
         <v/>
       </c>
-      <c r="H33" s="70">
+      <c r="H33" s="73">
         <f>IFERROR(G33/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="I33" s="70">
+      <c r="I33" s="73">
         <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G33,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
@@ -6013,35 +6661,41 @@
         </is>
       </c>
       <c r="Q33" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="59" t="n">
         <v>0.00303</v>
       </c>
-      <c r="R33" s="57" t="n">
+      <c r="T33" s="60" t="n">
         <v>0.98539</v>
       </c>
-      <c r="S33" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" s="60" t="n">
+      <c r="U33" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" s="63" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="66">
+      <c r="A34" s="69">
         <f>IF($I34&lt;=$B$9,"A",IF($I34&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B34" s="67" t="inlineStr">
+      <c r="B34" s="70" t="inlineStr">
         <is>
           <t>SKU23</t>
         </is>
       </c>
-      <c r="C34" s="67" t="n">
+      <c r="C34" s="70" t="n">
         <v>28</v>
       </c>
-      <c r="D34" s="68" t="inlineStr">
+      <c r="D34" s="71" t="inlineStr">
         <is>
           <t>Suporte para Monitor</t>
         </is>
@@ -6052,15 +6706,15 @@
       <c r="F34" s="53" t="n">
         <v>140</v>
       </c>
-      <c r="G34" s="69">
+      <c r="G34" s="72">
         <f>IFERROR(E34*F34,0)</f>
         <v/>
       </c>
-      <c r="H34" s="70">
+      <c r="H34" s="73">
         <f>IFERROR(G34/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="I34" s="70">
+      <c r="I34" s="73">
         <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G34,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
@@ -6070,35 +6724,41 @@
         </is>
       </c>
       <c r="Q34" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="59" t="n">
         <v>0.0027</v>
       </c>
-      <c r="R34" s="57" t="n">
+      <c r="T34" s="60" t="n">
         <v>0.98809</v>
       </c>
-      <c r="S34" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" s="60" t="n">
+      <c r="U34" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" s="63" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="66">
+      <c r="A35" s="69">
         <f>IF($I35&lt;=$B$9,"A",IF($I35&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B35" s="67" t="inlineStr">
+      <c r="B35" s="70" t="inlineStr">
         <is>
           <t>SKU24</t>
         </is>
       </c>
-      <c r="C35" s="67" t="n">
+      <c r="C35" s="70" t="n">
         <v>1</v>
       </c>
-      <c r="D35" s="68" t="inlineStr">
+      <c r="D35" s="71" t="inlineStr">
         <is>
           <t>Cabo HDMI 2m</t>
         </is>
@@ -6109,15 +6769,15 @@
       <c r="F35" s="53" t="n">
         <v>25</v>
       </c>
-      <c r="G35" s="69">
+      <c r="G35" s="72">
         <f>IFERROR(E35*F35,0)</f>
         <v/>
       </c>
-      <c r="H35" s="70">
+      <c r="H35" s="73">
         <f>IFERROR(G35/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="I35" s="70">
+      <c r="I35" s="73">
         <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G35,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
@@ -6127,35 +6787,41 @@
         </is>
       </c>
       <c r="Q35" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="59" t="n">
         <v>0.00205</v>
       </c>
-      <c r="R35" s="57" t="n">
+      <c r="T35" s="60" t="n">
         <v>0.99013</v>
       </c>
-      <c r="S35" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" s="60" t="n">
+      <c r="U35" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" s="63" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="66">
+      <c r="A36" s="69">
         <f>IF($I36&lt;=$B$9,"A",IF($I36&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B36" s="67" t="inlineStr">
+      <c r="B36" s="70" t="inlineStr">
         <is>
           <t>SKU25</t>
         </is>
       </c>
-      <c r="C36" s="67" t="n">
+      <c r="C36" s="70" t="n">
         <v>24</v>
       </c>
-      <c r="D36" s="68" t="inlineStr">
+      <c r="D36" s="71" t="inlineStr">
         <is>
           <t>Mousepad Simples</t>
         </is>
@@ -6166,15 +6832,15 @@
       <c r="F36" s="53" t="n">
         <v>8</v>
       </c>
-      <c r="G36" s="69">
+      <c r="G36" s="72">
         <f>IFERROR(E36*F36,0)</f>
         <v/>
       </c>
-      <c r="H36" s="70">
+      <c r="H36" s="73">
         <f>IFERROR(G36/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="I36" s="70">
+      <c r="I36" s="73">
         <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G36,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
@@ -6184,35 +6850,41 @@
         </is>
       </c>
       <c r="Q36" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="59" t="n">
         <v>0.00193</v>
       </c>
-      <c r="R36" s="57" t="n">
+      <c r="T36" s="60" t="n">
         <v>0.9920600000000001</v>
       </c>
-      <c r="S36" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" s="60" t="n">
+      <c r="U36" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" s="63" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="66">
+      <c r="A37" s="69">
         <f>IF($I37&lt;=$B$9,"A",IF($I37&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B37" s="67" t="inlineStr">
+      <c r="B37" s="70" t="inlineStr">
         <is>
           <t>SKU26</t>
         </is>
       </c>
-      <c r="C37" s="67" t="n">
+      <c r="C37" s="70" t="n">
         <v>3</v>
       </c>
-      <c r="D37" s="68" t="inlineStr">
+      <c r="D37" s="71" t="inlineStr">
         <is>
           <t>Mouse Optico Simples</t>
         </is>
@@ -6223,15 +6895,15 @@
       <c r="F37" s="53" t="n">
         <v>15</v>
       </c>
-      <c r="G37" s="69">
+      <c r="G37" s="72">
         <f>IFERROR(E37*F37,0)</f>
         <v/>
       </c>
-      <c r="H37" s="70">
+      <c r="H37" s="73">
         <f>IFERROR(G37/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="I37" s="70">
+      <c r="I37" s="73">
         <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G37,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
@@ -6241,35 +6913,41 @@
         </is>
       </c>
       <c r="Q37" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="59" t="n">
         <v>0.00173</v>
       </c>
-      <c r="R37" s="57" t="n">
+      <c r="T37" s="60" t="n">
         <v>0.99379</v>
       </c>
-      <c r="S37" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" s="60" t="n">
+      <c r="U37" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" s="63" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="66">
+      <c r="A38" s="69">
         <f>IF($I38&lt;=$B$9,"A",IF($I38&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B38" s="67" t="inlineStr">
+      <c r="B38" s="70" t="inlineStr">
         <is>
           <t>SKU27</t>
         </is>
       </c>
-      <c r="C38" s="67" t="n">
+      <c r="C38" s="70" t="n">
         <v>25</v>
       </c>
-      <c r="D38" s="68" t="inlineStr">
+      <c r="D38" s="71" t="inlineStr">
         <is>
           <t>Organizador de Cabos</t>
         </is>
@@ -6280,15 +6958,15 @@
       <c r="F38" s="53" t="n">
         <v>10</v>
       </c>
-      <c r="G38" s="69">
+      <c r="G38" s="72">
         <f>IFERROR(E38*F38,0)</f>
         <v/>
       </c>
-      <c r="H38" s="70">
+      <c r="H38" s="73">
         <f>IFERROR(G38/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="I38" s="70">
+      <c r="I38" s="73">
         <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G38,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
@@ -6298,35 +6976,41 @@
         </is>
       </c>
       <c r="Q38" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" s="59" t="n">
         <v>0.00173</v>
       </c>
-      <c r="R38" s="57" t="n">
+      <c r="T38" s="60" t="n">
         <v>0.99552</v>
       </c>
-      <c r="S38" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" s="60" t="n">
+      <c r="U38" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" s="63" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="66">
+      <c r="A39" s="69">
         <f>IF($I39&lt;=$B$9,"A",IF($I39&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B39" s="67" t="inlineStr">
+      <c r="B39" s="70" t="inlineStr">
         <is>
           <t>SKU28</t>
         </is>
       </c>
-      <c r="C39" s="67" t="n">
+      <c r="C39" s="70" t="n">
         <v>27</v>
       </c>
-      <c r="D39" s="68" t="inlineStr">
+      <c r="D39" s="71" t="inlineStr">
         <is>
           <t>Ar comprimido (Lata)</t>
         </is>
@@ -6337,15 +7021,15 @@
       <c r="F39" s="53" t="n">
         <v>45</v>
       </c>
-      <c r="G39" s="69">
+      <c r="G39" s="72">
         <f>IFERROR(E39*F39,0)</f>
         <v/>
       </c>
-      <c r="H39" s="70">
+      <c r="H39" s="73">
         <f>IFERROR(G39/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="I39" s="70">
+      <c r="I39" s="73">
         <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G39,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
@@ -6355,35 +7039,41 @@
         </is>
       </c>
       <c r="Q39" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="59" t="n">
         <v>0.00152</v>
       </c>
-      <c r="R39" s="57" t="n">
+      <c r="T39" s="60" t="n">
         <v>0.99704</v>
       </c>
-      <c r="S39" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" s="60" t="n">
+      <c r="U39" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" s="63" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="66">
+      <c r="A40" s="69">
         <f>IF($I40&lt;=$B$9,"A",IF($I40&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B40" s="67" t="inlineStr">
+      <c r="B40" s="70" t="inlineStr">
         <is>
           <t>SKU29</t>
         </is>
       </c>
-      <c r="C40" s="67" t="n">
+      <c r="C40" s="70" t="n">
         <v>26</v>
       </c>
-      <c r="D40" s="68" t="inlineStr">
+      <c r="D40" s="71" t="inlineStr">
         <is>
           <t>Pasta Termica</t>
         </is>
@@ -6394,15 +7084,15 @@
       <c r="F40" s="53" t="n">
         <v>35</v>
       </c>
-      <c r="G40" s="69">
+      <c r="G40" s="72">
         <f>IFERROR(E40*F40,0)</f>
         <v/>
       </c>
-      <c r="H40" s="70">
+      <c r="H40" s="73">
         <f>IFERROR(G40/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="I40" s="70">
+      <c r="I40" s="73">
         <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G40,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
@@ -6412,35 +7102,41 @@
         </is>
       </c>
       <c r="Q40" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="59" t="n">
         <v>0.00152</v>
       </c>
-      <c r="R40" s="57" t="n">
+      <c r="T40" s="60" t="n">
         <v>0.99856</v>
       </c>
-      <c r="S40" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" s="60" t="n">
+      <c r="U40" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" s="63" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="66">
+      <c r="A41" s="69">
         <f>IF($I41&lt;=$B$9,"A",IF($I41&lt;=$B$10,"B","C"))</f>
         <v/>
       </c>
-      <c r="B41" s="67" t="inlineStr">
+      <c r="B41" s="70" t="inlineStr">
         <is>
           <t>SKU30</t>
         </is>
       </c>
-      <c r="C41" s="67" t="n">
+      <c r="C41" s="70" t="n">
         <v>30</v>
       </c>
-      <c r="D41" s="68" t="inlineStr">
+      <c r="D41" s="71" t="inlineStr">
         <is>
           <t>Conector RJ45 (Cento)</t>
         </is>
@@ -6451,67 +7147,73 @@
       <c r="F41" s="53" t="n">
         <v>30</v>
       </c>
-      <c r="G41" s="69">
+      <c r="G41" s="72">
         <f>IFERROR(E41*F41,0)</f>
         <v/>
       </c>
-      <c r="H41" s="70">
+      <c r="H41" s="73">
         <f>IFERROR(G41/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="I41" s="70">
+      <c r="I41" s="73">
         <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G41,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P41" s="56" t="inlineStr">
         <is>
-          <t>C — SKU30 — Conector RJ45 (Cento)</t>
+          <t>C — SKU30 — Conector RJ45 (Cento</t>
         </is>
       </c>
       <c r="Q41" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="59" t="n">
         <v>0.00144</v>
       </c>
-      <c r="R41" s="57" t="n">
+      <c r="T41" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="S41" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" s="60" t="n">
+      <c r="U41" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" s="63" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="71" t="inlineStr">
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="74" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B42" s="72" t="n"/>
-      <c r="C42" s="72" t="n"/>
-      <c r="D42" s="72" t="n"/>
-      <c r="E42" s="73">
+      <c r="B42" s="75" t="n"/>
+      <c r="C42" s="75" t="n"/>
+      <c r="D42" s="75" t="n"/>
+      <c r="E42" s="76">
         <f>SUM(E12:E41)</f>
         <v/>
       </c>
-      <c r="F42" s="74" t="n"/>
-      <c r="G42" s="75">
+      <c r="F42" s="77" t="n"/>
+      <c r="G42" s="78">
         <f>SUM(G12:G41)</f>
         <v/>
       </c>
-      <c r="H42" s="76" t="n">
+      <c r="H42" s="79" t="n">
         <v>1</v>
       </c>
-      <c r="I42" s="76" t="n">
+      <c r="I42" s="79" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="F0B1"/>
-  <mergeCells count="20">
+  <mergeCells count="21">
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
@@ -6530,6 +7232,7 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="K8:N8"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="E3:F3"/>
   </mergeCells>
@@ -6545,11 +7248,11 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="❌ Valor Inválido" error="Limite A: entre 50% e 89%" type="decimal" operator="between">
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="❌ Valor Inválido — Tente Novamente" error="Digite um valor entre 0,50 e 0,89 (ex: 0,80 para 80%)" promptTitle="ℹ️ Dica de Preenchimento" prompt="Digite um percentual decimal (ex: 0,80 para 80%)" type="decimal" operator="between">
       <formula1>0.5</formula1>
-      <formula2>0.89</formula2>
+      <formula2>0.99</formula2>
     </dataValidation>
-    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="❌ Valor Inválido" error="Limite B: entre 50% e 99%" type="decimal" operator="between">
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="❌ Valor Inválido — Tente Novamente" error="Digite um valor entre 0,50 e 0,99 (ex: 0,95 para 95%)" promptTitle="ℹ️ Dica de Preenchimento" prompt="Digite um percentual decimal (ex: 0,80 para 80%)" type="decimal" operator="between">
       <formula1>0.5</formula1>
       <formula2>0.99</formula2>
     </dataValidation>
@@ -6557,4 +7260,2693 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C8A400"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AG47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5.2" customWidth="1" min="1" max="1"/>
+    <col width="5.2" customWidth="1" min="2" max="2"/>
+    <col width="5.2" customWidth="1" min="3" max="3"/>
+    <col width="5.2" customWidth="1" min="4" max="4"/>
+    <col width="5.2" customWidth="1" min="5" max="5"/>
+    <col width="5.2" customWidth="1" min="6" max="6"/>
+    <col width="5.2" customWidth="1" min="7" max="7"/>
+    <col width="1.5" customWidth="1" min="8" max="8"/>
+    <col width="5.2" customWidth="1" min="9" max="9"/>
+    <col width="5.2" customWidth="1" min="10" max="10"/>
+    <col width="5.2" customWidth="1" min="11" max="11"/>
+    <col width="5.2" customWidth="1" min="12" max="12"/>
+    <col width="5.2" customWidth="1" min="13" max="13"/>
+    <col width="5.2" customWidth="1" min="14" max="14"/>
+    <col width="5.2" customWidth="1" min="15" max="15"/>
+    <col width="1.5" customWidth="1" min="16" max="16"/>
+    <col width="5.2" customWidth="1" min="17" max="17"/>
+    <col width="5.2" customWidth="1" min="18" max="18"/>
+    <col width="5.2" customWidth="1" min="19" max="19"/>
+    <col width="5.2" customWidth="1" min="20" max="20"/>
+    <col width="5.2" customWidth="1" min="21" max="21"/>
+    <col width="5.2" customWidth="1" min="22" max="22"/>
+    <col width="5.2" customWidth="1" min="23" max="23"/>
+    <col width="1.5" customWidth="1" min="24" max="24"/>
+    <col width="5.2" customWidth="1" min="25" max="25"/>
+    <col width="5.2" customWidth="1" min="26" max="26"/>
+    <col width="5.2" customWidth="1" min="27" max="27"/>
+    <col width="5.2" customWidth="1" min="28" max="28"/>
+    <col width="5.2" customWidth="1" min="29" max="29"/>
+    <col width="5.2" customWidth="1" min="30" max="30"/>
+    <col width="5.2" customWidth="1" min="31" max="31"/>
+    <col width="1.5" customWidth="1" min="32" max="32"/>
+    <col width="5.2" customWidth="1" min="33" max="33"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="10" customHeight="1">
+      <c r="A1" s="4" t="n"/>
+      <c r="B1" s="3" t="n"/>
+      <c r="C1" s="5" t="n"/>
+      <c r="D1" s="6" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="5" t="n"/>
+      <c r="H1" s="6" t="n"/>
+      <c r="I1" s="4" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="5" t="n"/>
+      <c r="L1" s="6" t="n"/>
+      <c r="M1" s="4" t="n"/>
+      <c r="N1" s="3" t="n"/>
+      <c r="O1" s="5" t="n"/>
+      <c r="P1" s="6" t="n"/>
+      <c r="Q1" s="4" t="n"/>
+      <c r="R1" s="3" t="n"/>
+      <c r="S1" s="5" t="n"/>
+      <c r="T1" s="6" t="n"/>
+      <c r="U1" s="4" t="n"/>
+      <c r="V1" s="3" t="n"/>
+      <c r="W1" s="5" t="n"/>
+      <c r="X1" s="6" t="n"/>
+      <c r="Y1" s="4" t="n"/>
+      <c r="Z1" s="3" t="n"/>
+      <c r="AA1" s="5" t="n"/>
+      <c r="AB1" s="6" t="n"/>
+      <c r="AC1" s="4" t="n"/>
+      <c r="AD1" s="3" t="n"/>
+      <c r="AE1" s="5" t="n"/>
+      <c r="AF1" s="6" t="n"/>
+      <c r="AG1" s="4" t="n"/>
+    </row>
+    <row r="2" ht="54" customHeight="1">
+      <c r="A2" s="80" t="inlineStr">
+        <is>
+          <t>🇯🇲  CALENDÁRIO 2026  —  One Love, One Excel! ✌️</t>
+        </is>
+      </c>
+      <c r="AG2" s="81" t="n"/>
+    </row>
+    <row r="3" ht="10" customHeight="1">
+      <c r="A3" s="5" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="6" t="n"/>
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="6" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="3" t="n"/>
+      <c r="O3" s="4" t="n"/>
+      <c r="P3" s="6" t="n"/>
+      <c r="Q3" s="5" t="n"/>
+      <c r="R3" s="3" t="n"/>
+      <c r="S3" s="4" t="n"/>
+      <c r="T3" s="6" t="n"/>
+      <c r="U3" s="5" t="n"/>
+      <c r="V3" s="3" t="n"/>
+      <c r="W3" s="4" t="n"/>
+      <c r="X3" s="6" t="n"/>
+      <c r="Y3" s="5" t="n"/>
+      <c r="Z3" s="3" t="n"/>
+      <c r="AA3" s="4" t="n"/>
+      <c r="AB3" s="6" t="n"/>
+      <c r="AC3" s="5" t="n"/>
+      <c r="AD3" s="3" t="n"/>
+      <c r="AE3" s="4" t="n"/>
+      <c r="AF3" s="6" t="n"/>
+      <c r="AG3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="8" customHeight="1">
+      <c r="A4" s="81" t="n"/>
+      <c r="B4" s="81" t="n"/>
+      <c r="C4" s="81" t="n"/>
+      <c r="D4" s="81" t="n"/>
+      <c r="E4" s="81" t="n"/>
+      <c r="F4" s="81" t="n"/>
+      <c r="G4" s="81" t="n"/>
+      <c r="H4" s="81" t="n"/>
+      <c r="I4" s="81" t="n"/>
+      <c r="J4" s="81" t="n"/>
+      <c r="K4" s="81" t="n"/>
+      <c r="L4" s="81" t="n"/>
+      <c r="M4" s="81" t="n"/>
+      <c r="N4" s="81" t="n"/>
+      <c r="O4" s="81" t="n"/>
+      <c r="P4" s="81" t="n"/>
+      <c r="Q4" s="81" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="81" t="n"/>
+      <c r="U4" s="81" t="n"/>
+      <c r="V4" s="81" t="n"/>
+      <c r="W4" s="81" t="n"/>
+      <c r="X4" s="81" t="n"/>
+      <c r="Y4" s="81" t="n"/>
+      <c r="Z4" s="81" t="n"/>
+      <c r="AA4" s="81" t="n"/>
+      <c r="AB4" s="81" t="n"/>
+      <c r="AC4" s="81" t="n"/>
+      <c r="AD4" s="81" t="n"/>
+      <c r="AE4" s="81" t="n"/>
+      <c r="AF4" s="81" t="n"/>
+      <c r="AG4" s="81" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="82" t="inlineStr">
+        <is>
+          <t>🟢 Itens Classe A — revisar diariamente   |   🟡 Itens Classe B — revisar semanalmente   |   🔴 Itens Classe C — revisar mensalmente</t>
+        </is>
+      </c>
+      <c r="Q5" s="81" t="n"/>
+      <c r="R5" s="81" t="n"/>
+      <c r="S5" s="81" t="n"/>
+      <c r="T5" s="81" t="n"/>
+      <c r="U5" s="81" t="n"/>
+      <c r="V5" s="81" t="n"/>
+      <c r="W5" s="81" t="n"/>
+      <c r="X5" s="81" t="n"/>
+      <c r="Y5" s="81" t="n"/>
+      <c r="Z5" s="81" t="n"/>
+      <c r="AA5" s="81" t="n"/>
+      <c r="AB5" s="81" t="n"/>
+      <c r="AC5" s="81" t="n"/>
+      <c r="AD5" s="81" t="n"/>
+      <c r="AE5" s="81" t="n"/>
+      <c r="AF5" s="81" t="n"/>
+      <c r="AG5" s="81" t="n"/>
+    </row>
+    <row r="6" ht="6" customHeight="1">
+      <c r="A6" s="81" t="n"/>
+      <c r="B6" s="81" t="n"/>
+      <c r="C6" s="81" t="n"/>
+      <c r="D6" s="81" t="n"/>
+      <c r="E6" s="81" t="n"/>
+      <c r="F6" s="81" t="n"/>
+      <c r="G6" s="81" t="n"/>
+      <c r="H6" s="81" t="n"/>
+      <c r="I6" s="81" t="n"/>
+      <c r="J6" s="81" t="n"/>
+      <c r="K6" s="81" t="n"/>
+      <c r="L6" s="81" t="n"/>
+      <c r="M6" s="81" t="n"/>
+      <c r="N6" s="81" t="n"/>
+      <c r="O6" s="81" t="n"/>
+      <c r="P6" s="81" t="n"/>
+      <c r="Q6" s="81" t="n"/>
+      <c r="R6" s="81" t="n"/>
+      <c r="S6" s="81" t="n"/>
+      <c r="T6" s="81" t="n"/>
+      <c r="U6" s="81" t="n"/>
+      <c r="V6" s="81" t="n"/>
+      <c r="W6" s="81" t="n"/>
+      <c r="X6" s="81" t="n"/>
+      <c r="Y6" s="81" t="n"/>
+      <c r="Z6" s="81" t="n"/>
+      <c r="AA6" s="81" t="n"/>
+      <c r="AB6" s="81" t="n"/>
+      <c r="AC6" s="81" t="n"/>
+      <c r="AD6" s="81" t="n"/>
+      <c r="AE6" s="81" t="n"/>
+      <c r="AF6" s="81" t="n"/>
+      <c r="AG6" s="81" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="83" t="inlineStr">
+        <is>
+          <t>JANEIRO 2026</t>
+        </is>
+      </c>
+      <c r="H7" s="81" t="n"/>
+      <c r="I7" s="83" t="inlineStr">
+        <is>
+          <t>FEVEREIRO 2026</t>
+        </is>
+      </c>
+      <c r="P7" s="81" t="n"/>
+      <c r="Q7" s="83" t="inlineStr">
+        <is>
+          <t>MARÇO 2026</t>
+        </is>
+      </c>
+      <c r="X7" s="81" t="n"/>
+      <c r="Y7" s="84" t="inlineStr">
+        <is>
+          <t>ABRIL 2026</t>
+        </is>
+      </c>
+      <c r="AF7" s="81" t="n"/>
+      <c r="AG7" s="81" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="85" t="inlineStr">
+        <is>
+          <t>Seg</t>
+        </is>
+      </c>
+      <c r="B8" s="85" t="inlineStr">
+        <is>
+          <t>Ter</t>
+        </is>
+      </c>
+      <c r="C8" s="85" t="inlineStr">
+        <is>
+          <t>Qua</t>
+        </is>
+      </c>
+      <c r="D8" s="85" t="inlineStr">
+        <is>
+          <t>Qui</t>
+        </is>
+      </c>
+      <c r="E8" s="85" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="F8" s="86" t="inlineStr">
+        <is>
+          <t>Sáb</t>
+        </is>
+      </c>
+      <c r="G8" s="86" t="inlineStr">
+        <is>
+          <t>Dom</t>
+        </is>
+      </c>
+      <c r="H8" s="81" t="n"/>
+      <c r="I8" s="85" t="inlineStr">
+        <is>
+          <t>Seg</t>
+        </is>
+      </c>
+      <c r="J8" s="85" t="inlineStr">
+        <is>
+          <t>Ter</t>
+        </is>
+      </c>
+      <c r="K8" s="85" t="inlineStr">
+        <is>
+          <t>Qua</t>
+        </is>
+      </c>
+      <c r="L8" s="85" t="inlineStr">
+        <is>
+          <t>Qui</t>
+        </is>
+      </c>
+      <c r="M8" s="85" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="N8" s="86" t="inlineStr">
+        <is>
+          <t>Sáb</t>
+        </is>
+      </c>
+      <c r="O8" s="86" t="inlineStr">
+        <is>
+          <t>Dom</t>
+        </is>
+      </c>
+      <c r="P8" s="81" t="n"/>
+      <c r="Q8" s="85" t="inlineStr">
+        <is>
+          <t>Seg</t>
+        </is>
+      </c>
+      <c r="R8" s="85" t="inlineStr">
+        <is>
+          <t>Ter</t>
+        </is>
+      </c>
+      <c r="S8" s="85" t="inlineStr">
+        <is>
+          <t>Qua</t>
+        </is>
+      </c>
+      <c r="T8" s="85" t="inlineStr">
+        <is>
+          <t>Qui</t>
+        </is>
+      </c>
+      <c r="U8" s="85" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="V8" s="86" t="inlineStr">
+        <is>
+          <t>Sáb</t>
+        </is>
+      </c>
+      <c r="W8" s="86" t="inlineStr">
+        <is>
+          <t>Dom</t>
+        </is>
+      </c>
+      <c r="X8" s="81" t="n"/>
+      <c r="Y8" s="85" t="inlineStr">
+        <is>
+          <t>Seg</t>
+        </is>
+      </c>
+      <c r="Z8" s="85" t="inlineStr">
+        <is>
+          <t>Ter</t>
+        </is>
+      </c>
+      <c r="AA8" s="85" t="inlineStr">
+        <is>
+          <t>Qua</t>
+        </is>
+      </c>
+      <c r="AB8" s="85" t="inlineStr">
+        <is>
+          <t>Qui</t>
+        </is>
+      </c>
+      <c r="AC8" s="85" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="AD8" s="86" t="inlineStr">
+        <is>
+          <t>Sáb</t>
+        </is>
+      </c>
+      <c r="AE8" s="86" t="inlineStr">
+        <is>
+          <t>Dom</t>
+        </is>
+      </c>
+      <c r="AF8" s="81" t="n"/>
+      <c r="AG8" s="81" t="n"/>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="87" t="inlineStr"/>
+      <c r="B9" s="87" t="inlineStr"/>
+      <c r="C9" s="87" t="inlineStr"/>
+      <c r="D9" s="88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="89" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="90" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" s="81" t="n"/>
+      <c r="I9" s="87" t="inlineStr"/>
+      <c r="J9" s="87" t="inlineStr"/>
+      <c r="K9" s="87" t="inlineStr"/>
+      <c r="L9" s="87" t="inlineStr"/>
+      <c r="M9" s="87" t="inlineStr"/>
+      <c r="N9" s="87" t="inlineStr"/>
+      <c r="O9" s="91" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" s="81" t="n"/>
+      <c r="Q9" s="87" t="inlineStr"/>
+      <c r="R9" s="87" t="inlineStr"/>
+      <c r="S9" s="87" t="inlineStr"/>
+      <c r="T9" s="87" t="inlineStr"/>
+      <c r="U9" s="87" t="inlineStr"/>
+      <c r="V9" s="87" t="inlineStr"/>
+      <c r="W9" s="91" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" s="81" t="n"/>
+      <c r="Y9" s="87" t="inlineStr"/>
+      <c r="Z9" s="87" t="inlineStr"/>
+      <c r="AA9" s="88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="89" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC9" s="89" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD9" s="90" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE9" s="90" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF9" s="81" t="n"/>
+      <c r="AG9" s="81" t="n"/>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="89" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="89" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="89" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" s="88" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" s="89" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" s="90" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" s="90" t="n">
+        <v>11</v>
+      </c>
+      <c r="H10" s="81" t="n"/>
+      <c r="I10" s="89" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" s="89" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" s="89" t="n">
+        <v>4</v>
+      </c>
+      <c r="L10" s="89" t="n">
+        <v>5</v>
+      </c>
+      <c r="M10" s="89" t="n">
+        <v>6</v>
+      </c>
+      <c r="N10" s="90" t="n">
+        <v>7</v>
+      </c>
+      <c r="O10" s="91" t="n">
+        <v>8</v>
+      </c>
+      <c r="P10" s="81" t="n"/>
+      <c r="Q10" s="89" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" s="89" t="n">
+        <v>3</v>
+      </c>
+      <c r="S10" s="89" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" s="89" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" s="89" t="n">
+        <v>6</v>
+      </c>
+      <c r="V10" s="90" t="n">
+        <v>7</v>
+      </c>
+      <c r="W10" s="91" t="n">
+        <v>8</v>
+      </c>
+      <c r="X10" s="81" t="n"/>
+      <c r="Y10" s="89" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z10" s="89" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA10" s="88" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB10" s="89" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC10" s="89" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD10" s="90" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE10" s="90" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF10" s="81" t="n"/>
+      <c r="AG10" s="81" t="n"/>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="89" t="n">
+        <v>12</v>
+      </c>
+      <c r="B11" s="89" t="n">
+        <v>13</v>
+      </c>
+      <c r="C11" s="89" t="n">
+        <v>14</v>
+      </c>
+      <c r="D11" s="88" t="n">
+        <v>15</v>
+      </c>
+      <c r="E11" s="89" t="n">
+        <v>16</v>
+      </c>
+      <c r="F11" s="90" t="n">
+        <v>17</v>
+      </c>
+      <c r="G11" s="90" t="n">
+        <v>18</v>
+      </c>
+      <c r="H11" s="81" t="n"/>
+      <c r="I11" s="89" t="n">
+        <v>9</v>
+      </c>
+      <c r="J11" s="89" t="n">
+        <v>10</v>
+      </c>
+      <c r="K11" s="89" t="n">
+        <v>11</v>
+      </c>
+      <c r="L11" s="89" t="n">
+        <v>12</v>
+      </c>
+      <c r="M11" s="89" t="n">
+        <v>13</v>
+      </c>
+      <c r="N11" s="90" t="n">
+        <v>14</v>
+      </c>
+      <c r="O11" s="91" t="n">
+        <v>15</v>
+      </c>
+      <c r="P11" s="81" t="n"/>
+      <c r="Q11" s="89" t="n">
+        <v>9</v>
+      </c>
+      <c r="R11" s="89" t="n">
+        <v>10</v>
+      </c>
+      <c r="S11" s="89" t="n">
+        <v>11</v>
+      </c>
+      <c r="T11" s="89" t="n">
+        <v>12</v>
+      </c>
+      <c r="U11" s="89" t="n">
+        <v>13</v>
+      </c>
+      <c r="V11" s="90" t="n">
+        <v>14</v>
+      </c>
+      <c r="W11" s="91" t="n">
+        <v>15</v>
+      </c>
+      <c r="X11" s="81" t="n"/>
+      <c r="Y11" s="89" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z11" s="89" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA11" s="88" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB11" s="89" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC11" s="89" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD11" s="90" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE11" s="90" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF11" s="81" t="n"/>
+      <c r="AG11" s="81" t="n"/>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="89" t="n">
+        <v>19</v>
+      </c>
+      <c r="B12" s="89" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" s="89" t="n">
+        <v>21</v>
+      </c>
+      <c r="D12" s="88" t="n">
+        <v>22</v>
+      </c>
+      <c r="E12" s="89" t="n">
+        <v>23</v>
+      </c>
+      <c r="F12" s="90" t="n">
+        <v>24</v>
+      </c>
+      <c r="G12" s="90" t="n">
+        <v>25</v>
+      </c>
+      <c r="H12" s="81" t="n"/>
+      <c r="I12" s="89" t="n">
+        <v>16</v>
+      </c>
+      <c r="J12" s="89" t="n">
+        <v>17</v>
+      </c>
+      <c r="K12" s="89" t="n">
+        <v>18</v>
+      </c>
+      <c r="L12" s="89" t="n">
+        <v>19</v>
+      </c>
+      <c r="M12" s="89" t="n">
+        <v>20</v>
+      </c>
+      <c r="N12" s="90" t="n">
+        <v>21</v>
+      </c>
+      <c r="O12" s="91" t="n">
+        <v>22</v>
+      </c>
+      <c r="P12" s="81" t="n"/>
+      <c r="Q12" s="89" t="n">
+        <v>16</v>
+      </c>
+      <c r="R12" s="89" t="n">
+        <v>17</v>
+      </c>
+      <c r="S12" s="89" t="n">
+        <v>18</v>
+      </c>
+      <c r="T12" s="89" t="n">
+        <v>19</v>
+      </c>
+      <c r="U12" s="89" t="n">
+        <v>20</v>
+      </c>
+      <c r="V12" s="90" t="n">
+        <v>21</v>
+      </c>
+      <c r="W12" s="91" t="n">
+        <v>22</v>
+      </c>
+      <c r="X12" s="81" t="n"/>
+      <c r="Y12" s="89" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z12" s="89" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA12" s="88" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB12" s="89" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC12" s="89" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD12" s="90" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE12" s="90" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF12" s="81" t="n"/>
+      <c r="AG12" s="81" t="n"/>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="89" t="n">
+        <v>26</v>
+      </c>
+      <c r="B13" s="89" t="n">
+        <v>27</v>
+      </c>
+      <c r="C13" s="89" t="n">
+        <v>28</v>
+      </c>
+      <c r="D13" s="89" t="n">
+        <v>29</v>
+      </c>
+      <c r="E13" s="89" t="n">
+        <v>30</v>
+      </c>
+      <c r="F13" s="90" t="n">
+        <v>31</v>
+      </c>
+      <c r="G13" s="87" t="inlineStr"/>
+      <c r="H13" s="81" t="n"/>
+      <c r="I13" s="89" t="n">
+        <v>23</v>
+      </c>
+      <c r="J13" s="89" t="n">
+        <v>24</v>
+      </c>
+      <c r="K13" s="89" t="n">
+        <v>25</v>
+      </c>
+      <c r="L13" s="89" t="n">
+        <v>26</v>
+      </c>
+      <c r="M13" s="89" t="n">
+        <v>27</v>
+      </c>
+      <c r="N13" s="90" t="n">
+        <v>28</v>
+      </c>
+      <c r="O13" s="87" t="inlineStr"/>
+      <c r="P13" s="81" t="n"/>
+      <c r="Q13" s="89" t="n">
+        <v>23</v>
+      </c>
+      <c r="R13" s="89" t="n">
+        <v>24</v>
+      </c>
+      <c r="S13" s="89" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" s="89" t="n">
+        <v>26</v>
+      </c>
+      <c r="U13" s="89" t="n">
+        <v>27</v>
+      </c>
+      <c r="V13" s="90" t="n">
+        <v>28</v>
+      </c>
+      <c r="W13" s="90" t="n">
+        <v>29</v>
+      </c>
+      <c r="X13" s="81" t="n"/>
+      <c r="Y13" s="89" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z13" s="89" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA13" s="89" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB13" s="89" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC13" s="87" t="inlineStr"/>
+      <c r="AD13" s="87" t="inlineStr"/>
+      <c r="AE13" s="87" t="inlineStr"/>
+      <c r="AF13" s="81" t="n"/>
+      <c r="AG13" s="81" t="n"/>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="87" t="n"/>
+      <c r="B14" s="87" t="n"/>
+      <c r="C14" s="87" t="n"/>
+      <c r="D14" s="87" t="n"/>
+      <c r="E14" s="87" t="n"/>
+      <c r="F14" s="87" t="n"/>
+      <c r="G14" s="87" t="n"/>
+      <c r="H14" s="81" t="n"/>
+      <c r="I14" s="87" t="n"/>
+      <c r="J14" s="87" t="n"/>
+      <c r="K14" s="87" t="n"/>
+      <c r="L14" s="87" t="n"/>
+      <c r="M14" s="87" t="n"/>
+      <c r="N14" s="87" t="n"/>
+      <c r="O14" s="87" t="n"/>
+      <c r="P14" s="81" t="n"/>
+      <c r="Q14" s="89" t="n">
+        <v>30</v>
+      </c>
+      <c r="R14" s="89" t="n">
+        <v>31</v>
+      </c>
+      <c r="S14" s="87" t="inlineStr"/>
+      <c r="T14" s="87" t="inlineStr"/>
+      <c r="U14" s="87" t="inlineStr"/>
+      <c r="V14" s="87" t="inlineStr"/>
+      <c r="W14" s="87" t="inlineStr"/>
+      <c r="X14" s="81" t="n"/>
+      <c r="Y14" s="87" t="n"/>
+      <c r="Z14" s="87" t="n"/>
+      <c r="AA14" s="87" t="n"/>
+      <c r="AB14" s="87" t="n"/>
+      <c r="AC14" s="87" t="n"/>
+      <c r="AD14" s="87" t="n"/>
+      <c r="AE14" s="87" t="n"/>
+      <c r="AF14" s="81" t="n"/>
+      <c r="AG14" s="81" t="n"/>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="81" t="n"/>
+      <c r="B15" s="81" t="n"/>
+      <c r="C15" s="81" t="n"/>
+      <c r="D15" s="81" t="n"/>
+      <c r="E15" s="81" t="n"/>
+      <c r="F15" s="81" t="n"/>
+      <c r="G15" s="81" t="n"/>
+      <c r="H15" s="81" t="n"/>
+      <c r="I15" s="81" t="n"/>
+      <c r="J15" s="81" t="n"/>
+      <c r="K15" s="81" t="n"/>
+      <c r="L15" s="81" t="n"/>
+      <c r="M15" s="81" t="n"/>
+      <c r="N15" s="81" t="n"/>
+      <c r="O15" s="81" t="n"/>
+      <c r="P15" s="81" t="n"/>
+      <c r="Q15" s="81" t="n"/>
+      <c r="R15" s="81" t="n"/>
+      <c r="S15" s="81" t="n"/>
+      <c r="T15" s="81" t="n"/>
+      <c r="U15" s="81" t="n"/>
+      <c r="V15" s="81" t="n"/>
+      <c r="W15" s="81" t="n"/>
+      <c r="X15" s="81" t="n"/>
+      <c r="Y15" s="81" t="n"/>
+      <c r="Z15" s="81" t="n"/>
+      <c r="AA15" s="81" t="n"/>
+      <c r="AB15" s="81" t="n"/>
+      <c r="AC15" s="81" t="n"/>
+      <c r="AD15" s="81" t="n"/>
+      <c r="AE15" s="81" t="n"/>
+      <c r="AF15" s="81" t="n"/>
+      <c r="AG15" s="81" t="n"/>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="81" t="n"/>
+      <c r="B16" s="81" t="n"/>
+      <c r="C16" s="81" t="n"/>
+      <c r="D16" s="81" t="n"/>
+      <c r="E16" s="81" t="n"/>
+      <c r="F16" s="81" t="n"/>
+      <c r="G16" s="81" t="n"/>
+      <c r="H16" s="81" t="n"/>
+      <c r="I16" s="81" t="n"/>
+      <c r="J16" s="81" t="n"/>
+      <c r="K16" s="81" t="n"/>
+      <c r="L16" s="81" t="n"/>
+      <c r="M16" s="81" t="n"/>
+      <c r="N16" s="81" t="n"/>
+      <c r="O16" s="81" t="n"/>
+      <c r="P16" s="81" t="n"/>
+      <c r="Q16" s="81" t="n"/>
+      <c r="R16" s="81" t="n"/>
+      <c r="S16" s="81" t="n"/>
+      <c r="T16" s="81" t="n"/>
+      <c r="U16" s="81" t="n"/>
+      <c r="V16" s="81" t="n"/>
+      <c r="W16" s="81" t="n"/>
+      <c r="X16" s="81" t="n"/>
+      <c r="Y16" s="81" t="n"/>
+      <c r="Z16" s="81" t="n"/>
+      <c r="AA16" s="81" t="n"/>
+      <c r="AB16" s="81" t="n"/>
+      <c r="AC16" s="81" t="n"/>
+      <c r="AD16" s="81" t="n"/>
+      <c r="AE16" s="81" t="n"/>
+      <c r="AF16" s="81" t="n"/>
+      <c r="AG16" s="81" t="n"/>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="81" t="n"/>
+      <c r="B17" s="81" t="n"/>
+      <c r="C17" s="81" t="n"/>
+      <c r="D17" s="81" t="n"/>
+      <c r="E17" s="81" t="n"/>
+      <c r="F17" s="81" t="n"/>
+      <c r="G17" s="81" t="n"/>
+      <c r="H17" s="81" t="n"/>
+      <c r="I17" s="81" t="n"/>
+      <c r="J17" s="81" t="n"/>
+      <c r="K17" s="81" t="n"/>
+      <c r="L17" s="81" t="n"/>
+      <c r="M17" s="81" t="n"/>
+      <c r="N17" s="81" t="n"/>
+      <c r="O17" s="81" t="n"/>
+      <c r="P17" s="81" t="n"/>
+      <c r="Q17" s="81" t="n"/>
+      <c r="R17" s="81" t="n"/>
+      <c r="S17" s="81" t="n"/>
+      <c r="T17" s="81" t="n"/>
+      <c r="U17" s="81" t="n"/>
+      <c r="V17" s="81" t="n"/>
+      <c r="W17" s="81" t="n"/>
+      <c r="X17" s="81" t="n"/>
+      <c r="Y17" s="81" t="n"/>
+      <c r="Z17" s="81" t="n"/>
+      <c r="AA17" s="81" t="n"/>
+      <c r="AB17" s="81" t="n"/>
+      <c r="AC17" s="81" t="n"/>
+      <c r="AD17" s="81" t="n"/>
+      <c r="AE17" s="81" t="n"/>
+      <c r="AF17" s="81" t="n"/>
+      <c r="AG17" s="81" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="84" t="inlineStr">
+        <is>
+          <t>MAIO 2026</t>
+        </is>
+      </c>
+      <c r="H18" s="81" t="n"/>
+      <c r="I18" s="84" t="inlineStr">
+        <is>
+          <t>JUNHO 2026</t>
+        </is>
+      </c>
+      <c r="P18" s="81" t="n"/>
+      <c r="Q18" s="92" t="inlineStr">
+        <is>
+          <t>JULHO 2026</t>
+        </is>
+      </c>
+      <c r="X18" s="81" t="n"/>
+      <c r="Y18" s="92" t="inlineStr">
+        <is>
+          <t>AGOSTO 2026</t>
+        </is>
+      </c>
+      <c r="AF18" s="81" t="n"/>
+      <c r="AG18" s="81" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="85" t="inlineStr">
+        <is>
+          <t>Seg</t>
+        </is>
+      </c>
+      <c r="B19" s="85" t="inlineStr">
+        <is>
+          <t>Ter</t>
+        </is>
+      </c>
+      <c r="C19" s="85" t="inlineStr">
+        <is>
+          <t>Qua</t>
+        </is>
+      </c>
+      <c r="D19" s="85" t="inlineStr">
+        <is>
+          <t>Qui</t>
+        </is>
+      </c>
+      <c r="E19" s="85" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="F19" s="86" t="inlineStr">
+        <is>
+          <t>Sáb</t>
+        </is>
+      </c>
+      <c r="G19" s="86" t="inlineStr">
+        <is>
+          <t>Dom</t>
+        </is>
+      </c>
+      <c r="H19" s="81" t="n"/>
+      <c r="I19" s="85" t="inlineStr">
+        <is>
+          <t>Seg</t>
+        </is>
+      </c>
+      <c r="J19" s="85" t="inlineStr">
+        <is>
+          <t>Ter</t>
+        </is>
+      </c>
+      <c r="K19" s="85" t="inlineStr">
+        <is>
+          <t>Qua</t>
+        </is>
+      </c>
+      <c r="L19" s="85" t="inlineStr">
+        <is>
+          <t>Qui</t>
+        </is>
+      </c>
+      <c r="M19" s="85" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="N19" s="86" t="inlineStr">
+        <is>
+          <t>Sáb</t>
+        </is>
+      </c>
+      <c r="O19" s="86" t="inlineStr">
+        <is>
+          <t>Dom</t>
+        </is>
+      </c>
+      <c r="P19" s="81" t="n"/>
+      <c r="Q19" s="85" t="inlineStr">
+        <is>
+          <t>Seg</t>
+        </is>
+      </c>
+      <c r="R19" s="85" t="inlineStr">
+        <is>
+          <t>Ter</t>
+        </is>
+      </c>
+      <c r="S19" s="85" t="inlineStr">
+        <is>
+          <t>Qua</t>
+        </is>
+      </c>
+      <c r="T19" s="85" t="inlineStr">
+        <is>
+          <t>Qui</t>
+        </is>
+      </c>
+      <c r="U19" s="85" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="V19" s="86" t="inlineStr">
+        <is>
+          <t>Sáb</t>
+        </is>
+      </c>
+      <c r="W19" s="86" t="inlineStr">
+        <is>
+          <t>Dom</t>
+        </is>
+      </c>
+      <c r="X19" s="81" t="n"/>
+      <c r="Y19" s="85" t="inlineStr">
+        <is>
+          <t>Seg</t>
+        </is>
+      </c>
+      <c r="Z19" s="85" t="inlineStr">
+        <is>
+          <t>Ter</t>
+        </is>
+      </c>
+      <c r="AA19" s="85" t="inlineStr">
+        <is>
+          <t>Qua</t>
+        </is>
+      </c>
+      <c r="AB19" s="85" t="inlineStr">
+        <is>
+          <t>Qui</t>
+        </is>
+      </c>
+      <c r="AC19" s="85" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="AD19" s="86" t="inlineStr">
+        <is>
+          <t>Sáb</t>
+        </is>
+      </c>
+      <c r="AE19" s="86" t="inlineStr">
+        <is>
+          <t>Dom</t>
+        </is>
+      </c>
+      <c r="AF19" s="81" t="n"/>
+      <c r="AG19" s="81" t="n"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="87" t="inlineStr"/>
+      <c r="B20" s="87" t="inlineStr"/>
+      <c r="C20" s="87" t="inlineStr"/>
+      <c r="D20" s="87" t="inlineStr"/>
+      <c r="E20" s="88" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" s="81" t="n"/>
+      <c r="I20" s="88" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="89" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" s="89" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" s="89" t="n">
+        <v>4</v>
+      </c>
+      <c r="M20" s="89" t="n">
+        <v>5</v>
+      </c>
+      <c r="N20" s="90" t="n">
+        <v>6</v>
+      </c>
+      <c r="O20" s="90" t="n">
+        <v>7</v>
+      </c>
+      <c r="P20" s="81" t="n"/>
+      <c r="Q20" s="87" t="inlineStr"/>
+      <c r="R20" s="87" t="inlineStr"/>
+      <c r="S20" s="88" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" s="89" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" s="89" t="n">
+        <v>3</v>
+      </c>
+      <c r="V20" s="90" t="n">
+        <v>4</v>
+      </c>
+      <c r="W20" s="90" t="n">
+        <v>5</v>
+      </c>
+      <c r="X20" s="81" t="n"/>
+      <c r="Y20" s="87" t="inlineStr"/>
+      <c r="Z20" s="87" t="inlineStr"/>
+      <c r="AA20" s="87" t="inlineStr"/>
+      <c r="AB20" s="87" t="inlineStr"/>
+      <c r="AC20" s="87" t="inlineStr"/>
+      <c r="AD20" s="91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE20" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF20" s="81" t="n"/>
+      <c r="AG20" s="81" t="n"/>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="89" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="89" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" s="89" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" s="89" t="n">
+        <v>7</v>
+      </c>
+      <c r="E21" s="88" t="n">
+        <v>8</v>
+      </c>
+      <c r="F21" s="90" t="n">
+        <v>9</v>
+      </c>
+      <c r="G21" s="90" t="n">
+        <v>10</v>
+      </c>
+      <c r="H21" s="81" t="n"/>
+      <c r="I21" s="88" t="n">
+        <v>8</v>
+      </c>
+      <c r="J21" s="89" t="n">
+        <v>9</v>
+      </c>
+      <c r="K21" s="89" t="n">
+        <v>10</v>
+      </c>
+      <c r="L21" s="89" t="n">
+        <v>11</v>
+      </c>
+      <c r="M21" s="89" t="n">
+        <v>12</v>
+      </c>
+      <c r="N21" s="90" t="n">
+        <v>13</v>
+      </c>
+      <c r="O21" s="90" t="n">
+        <v>14</v>
+      </c>
+      <c r="P21" s="81" t="n"/>
+      <c r="Q21" s="89" t="n">
+        <v>6</v>
+      </c>
+      <c r="R21" s="89" t="n">
+        <v>7</v>
+      </c>
+      <c r="S21" s="88" t="n">
+        <v>8</v>
+      </c>
+      <c r="T21" s="89" t="n">
+        <v>9</v>
+      </c>
+      <c r="U21" s="89" t="n">
+        <v>10</v>
+      </c>
+      <c r="V21" s="90" t="n">
+        <v>11</v>
+      </c>
+      <c r="W21" s="90" t="n">
+        <v>12</v>
+      </c>
+      <c r="X21" s="81" t="n"/>
+      <c r="Y21" s="89" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="89" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA21" s="89" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB21" s="89" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC21" s="89" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD21" s="91" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE21" s="90" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF21" s="81" t="n"/>
+      <c r="AG21" s="81" t="n"/>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="89" t="n">
+        <v>11</v>
+      </c>
+      <c r="B22" s="89" t="n">
+        <v>12</v>
+      </c>
+      <c r="C22" s="89" t="n">
+        <v>13</v>
+      </c>
+      <c r="D22" s="89" t="n">
+        <v>14</v>
+      </c>
+      <c r="E22" s="88" t="n">
+        <v>15</v>
+      </c>
+      <c r="F22" s="90" t="n">
+        <v>16</v>
+      </c>
+      <c r="G22" s="90" t="n">
+        <v>17</v>
+      </c>
+      <c r="H22" s="81" t="n"/>
+      <c r="I22" s="88" t="n">
+        <v>15</v>
+      </c>
+      <c r="J22" s="89" t="n">
+        <v>16</v>
+      </c>
+      <c r="K22" s="89" t="n">
+        <v>17</v>
+      </c>
+      <c r="L22" s="89" t="n">
+        <v>18</v>
+      </c>
+      <c r="M22" s="89" t="n">
+        <v>19</v>
+      </c>
+      <c r="N22" s="90" t="n">
+        <v>20</v>
+      </c>
+      <c r="O22" s="90" t="n">
+        <v>21</v>
+      </c>
+      <c r="P22" s="81" t="n"/>
+      <c r="Q22" s="89" t="n">
+        <v>13</v>
+      </c>
+      <c r="R22" s="89" t="n">
+        <v>14</v>
+      </c>
+      <c r="S22" s="88" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" s="89" t="n">
+        <v>16</v>
+      </c>
+      <c r="U22" s="89" t="n">
+        <v>17</v>
+      </c>
+      <c r="V22" s="90" t="n">
+        <v>18</v>
+      </c>
+      <c r="W22" s="90" t="n">
+        <v>19</v>
+      </c>
+      <c r="X22" s="81" t="n"/>
+      <c r="Y22" s="89" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z22" s="89" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA22" s="89" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB22" s="89" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC22" s="89" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD22" s="91" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE22" s="90" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF22" s="81" t="n"/>
+      <c r="AG22" s="81" t="n"/>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="89" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="89" t="n">
+        <v>19</v>
+      </c>
+      <c r="C23" s="89" t="n">
+        <v>20</v>
+      </c>
+      <c r="D23" s="89" t="n">
+        <v>21</v>
+      </c>
+      <c r="E23" s="88" t="n">
+        <v>22</v>
+      </c>
+      <c r="F23" s="90" t="n">
+        <v>23</v>
+      </c>
+      <c r="G23" s="90" t="n">
+        <v>24</v>
+      </c>
+      <c r="H23" s="81" t="n"/>
+      <c r="I23" s="88" t="n">
+        <v>22</v>
+      </c>
+      <c r="J23" s="89" t="n">
+        <v>23</v>
+      </c>
+      <c r="K23" s="89" t="n">
+        <v>24</v>
+      </c>
+      <c r="L23" s="89" t="n">
+        <v>25</v>
+      </c>
+      <c r="M23" s="89" t="n">
+        <v>26</v>
+      </c>
+      <c r="N23" s="90" t="n">
+        <v>27</v>
+      </c>
+      <c r="O23" s="90" t="n">
+        <v>28</v>
+      </c>
+      <c r="P23" s="81" t="n"/>
+      <c r="Q23" s="89" t="n">
+        <v>20</v>
+      </c>
+      <c r="R23" s="89" t="n">
+        <v>21</v>
+      </c>
+      <c r="S23" s="88" t="n">
+        <v>22</v>
+      </c>
+      <c r="T23" s="89" t="n">
+        <v>23</v>
+      </c>
+      <c r="U23" s="89" t="n">
+        <v>24</v>
+      </c>
+      <c r="V23" s="90" t="n">
+        <v>25</v>
+      </c>
+      <c r="W23" s="90" t="n">
+        <v>26</v>
+      </c>
+      <c r="X23" s="81" t="n"/>
+      <c r="Y23" s="89" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z23" s="89" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA23" s="89" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB23" s="89" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC23" s="89" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD23" s="91" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE23" s="90" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF23" s="81" t="n"/>
+      <c r="AG23" s="81" t="n"/>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="89" t="n">
+        <v>25</v>
+      </c>
+      <c r="B24" s="89" t="n">
+        <v>26</v>
+      </c>
+      <c r="C24" s="89" t="n">
+        <v>27</v>
+      </c>
+      <c r="D24" s="89" t="n">
+        <v>28</v>
+      </c>
+      <c r="E24" s="89" t="n">
+        <v>29</v>
+      </c>
+      <c r="F24" s="90" t="n">
+        <v>30</v>
+      </c>
+      <c r="G24" s="90" t="n">
+        <v>31</v>
+      </c>
+      <c r="H24" s="81" t="n"/>
+      <c r="I24" s="89" t="n">
+        <v>29</v>
+      </c>
+      <c r="J24" s="89" t="n">
+        <v>30</v>
+      </c>
+      <c r="K24" s="87" t="inlineStr"/>
+      <c r="L24" s="87" t="inlineStr"/>
+      <c r="M24" s="87" t="inlineStr"/>
+      <c r="N24" s="87" t="inlineStr"/>
+      <c r="O24" s="87" t="inlineStr"/>
+      <c r="P24" s="81" t="n"/>
+      <c r="Q24" s="89" t="n">
+        <v>27</v>
+      </c>
+      <c r="R24" s="89" t="n">
+        <v>28</v>
+      </c>
+      <c r="S24" s="89" t="n">
+        <v>29</v>
+      </c>
+      <c r="T24" s="89" t="n">
+        <v>30</v>
+      </c>
+      <c r="U24" s="89" t="n">
+        <v>31</v>
+      </c>
+      <c r="V24" s="87" t="inlineStr"/>
+      <c r="W24" s="87" t="inlineStr"/>
+      <c r="X24" s="81" t="n"/>
+      <c r="Y24" s="89" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z24" s="89" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA24" s="89" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB24" s="89" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC24" s="89" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD24" s="90" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE24" s="90" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF24" s="81" t="n"/>
+      <c r="AG24" s="81" t="n"/>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="87" t="n"/>
+      <c r="B25" s="87" t="n"/>
+      <c r="C25" s="87" t="n"/>
+      <c r="D25" s="87" t="n"/>
+      <c r="E25" s="87" t="n"/>
+      <c r="F25" s="87" t="n"/>
+      <c r="G25" s="87" t="n"/>
+      <c r="H25" s="81" t="n"/>
+      <c r="I25" s="87" t="n"/>
+      <c r="J25" s="87" t="n"/>
+      <c r="K25" s="87" t="n"/>
+      <c r="L25" s="87" t="n"/>
+      <c r="M25" s="87" t="n"/>
+      <c r="N25" s="87" t="n"/>
+      <c r="O25" s="87" t="n"/>
+      <c r="P25" s="81" t="n"/>
+      <c r="Q25" s="87" t="n"/>
+      <c r="R25" s="87" t="n"/>
+      <c r="S25" s="87" t="n"/>
+      <c r="T25" s="87" t="n"/>
+      <c r="U25" s="87" t="n"/>
+      <c r="V25" s="87" t="n"/>
+      <c r="W25" s="87" t="n"/>
+      <c r="X25" s="81" t="n"/>
+      <c r="Y25" s="89" t="n">
+        <v>31</v>
+      </c>
+      <c r="Z25" s="87" t="inlineStr"/>
+      <c r="AA25" s="87" t="inlineStr"/>
+      <c r="AB25" s="87" t="inlineStr"/>
+      <c r="AC25" s="87" t="inlineStr"/>
+      <c r="AD25" s="87" t="inlineStr"/>
+      <c r="AE25" s="87" t="inlineStr"/>
+      <c r="AF25" s="81" t="n"/>
+      <c r="AG25" s="81" t="n"/>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="81" t="n"/>
+      <c r="B26" s="81" t="n"/>
+      <c r="C26" s="81" t="n"/>
+      <c r="D26" s="81" t="n"/>
+      <c r="E26" s="81" t="n"/>
+      <c r="F26" s="81" t="n"/>
+      <c r="G26" s="81" t="n"/>
+      <c r="H26" s="81" t="n"/>
+      <c r="I26" s="81" t="n"/>
+      <c r="J26" s="81" t="n"/>
+      <c r="K26" s="81" t="n"/>
+      <c r="L26" s="81" t="n"/>
+      <c r="M26" s="81" t="n"/>
+      <c r="N26" s="81" t="n"/>
+      <c r="O26" s="81" t="n"/>
+      <c r="P26" s="81" t="n"/>
+      <c r="Q26" s="81" t="n"/>
+      <c r="R26" s="81" t="n"/>
+      <c r="S26" s="81" t="n"/>
+      <c r="T26" s="81" t="n"/>
+      <c r="U26" s="81" t="n"/>
+      <c r="V26" s="81" t="n"/>
+      <c r="W26" s="81" t="n"/>
+      <c r="X26" s="81" t="n"/>
+      <c r="Y26" s="81" t="n"/>
+      <c r="Z26" s="81" t="n"/>
+      <c r="AA26" s="81" t="n"/>
+      <c r="AB26" s="81" t="n"/>
+      <c r="AC26" s="81" t="n"/>
+      <c r="AD26" s="81" t="n"/>
+      <c r="AE26" s="81" t="n"/>
+      <c r="AF26" s="81" t="n"/>
+      <c r="AG26" s="81" t="n"/>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="81" t="n"/>
+      <c r="B27" s="81" t="n"/>
+      <c r="C27" s="81" t="n"/>
+      <c r="D27" s="81" t="n"/>
+      <c r="E27" s="81" t="n"/>
+      <c r="F27" s="81" t="n"/>
+      <c r="G27" s="81" t="n"/>
+      <c r="H27" s="81" t="n"/>
+      <c r="I27" s="81" t="n"/>
+      <c r="J27" s="81" t="n"/>
+      <c r="K27" s="81" t="n"/>
+      <c r="L27" s="81" t="n"/>
+      <c r="M27" s="81" t="n"/>
+      <c r="N27" s="81" t="n"/>
+      <c r="O27" s="81" t="n"/>
+      <c r="P27" s="81" t="n"/>
+      <c r="Q27" s="81" t="n"/>
+      <c r="R27" s="81" t="n"/>
+      <c r="S27" s="81" t="n"/>
+      <c r="T27" s="81" t="n"/>
+      <c r="U27" s="81" t="n"/>
+      <c r="V27" s="81" t="n"/>
+      <c r="W27" s="81" t="n"/>
+      <c r="X27" s="81" t="n"/>
+      <c r="Y27" s="81" t="n"/>
+      <c r="Z27" s="81" t="n"/>
+      <c r="AA27" s="81" t="n"/>
+      <c r="AB27" s="81" t="n"/>
+      <c r="AC27" s="81" t="n"/>
+      <c r="AD27" s="81" t="n"/>
+      <c r="AE27" s="81" t="n"/>
+      <c r="AF27" s="81" t="n"/>
+      <c r="AG27" s="81" t="n"/>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="81" t="n"/>
+      <c r="B28" s="81" t="n"/>
+      <c r="C28" s="81" t="n"/>
+      <c r="D28" s="81" t="n"/>
+      <c r="E28" s="81" t="n"/>
+      <c r="F28" s="81" t="n"/>
+      <c r="G28" s="81" t="n"/>
+      <c r="H28" s="81" t="n"/>
+      <c r="I28" s="81" t="n"/>
+      <c r="J28" s="81" t="n"/>
+      <c r="K28" s="81" t="n"/>
+      <c r="L28" s="81" t="n"/>
+      <c r="M28" s="81" t="n"/>
+      <c r="N28" s="81" t="n"/>
+      <c r="O28" s="81" t="n"/>
+      <c r="P28" s="81" t="n"/>
+      <c r="Q28" s="81" t="n"/>
+      <c r="R28" s="81" t="n"/>
+      <c r="S28" s="81" t="n"/>
+      <c r="T28" s="81" t="n"/>
+      <c r="U28" s="81" t="n"/>
+      <c r="V28" s="81" t="n"/>
+      <c r="W28" s="81" t="n"/>
+      <c r="X28" s="81" t="n"/>
+      <c r="Y28" s="81" t="n"/>
+      <c r="Z28" s="81" t="n"/>
+      <c r="AA28" s="81" t="n"/>
+      <c r="AB28" s="81" t="n"/>
+      <c r="AC28" s="81" t="n"/>
+      <c r="AD28" s="81" t="n"/>
+      <c r="AE28" s="81" t="n"/>
+      <c r="AF28" s="81" t="n"/>
+      <c r="AG28" s="81" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="92" t="inlineStr">
+        <is>
+          <t>SETEMBRO 2026</t>
+        </is>
+      </c>
+      <c r="H29" s="81" t="n"/>
+      <c r="I29" s="83" t="inlineStr">
+        <is>
+          <t>OUTUBRO 2026</t>
+        </is>
+      </c>
+      <c r="P29" s="81" t="n"/>
+      <c r="Q29" s="84" t="inlineStr">
+        <is>
+          <t>NOVEMBRO 2026</t>
+        </is>
+      </c>
+      <c r="X29" s="81" t="n"/>
+      <c r="Y29" s="92" t="inlineStr">
+        <is>
+          <t>DEZEMBRO 2026</t>
+        </is>
+      </c>
+      <c r="AF29" s="81" t="n"/>
+      <c r="AG29" s="81" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="85" t="inlineStr">
+        <is>
+          <t>Seg</t>
+        </is>
+      </c>
+      <c r="B30" s="85" t="inlineStr">
+        <is>
+          <t>Ter</t>
+        </is>
+      </c>
+      <c r="C30" s="85" t="inlineStr">
+        <is>
+          <t>Qua</t>
+        </is>
+      </c>
+      <c r="D30" s="85" t="inlineStr">
+        <is>
+          <t>Qui</t>
+        </is>
+      </c>
+      <c r="E30" s="85" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="F30" s="86" t="inlineStr">
+        <is>
+          <t>Sáb</t>
+        </is>
+      </c>
+      <c r="G30" s="86" t="inlineStr">
+        <is>
+          <t>Dom</t>
+        </is>
+      </c>
+      <c r="H30" s="81" t="n"/>
+      <c r="I30" s="85" t="inlineStr">
+        <is>
+          <t>Seg</t>
+        </is>
+      </c>
+      <c r="J30" s="85" t="inlineStr">
+        <is>
+          <t>Ter</t>
+        </is>
+      </c>
+      <c r="K30" s="85" t="inlineStr">
+        <is>
+          <t>Qua</t>
+        </is>
+      </c>
+      <c r="L30" s="85" t="inlineStr">
+        <is>
+          <t>Qui</t>
+        </is>
+      </c>
+      <c r="M30" s="85" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="N30" s="86" t="inlineStr">
+        <is>
+          <t>Sáb</t>
+        </is>
+      </c>
+      <c r="O30" s="86" t="inlineStr">
+        <is>
+          <t>Dom</t>
+        </is>
+      </c>
+      <c r="P30" s="81" t="n"/>
+      <c r="Q30" s="85" t="inlineStr">
+        <is>
+          <t>Seg</t>
+        </is>
+      </c>
+      <c r="R30" s="85" t="inlineStr">
+        <is>
+          <t>Ter</t>
+        </is>
+      </c>
+      <c r="S30" s="85" t="inlineStr">
+        <is>
+          <t>Qua</t>
+        </is>
+      </c>
+      <c r="T30" s="85" t="inlineStr">
+        <is>
+          <t>Qui</t>
+        </is>
+      </c>
+      <c r="U30" s="85" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="V30" s="86" t="inlineStr">
+        <is>
+          <t>Sáb</t>
+        </is>
+      </c>
+      <c r="W30" s="86" t="inlineStr">
+        <is>
+          <t>Dom</t>
+        </is>
+      </c>
+      <c r="X30" s="81" t="n"/>
+      <c r="Y30" s="85" t="inlineStr">
+        <is>
+          <t>Seg</t>
+        </is>
+      </c>
+      <c r="Z30" s="85" t="inlineStr">
+        <is>
+          <t>Ter</t>
+        </is>
+      </c>
+      <c r="AA30" s="85" t="inlineStr">
+        <is>
+          <t>Qua</t>
+        </is>
+      </c>
+      <c r="AB30" s="85" t="inlineStr">
+        <is>
+          <t>Qui</t>
+        </is>
+      </c>
+      <c r="AC30" s="85" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="AD30" s="86" t="inlineStr">
+        <is>
+          <t>Sáb</t>
+        </is>
+      </c>
+      <c r="AE30" s="86" t="inlineStr">
+        <is>
+          <t>Dom</t>
+        </is>
+      </c>
+      <c r="AF30" s="81" t="n"/>
+      <c r="AG30" s="81" t="n"/>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="87" t="inlineStr"/>
+      <c r="B31" s="88" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="89" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="89" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" s="89" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" s="90" t="n">
+        <v>5</v>
+      </c>
+      <c r="G31" s="90" t="n">
+        <v>6</v>
+      </c>
+      <c r="H31" s="81" t="n"/>
+      <c r="I31" s="87" t="inlineStr"/>
+      <c r="J31" s="87" t="inlineStr"/>
+      <c r="K31" s="87" t="inlineStr"/>
+      <c r="L31" s="88" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" s="89" t="n">
+        <v>2</v>
+      </c>
+      <c r="N31" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="O31" s="90" t="n">
+        <v>4</v>
+      </c>
+      <c r="P31" s="81" t="n"/>
+      <c r="Q31" s="87" t="inlineStr"/>
+      <c r="R31" s="87" t="inlineStr"/>
+      <c r="S31" s="87" t="inlineStr"/>
+      <c r="T31" s="87" t="inlineStr"/>
+      <c r="U31" s="87" t="inlineStr"/>
+      <c r="V31" s="87" t="inlineStr"/>
+      <c r="W31" s="91" t="n">
+        <v>1</v>
+      </c>
+      <c r="X31" s="81" t="n"/>
+      <c r="Y31" s="87" t="inlineStr"/>
+      <c r="Z31" s="88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA31" s="89" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB31" s="89" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC31" s="89" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD31" s="90" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE31" s="90" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF31" s="81" t="n"/>
+      <c r="AG31" s="81" t="n"/>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="89" t="n">
+        <v>7</v>
+      </c>
+      <c r="B32" s="88" t="n">
+        <v>8</v>
+      </c>
+      <c r="C32" s="89" t="n">
+        <v>9</v>
+      </c>
+      <c r="D32" s="89" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" s="89" t="n">
+        <v>11</v>
+      </c>
+      <c r="F32" s="90" t="n">
+        <v>12</v>
+      </c>
+      <c r="G32" s="90" t="n">
+        <v>13</v>
+      </c>
+      <c r="H32" s="81" t="n"/>
+      <c r="I32" s="89" t="n">
+        <v>5</v>
+      </c>
+      <c r="J32" s="89" t="n">
+        <v>6</v>
+      </c>
+      <c r="K32" s="89" t="n">
+        <v>7</v>
+      </c>
+      <c r="L32" s="88" t="n">
+        <v>8</v>
+      </c>
+      <c r="M32" s="89" t="n">
+        <v>9</v>
+      </c>
+      <c r="N32" s="90" t="n">
+        <v>10</v>
+      </c>
+      <c r="O32" s="90" t="n">
+        <v>11</v>
+      </c>
+      <c r="P32" s="81" t="n"/>
+      <c r="Q32" s="89" t="n">
+        <v>2</v>
+      </c>
+      <c r="R32" s="89" t="n">
+        <v>3</v>
+      </c>
+      <c r="S32" s="89" t="n">
+        <v>4</v>
+      </c>
+      <c r="T32" s="89" t="n">
+        <v>5</v>
+      </c>
+      <c r="U32" s="89" t="n">
+        <v>6</v>
+      </c>
+      <c r="V32" s="90" t="n">
+        <v>7</v>
+      </c>
+      <c r="W32" s="91" t="n">
+        <v>8</v>
+      </c>
+      <c r="X32" s="81" t="n"/>
+      <c r="Y32" s="89" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z32" s="88" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA32" s="89" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB32" s="89" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC32" s="89" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD32" s="90" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE32" s="90" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF32" s="81" t="n"/>
+      <c r="AG32" s="81" t="n"/>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="89" t="n">
+        <v>14</v>
+      </c>
+      <c r="B33" s="88" t="n">
+        <v>15</v>
+      </c>
+      <c r="C33" s="89" t="n">
+        <v>16</v>
+      </c>
+      <c r="D33" s="89" t="n">
+        <v>17</v>
+      </c>
+      <c r="E33" s="89" t="n">
+        <v>18</v>
+      </c>
+      <c r="F33" s="90" t="n">
+        <v>19</v>
+      </c>
+      <c r="G33" s="90" t="n">
+        <v>20</v>
+      </c>
+      <c r="H33" s="81" t="n"/>
+      <c r="I33" s="89" t="n">
+        <v>12</v>
+      </c>
+      <c r="J33" s="89" t="n">
+        <v>13</v>
+      </c>
+      <c r="K33" s="89" t="n">
+        <v>14</v>
+      </c>
+      <c r="L33" s="88" t="n">
+        <v>15</v>
+      </c>
+      <c r="M33" s="89" t="n">
+        <v>16</v>
+      </c>
+      <c r="N33" s="90" t="n">
+        <v>17</v>
+      </c>
+      <c r="O33" s="90" t="n">
+        <v>18</v>
+      </c>
+      <c r="P33" s="81" t="n"/>
+      <c r="Q33" s="89" t="n">
+        <v>9</v>
+      </c>
+      <c r="R33" s="89" t="n">
+        <v>10</v>
+      </c>
+      <c r="S33" s="89" t="n">
+        <v>11</v>
+      </c>
+      <c r="T33" s="89" t="n">
+        <v>12</v>
+      </c>
+      <c r="U33" s="89" t="n">
+        <v>13</v>
+      </c>
+      <c r="V33" s="90" t="n">
+        <v>14</v>
+      </c>
+      <c r="W33" s="91" t="n">
+        <v>15</v>
+      </c>
+      <c r="X33" s="81" t="n"/>
+      <c r="Y33" s="89" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z33" s="88" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA33" s="89" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB33" s="89" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC33" s="89" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD33" s="90" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE33" s="90" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF33" s="81" t="n"/>
+      <c r="AG33" s="81" t="n"/>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="89" t="n">
+        <v>21</v>
+      </c>
+      <c r="B34" s="88" t="n">
+        <v>22</v>
+      </c>
+      <c r="C34" s="89" t="n">
+        <v>23</v>
+      </c>
+      <c r="D34" s="89" t="n">
+        <v>24</v>
+      </c>
+      <c r="E34" s="89" t="n">
+        <v>25</v>
+      </c>
+      <c r="F34" s="90" t="n">
+        <v>26</v>
+      </c>
+      <c r="G34" s="90" t="n">
+        <v>27</v>
+      </c>
+      <c r="H34" s="81" t="n"/>
+      <c r="I34" s="89" t="n">
+        <v>19</v>
+      </c>
+      <c r="J34" s="89" t="n">
+        <v>20</v>
+      </c>
+      <c r="K34" s="89" t="n">
+        <v>21</v>
+      </c>
+      <c r="L34" s="88" t="n">
+        <v>22</v>
+      </c>
+      <c r="M34" s="89" t="n">
+        <v>23</v>
+      </c>
+      <c r="N34" s="90" t="n">
+        <v>24</v>
+      </c>
+      <c r="O34" s="90" t="n">
+        <v>25</v>
+      </c>
+      <c r="P34" s="81" t="n"/>
+      <c r="Q34" s="89" t="n">
+        <v>16</v>
+      </c>
+      <c r="R34" s="89" t="n">
+        <v>17</v>
+      </c>
+      <c r="S34" s="89" t="n">
+        <v>18</v>
+      </c>
+      <c r="T34" s="89" t="n">
+        <v>19</v>
+      </c>
+      <c r="U34" s="89" t="n">
+        <v>20</v>
+      </c>
+      <c r="V34" s="90" t="n">
+        <v>21</v>
+      </c>
+      <c r="W34" s="91" t="n">
+        <v>22</v>
+      </c>
+      <c r="X34" s="81" t="n"/>
+      <c r="Y34" s="89" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z34" s="88" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA34" s="89" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB34" s="89" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC34" s="89" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD34" s="90" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE34" s="90" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF34" s="81" t="n"/>
+      <c r="AG34" s="81" t="n"/>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="89" t="n">
+        <v>28</v>
+      </c>
+      <c r="B35" s="89" t="n">
+        <v>29</v>
+      </c>
+      <c r="C35" s="89" t="n">
+        <v>30</v>
+      </c>
+      <c r="D35" s="87" t="inlineStr"/>
+      <c r="E35" s="87" t="inlineStr"/>
+      <c r="F35" s="87" t="inlineStr"/>
+      <c r="G35" s="87" t="inlineStr"/>
+      <c r="H35" s="81" t="n"/>
+      <c r="I35" s="89" t="n">
+        <v>26</v>
+      </c>
+      <c r="J35" s="89" t="n">
+        <v>27</v>
+      </c>
+      <c r="K35" s="89" t="n">
+        <v>28</v>
+      </c>
+      <c r="L35" s="89" t="n">
+        <v>29</v>
+      </c>
+      <c r="M35" s="89" t="n">
+        <v>30</v>
+      </c>
+      <c r="N35" s="90" t="n">
+        <v>31</v>
+      </c>
+      <c r="O35" s="87" t="inlineStr"/>
+      <c r="P35" s="81" t="n"/>
+      <c r="Q35" s="89" t="n">
+        <v>23</v>
+      </c>
+      <c r="R35" s="89" t="n">
+        <v>24</v>
+      </c>
+      <c r="S35" s="89" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" s="89" t="n">
+        <v>26</v>
+      </c>
+      <c r="U35" s="89" t="n">
+        <v>27</v>
+      </c>
+      <c r="V35" s="90" t="n">
+        <v>28</v>
+      </c>
+      <c r="W35" s="90" t="n">
+        <v>29</v>
+      </c>
+      <c r="X35" s="81" t="n"/>
+      <c r="Y35" s="89" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z35" s="89" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA35" s="89" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB35" s="89" t="n">
+        <v>31</v>
+      </c>
+      <c r="AC35" s="87" t="inlineStr"/>
+      <c r="AD35" s="87" t="inlineStr"/>
+      <c r="AE35" s="87" t="inlineStr"/>
+      <c r="AF35" s="81" t="n"/>
+      <c r="AG35" s="81" t="n"/>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="87" t="n"/>
+      <c r="B36" s="87" t="n"/>
+      <c r="C36" s="87" t="n"/>
+      <c r="D36" s="87" t="n"/>
+      <c r="E36" s="87" t="n"/>
+      <c r="F36" s="87" t="n"/>
+      <c r="G36" s="87" t="n"/>
+      <c r="H36" s="81" t="n"/>
+      <c r="I36" s="87" t="n"/>
+      <c r="J36" s="87" t="n"/>
+      <c r="K36" s="87" t="n"/>
+      <c r="L36" s="87" t="n"/>
+      <c r="M36" s="87" t="n"/>
+      <c r="N36" s="87" t="n"/>
+      <c r="O36" s="87" t="n"/>
+      <c r="P36" s="81" t="n"/>
+      <c r="Q36" s="89" t="n">
+        <v>30</v>
+      </c>
+      <c r="R36" s="87" t="inlineStr"/>
+      <c r="S36" s="87" t="inlineStr"/>
+      <c r="T36" s="87" t="inlineStr"/>
+      <c r="U36" s="87" t="inlineStr"/>
+      <c r="V36" s="87" t="inlineStr"/>
+      <c r="W36" s="87" t="inlineStr"/>
+      <c r="X36" s="81" t="n"/>
+      <c r="Y36" s="87" t="n"/>
+      <c r="Z36" s="87" t="n"/>
+      <c r="AA36" s="87" t="n"/>
+      <c r="AB36" s="87" t="n"/>
+      <c r="AC36" s="87" t="n"/>
+      <c r="AD36" s="87" t="n"/>
+      <c r="AE36" s="87" t="n"/>
+      <c r="AF36" s="81" t="n"/>
+      <c r="AG36" s="81" t="n"/>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="81" t="n"/>
+      <c r="B37" s="81" t="n"/>
+      <c r="C37" s="81" t="n"/>
+      <c r="D37" s="81" t="n"/>
+      <c r="E37" s="81" t="n"/>
+      <c r="F37" s="81" t="n"/>
+      <c r="G37" s="81" t="n"/>
+      <c r="H37" s="81" t="n"/>
+      <c r="I37" s="81" t="n"/>
+      <c r="J37" s="81" t="n"/>
+      <c r="K37" s="81" t="n"/>
+      <c r="L37" s="81" t="n"/>
+      <c r="M37" s="81" t="n"/>
+      <c r="N37" s="81" t="n"/>
+      <c r="O37" s="81" t="n"/>
+      <c r="P37" s="81" t="n"/>
+      <c r="Q37" s="81" t="n"/>
+      <c r="R37" s="81" t="n"/>
+      <c r="S37" s="81" t="n"/>
+      <c r="T37" s="81" t="n"/>
+      <c r="U37" s="81" t="n"/>
+      <c r="V37" s="81" t="n"/>
+      <c r="W37" s="81" t="n"/>
+      <c r="X37" s="81" t="n"/>
+      <c r="Y37" s="81" t="n"/>
+      <c r="Z37" s="81" t="n"/>
+      <c r="AA37" s="81" t="n"/>
+      <c r="AB37" s="81" t="n"/>
+      <c r="AC37" s="81" t="n"/>
+      <c r="AD37" s="81" t="n"/>
+      <c r="AE37" s="81" t="n"/>
+      <c r="AF37" s="81" t="n"/>
+      <c r="AG37" s="81" t="n"/>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="81" t="n"/>
+      <c r="B38" s="81" t="n"/>
+      <c r="C38" s="81" t="n"/>
+      <c r="D38" s="81" t="n"/>
+      <c r="E38" s="81" t="n"/>
+      <c r="F38" s="81" t="n"/>
+      <c r="G38" s="81" t="n"/>
+      <c r="H38" s="81" t="n"/>
+      <c r="I38" s="81" t="n"/>
+      <c r="J38" s="81" t="n"/>
+      <c r="K38" s="81" t="n"/>
+      <c r="L38" s="81" t="n"/>
+      <c r="M38" s="81" t="n"/>
+      <c r="N38" s="81" t="n"/>
+      <c r="O38" s="81" t="n"/>
+      <c r="P38" s="81" t="n"/>
+      <c r="Q38" s="81" t="n"/>
+      <c r="R38" s="81" t="n"/>
+      <c r="S38" s="81" t="n"/>
+      <c r="T38" s="81" t="n"/>
+      <c r="U38" s="81" t="n"/>
+      <c r="V38" s="81" t="n"/>
+      <c r="W38" s="81" t="n"/>
+      <c r="X38" s="81" t="n"/>
+      <c r="Y38" s="81" t="n"/>
+      <c r="Z38" s="81" t="n"/>
+      <c r="AA38" s="81" t="n"/>
+      <c r="AB38" s="81" t="n"/>
+      <c r="AC38" s="81" t="n"/>
+      <c r="AD38" s="81" t="n"/>
+      <c r="AE38" s="81" t="n"/>
+      <c r="AF38" s="81" t="n"/>
+      <c r="AG38" s="81" t="n"/>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="81" t="n"/>
+      <c r="B39" s="81" t="n"/>
+      <c r="C39" s="81" t="n"/>
+      <c r="D39" s="81" t="n"/>
+      <c r="E39" s="81" t="n"/>
+      <c r="F39" s="81" t="n"/>
+      <c r="G39" s="81" t="n"/>
+      <c r="H39" s="81" t="n"/>
+      <c r="I39" s="81" t="n"/>
+      <c r="J39" s="81" t="n"/>
+      <c r="K39" s="81" t="n"/>
+      <c r="L39" s="81" t="n"/>
+      <c r="M39" s="81" t="n"/>
+      <c r="N39" s="81" t="n"/>
+      <c r="O39" s="81" t="n"/>
+      <c r="P39" s="81" t="n"/>
+      <c r="Q39" s="81" t="n"/>
+      <c r="R39" s="81" t="n"/>
+      <c r="S39" s="81" t="n"/>
+      <c r="T39" s="81" t="n"/>
+      <c r="U39" s="81" t="n"/>
+      <c r="V39" s="81" t="n"/>
+      <c r="W39" s="81" t="n"/>
+      <c r="X39" s="81" t="n"/>
+      <c r="Y39" s="81" t="n"/>
+      <c r="Z39" s="81" t="n"/>
+      <c r="AA39" s="81" t="n"/>
+      <c r="AB39" s="81" t="n"/>
+      <c r="AC39" s="81" t="n"/>
+      <c r="AD39" s="81" t="n"/>
+      <c r="AE39" s="81" t="n"/>
+      <c r="AF39" s="81" t="n"/>
+      <c r="AG39" s="81" t="n"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="93" t="inlineStr">
+        <is>
+          <t>🟢 = Dias de revisão ABC marcados   |   🔴 = Finais de semana   |   🇯🇲 Jah bless your schedule! — One Love, One Excel! 2026</t>
+        </is>
+      </c>
+      <c r="AG40" s="81" t="n"/>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="81" t="n"/>
+      <c r="B41" s="81" t="n"/>
+      <c r="C41" s="81" t="n"/>
+      <c r="D41" s="81" t="n"/>
+      <c r="E41" s="81" t="n"/>
+      <c r="F41" s="81" t="n"/>
+      <c r="G41" s="81" t="n"/>
+      <c r="H41" s="81" t="n"/>
+      <c r="I41" s="81" t="n"/>
+      <c r="J41" s="81" t="n"/>
+      <c r="K41" s="81" t="n"/>
+      <c r="L41" s="81" t="n"/>
+      <c r="M41" s="81" t="n"/>
+      <c r="N41" s="81" t="n"/>
+      <c r="O41" s="81" t="n"/>
+      <c r="P41" s="81" t="n"/>
+      <c r="Q41" s="81" t="n"/>
+      <c r="R41" s="81" t="n"/>
+      <c r="S41" s="81" t="n"/>
+      <c r="T41" s="81" t="n"/>
+      <c r="U41" s="81" t="n"/>
+      <c r="V41" s="81" t="n"/>
+      <c r="W41" s="81" t="n"/>
+      <c r="X41" s="81" t="n"/>
+      <c r="Y41" s="81" t="n"/>
+      <c r="Z41" s="81" t="n"/>
+      <c r="AA41" s="81" t="n"/>
+      <c r="AB41" s="81" t="n"/>
+      <c r="AC41" s="81" t="n"/>
+      <c r="AD41" s="81" t="n"/>
+      <c r="AE41" s="81" t="n"/>
+      <c r="AF41" s="81" t="n"/>
+      <c r="AG41" s="81" t="n"/>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="81" t="n"/>
+      <c r="B42" s="81" t="n"/>
+      <c r="C42" s="81" t="n"/>
+      <c r="D42" s="81" t="n"/>
+      <c r="E42" s="81" t="n"/>
+      <c r="F42" s="81" t="n"/>
+      <c r="G42" s="81" t="n"/>
+      <c r="H42" s="81" t="n"/>
+      <c r="I42" s="81" t="n"/>
+      <c r="J42" s="81" t="n"/>
+      <c r="K42" s="81" t="n"/>
+      <c r="L42" s="81" t="n"/>
+      <c r="M42" s="81" t="n"/>
+      <c r="N42" s="81" t="n"/>
+      <c r="O42" s="81" t="n"/>
+      <c r="P42" s="81" t="n"/>
+      <c r="Q42" s="81" t="n"/>
+      <c r="R42" s="81" t="n"/>
+      <c r="S42" s="81" t="n"/>
+      <c r="T42" s="81" t="n"/>
+      <c r="U42" s="81" t="n"/>
+      <c r="V42" s="81" t="n"/>
+      <c r="W42" s="81" t="n"/>
+      <c r="X42" s="81" t="n"/>
+      <c r="Y42" s="81" t="n"/>
+      <c r="Z42" s="81" t="n"/>
+      <c r="AA42" s="81" t="n"/>
+      <c r="AB42" s="81" t="n"/>
+      <c r="AC42" s="81" t="n"/>
+      <c r="AD42" s="81" t="n"/>
+      <c r="AE42" s="81" t="n"/>
+      <c r="AF42" s="81" t="n"/>
+      <c r="AG42" s="81" t="n"/>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="81" t="n"/>
+      <c r="B43" s="81" t="n"/>
+      <c r="C43" s="81" t="n"/>
+      <c r="D43" s="81" t="n"/>
+      <c r="E43" s="81" t="n"/>
+      <c r="F43" s="81" t="n"/>
+      <c r="G43" s="81" t="n"/>
+      <c r="H43" s="81" t="n"/>
+      <c r="I43" s="81" t="n"/>
+      <c r="J43" s="81" t="n"/>
+      <c r="K43" s="81" t="n"/>
+      <c r="L43" s="81" t="n"/>
+      <c r="M43" s="81" t="n"/>
+      <c r="N43" s="81" t="n"/>
+      <c r="O43" s="81" t="n"/>
+      <c r="P43" s="81" t="n"/>
+      <c r="Q43" s="81" t="n"/>
+      <c r="R43" s="81" t="n"/>
+      <c r="S43" s="81" t="n"/>
+      <c r="T43" s="81" t="n"/>
+      <c r="U43" s="81" t="n"/>
+      <c r="V43" s="81" t="n"/>
+      <c r="W43" s="81" t="n"/>
+      <c r="X43" s="81" t="n"/>
+      <c r="Y43" s="81" t="n"/>
+      <c r="Z43" s="81" t="n"/>
+      <c r="AA43" s="81" t="n"/>
+      <c r="AB43" s="81" t="n"/>
+      <c r="AC43" s="81" t="n"/>
+      <c r="AD43" s="81" t="n"/>
+      <c r="AE43" s="81" t="n"/>
+      <c r="AF43" s="81" t="n"/>
+      <c r="AG43" s="81" t="n"/>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="81" t="n"/>
+      <c r="B44" s="81" t="n"/>
+      <c r="C44" s="81" t="n"/>
+      <c r="D44" s="81" t="n"/>
+      <c r="E44" s="81" t="n"/>
+      <c r="F44" s="81" t="n"/>
+      <c r="G44" s="81" t="n"/>
+      <c r="H44" s="81" t="n"/>
+      <c r="I44" s="81" t="n"/>
+      <c r="J44" s="81" t="n"/>
+      <c r="K44" s="81" t="n"/>
+      <c r="L44" s="81" t="n"/>
+      <c r="M44" s="81" t="n"/>
+      <c r="N44" s="81" t="n"/>
+      <c r="O44" s="81" t="n"/>
+      <c r="P44" s="81" t="n"/>
+      <c r="Q44" s="81" t="n"/>
+      <c r="R44" s="81" t="n"/>
+      <c r="S44" s="81" t="n"/>
+      <c r="T44" s="81" t="n"/>
+      <c r="U44" s="81" t="n"/>
+      <c r="V44" s="81" t="n"/>
+      <c r="W44" s="81" t="n"/>
+      <c r="X44" s="81" t="n"/>
+      <c r="Y44" s="81" t="n"/>
+      <c r="Z44" s="81" t="n"/>
+      <c r="AA44" s="81" t="n"/>
+      <c r="AB44" s="81" t="n"/>
+      <c r="AC44" s="81" t="n"/>
+      <c r="AD44" s="81" t="n"/>
+      <c r="AE44" s="81" t="n"/>
+      <c r="AF44" s="81" t="n"/>
+      <c r="AG44" s="81" t="n"/>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="81" t="n"/>
+      <c r="B45" s="81" t="n"/>
+      <c r="C45" s="81" t="n"/>
+      <c r="D45" s="81" t="n"/>
+      <c r="E45" s="81" t="n"/>
+      <c r="F45" s="81" t="n"/>
+      <c r="G45" s="81" t="n"/>
+      <c r="H45" s="81" t="n"/>
+      <c r="I45" s="81" t="n"/>
+      <c r="J45" s="81" t="n"/>
+      <c r="K45" s="81" t="n"/>
+      <c r="L45" s="81" t="n"/>
+      <c r="M45" s="81" t="n"/>
+      <c r="N45" s="81" t="n"/>
+      <c r="O45" s="81" t="n"/>
+      <c r="P45" s="81" t="n"/>
+      <c r="Q45" s="81" t="n"/>
+      <c r="R45" s="81" t="n"/>
+      <c r="S45" s="81" t="n"/>
+      <c r="T45" s="81" t="n"/>
+      <c r="U45" s="81" t="n"/>
+      <c r="V45" s="81" t="n"/>
+      <c r="W45" s="81" t="n"/>
+      <c r="X45" s="81" t="n"/>
+      <c r="Y45" s="81" t="n"/>
+      <c r="Z45" s="81" t="n"/>
+      <c r="AA45" s="81" t="n"/>
+      <c r="AB45" s="81" t="n"/>
+      <c r="AC45" s="81" t="n"/>
+      <c r="AD45" s="81" t="n"/>
+      <c r="AE45" s="81" t="n"/>
+      <c r="AF45" s="81" t="n"/>
+      <c r="AG45" s="81" t="n"/>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="81" t="n"/>
+      <c r="B46" s="81" t="n"/>
+      <c r="C46" s="81" t="n"/>
+      <c r="D46" s="81" t="n"/>
+      <c r="E46" s="81" t="n"/>
+      <c r="F46" s="81" t="n"/>
+      <c r="G46" s="81" t="n"/>
+      <c r="H46" s="81" t="n"/>
+      <c r="I46" s="81" t="n"/>
+      <c r="J46" s="81" t="n"/>
+      <c r="K46" s="81" t="n"/>
+      <c r="L46" s="81" t="n"/>
+      <c r="M46" s="81" t="n"/>
+      <c r="N46" s="81" t="n"/>
+      <c r="O46" s="81" t="n"/>
+      <c r="P46" s="81" t="n"/>
+      <c r="Q46" s="81" t="n"/>
+      <c r="R46" s="81" t="n"/>
+      <c r="S46" s="81" t="n"/>
+      <c r="T46" s="81" t="n"/>
+      <c r="U46" s="81" t="n"/>
+      <c r="V46" s="81" t="n"/>
+      <c r="W46" s="81" t="n"/>
+      <c r="X46" s="81" t="n"/>
+      <c r="Y46" s="81" t="n"/>
+      <c r="Z46" s="81" t="n"/>
+      <c r="AA46" s="81" t="n"/>
+      <c r="AB46" s="81" t="n"/>
+      <c r="AC46" s="81" t="n"/>
+      <c r="AD46" s="81" t="n"/>
+      <c r="AE46" s="81" t="n"/>
+      <c r="AF46" s="81" t="n"/>
+      <c r="AG46" s="81" t="n"/>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="81" t="n"/>
+      <c r="B47" s="81" t="n"/>
+      <c r="C47" s="81" t="n"/>
+      <c r="D47" s="81" t="n"/>
+      <c r="E47" s="81" t="n"/>
+      <c r="F47" s="81" t="n"/>
+      <c r="G47" s="81" t="n"/>
+      <c r="H47" s="81" t="n"/>
+      <c r="I47" s="81" t="n"/>
+      <c r="J47" s="81" t="n"/>
+      <c r="K47" s="81" t="n"/>
+      <c r="L47" s="81" t="n"/>
+      <c r="M47" s="81" t="n"/>
+      <c r="N47" s="81" t="n"/>
+      <c r="O47" s="81" t="n"/>
+      <c r="P47" s="81" t="n"/>
+      <c r="Q47" s="81" t="n"/>
+      <c r="R47" s="81" t="n"/>
+      <c r="S47" s="81" t="n"/>
+      <c r="T47" s="81" t="n"/>
+      <c r="U47" s="81" t="n"/>
+      <c r="V47" s="81" t="n"/>
+      <c r="W47" s="81" t="n"/>
+      <c r="X47" s="81" t="n"/>
+      <c r="Y47" s="81" t="n"/>
+      <c r="Z47" s="81" t="n"/>
+      <c r="AA47" s="81" t="n"/>
+      <c r="AB47" s="81" t="n"/>
+      <c r="AC47" s="81" t="n"/>
+      <c r="AD47" s="81" t="n"/>
+      <c r="AE47" s="81" t="n"/>
+      <c r="AF47" s="81" t="n"/>
+      <c r="AG47" s="81" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A5:P5"/>
+    <mergeCell ref="Q18:W18"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="I18:O18"/>
+    <mergeCell ref="Q7:W7"/>
+    <mergeCell ref="Y18:AE18"/>
+    <mergeCell ref="A40:AF40"/>
+    <mergeCell ref="I29:O29"/>
+    <mergeCell ref="I7:O7"/>
+    <mergeCell ref="Y7:AE7"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="Q29:W29"/>
+    <mergeCell ref="Y29:AE29"/>
+    <mergeCell ref="A2:AF2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/curva_abc_reggae.xlsx
+++ b/curva_abc_reggae.xlsx
@@ -180,61 +180,63 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="solid"/>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00009B3A"/>
+        <fgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD700"/>
+        <fgColor rgb="FF009B3A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC0000"/>
+        <fgColor rgb="FFFFD700"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00141414"/>
+        <fgColor rgb="FFCC0000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00006B28"/>
+        <fgColor rgb="FF141414"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8A400"/>
+        <fgColor rgb="FF006B28"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="008B0000"/>
+        <fgColor rgb="FFC8A400"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000D2010"/>
+        <fgColor rgb="FF8B0000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00080808"/>
+        <fgColor rgb="FF0D2010"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000D1A0D"/>
+        <fgColor rgb="FF080808"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001A0000"/>
+        <fgColor rgb="FF0D1A0D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -687,7 +689,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00D6F5E3"/>
+          <fgColor rgb="FFD6F5E3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -697,7 +699,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFFBD0"/>
+          <fgColor rgb="FFFFFBD0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -707,7 +709,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFECEC"/>
+          <fgColor rgb="FFFFECEC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -719,7 +721,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00009B3A"/>
+          <fgColor rgb="FF009B3A"/>
         </patternFill>
       </fill>
     </dxf>
@@ -731,7 +733,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00C8A400"/>
+          <fgColor rgb="FFC8A400"/>
         </patternFill>
       </fill>
     </dxf>
@@ -743,7 +745,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="008B0000"/>
+          <fgColor rgb="FF8B0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1043,7 +1045,7 @@
           <max val="1"/>
           <min val="0"/>
         </scaling>
-        <axPos val="l"/>
+        <axPos val="r"/>
         <majorGridlines/>
         <title>
           <tx>
@@ -1299,7 +1301,7 @@
           <max val="1"/>
           <min val="0"/>
         </scaling>
-        <axPos val="l"/>
+        <axPos val="r"/>
         <majorGridlines/>
         <title>
           <tx>
@@ -1555,7 +1557,7 @@
           <max val="1"/>
           <min val="0"/>
         </scaling>
-        <axPos val="l"/>
+        <axPos val="r"/>
         <majorGridlines/>
         <title>
           <tx>
@@ -2405,7 +2407,7 @@
         <v/>
       </c>
       <c r="I12" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$21,"&gt;="&amp;G12,$G$12:$G$21)/SUM($G$12:$G$21),0)</f>
+        <f>IFERROR(SUM($G$12:G12)/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
       <c r="P12" t="inlineStr">
@@ -2459,7 +2461,7 @@
         <v/>
       </c>
       <c r="I13" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$21,"&gt;="&amp;G13,$G$12:$G$21)/SUM($G$12:$G$21),0)</f>
+        <f>IFERROR(SUM($G$12:G13)/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
       <c r="P13" t="inlineStr">
@@ -2513,7 +2515,7 @@
         <v/>
       </c>
       <c r="I14" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$21,"&gt;="&amp;G14,$G$12:$G$21)/SUM($G$12:$G$21),0)</f>
+        <f>IFERROR(SUM($G$12:G14)/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
       <c r="P14" t="inlineStr">
@@ -2567,7 +2569,7 @@
         <v/>
       </c>
       <c r="I15" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$21,"&gt;="&amp;G15,$G$12:$G$21)/SUM($G$12:$G$21),0)</f>
+        <f>IFERROR(SUM($G$12:G15)/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
       <c r="P15" t="inlineStr">
@@ -2621,7 +2623,7 @@
         <v/>
       </c>
       <c r="I16" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$21,"&gt;="&amp;G16,$G$12:$G$21)/SUM($G$12:$G$21),0)</f>
+        <f>IFERROR(SUM($G$12:G16)/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
       <c r="P16" t="inlineStr">
@@ -2649,22 +2651,22 @@
       </c>
       <c r="B17" s="48" t="inlineStr">
         <is>
-          <t>SKU06</t>
+          <t>SKU08</t>
         </is>
       </c>
       <c r="C17" s="48" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D17" s="49" t="inlineStr">
         <is>
-          <t>Mouse sem fio</t>
+          <t>Teclado USB</t>
         </is>
       </c>
       <c r="E17" s="50" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F17" s="51" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="G17" s="52">
         <f>IFERROR(E17*F17,0)</f>
@@ -2675,7 +2677,7 @@
         <v/>
       </c>
       <c r="I17" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$21,"&gt;="&amp;G17,$G$12:$G$21)/SUM($G$12:$G$21),0)</f>
+        <f>IFERROR(SUM($G$12:G17)/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
       <c r="P17" t="inlineStr">
@@ -2703,22 +2705,22 @@
       </c>
       <c r="B18" s="48" t="inlineStr">
         <is>
-          <t>SKU07</t>
+          <t>SKU06</t>
         </is>
       </c>
       <c r="C18" s="48" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D18" s="49" t="inlineStr">
         <is>
-          <t>Patch Cord 1m</t>
+          <t>Mouse sem fio</t>
         </is>
       </c>
       <c r="E18" s="50" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="F18" s="51" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="G18" s="52">
         <f>IFERROR(E18*F18,0)</f>
@@ -2729,7 +2731,7 @@
         <v/>
       </c>
       <c r="I18" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$21,"&gt;="&amp;G18,$G$12:$G$21)/SUM($G$12:$G$21),0)</f>
+        <f>IFERROR(SUM($G$12:G18)/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
       <c r="P18" t="inlineStr">
@@ -2757,22 +2759,22 @@
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>SKU08</t>
+          <t>SKU09</t>
         </is>
       </c>
       <c r="C19" s="48" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D19" s="49" t="inlineStr">
         <is>
-          <t>Teclado USB</t>
+          <t>Cabo Rede Cat6 (m)</t>
         </is>
       </c>
       <c r="E19" s="50" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="F19" s="51" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="G19" s="52">
         <f>IFERROR(E19*F19,0)</f>
@@ -2783,7 +2785,7 @@
         <v/>
       </c>
       <c r="I19" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$21,"&gt;="&amp;G19,$G$12:$G$21)/SUM($G$12:$G$21),0)</f>
+        <f>IFERROR(SUM($G$12:G19)/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
       <c r="P19" t="inlineStr">
@@ -2811,22 +2813,22 @@
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>SKU09</t>
+          <t>SKU07</t>
         </is>
       </c>
       <c r="C20" s="48" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D20" s="49" t="inlineStr">
         <is>
-          <t>Cabo Rede Cat6 (m)</t>
+          <t>Patch Cord 1m</t>
         </is>
       </c>
       <c r="E20" s="50" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F20" s="51" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G20" s="52">
         <f>IFERROR(E20*F20,0)</f>
@@ -2837,7 +2839,7 @@
         <v/>
       </c>
       <c r="I20" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$21,"&gt;="&amp;G20,$G$12:$G$21)/SUM($G$12:$G$21),0)</f>
+        <f>IFERROR(SUM($G$12:G20)/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
       <c r="P20" t="inlineStr">
@@ -2891,7 +2893,7 @@
         <v/>
       </c>
       <c r="I21" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$21,"&gt;="&amp;G21,$G$12:$G$21)/SUM($G$12:$G$21),0)</f>
+        <f>IFERROR(SUM($G$12:G21)/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
       <c r="P21" t="inlineStr">
@@ -3340,7 +3342,7 @@
         <v/>
       </c>
       <c r="I12" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G12,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUM($G$12:G12)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P12" t="inlineStr">
@@ -3394,7 +3396,7 @@
         <v/>
       </c>
       <c r="I13" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G13,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUM($G$12:G13)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P13" t="inlineStr">
@@ -3448,7 +3450,7 @@
         <v/>
       </c>
       <c r="I14" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G14,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUM($G$12:G14)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P14" t="inlineStr">
@@ -3502,7 +3504,7 @@
         <v/>
       </c>
       <c r="I15" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G15,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUM($G$12:G15)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P15" t="inlineStr">
@@ -3556,7 +3558,7 @@
         <v/>
       </c>
       <c r="I16" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G16,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUM($G$12:G16)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P16" t="inlineStr">
@@ -3610,7 +3612,7 @@
         <v/>
       </c>
       <c r="I17" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G17,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUM($G$12:G17)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P17" t="inlineStr">
@@ -3664,7 +3666,7 @@
         <v/>
       </c>
       <c r="I18" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G18,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUM($G$12:G18)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P18" t="inlineStr">
@@ -3692,22 +3694,22 @@
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>SKU08</t>
+          <t>SKU09</t>
         </is>
       </c>
       <c r="C19" s="48" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D19" s="49" t="inlineStr">
         <is>
-          <t>Roteador Wi-Fi 6</t>
+          <t>SSD 480GB Sata</t>
         </is>
       </c>
       <c r="E19" s="50" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="F19" s="51" t="n">
-        <v>650</v>
+        <v>190</v>
       </c>
       <c r="G19" s="52">
         <f>IFERROR(E19*F19,0)</f>
@@ -3718,7 +3720,7 @@
         <v/>
       </c>
       <c r="I19" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G19,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUM($G$12:G19)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P19" t="inlineStr">
@@ -3746,22 +3748,22 @@
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>SKU09</t>
+          <t>SKU08</t>
         </is>
       </c>
       <c r="C20" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="D20" s="49" t="inlineStr">
+        <is>
+          <t>Roteador Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E20" s="50" t="n">
         <v>15</v>
       </c>
-      <c r="D20" s="49" t="inlineStr">
-        <is>
-          <t>SSD 480GB Sata</t>
-        </is>
-      </c>
-      <c r="E20" s="50" t="n">
-        <v>55</v>
-      </c>
       <c r="F20" s="51" t="n">
-        <v>190</v>
+        <v>650</v>
       </c>
       <c r="G20" s="52">
         <f>IFERROR(E20*F20,0)</f>
@@ -3772,7 +3774,7 @@
         <v/>
       </c>
       <c r="I20" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G20,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUM($G$12:G20)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P20" t="inlineStr">
@@ -3826,7 +3828,7 @@
         <v/>
       </c>
       <c r="I21" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G21,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUM($G$12:G21)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P21" t="inlineStr">
@@ -3880,7 +3882,7 @@
         <v/>
       </c>
       <c r="I22" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G22,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUM($G$12:G22)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P22" t="inlineStr">
@@ -3934,7 +3936,7 @@
         <v/>
       </c>
       <c r="I23" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G23,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUM($G$12:G23)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P23" t="inlineStr">
@@ -3988,7 +3990,7 @@
         <v/>
       </c>
       <c r="I24" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G24,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUM($G$12:G24)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P24" t="inlineStr">
@@ -4042,7 +4044,7 @@
         <v/>
       </c>
       <c r="I25" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G25,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUM($G$12:G25)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P25" t="inlineStr">
@@ -4096,7 +4098,7 @@
         <v/>
       </c>
       <c r="I26" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G26,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUM($G$12:G26)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P26" t="inlineStr">
@@ -4150,7 +4152,7 @@
         <v/>
       </c>
       <c r="I27" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G27,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUM($G$12:G27)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P27" t="inlineStr">
@@ -4204,7 +4206,7 @@
         <v/>
       </c>
       <c r="I28" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G28,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUM($G$12:G28)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P28" t="inlineStr">
@@ -4258,7 +4260,7 @@
         <v/>
       </c>
       <c r="I29" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G29,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUM($G$12:G29)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P29" t="inlineStr">
@@ -4286,22 +4288,22 @@
       </c>
       <c r="B30" s="48" t="inlineStr">
         <is>
-          <t>SKU19</t>
+          <t>SKU20</t>
         </is>
       </c>
       <c r="C30" s="48" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D30" s="49" t="inlineStr">
         <is>
-          <t>Mouse Optico Simples</t>
+          <t>Patch Cord RJ45 1m</t>
         </is>
       </c>
       <c r="E30" s="50" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="F30" s="51" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G30" s="52">
         <f>IFERROR(E30*F30,0)</f>
@@ -4312,7 +4314,7 @@
         <v/>
       </c>
       <c r="I30" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G30,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUM($G$12:G30)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P30" t="inlineStr">
@@ -4340,22 +4342,22 @@
       </c>
       <c r="B31" s="48" t="inlineStr">
         <is>
-          <t>SKU20</t>
+          <t>SKU19</t>
         </is>
       </c>
       <c r="C31" s="48" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D31" s="49" t="inlineStr">
         <is>
-          <t>Patch Cord RJ45 1m</t>
+          <t>Mouse Optico Simples</t>
         </is>
       </c>
       <c r="E31" s="50" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="F31" s="51" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G31" s="52">
         <f>IFERROR(E31*F31,0)</f>
@@ -4366,7 +4368,7 @@
         <v/>
       </c>
       <c r="I31" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G31,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUM($G$12:G31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P31" t="inlineStr">
@@ -4815,7 +4817,7 @@
         <v/>
       </c>
       <c r="I12" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G12,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUM($G$12:G12)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P12" t="inlineStr">
@@ -4869,7 +4871,7 @@
         <v/>
       </c>
       <c r="I13" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G13,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUM($G$12:G13)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P13" t="inlineStr">
@@ -4923,7 +4925,7 @@
         <v/>
       </c>
       <c r="I14" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G14,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUM($G$12:G14)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P14" t="inlineStr">
@@ -4977,7 +4979,7 @@
         <v/>
       </c>
       <c r="I15" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G15,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUM($G$12:G15)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P15" t="inlineStr">
@@ -5031,7 +5033,7 @@
         <v/>
       </c>
       <c r="I16" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G16,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUM($G$12:G16)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P16" t="inlineStr">
@@ -5085,7 +5087,7 @@
         <v/>
       </c>
       <c r="I17" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G17,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUM($G$12:G17)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P17" t="inlineStr">
@@ -5139,7 +5141,7 @@
         <v/>
       </c>
       <c r="I18" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G18,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUM($G$12:G18)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P18" t="inlineStr">
@@ -5193,7 +5195,7 @@
         <v/>
       </c>
       <c r="I19" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G19,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUM($G$12:G19)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P19" t="inlineStr">
@@ -5247,7 +5249,7 @@
         <v/>
       </c>
       <c r="I20" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G20,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUM($G$12:G20)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P20" t="inlineStr">
@@ -5301,7 +5303,7 @@
         <v/>
       </c>
       <c r="I21" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G21,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUM($G$12:G21)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P21" t="inlineStr">
@@ -5355,7 +5357,7 @@
         <v/>
       </c>
       <c r="I22" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G22,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUM($G$12:G22)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P22" t="inlineStr">
@@ -5409,7 +5411,7 @@
         <v/>
       </c>
       <c r="I23" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G23,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUM($G$12:G23)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P23" t="inlineStr">
@@ -5463,7 +5465,7 @@
         <v/>
       </c>
       <c r="I24" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G24,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUM($G$12:G24)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P24" t="inlineStr">
@@ -5517,7 +5519,7 @@
         <v/>
       </c>
       <c r="I25" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G25,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUM($G$12:G25)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P25" t="inlineStr">
@@ -5571,7 +5573,7 @@
         <v/>
       </c>
       <c r="I26" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G26,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUM($G$12:G26)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P26" t="inlineStr">
@@ -5625,7 +5627,7 @@
         <v/>
       </c>
       <c r="I27" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G27,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUM($G$12:G27)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P27" t="inlineStr">
@@ -5679,7 +5681,7 @@
         <v/>
       </c>
       <c r="I28" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G28,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUM($G$12:G28)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P28" t="inlineStr">
@@ -5733,7 +5735,7 @@
         <v/>
       </c>
       <c r="I29" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G29,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUM($G$12:G29)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P29" t="inlineStr">
@@ -5787,7 +5789,7 @@
         <v/>
       </c>
       <c r="I30" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G30,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUM($G$12:G30)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P30" t="inlineStr">
@@ -5841,7 +5843,7 @@
         <v/>
       </c>
       <c r="I31" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G31,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUM($G$12:G31)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P31" t="inlineStr">
@@ -5895,7 +5897,7 @@
         <v/>
       </c>
       <c r="I32" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G32,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUM($G$12:G32)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P32" t="inlineStr">
@@ -5949,7 +5951,7 @@
         <v/>
       </c>
       <c r="I33" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G33,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUM($G$12:G33)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P33" t="inlineStr">
@@ -6003,7 +6005,7 @@
         <v/>
       </c>
       <c r="I34" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G34,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUM($G$12:G34)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P34" t="inlineStr">
@@ -6057,7 +6059,7 @@
         <v/>
       </c>
       <c r="I35" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G35,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUM($G$12:G35)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P35" t="inlineStr">
@@ -6111,7 +6113,7 @@
         <v/>
       </c>
       <c r="I36" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G36,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUM($G$12:G36)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P36" t="inlineStr">
@@ -6165,7 +6167,7 @@
         <v/>
       </c>
       <c r="I37" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G37,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUM($G$12:G37)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P37" t="inlineStr">
@@ -6219,7 +6221,7 @@
         <v/>
       </c>
       <c r="I38" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G38,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUM($G$12:G38)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P38" t="inlineStr">
@@ -6273,7 +6275,7 @@
         <v/>
       </c>
       <c r="I39" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G39,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUM($G$12:G39)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P39" t="inlineStr">
@@ -6327,7 +6329,7 @@
         <v/>
       </c>
       <c r="I40" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G40,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUM($G$12:G40)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P40" t="inlineStr">
@@ -6381,7 +6383,7 @@
         <v/>
       </c>
       <c r="I41" s="53">
-        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G41,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUM($G$12:G41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P41" t="inlineStr">

--- a/curva_abc_reggae.xlsx
+++ b/curva_abc_reggae.xlsx
@@ -863,9 +863,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'🟢 Primeira'!$P$12:$P$21</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -891,9 +891,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'🟢 Primeira'!$P$12:$P$21</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -919,9 +919,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'🟢 Primeira'!$P$12:$P$21</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -971,9 +971,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'🟢 Primeira'!$P$12:$P$21</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1000,7 +1000,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Produtos ordenados por V.T. decrescente (nome + classe no rotulo)</a:t>
+                  <a:t>Produtos (ordem decrescente de V.T.)</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -1119,9 +1119,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'🟡 01'!$P$12:$P$31</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1147,9 +1147,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'🟡 01'!$P$12:$P$31</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1175,9 +1175,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'🟡 01'!$P$12:$P$31</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1227,9 +1227,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'🟡 01'!$P$12:$P$31</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1256,7 +1256,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Produtos ordenados por V.T. decrescente (nome + classe no rotulo)</a:t>
+                  <a:t>Produtos (ordem decrescente de V.T.)</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -1375,9 +1375,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'🔴 02'!$P$12:$P$41</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1403,9 +1403,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'🔴 02'!$P$12:$P$41</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1431,9 +1431,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'🔴 02'!$P$12:$P$41</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1483,9 +1483,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'🔴 02'!$P$12:$P$41</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1512,7 +1512,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Produtos ordenados por V.T. decrescente (nome + classe no rotulo)</a:t>
+                  <a:t>Produtos (ordem decrescente de V.T.)</a:t>
                 </a:r>
               </a:p>
             </rich>

--- a/curva_abc_reggae.xlsx
+++ b/curva_abc_reggae.xlsx
@@ -865,11 +865,78 @@
           <cat>
             <strRef>
               <f>'🟢 Primeira'!$P$12:$P$21</f>
+              <strCache>
+                <ptCount val="10"/>
+                <pt idx="0">
+                  <v>A | SKU01 | Servidor Backup</v>
+                </pt>
+                <pt idx="1">
+                  <v>A | SKU02 | Monitor 27" 4K</v>
+                </pt>
+                <pt idx="2">
+                  <v>B | SKU03 | Notebook Administrat</v>
+                </pt>
+                <pt idx="3">
+                  <v>B | SKU04 | Nobreak Profissional</v>
+                </pt>
+                <pt idx="4">
+                  <v>B | SKU05 | Switch Gerenciavel</v>
+                </pt>
+                <pt idx="5">
+                  <v>C | SKU08 | Teclado USB</v>
+                </pt>
+                <pt idx="6">
+                  <v>C | SKU06 | Mouse sem fio</v>
+                </pt>
+                <pt idx="7">
+                  <v>C | SKU09 | Cabo Rede Cat6 (m)</v>
+                </pt>
+                <pt idx="8">
+                  <v>C | SKU07 | Patch Cord 1m</v>
+                </pt>
+                <pt idx="9">
+                  <v>C | SKU10 | Mousepad Slim</v>
+                </pt>
+              </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
               <f>'🟢 Primeira'!$Q$12:$Q$21</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="10"/>
+                <pt idx="0">
+                  <v>50000</v>
+                </pt>
+                <pt idx="1">
+                  <v>30000</v>
+                </pt>
+                <pt idx="2">
+                  <v>0</v>
+                </pt>
+                <pt idx="3">
+                  <v>0</v>
+                </pt>
+                <pt idx="4">
+                  <v>0</v>
+                </pt>
+                <pt idx="5">
+                  <v>0</v>
+                </pt>
+                <pt idx="6">
+                  <v>0</v>
+                </pt>
+                <pt idx="7">
+                  <v>0</v>
+                </pt>
+                <pt idx="8">
+                  <v>0</v>
+                </pt>
+                <pt idx="9">
+                  <v>0</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
         </ser>
@@ -893,11 +960,78 @@
           <cat>
             <strRef>
               <f>'🟢 Primeira'!$P$12:$P$21</f>
+              <strCache>
+                <ptCount val="10"/>
+                <pt idx="0">
+                  <v>A | SKU01 | Servidor Backup</v>
+                </pt>
+                <pt idx="1">
+                  <v>A | SKU02 | Monitor 27" 4K</v>
+                </pt>
+                <pt idx="2">
+                  <v>B | SKU03 | Notebook Administrat</v>
+                </pt>
+                <pt idx="3">
+                  <v>B | SKU04 | Nobreak Profissional</v>
+                </pt>
+                <pt idx="4">
+                  <v>B | SKU05 | Switch Gerenciavel</v>
+                </pt>
+                <pt idx="5">
+                  <v>C | SKU08 | Teclado USB</v>
+                </pt>
+                <pt idx="6">
+                  <v>C | SKU06 | Mouse sem fio</v>
+                </pt>
+                <pt idx="7">
+                  <v>C | SKU09 | Cabo Rede Cat6 (m)</v>
+                </pt>
+                <pt idx="8">
+                  <v>C | SKU07 | Patch Cord 1m</v>
+                </pt>
+                <pt idx="9">
+                  <v>C | SKU10 | Mousepad Slim</v>
+                </pt>
+              </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
               <f>'🟢 Primeira'!$R$12:$R$21</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="10"/>
+                <pt idx="0">
+                  <v>0</v>
+                </pt>
+                <pt idx="1">
+                  <v>0</v>
+                </pt>
+                <pt idx="2">
+                  <v>27000</v>
+                </pt>
+                <pt idx="3">
+                  <v>10000</v>
+                </pt>
+                <pt idx="4">
+                  <v>6000</v>
+                </pt>
+                <pt idx="5">
+                  <v>0</v>
+                </pt>
+                <pt idx="6">
+                  <v>0</v>
+                </pt>
+                <pt idx="7">
+                  <v>0</v>
+                </pt>
+                <pt idx="8">
+                  <v>0</v>
+                </pt>
+                <pt idx="9">
+                  <v>0</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
         </ser>
@@ -921,11 +1055,78 @@
           <cat>
             <strRef>
               <f>'🟢 Primeira'!$P$12:$P$21</f>
+              <strCache>
+                <ptCount val="10"/>
+                <pt idx="0">
+                  <v>A | SKU01 | Servidor Backup</v>
+                </pt>
+                <pt idx="1">
+                  <v>A | SKU02 | Monitor 27" 4K</v>
+                </pt>
+                <pt idx="2">
+                  <v>B | SKU03 | Notebook Administrat</v>
+                </pt>
+                <pt idx="3">
+                  <v>B | SKU04 | Nobreak Profissional</v>
+                </pt>
+                <pt idx="4">
+                  <v>B | SKU05 | Switch Gerenciavel</v>
+                </pt>
+                <pt idx="5">
+                  <v>C | SKU08 | Teclado USB</v>
+                </pt>
+                <pt idx="6">
+                  <v>C | SKU06 | Mouse sem fio</v>
+                </pt>
+                <pt idx="7">
+                  <v>C | SKU09 | Cabo Rede Cat6 (m)</v>
+                </pt>
+                <pt idx="8">
+                  <v>C | SKU07 | Patch Cord 1m</v>
+                </pt>
+                <pt idx="9">
+                  <v>C | SKU10 | Mousepad Slim</v>
+                </pt>
+              </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
               <f>'🟢 Primeira'!$S$12:$S$21</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="10"/>
+                <pt idx="0">
+                  <v>0</v>
+                </pt>
+                <pt idx="1">
+                  <v>0</v>
+                </pt>
+                <pt idx="2">
+                  <v>0</v>
+                </pt>
+                <pt idx="3">
+                  <v>0</v>
+                </pt>
+                <pt idx="4">
+                  <v>0</v>
+                </pt>
+                <pt idx="5">
+                  <v>2800</v>
+                </pt>
+                <pt idx="6">
+                  <v>2000</v>
+                </pt>
+                <pt idx="7">
+                  <v>1600</v>
+                </pt>
+                <pt idx="8">
+                  <v>1500</v>
+                </pt>
+                <pt idx="9">
+                  <v>1440</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
         </ser>
@@ -973,11 +1174,78 @@
           <cat>
             <strRef>
               <f>'🟢 Primeira'!$P$12:$P$21</f>
+              <strCache>
+                <ptCount val="10"/>
+                <pt idx="0">
+                  <v>A | SKU01 | Servidor Backup</v>
+                </pt>
+                <pt idx="1">
+                  <v>A | SKU02 | Monitor 27" 4K</v>
+                </pt>
+                <pt idx="2">
+                  <v>B | SKU03 | Notebook Administrat</v>
+                </pt>
+                <pt idx="3">
+                  <v>B | SKU04 | Nobreak Profissional</v>
+                </pt>
+                <pt idx="4">
+                  <v>B | SKU05 | Switch Gerenciavel</v>
+                </pt>
+                <pt idx="5">
+                  <v>C | SKU08 | Teclado USB</v>
+                </pt>
+                <pt idx="6">
+                  <v>C | SKU06 | Mouse sem fio</v>
+                </pt>
+                <pt idx="7">
+                  <v>C | SKU09 | Cabo Rede Cat6 (m)</v>
+                </pt>
+                <pt idx="8">
+                  <v>C | SKU07 | Patch Cord 1m</v>
+                </pt>
+                <pt idx="9">
+                  <v>C | SKU10 | Mousepad Slim</v>
+                </pt>
+              </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
               <f>'🟢 Primeira'!$T$12:$T$21</f>
+              <numCache>
+                <formatCode>0%</formatCode>
+                <ptCount val="10"/>
+                <pt idx="0">
+                  <v>0.37781</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.6045</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.80852</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.88409</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.92942</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.95058</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.96569</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.97778</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.98912</v>
+                </pt>
+                <pt idx="9">
+                  <v>1.0</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -1121,11 +1389,138 @@
           <cat>
             <strRef>
               <f>'🟡 01'!$P$12:$P$31</f>
+              <strCache>
+                <ptCount val="20"/>
+                <pt idx="0">
+                  <v>A | SKU01 | Notebook Executivo i</v>
+                </pt>
+                <pt idx="1">
+                  <v>A | SKU02 | Servidor de Dados Pr</v>
+                </pt>
+                <pt idx="2">
+                  <v>A | SKU03 | Impressora Multifunc</v>
+                </pt>
+                <pt idx="3">
+                  <v>A | SKU04 | Toner Impressora Las</v>
+                </pt>
+                <pt idx="4">
+                  <v>B | SKU05 | Memoria RAM 16GB</v>
+                </pt>
+                <pt idx="5">
+                  <v>B | SKU06 | Monitor LED 24"</v>
+                </pt>
+                <pt idx="6">
+                  <v>B | SKU07 | Webcam Full HD</v>
+                </pt>
+                <pt idx="7">
+                  <v>B | SKU09 | SSD 480GB Sata</v>
+                </pt>
+                <pt idx="8">
+                  <v>B | SKU08 | Roteador Wi-Fi 6</v>
+                </pt>
+                <pt idx="9">
+                  <v>B | SKU10 | Nobreak 1500VA</v>
+                </pt>
+                <pt idx="10">
+                  <v>B | SKU11 | HD Externo 2TB</v>
+                </pt>
+                <pt idx="11">
+                  <v>B | SKU12 | Teclado Mecanico RGB</v>
+                </pt>
+                <pt idx="12">
+                  <v>C | SKU13 | Pen Drive 64GB</v>
+                </pt>
+                <pt idx="13">
+                  <v>C | SKU14 | Headset com Microfon</v>
+                </pt>
+                <pt idx="14">
+                  <v>C | SKU15 | Pacote de Papel A4</v>
+                </pt>
+                <pt idx="15">
+                  <v>C | SKU16 | Filtro de Linha 5 To</v>
+                </pt>
+                <pt idx="16">
+                  <v>C | SKU17 | Cabo HDMI 2m</v>
+                </pt>
+                <pt idx="17">
+                  <v>C | SKU18 | Adaptador USB-C</v>
+                </pt>
+                <pt idx="18">
+                  <v>C | SKU20 | Patch Cord RJ45 1m</v>
+                </pt>
+                <pt idx="19">
+                  <v>C | SKU19 | Mouse Optico Simples</v>
+                </pt>
+              </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
               <f>'🟡 01'!$Q$12:$Q$31</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="20"/>
+                <pt idx="0">
+                  <v>227500</v>
+                </pt>
+                <pt idx="1">
+                  <v>180000</v>
+                </pt>
+                <pt idx="2">
+                  <v>60500</v>
+                </pt>
+                <pt idx="3">
+                  <v>46240</v>
+                </pt>
+                <pt idx="4">
+                  <v>0</v>
+                </pt>
+                <pt idx="5">
+                  <v>0</v>
+                </pt>
+                <pt idx="6">
+                  <v>0</v>
+                </pt>
+                <pt idx="7">
+                  <v>0</v>
+                </pt>
+                <pt idx="8">
+                  <v>0</v>
+                </pt>
+                <pt idx="9">
+                  <v>0</v>
+                </pt>
+                <pt idx="10">
+                  <v>0</v>
+                </pt>
+                <pt idx="11">
+                  <v>0</v>
+                </pt>
+                <pt idx="12">
+                  <v>0</v>
+                </pt>
+                <pt idx="13">
+                  <v>0</v>
+                </pt>
+                <pt idx="14">
+                  <v>0</v>
+                </pt>
+                <pt idx="15">
+                  <v>0</v>
+                </pt>
+                <pt idx="16">
+                  <v>0</v>
+                </pt>
+                <pt idx="17">
+                  <v>0</v>
+                </pt>
+                <pt idx="18">
+                  <v>0</v>
+                </pt>
+                <pt idx="19">
+                  <v>0</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
         </ser>
@@ -1149,11 +1544,138 @@
           <cat>
             <strRef>
               <f>'🟡 01'!$P$12:$P$31</f>
+              <strCache>
+                <ptCount val="20"/>
+                <pt idx="0">
+                  <v>A | SKU01 | Notebook Executivo i</v>
+                </pt>
+                <pt idx="1">
+                  <v>A | SKU02 | Servidor de Dados Pr</v>
+                </pt>
+                <pt idx="2">
+                  <v>A | SKU03 | Impressora Multifunc</v>
+                </pt>
+                <pt idx="3">
+                  <v>A | SKU04 | Toner Impressora Las</v>
+                </pt>
+                <pt idx="4">
+                  <v>B | SKU05 | Memoria RAM 16GB</v>
+                </pt>
+                <pt idx="5">
+                  <v>B | SKU06 | Monitor LED 24"</v>
+                </pt>
+                <pt idx="6">
+                  <v>B | SKU07 | Webcam Full HD</v>
+                </pt>
+                <pt idx="7">
+                  <v>B | SKU09 | SSD 480GB Sata</v>
+                </pt>
+                <pt idx="8">
+                  <v>B | SKU08 | Roteador Wi-Fi 6</v>
+                </pt>
+                <pt idx="9">
+                  <v>B | SKU10 | Nobreak 1500VA</v>
+                </pt>
+                <pt idx="10">
+                  <v>B | SKU11 | HD Externo 2TB</v>
+                </pt>
+                <pt idx="11">
+                  <v>B | SKU12 | Teclado Mecanico RGB</v>
+                </pt>
+                <pt idx="12">
+                  <v>C | SKU13 | Pen Drive 64GB</v>
+                </pt>
+                <pt idx="13">
+                  <v>C | SKU14 | Headset com Microfon</v>
+                </pt>
+                <pt idx="14">
+                  <v>C | SKU15 | Pacote de Papel A4</v>
+                </pt>
+                <pt idx="15">
+                  <v>C | SKU16 | Filtro de Linha 5 To</v>
+                </pt>
+                <pt idx="16">
+                  <v>C | SKU17 | Cabo HDMI 2m</v>
+                </pt>
+                <pt idx="17">
+                  <v>C | SKU18 | Adaptador USB-C</v>
+                </pt>
+                <pt idx="18">
+                  <v>C | SKU20 | Patch Cord RJ45 1m</v>
+                </pt>
+                <pt idx="19">
+                  <v>C | SKU19 | Mouse Optico Simples</v>
+                </pt>
+              </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
               <f>'🟡 01'!$R$12:$R$31</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="20"/>
+                <pt idx="0">
+                  <v>0</v>
+                </pt>
+                <pt idx="1">
+                  <v>0</v>
+                </pt>
+                <pt idx="2">
+                  <v>0</v>
+                </pt>
+                <pt idx="3">
+                  <v>0</v>
+                </pt>
+                <pt idx="4">
+                  <v>17100</v>
+                </pt>
+                <pt idx="5">
+                  <v>17000</v>
+                </pt>
+                <pt idx="6">
+                  <v>14760</v>
+                </pt>
+                <pt idx="7">
+                  <v>10450</v>
+                </pt>
+                <pt idx="8">
+                  <v>9750</v>
+                </pt>
+                <pt idx="9">
+                  <v>9600</v>
+                </pt>
+                <pt idx="10">
+                  <v>7560</v>
+                </pt>
+                <pt idx="11">
+                  <v>7500</v>
+                </pt>
+                <pt idx="12">
+                  <v>0</v>
+                </pt>
+                <pt idx="13">
+                  <v>0</v>
+                </pt>
+                <pt idx="14">
+                  <v>0</v>
+                </pt>
+                <pt idx="15">
+                  <v>0</v>
+                </pt>
+                <pt idx="16">
+                  <v>0</v>
+                </pt>
+                <pt idx="17">
+                  <v>0</v>
+                </pt>
+                <pt idx="18">
+                  <v>0</v>
+                </pt>
+                <pt idx="19">
+                  <v>0</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
         </ser>
@@ -1177,11 +1699,138 @@
           <cat>
             <strRef>
               <f>'🟡 01'!$P$12:$P$31</f>
+              <strCache>
+                <ptCount val="20"/>
+                <pt idx="0">
+                  <v>A | SKU01 | Notebook Executivo i</v>
+                </pt>
+                <pt idx="1">
+                  <v>A | SKU02 | Servidor de Dados Pr</v>
+                </pt>
+                <pt idx="2">
+                  <v>A | SKU03 | Impressora Multifunc</v>
+                </pt>
+                <pt idx="3">
+                  <v>A | SKU04 | Toner Impressora Las</v>
+                </pt>
+                <pt idx="4">
+                  <v>B | SKU05 | Memoria RAM 16GB</v>
+                </pt>
+                <pt idx="5">
+                  <v>B | SKU06 | Monitor LED 24"</v>
+                </pt>
+                <pt idx="6">
+                  <v>B | SKU07 | Webcam Full HD</v>
+                </pt>
+                <pt idx="7">
+                  <v>B | SKU09 | SSD 480GB Sata</v>
+                </pt>
+                <pt idx="8">
+                  <v>B | SKU08 | Roteador Wi-Fi 6</v>
+                </pt>
+                <pt idx="9">
+                  <v>B | SKU10 | Nobreak 1500VA</v>
+                </pt>
+                <pt idx="10">
+                  <v>B | SKU11 | HD Externo 2TB</v>
+                </pt>
+                <pt idx="11">
+                  <v>B | SKU12 | Teclado Mecanico RGB</v>
+                </pt>
+                <pt idx="12">
+                  <v>C | SKU13 | Pen Drive 64GB</v>
+                </pt>
+                <pt idx="13">
+                  <v>C | SKU14 | Headset com Microfon</v>
+                </pt>
+                <pt idx="14">
+                  <v>C | SKU15 | Pacote de Papel A4</v>
+                </pt>
+                <pt idx="15">
+                  <v>C | SKU16 | Filtro de Linha 5 To</v>
+                </pt>
+                <pt idx="16">
+                  <v>C | SKU17 | Cabo HDMI 2m</v>
+                </pt>
+                <pt idx="17">
+                  <v>C | SKU18 | Adaptador USB-C</v>
+                </pt>
+                <pt idx="18">
+                  <v>C | SKU20 | Patch Cord RJ45 1m</v>
+                </pt>
+                <pt idx="19">
+                  <v>C | SKU19 | Mouse Optico Simples</v>
+                </pt>
+              </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
               <f>'🟡 01'!$S$12:$S$31</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="20"/>
+                <pt idx="0">
+                  <v>0</v>
+                </pt>
+                <pt idx="1">
+                  <v>0</v>
+                </pt>
+                <pt idx="2">
+                  <v>0</v>
+                </pt>
+                <pt idx="3">
+                  <v>0</v>
+                </pt>
+                <pt idx="4">
+                  <v>0</v>
+                </pt>
+                <pt idx="5">
+                  <v>0</v>
+                </pt>
+                <pt idx="6">
+                  <v>0</v>
+                </pt>
+                <pt idx="7">
+                  <v>0</v>
+                </pt>
+                <pt idx="8">
+                  <v>0</v>
+                </pt>
+                <pt idx="9">
+                  <v>0</v>
+                </pt>
+                <pt idx="10">
+                  <v>0</v>
+                </pt>
+                <pt idx="11">
+                  <v>0</v>
+                </pt>
+                <pt idx="12">
+                  <v>7200</v>
+                </pt>
+                <pt idx="13">
+                  <v>7040</v>
+                </pt>
+                <pt idx="14">
+                  <v>6636</v>
+                </pt>
+                <pt idx="15">
+                  <v>4400</v>
+                </pt>
+                <pt idx="16">
+                  <v>3750</v>
+                </pt>
+                <pt idx="17">
+                  <v>3150</v>
+                </pt>
+                <pt idx="18">
+                  <v>2400</v>
+                </pt>
+                <pt idx="19">
+                  <v>1800</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
         </ser>
@@ -1229,11 +1878,138 @@
           <cat>
             <strRef>
               <f>'🟡 01'!$P$12:$P$31</f>
+              <strCache>
+                <ptCount val="20"/>
+                <pt idx="0">
+                  <v>A | SKU01 | Notebook Executivo i</v>
+                </pt>
+                <pt idx="1">
+                  <v>A | SKU02 | Servidor de Dados Pr</v>
+                </pt>
+                <pt idx="2">
+                  <v>A | SKU03 | Impressora Multifunc</v>
+                </pt>
+                <pt idx="3">
+                  <v>A | SKU04 | Toner Impressora Las</v>
+                </pt>
+                <pt idx="4">
+                  <v>B | SKU05 | Memoria RAM 16GB</v>
+                </pt>
+                <pt idx="5">
+                  <v>B | SKU06 | Monitor LED 24"</v>
+                </pt>
+                <pt idx="6">
+                  <v>B | SKU07 | Webcam Full HD</v>
+                </pt>
+                <pt idx="7">
+                  <v>B | SKU09 | SSD 480GB Sata</v>
+                </pt>
+                <pt idx="8">
+                  <v>B | SKU08 | Roteador Wi-Fi 6</v>
+                </pt>
+                <pt idx="9">
+                  <v>B | SKU10 | Nobreak 1500VA</v>
+                </pt>
+                <pt idx="10">
+                  <v>B | SKU11 | HD Externo 2TB</v>
+                </pt>
+                <pt idx="11">
+                  <v>B | SKU12 | Teclado Mecanico RGB</v>
+                </pt>
+                <pt idx="12">
+                  <v>C | SKU13 | Pen Drive 64GB</v>
+                </pt>
+                <pt idx="13">
+                  <v>C | SKU14 | Headset com Microfon</v>
+                </pt>
+                <pt idx="14">
+                  <v>C | SKU15 | Pacote de Papel A4</v>
+                </pt>
+                <pt idx="15">
+                  <v>C | SKU16 | Filtro de Linha 5 To</v>
+                </pt>
+                <pt idx="16">
+                  <v>C | SKU17 | Cabo HDMI 2m</v>
+                </pt>
+                <pt idx="17">
+                  <v>C | SKU18 | Adaptador USB-C</v>
+                </pt>
+                <pt idx="18">
+                  <v>C | SKU20 | Patch Cord RJ45 1m</v>
+                </pt>
+                <pt idx="19">
+                  <v>C | SKU19 | Mouse Optico Simples</v>
+                </pt>
+              </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
               <f>'🟡 01'!$T$12:$T$31</f>
+              <numCache>
+                <formatCode>0%</formatCode>
+                <ptCount val="20"/>
+                <pt idx="0">
+                  <v>0.35308</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.63243</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.72633</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.79809</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.82463</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.85102</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.87392</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.89014</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.90527</v>
+                </pt>
+                <pt idx="9">
+                  <v>0.92017</v>
+                </pt>
+                <pt idx="10">
+                  <v>0.93191</v>
+                </pt>
+                <pt idx="11">
+                  <v>0.94354</v>
+                </pt>
+                <pt idx="12">
+                  <v>0.95472</v>
+                </pt>
+                <pt idx="13">
+                  <v>0.96565</v>
+                </pt>
+                <pt idx="14">
+                  <v>0.97594</v>
+                </pt>
+                <pt idx="15">
+                  <v>0.98277</v>
+                </pt>
+                <pt idx="16">
+                  <v>0.98859</v>
+                </pt>
+                <pt idx="17">
+                  <v>0.99348</v>
+                </pt>
+                <pt idx="18">
+                  <v>0.99721</v>
+                </pt>
+                <pt idx="19">
+                  <v>1.0</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -1377,11 +2153,198 @@
           <cat>
             <strRef>
               <f>'🔴 02'!$P$12:$P$41</f>
+              <strCache>
+                <ptCount val="30"/>
+                <pt idx="0">
+                  <v>A | SKU01 | Servidor Rack Dell P</v>
+                </pt>
+                <pt idx="1">
+                  <v>A | SKU02 | Workstation Grafica</v>
+                </pt>
+                <pt idx="2">
+                  <v>A | SKU03 | Notebook i7 32GB RAM</v>
+                </pt>
+                <pt idx="3">
+                  <v>A | SKU04 | Switch Gerenciavel 4</v>
+                </pt>
+                <pt idx="4">
+                  <v>B | SKU05 | Placa de Video RTX</v>
+                </pt>
+                <pt idx="5">
+                  <v>B | SKU06 | Storage NAS 40TB</v>
+                </pt>
+                <pt idx="6">
+                  <v>B | SKU07 | Memoria RAM 16GB</v>
+                </pt>
+                <pt idx="7">
+                  <v>B | SKU08 | Toner Impressora Las</v>
+                </pt>
+                <pt idx="8">
+                  <v>B | SKU09 | Monitor LED 24"</v>
+                </pt>
+                <pt idx="9">
+                  <v>B | SKU10 | Roteador Wi-Fi 6</v>
+                </pt>
+                <pt idx="10">
+                  <v>B | SKU11 | SSD 480GB Sata</v>
+                </pt>
+                <pt idx="11">
+                  <v>B | SKU12 | Nobreak 1500VA</v>
+                </pt>
+                <pt idx="12">
+                  <v>B | SKU13 | HD Externo 2TB</v>
+                </pt>
+                <pt idx="13">
+                  <v>B | SKU14 | Teclado Mecanico RGB</v>
+                </pt>
+                <pt idx="14">
+                  <v>C | SKU15 | Pen Drive 64GB</v>
+                </pt>
+                <pt idx="15">
+                  <v>C | SKU16 | Headset com Microfon</v>
+                </pt>
+                <pt idx="16">
+                  <v>C | SKU17 | Pacote de Papel A4</v>
+                </pt>
+                <pt idx="17">
+                  <v>C | SKU18 | Teclado de Entrada</v>
+                </pt>
+                <pt idx="18">
+                  <v>C | SKU19 | Filtro de Linha</v>
+                </pt>
+                <pt idx="19">
+                  <v>C | SKU20 | Webcam Full HD</v>
+                </pt>
+                <pt idx="20">
+                  <v>C | SKU21 | Pilhas AA (Pacote)</v>
+                </pt>
+                <pt idx="21">
+                  <v>C | SKU22 | Adaptador USB-C</v>
+                </pt>
+                <pt idx="22">
+                  <v>C | SKU23 | Suporte para Monitor</v>
+                </pt>
+                <pt idx="23">
+                  <v>C | SKU24 | Cabo HDMI 2m</v>
+                </pt>
+                <pt idx="24">
+                  <v>C | SKU25 | Mousepad Simples</v>
+                </pt>
+                <pt idx="25">
+                  <v>C | SKU26 | Mouse Optico Simples</v>
+                </pt>
+                <pt idx="26">
+                  <v>C | SKU27 | Organizador de Cabos</v>
+                </pt>
+                <pt idx="27">
+                  <v>C | SKU28 | Ar comprimido (Lata)</v>
+                </pt>
+                <pt idx="28">
+                  <v>C | SKU29 | Pasta Termica</v>
+                </pt>
+                <pt idx="29">
+                  <v>C | SKU30 | Conector RJ45 (Cento</v>
+                </pt>
+              </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
               <f>'🔴 02'!$Q$12:$Q$41</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="30"/>
+                <pt idx="0">
+                  <v>337500</v>
+                </pt>
+                <pt idx="1">
+                  <v>228000</v>
+                </pt>
+                <pt idx="2">
+                  <v>201600</v>
+                </pt>
+                <pt idx="3">
+                  <v>48000</v>
+                </pt>
+                <pt idx="4">
+                  <v>0</v>
+                </pt>
+                <pt idx="5">
+                  <v>0</v>
+                </pt>
+                <pt idx="6">
+                  <v>0</v>
+                </pt>
+                <pt idx="7">
+                  <v>0</v>
+                </pt>
+                <pt idx="8">
+                  <v>0</v>
+                </pt>
+                <pt idx="9">
+                  <v>0</v>
+                </pt>
+                <pt idx="10">
+                  <v>0</v>
+                </pt>
+                <pt idx="11">
+                  <v>0</v>
+                </pt>
+                <pt idx="12">
+                  <v>0</v>
+                </pt>
+                <pt idx="13">
+                  <v>0</v>
+                </pt>
+                <pt idx="14">
+                  <v>0</v>
+                </pt>
+                <pt idx="15">
+                  <v>0</v>
+                </pt>
+                <pt idx="16">
+                  <v>0</v>
+                </pt>
+                <pt idx="17">
+                  <v>0</v>
+                </pt>
+                <pt idx="18">
+                  <v>0</v>
+                </pt>
+                <pt idx="19">
+                  <v>0</v>
+                </pt>
+                <pt idx="20">
+                  <v>0</v>
+                </pt>
+                <pt idx="21">
+                  <v>0</v>
+                </pt>
+                <pt idx="22">
+                  <v>0</v>
+                </pt>
+                <pt idx="23">
+                  <v>0</v>
+                </pt>
+                <pt idx="24">
+                  <v>0</v>
+                </pt>
+                <pt idx="25">
+                  <v>0</v>
+                </pt>
+                <pt idx="26">
+                  <v>0</v>
+                </pt>
+                <pt idx="27">
+                  <v>0</v>
+                </pt>
+                <pt idx="28">
+                  <v>0</v>
+                </pt>
+                <pt idx="29">
+                  <v>0</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
         </ser>
@@ -1405,11 +2368,198 @@
           <cat>
             <strRef>
               <f>'🔴 02'!$P$12:$P$41</f>
+              <strCache>
+                <ptCount val="30"/>
+                <pt idx="0">
+                  <v>A | SKU01 | Servidor Rack Dell P</v>
+                </pt>
+                <pt idx="1">
+                  <v>A | SKU02 | Workstation Grafica</v>
+                </pt>
+                <pt idx="2">
+                  <v>A | SKU03 | Notebook i7 32GB RAM</v>
+                </pt>
+                <pt idx="3">
+                  <v>A | SKU04 | Switch Gerenciavel 4</v>
+                </pt>
+                <pt idx="4">
+                  <v>B | SKU05 | Placa de Video RTX</v>
+                </pt>
+                <pt idx="5">
+                  <v>B | SKU06 | Storage NAS 40TB</v>
+                </pt>
+                <pt idx="6">
+                  <v>B | SKU07 | Memoria RAM 16GB</v>
+                </pt>
+                <pt idx="7">
+                  <v>B | SKU08 | Toner Impressora Las</v>
+                </pt>
+                <pt idx="8">
+                  <v>B | SKU09 | Monitor LED 24"</v>
+                </pt>
+                <pt idx="9">
+                  <v>B | SKU10 | Roteador Wi-Fi 6</v>
+                </pt>
+                <pt idx="10">
+                  <v>B | SKU11 | SSD 480GB Sata</v>
+                </pt>
+                <pt idx="11">
+                  <v>B | SKU12 | Nobreak 1500VA</v>
+                </pt>
+                <pt idx="12">
+                  <v>B | SKU13 | HD Externo 2TB</v>
+                </pt>
+                <pt idx="13">
+                  <v>B | SKU14 | Teclado Mecanico RGB</v>
+                </pt>
+                <pt idx="14">
+                  <v>C | SKU15 | Pen Drive 64GB</v>
+                </pt>
+                <pt idx="15">
+                  <v>C | SKU16 | Headset com Microfon</v>
+                </pt>
+                <pt idx="16">
+                  <v>C | SKU17 | Pacote de Papel A4</v>
+                </pt>
+                <pt idx="17">
+                  <v>C | SKU18 | Teclado de Entrada</v>
+                </pt>
+                <pt idx="18">
+                  <v>C | SKU19 | Filtro de Linha</v>
+                </pt>
+                <pt idx="19">
+                  <v>C | SKU20 | Webcam Full HD</v>
+                </pt>
+                <pt idx="20">
+                  <v>C | SKU21 | Pilhas AA (Pacote)</v>
+                </pt>
+                <pt idx="21">
+                  <v>C | SKU22 | Adaptador USB-C</v>
+                </pt>
+                <pt idx="22">
+                  <v>C | SKU23 | Suporte para Monitor</v>
+                </pt>
+                <pt idx="23">
+                  <v>C | SKU24 | Cabo HDMI 2m</v>
+                </pt>
+                <pt idx="24">
+                  <v>C | SKU25 | Mousepad Simples</v>
+                </pt>
+                <pt idx="25">
+                  <v>C | SKU26 | Mouse Optico Simples</v>
+                </pt>
+                <pt idx="26">
+                  <v>C | SKU27 | Organizador de Cabos</v>
+                </pt>
+                <pt idx="27">
+                  <v>C | SKU28 | Ar comprimido (Lata)</v>
+                </pt>
+                <pt idx="28">
+                  <v>C | SKU29 | Pasta Termica</v>
+                </pt>
+                <pt idx="29">
+                  <v>C | SKU30 | Conector RJ45 (Cento</v>
+                </pt>
+              </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
               <f>'🔴 02'!$R$12:$R$41</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="30"/>
+                <pt idx="0">
+                  <v>0</v>
+                </pt>
+                <pt idx="1">
+                  <v>0</v>
+                </pt>
+                <pt idx="2">
+                  <v>0</v>
+                </pt>
+                <pt idx="3">
+                  <v>0</v>
+                </pt>
+                <pt idx="4">
+                  <v>44000</v>
+                </pt>
+                <pt idx="5">
+                  <v>37000</v>
+                </pt>
+                <pt idx="6">
+                  <v>17100</v>
+                </pt>
+                <pt idx="7">
+                  <v>12800</v>
+                </pt>
+                <pt idx="8">
+                  <v>12750</v>
+                </pt>
+                <pt idx="9">
+                  <v>11250</v>
+                </pt>
+                <pt idx="10">
+                  <v>10450</v>
+                </pt>
+                <pt idx="11">
+                  <v>9600</v>
+                </pt>
+                <pt idx="12">
+                  <v>7560</v>
+                </pt>
+                <pt idx="13">
+                  <v>7500</v>
+                </pt>
+                <pt idx="14">
+                  <v>0</v>
+                </pt>
+                <pt idx="15">
+                  <v>0</v>
+                </pt>
+                <pt idx="16">
+                  <v>0</v>
+                </pt>
+                <pt idx="17">
+                  <v>0</v>
+                </pt>
+                <pt idx="18">
+                  <v>0</v>
+                </pt>
+                <pt idx="19">
+                  <v>0</v>
+                </pt>
+                <pt idx="20">
+                  <v>0</v>
+                </pt>
+                <pt idx="21">
+                  <v>0</v>
+                </pt>
+                <pt idx="22">
+                  <v>0</v>
+                </pt>
+                <pt idx="23">
+                  <v>0</v>
+                </pt>
+                <pt idx="24">
+                  <v>0</v>
+                </pt>
+                <pt idx="25">
+                  <v>0</v>
+                </pt>
+                <pt idx="26">
+                  <v>0</v>
+                </pt>
+                <pt idx="27">
+                  <v>0</v>
+                </pt>
+                <pt idx="28">
+                  <v>0</v>
+                </pt>
+                <pt idx="29">
+                  <v>0</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
         </ser>
@@ -1433,11 +2583,198 @@
           <cat>
             <strRef>
               <f>'🔴 02'!$P$12:$P$41</f>
+              <strCache>
+                <ptCount val="30"/>
+                <pt idx="0">
+                  <v>A | SKU01 | Servidor Rack Dell P</v>
+                </pt>
+                <pt idx="1">
+                  <v>A | SKU02 | Workstation Grafica</v>
+                </pt>
+                <pt idx="2">
+                  <v>A | SKU03 | Notebook i7 32GB RAM</v>
+                </pt>
+                <pt idx="3">
+                  <v>A | SKU04 | Switch Gerenciavel 4</v>
+                </pt>
+                <pt idx="4">
+                  <v>B | SKU05 | Placa de Video RTX</v>
+                </pt>
+                <pt idx="5">
+                  <v>B | SKU06 | Storage NAS 40TB</v>
+                </pt>
+                <pt idx="6">
+                  <v>B | SKU07 | Memoria RAM 16GB</v>
+                </pt>
+                <pt idx="7">
+                  <v>B | SKU08 | Toner Impressora Las</v>
+                </pt>
+                <pt idx="8">
+                  <v>B | SKU09 | Monitor LED 24"</v>
+                </pt>
+                <pt idx="9">
+                  <v>B | SKU10 | Roteador Wi-Fi 6</v>
+                </pt>
+                <pt idx="10">
+                  <v>B | SKU11 | SSD 480GB Sata</v>
+                </pt>
+                <pt idx="11">
+                  <v>B | SKU12 | Nobreak 1500VA</v>
+                </pt>
+                <pt idx="12">
+                  <v>B | SKU13 | HD Externo 2TB</v>
+                </pt>
+                <pt idx="13">
+                  <v>B | SKU14 | Teclado Mecanico RGB</v>
+                </pt>
+                <pt idx="14">
+                  <v>C | SKU15 | Pen Drive 64GB</v>
+                </pt>
+                <pt idx="15">
+                  <v>C | SKU16 | Headset com Microfon</v>
+                </pt>
+                <pt idx="16">
+                  <v>C | SKU17 | Pacote de Papel A4</v>
+                </pt>
+                <pt idx="17">
+                  <v>C | SKU18 | Teclado de Entrada</v>
+                </pt>
+                <pt idx="18">
+                  <v>C | SKU19 | Filtro de Linha</v>
+                </pt>
+                <pt idx="19">
+                  <v>C | SKU20 | Webcam Full HD</v>
+                </pt>
+                <pt idx="20">
+                  <v>C | SKU21 | Pilhas AA (Pacote)</v>
+                </pt>
+                <pt idx="21">
+                  <v>C | SKU22 | Adaptador USB-C</v>
+                </pt>
+                <pt idx="22">
+                  <v>C | SKU23 | Suporte para Monitor</v>
+                </pt>
+                <pt idx="23">
+                  <v>C | SKU24 | Cabo HDMI 2m</v>
+                </pt>
+                <pt idx="24">
+                  <v>C | SKU25 | Mousepad Simples</v>
+                </pt>
+                <pt idx="25">
+                  <v>C | SKU26 | Mouse Optico Simples</v>
+                </pt>
+                <pt idx="26">
+                  <v>C | SKU27 | Organizador de Cabos</v>
+                </pt>
+                <pt idx="27">
+                  <v>C | SKU28 | Ar comprimido (Lata)</v>
+                </pt>
+                <pt idx="28">
+                  <v>C | SKU29 | Pasta Termica</v>
+                </pt>
+                <pt idx="29">
+                  <v>C | SKU30 | Conector RJ45 (Cento</v>
+                </pt>
+              </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
               <f>'🔴 02'!$S$12:$S$41</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="30"/>
+                <pt idx="0">
+                  <v>0</v>
+                </pt>
+                <pt idx="1">
+                  <v>0</v>
+                </pt>
+                <pt idx="2">
+                  <v>0</v>
+                </pt>
+                <pt idx="3">
+                  <v>0</v>
+                </pt>
+                <pt idx="4">
+                  <v>0</v>
+                </pt>
+                <pt idx="5">
+                  <v>0</v>
+                </pt>
+                <pt idx="6">
+                  <v>0</v>
+                </pt>
+                <pt idx="7">
+                  <v>0</v>
+                </pt>
+                <pt idx="8">
+                  <v>0</v>
+                </pt>
+                <pt idx="9">
+                  <v>0</v>
+                </pt>
+                <pt idx="10">
+                  <v>0</v>
+                </pt>
+                <pt idx="11">
+                  <v>0</v>
+                </pt>
+                <pt idx="12">
+                  <v>0</v>
+                </pt>
+                <pt idx="13">
+                  <v>0</v>
+                </pt>
+                <pt idx="14">
+                  <v>6750</v>
+                </pt>
+                <pt idx="15">
+                  <v>6600</v>
+                </pt>
+                <pt idx="16">
+                  <v>5600</v>
+                </pt>
+                <pt idx="17">
+                  <v>4500</v>
+                </pt>
+                <pt idx="18">
+                  <v>4400</v>
+                </pt>
+                <pt idx="19">
+                  <v>3960</v>
+                </pt>
+                <pt idx="20">
+                  <v>3600</v>
+                </pt>
+                <pt idx="21">
+                  <v>3150</v>
+                </pt>
+                <pt idx="22">
+                  <v>2800</v>
+                </pt>
+                <pt idx="23">
+                  <v>2125</v>
+                </pt>
+                <pt idx="24">
+                  <v>2000</v>
+                </pt>
+                <pt idx="25">
+                  <v>1800</v>
+                </pt>
+                <pt idx="26">
+                  <v>1800</v>
+                </pt>
+                <pt idx="27">
+                  <v>1575</v>
+                </pt>
+                <pt idx="28">
+                  <v>1575</v>
+                </pt>
+                <pt idx="29">
+                  <v>1500</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
         </ser>
@@ -1485,11 +2822,198 @@
           <cat>
             <strRef>
               <f>'🔴 02'!$P$12:$P$41</f>
+              <strCache>
+                <ptCount val="30"/>
+                <pt idx="0">
+                  <v>A | SKU01 | Servidor Rack Dell P</v>
+                </pt>
+                <pt idx="1">
+                  <v>A | SKU02 | Workstation Grafica</v>
+                </pt>
+                <pt idx="2">
+                  <v>A | SKU03 | Notebook i7 32GB RAM</v>
+                </pt>
+                <pt idx="3">
+                  <v>A | SKU04 | Switch Gerenciavel 4</v>
+                </pt>
+                <pt idx="4">
+                  <v>B | SKU05 | Placa de Video RTX</v>
+                </pt>
+                <pt idx="5">
+                  <v>B | SKU06 | Storage NAS 40TB</v>
+                </pt>
+                <pt idx="6">
+                  <v>B | SKU07 | Memoria RAM 16GB</v>
+                </pt>
+                <pt idx="7">
+                  <v>B | SKU08 | Toner Impressora Las</v>
+                </pt>
+                <pt idx="8">
+                  <v>B | SKU09 | Monitor LED 24"</v>
+                </pt>
+                <pt idx="9">
+                  <v>B | SKU10 | Roteador Wi-Fi 6</v>
+                </pt>
+                <pt idx="10">
+                  <v>B | SKU11 | SSD 480GB Sata</v>
+                </pt>
+                <pt idx="11">
+                  <v>B | SKU12 | Nobreak 1500VA</v>
+                </pt>
+                <pt idx="12">
+                  <v>B | SKU13 | HD Externo 2TB</v>
+                </pt>
+                <pt idx="13">
+                  <v>B | SKU14 | Teclado Mecanico RGB</v>
+                </pt>
+                <pt idx="14">
+                  <v>C | SKU15 | Pen Drive 64GB</v>
+                </pt>
+                <pt idx="15">
+                  <v>C | SKU16 | Headset com Microfon</v>
+                </pt>
+                <pt idx="16">
+                  <v>C | SKU17 | Pacote de Papel A4</v>
+                </pt>
+                <pt idx="17">
+                  <v>C | SKU18 | Teclado de Entrada</v>
+                </pt>
+                <pt idx="18">
+                  <v>C | SKU19 | Filtro de Linha</v>
+                </pt>
+                <pt idx="19">
+                  <v>C | SKU20 | Webcam Full HD</v>
+                </pt>
+                <pt idx="20">
+                  <v>C | SKU21 | Pilhas AA (Pacote)</v>
+                </pt>
+                <pt idx="21">
+                  <v>C | SKU22 | Adaptador USB-C</v>
+                </pt>
+                <pt idx="22">
+                  <v>C | SKU23 | Suporte para Monitor</v>
+                </pt>
+                <pt idx="23">
+                  <v>C | SKU24 | Cabo HDMI 2m</v>
+                </pt>
+                <pt idx="24">
+                  <v>C | SKU25 | Mousepad Simples</v>
+                </pt>
+                <pt idx="25">
+                  <v>C | SKU26 | Mouse Optico Simples</v>
+                </pt>
+                <pt idx="26">
+                  <v>C | SKU27 | Organizador de Cabos</v>
+                </pt>
+                <pt idx="27">
+                  <v>C | SKU28 | Ar comprimido (Lata)</v>
+                </pt>
+                <pt idx="28">
+                  <v>C | SKU29 | Pasta Termica</v>
+                </pt>
+                <pt idx="29">
+                  <v>C | SKU30 | Conector RJ45 (Cento</v>
+                </pt>
+              </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
               <f>'🔴 02'!$T$12:$T$41</f>
+              <numCache>
+                <formatCode>0%</formatCode>
+                <ptCount val="30"/>
+                <pt idx="0">
+                  <v>0.32488</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.54435</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.73842</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.78462</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.82698</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.86259</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.87905</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.89137</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.90365</v>
+                </pt>
+                <pt idx="9">
+                  <v>0.91448</v>
+                </pt>
+                <pt idx="10">
+                  <v>0.92454</v>
+                </pt>
+                <pt idx="11">
+                  <v>0.93378</v>
+                </pt>
+                <pt idx="12">
+                  <v>0.94105</v>
+                </pt>
+                <pt idx="13">
+                  <v>0.94827</v>
+                </pt>
+                <pt idx="14">
+                  <v>0.95477</v>
+                </pt>
+                <pt idx="15">
+                  <v>0.96113</v>
+                </pt>
+                <pt idx="16">
+                  <v>0.96652</v>
+                </pt>
+                <pt idx="17">
+                  <v>0.97085</v>
+                </pt>
+                <pt idx="18">
+                  <v>0.97508</v>
+                </pt>
+                <pt idx="19">
+                  <v>0.97889</v>
+                </pt>
+                <pt idx="20">
+                  <v>0.98236</v>
+                </pt>
+                <pt idx="21">
+                  <v>0.98539</v>
+                </pt>
+                <pt idx="22">
+                  <v>0.98809</v>
+                </pt>
+                <pt idx="23">
+                  <v>0.99013</v>
+                </pt>
+                <pt idx="24">
+                  <v>0.99206</v>
+                </pt>
+                <pt idx="25">
+                  <v>0.99379</v>
+                </pt>
+                <pt idx="26">
+                  <v>0.99552</v>
+                </pt>
+                <pt idx="27">
+                  <v>0.99704</v>
+                </pt>
+                <pt idx="28">
+                  <v>0.99856</v>
+                </pt>
+                <pt idx="29">
+                  <v>1.0</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="1"/>

--- a/curva_abc_reggae.xlsx
+++ b/curva_abc_reggae.xlsx
@@ -180,63 +180,61 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
+      <patternFill patternType="solid"/>
+    </fill>
+    <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF000000"/>
+        <fgColor rgb="00009B3A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF009B3A"/>
+        <fgColor rgb="00FFD700"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFD700"/>
+        <fgColor rgb="00CC0000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCC0000"/>
+        <fgColor rgb="00141414"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF141414"/>
+        <fgColor rgb="00006B28"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF006B28"/>
+        <fgColor rgb="00C8A400"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC8A400"/>
+        <fgColor rgb="008B0000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF8B0000"/>
+        <fgColor rgb="000D2010"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0D2010"/>
+        <fgColor rgb="00080808"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF080808"/>
+        <fgColor rgb="000D1A0D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0D1A0D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A0000"/>
+        <fgColor rgb="001A0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -689,7 +687,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFD6F5E3"/>
+          <fgColor rgb="00D6F5E3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -699,7 +697,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFBD0"/>
+          <fgColor rgb="00FFFBD0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -709,7 +707,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFECEC"/>
+          <fgColor rgb="00FFECEC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -721,7 +719,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF009B3A"/>
+          <fgColor rgb="00009B3A"/>
         </patternFill>
       </fill>
     </dxf>
@@ -733,7 +731,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFC8A400"/>
+          <fgColor rgb="00C8A400"/>
         </patternFill>
       </fill>
     </dxf>
@@ -745,7 +743,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF8B0000"/>
+          <fgColor rgb="008B0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1243,7 +1241,7 @@
                   <v>0.98912</v>
                 </pt>
                 <pt idx="9">
-                  <v>1.0</v>
+                  <v>1</v>
                 </pt>
               </numCache>
             </numRef>
@@ -1268,7 +1266,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Produtos (ordem decrescente de V.T.)</a:t>
+                  <a:t>Produtos ordenados por V.T. decrescente (nome + classe no rotulo)</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -1313,7 +1311,7 @@
           <max val="1"/>
           <min val="0"/>
         </scaling>
-        <axPos val="r"/>
+        <axPos val="l"/>
         <majorGridlines/>
         <title>
           <tx>
@@ -2007,7 +2005,7 @@
                   <v>0.99721</v>
                 </pt>
                 <pt idx="19">
-                  <v>1.0</v>
+                  <v>1</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2032,7 +2030,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Produtos (ordem decrescente de V.T.)</a:t>
+                  <a:t>Produtos ordenados por V.T. decrescente (nome + classe no rotulo)</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -2077,7 +2075,7 @@
           <max val="1"/>
           <min val="0"/>
         </scaling>
-        <axPos val="r"/>
+        <axPos val="l"/>
         <majorGridlines/>
         <title>
           <tx>
@@ -3011,7 +3009,7 @@
                   <v>0.99856</v>
                 </pt>
                 <pt idx="29">
-                  <v>1.0</v>
+                  <v>1</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3036,7 +3034,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Produtos (ordem decrescente de V.T.)</a:t>
+                  <a:t>Produtos ordenados por V.T. decrescente (nome + classe no rotulo)</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -3081,7 +3079,7 @@
           <max val="1"/>
           <min val="0"/>
         </scaling>
-        <axPos val="r"/>
+        <axPos val="l"/>
         <majorGridlines/>
         <title>
           <tx>
@@ -3931,7 +3929,7 @@
         <v/>
       </c>
       <c r="I12" s="53">
-        <f>IFERROR(SUM($G$12:G12)/SUM($G$12:$G$21),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$21,"&gt;="&amp;G12,$G$12:$G$21)/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
       <c r="P12" t="inlineStr">
@@ -3985,7 +3983,7 @@
         <v/>
       </c>
       <c r="I13" s="53">
-        <f>IFERROR(SUM($G$12:G13)/SUM($G$12:$G$21),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$21,"&gt;="&amp;G13,$G$12:$G$21)/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
       <c r="P13" t="inlineStr">
@@ -4039,7 +4037,7 @@
         <v/>
       </c>
       <c r="I14" s="53">
-        <f>IFERROR(SUM($G$12:G14)/SUM($G$12:$G$21),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$21,"&gt;="&amp;G14,$G$12:$G$21)/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
       <c r="P14" t="inlineStr">
@@ -4093,7 +4091,7 @@
         <v/>
       </c>
       <c r="I15" s="53">
-        <f>IFERROR(SUM($G$12:G15)/SUM($G$12:$G$21),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$21,"&gt;="&amp;G15,$G$12:$G$21)/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
       <c r="P15" t="inlineStr">
@@ -4147,7 +4145,7 @@
         <v/>
       </c>
       <c r="I16" s="53">
-        <f>IFERROR(SUM($G$12:G16)/SUM($G$12:$G$21),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$21,"&gt;="&amp;G16,$G$12:$G$21)/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
       <c r="P16" t="inlineStr">
@@ -4175,22 +4173,22 @@
       </c>
       <c r="B17" s="48" t="inlineStr">
         <is>
-          <t>SKU08</t>
+          <t>SKU06</t>
         </is>
       </c>
       <c r="C17" s="48" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D17" s="49" t="inlineStr">
         <is>
-          <t>Teclado USB</t>
+          <t>Mouse sem fio</t>
         </is>
       </c>
       <c r="E17" s="50" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="F17" s="51" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="G17" s="52">
         <f>IFERROR(E17*F17,0)</f>
@@ -4201,7 +4199,7 @@
         <v/>
       </c>
       <c r="I17" s="53">
-        <f>IFERROR(SUM($G$12:G17)/SUM($G$12:$G$21),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$21,"&gt;="&amp;G17,$G$12:$G$21)/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
       <c r="P17" t="inlineStr">
@@ -4229,22 +4227,22 @@
       </c>
       <c r="B18" s="48" t="inlineStr">
         <is>
-          <t>SKU06</t>
+          <t>SKU07</t>
         </is>
       </c>
       <c r="C18" s="48" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D18" s="49" t="inlineStr">
         <is>
-          <t>Mouse sem fio</t>
+          <t>Patch Cord 1m</t>
         </is>
       </c>
       <c r="E18" s="50" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="F18" s="51" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="G18" s="52">
         <f>IFERROR(E18*F18,0)</f>
@@ -4255,7 +4253,7 @@
         <v/>
       </c>
       <c r="I18" s="53">
-        <f>IFERROR(SUM($G$12:G18)/SUM($G$12:$G$21),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$21,"&gt;="&amp;G18,$G$12:$G$21)/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
       <c r="P18" t="inlineStr">
@@ -4283,22 +4281,22 @@
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>SKU09</t>
+          <t>SKU08</t>
         </is>
       </c>
       <c r="C19" s="48" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D19" s="49" t="inlineStr">
         <is>
-          <t>Cabo Rede Cat6 (m)</t>
+          <t>Teclado USB</t>
         </is>
       </c>
       <c r="E19" s="50" t="n">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="F19" s="51" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="G19" s="52">
         <f>IFERROR(E19*F19,0)</f>
@@ -4309,7 +4307,7 @@
         <v/>
       </c>
       <c r="I19" s="53">
-        <f>IFERROR(SUM($G$12:G19)/SUM($G$12:$G$21),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$21,"&gt;="&amp;G19,$G$12:$G$21)/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
       <c r="P19" t="inlineStr">
@@ -4337,22 +4335,22 @@
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>SKU07</t>
+          <t>SKU09</t>
         </is>
       </c>
       <c r="C20" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="49" t="inlineStr">
+        <is>
+          <t>Cabo Rede Cat6 (m)</t>
+        </is>
+      </c>
+      <c r="E20" s="50" t="n">
+        <v>200</v>
+      </c>
+      <c r="F20" s="51" t="n">
         <v>8</v>
-      </c>
-      <c r="D20" s="49" t="inlineStr">
-        <is>
-          <t>Patch Cord 1m</t>
-        </is>
-      </c>
-      <c r="E20" s="50" t="n">
-        <v>100</v>
-      </c>
-      <c r="F20" s="51" t="n">
-        <v>15</v>
       </c>
       <c r="G20" s="52">
         <f>IFERROR(E20*F20,0)</f>
@@ -4363,7 +4361,7 @@
         <v/>
       </c>
       <c r="I20" s="53">
-        <f>IFERROR(SUM($G$12:G20)/SUM($G$12:$G$21),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$21,"&gt;="&amp;G20,$G$12:$G$21)/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
       <c r="P20" t="inlineStr">
@@ -4417,7 +4415,7 @@
         <v/>
       </c>
       <c r="I21" s="53">
-        <f>IFERROR(SUM($G$12:G21)/SUM($G$12:$G$21),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$21,"&gt;="&amp;G21,$G$12:$G$21)/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
       <c r="P21" t="inlineStr">
@@ -4866,7 +4864,7 @@
         <v/>
       </c>
       <c r="I12" s="53">
-        <f>IFERROR(SUM($G$12:G12)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G12,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P12" t="inlineStr">
@@ -4920,7 +4918,7 @@
         <v/>
       </c>
       <c r="I13" s="53">
-        <f>IFERROR(SUM($G$12:G13)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G13,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P13" t="inlineStr">
@@ -4974,7 +4972,7 @@
         <v/>
       </c>
       <c r="I14" s="53">
-        <f>IFERROR(SUM($G$12:G14)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G14,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P14" t="inlineStr">
@@ -5028,7 +5026,7 @@
         <v/>
       </c>
       <c r="I15" s="53">
-        <f>IFERROR(SUM($G$12:G15)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G15,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P15" t="inlineStr">
@@ -5082,7 +5080,7 @@
         <v/>
       </c>
       <c r="I16" s="53">
-        <f>IFERROR(SUM($G$12:G16)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G16,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P16" t="inlineStr">
@@ -5136,7 +5134,7 @@
         <v/>
       </c>
       <c r="I17" s="53">
-        <f>IFERROR(SUM($G$12:G17)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G17,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P17" t="inlineStr">
@@ -5190,7 +5188,7 @@
         <v/>
       </c>
       <c r="I18" s="53">
-        <f>IFERROR(SUM($G$12:G18)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G18,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P18" t="inlineStr">
@@ -5218,22 +5216,22 @@
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>SKU09</t>
+          <t>SKU08</t>
         </is>
       </c>
       <c r="C19" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="D19" s="49" t="inlineStr">
+        <is>
+          <t>Roteador Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E19" s="50" t="n">
         <v>15</v>
       </c>
-      <c r="D19" s="49" t="inlineStr">
-        <is>
-          <t>SSD 480GB Sata</t>
-        </is>
-      </c>
-      <c r="E19" s="50" t="n">
-        <v>55</v>
-      </c>
       <c r="F19" s="51" t="n">
-        <v>190</v>
+        <v>650</v>
       </c>
       <c r="G19" s="52">
         <f>IFERROR(E19*F19,0)</f>
@@ -5244,7 +5242,7 @@
         <v/>
       </c>
       <c r="I19" s="53">
-        <f>IFERROR(SUM($G$12:G19)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G19,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P19" t="inlineStr">
@@ -5272,22 +5270,22 @@
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>SKU08</t>
+          <t>SKU09</t>
         </is>
       </c>
       <c r="C20" s="48" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D20" s="49" t="inlineStr">
         <is>
-          <t>Roteador Wi-Fi 6</t>
+          <t>SSD 480GB Sata</t>
         </is>
       </c>
       <c r="E20" s="50" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="F20" s="51" t="n">
-        <v>650</v>
+        <v>190</v>
       </c>
       <c r="G20" s="52">
         <f>IFERROR(E20*F20,0)</f>
@@ -5298,7 +5296,7 @@
         <v/>
       </c>
       <c r="I20" s="53">
-        <f>IFERROR(SUM($G$12:G20)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G20,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P20" t="inlineStr">
@@ -5352,7 +5350,7 @@
         <v/>
       </c>
       <c r="I21" s="53">
-        <f>IFERROR(SUM($G$12:G21)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G21,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P21" t="inlineStr">
@@ -5406,7 +5404,7 @@
         <v/>
       </c>
       <c r="I22" s="53">
-        <f>IFERROR(SUM($G$12:G22)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G22,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P22" t="inlineStr">
@@ -5460,7 +5458,7 @@
         <v/>
       </c>
       <c r="I23" s="53">
-        <f>IFERROR(SUM($G$12:G23)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G23,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P23" t="inlineStr">
@@ -5514,7 +5512,7 @@
         <v/>
       </c>
       <c r="I24" s="53">
-        <f>IFERROR(SUM($G$12:G24)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G24,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P24" t="inlineStr">
@@ -5568,7 +5566,7 @@
         <v/>
       </c>
       <c r="I25" s="53">
-        <f>IFERROR(SUM($G$12:G25)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G25,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P25" t="inlineStr">
@@ -5622,7 +5620,7 @@
         <v/>
       </c>
       <c r="I26" s="53">
-        <f>IFERROR(SUM($G$12:G26)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G26,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P26" t="inlineStr">
@@ -5676,7 +5674,7 @@
         <v/>
       </c>
       <c r="I27" s="53">
-        <f>IFERROR(SUM($G$12:G27)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G27,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P27" t="inlineStr">
@@ -5730,7 +5728,7 @@
         <v/>
       </c>
       <c r="I28" s="53">
-        <f>IFERROR(SUM($G$12:G28)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G28,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P28" t="inlineStr">
@@ -5784,7 +5782,7 @@
         <v/>
       </c>
       <c r="I29" s="53">
-        <f>IFERROR(SUM($G$12:G29)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G29,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P29" t="inlineStr">
@@ -5812,22 +5810,22 @@
       </c>
       <c r="B30" s="48" t="inlineStr">
         <is>
-          <t>SKU20</t>
+          <t>SKU19</t>
         </is>
       </c>
       <c r="C30" s="48" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D30" s="49" t="inlineStr">
         <is>
-          <t>Patch Cord RJ45 1m</t>
+          <t>Mouse Optico Simples</t>
         </is>
       </c>
       <c r="E30" s="50" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="F30" s="51" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G30" s="52">
         <f>IFERROR(E30*F30,0)</f>
@@ -5838,7 +5836,7 @@
         <v/>
       </c>
       <c r="I30" s="53">
-        <f>IFERROR(SUM($G$12:G30)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G30,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P30" t="inlineStr">
@@ -5866,22 +5864,22 @@
       </c>
       <c r="B31" s="48" t="inlineStr">
         <is>
-          <t>SKU19</t>
+          <t>SKU20</t>
         </is>
       </c>
       <c r="C31" s="48" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D31" s="49" t="inlineStr">
         <is>
-          <t>Mouse Optico Simples</t>
+          <t>Patch Cord RJ45 1m</t>
         </is>
       </c>
       <c r="E31" s="50" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="F31" s="51" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G31" s="52">
         <f>IFERROR(E31*F31,0)</f>
@@ -5892,7 +5890,7 @@
         <v/>
       </c>
       <c r="I31" s="53">
-        <f>IFERROR(SUM($G$12:G31)/SUM($G$12:$G$31),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$31,"&gt;="&amp;G31,$G$12:$G$31)/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
       <c r="P31" t="inlineStr">
@@ -6341,7 +6339,7 @@
         <v/>
       </c>
       <c r="I12" s="53">
-        <f>IFERROR(SUM($G$12:G12)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G12,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P12" t="inlineStr">
@@ -6395,7 +6393,7 @@
         <v/>
       </c>
       <c r="I13" s="53">
-        <f>IFERROR(SUM($G$12:G13)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G13,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P13" t="inlineStr">
@@ -6449,7 +6447,7 @@
         <v/>
       </c>
       <c r="I14" s="53">
-        <f>IFERROR(SUM($G$12:G14)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G14,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P14" t="inlineStr">
@@ -6503,7 +6501,7 @@
         <v/>
       </c>
       <c r="I15" s="53">
-        <f>IFERROR(SUM($G$12:G15)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G15,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P15" t="inlineStr">
@@ -6557,7 +6555,7 @@
         <v/>
       </c>
       <c r="I16" s="53">
-        <f>IFERROR(SUM($G$12:G16)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G16,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P16" t="inlineStr">
@@ -6611,7 +6609,7 @@
         <v/>
       </c>
       <c r="I17" s="53">
-        <f>IFERROR(SUM($G$12:G17)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G17,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P17" t="inlineStr">
@@ -6665,7 +6663,7 @@
         <v/>
       </c>
       <c r="I18" s="53">
-        <f>IFERROR(SUM($G$12:G18)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G18,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P18" t="inlineStr">
@@ -6719,7 +6717,7 @@
         <v/>
       </c>
       <c r="I19" s="53">
-        <f>IFERROR(SUM($G$12:G19)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G19,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P19" t="inlineStr">
@@ -6773,7 +6771,7 @@
         <v/>
       </c>
       <c r="I20" s="53">
-        <f>IFERROR(SUM($G$12:G20)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G20,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P20" t="inlineStr">
@@ -6827,7 +6825,7 @@
         <v/>
       </c>
       <c r="I21" s="53">
-        <f>IFERROR(SUM($G$12:G21)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G21,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P21" t="inlineStr">
@@ -6881,7 +6879,7 @@
         <v/>
       </c>
       <c r="I22" s="53">
-        <f>IFERROR(SUM($G$12:G22)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G22,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P22" t="inlineStr">
@@ -6935,7 +6933,7 @@
         <v/>
       </c>
       <c r="I23" s="53">
-        <f>IFERROR(SUM($G$12:G23)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G23,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P23" t="inlineStr">
@@ -6989,7 +6987,7 @@
         <v/>
       </c>
       <c r="I24" s="53">
-        <f>IFERROR(SUM($G$12:G24)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G24,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P24" t="inlineStr">
@@ -7043,7 +7041,7 @@
         <v/>
       </c>
       <c r="I25" s="53">
-        <f>IFERROR(SUM($G$12:G25)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G25,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P25" t="inlineStr">
@@ -7097,7 +7095,7 @@
         <v/>
       </c>
       <c r="I26" s="53">
-        <f>IFERROR(SUM($G$12:G26)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G26,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P26" t="inlineStr">
@@ -7151,7 +7149,7 @@
         <v/>
       </c>
       <c r="I27" s="53">
-        <f>IFERROR(SUM($G$12:G27)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G27,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P27" t="inlineStr">
@@ -7205,7 +7203,7 @@
         <v/>
       </c>
       <c r="I28" s="53">
-        <f>IFERROR(SUM($G$12:G28)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G28,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P28" t="inlineStr">
@@ -7259,7 +7257,7 @@
         <v/>
       </c>
       <c r="I29" s="53">
-        <f>IFERROR(SUM($G$12:G29)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G29,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P29" t="inlineStr">
@@ -7313,7 +7311,7 @@
         <v/>
       </c>
       <c r="I30" s="53">
-        <f>IFERROR(SUM($G$12:G30)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G30,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P30" t="inlineStr">
@@ -7367,7 +7365,7 @@
         <v/>
       </c>
       <c r="I31" s="53">
-        <f>IFERROR(SUM($G$12:G31)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G31,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P31" t="inlineStr">
@@ -7421,7 +7419,7 @@
         <v/>
       </c>
       <c r="I32" s="53">
-        <f>IFERROR(SUM($G$12:G32)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G32,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P32" t="inlineStr">
@@ -7475,7 +7473,7 @@
         <v/>
       </c>
       <c r="I33" s="53">
-        <f>IFERROR(SUM($G$12:G33)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G33,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P33" t="inlineStr">
@@ -7529,7 +7527,7 @@
         <v/>
       </c>
       <c r="I34" s="53">
-        <f>IFERROR(SUM($G$12:G34)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G34,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P34" t="inlineStr">
@@ -7583,7 +7581,7 @@
         <v/>
       </c>
       <c r="I35" s="53">
-        <f>IFERROR(SUM($G$12:G35)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G35,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P35" t="inlineStr">
@@ -7637,7 +7635,7 @@
         <v/>
       </c>
       <c r="I36" s="53">
-        <f>IFERROR(SUM($G$12:G36)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G36,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P36" t="inlineStr">
@@ -7691,7 +7689,7 @@
         <v/>
       </c>
       <c r="I37" s="53">
-        <f>IFERROR(SUM($G$12:G37)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G37,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P37" t="inlineStr">
@@ -7745,7 +7743,7 @@
         <v/>
       </c>
       <c r="I38" s="53">
-        <f>IFERROR(SUM($G$12:G38)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G38,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P38" t="inlineStr">
@@ -7799,7 +7797,7 @@
         <v/>
       </c>
       <c r="I39" s="53">
-        <f>IFERROR(SUM($G$12:G39)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G39,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P39" t="inlineStr">
@@ -7853,7 +7851,7 @@
         <v/>
       </c>
       <c r="I40" s="53">
-        <f>IFERROR(SUM($G$12:G40)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G40,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P40" t="inlineStr">
@@ -7907,7 +7905,7 @@
         <v/>
       </c>
       <c r="I41" s="53">
-        <f>IFERROR(SUM($G$12:G41)/SUM($G$12:$G$41),0)</f>
+        <f>IFERROR(SUMIF($G$12:$G$41,"&gt;="&amp;G41,$G$12:$G$41)/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
       <c r="P41" t="inlineStr">
